--- a/Report/RSReport/NSE_250_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_250_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-10</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-10</t>
+    <t>Price_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-17</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-17</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-17</t>
   </si>
   <si>
     <t>RS_Score_2026-07-10</t>
@@ -43,759 +46,756 @@
     <t>RS_Score_2026-06-26</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-19</t>
-  </si>
-  <si>
     <t>CUPID</t>
   </si>
   <si>
+    <t>BALAMINES</t>
+  </si>
+  <si>
     <t>STLTECH</t>
   </si>
   <si>
+    <t>OPTIEMUS</t>
+  </si>
+  <si>
+    <t>JUSTDIAL</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>RELAXO</t>
+  </si>
+  <si>
+    <t>LLOYDSENGG</t>
+  </si>
+  <si>
     <t>SPARC</t>
   </si>
   <si>
-    <t>BALAMINES</t>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>WEWORK</t>
+  </si>
+  <si>
+    <t>DIACABS</t>
+  </si>
+  <si>
+    <t>NEOGEN</t>
+  </si>
+  <si>
+    <t>APOLLO</t>
+  </si>
+  <si>
+    <t>AEQUS</t>
+  </si>
+  <si>
+    <t>MARKSANS</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>SUDEEPPHRM</t>
+  </si>
+  <si>
+    <t>SFL</t>
+  </si>
+  <si>
+    <t>INDIAGLYCO</t>
+  </si>
+  <si>
+    <t>JLHL</t>
+  </si>
+  <si>
+    <t>PARAS</t>
+  </si>
+  <si>
+    <t>AZAD</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>LLOYDSENT</t>
+  </si>
+  <si>
+    <t>CCAVENUE</t>
+  </si>
+  <si>
+    <t>TIMETECHNO</t>
+  </si>
+  <si>
+    <t>AARTIDRUGS</t>
+  </si>
+  <si>
+    <t>BORORENEW</t>
+  </si>
+  <si>
+    <t>EQUITASBNK</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
+  </si>
+  <si>
+    <t>ATLANTAELE</t>
+  </si>
+  <si>
+    <t>DATAMATICS</t>
+  </si>
+  <si>
+    <t>BBOX</t>
+  </si>
+  <si>
+    <t>PCJEWELLER</t>
+  </si>
+  <si>
+    <t>APLLTD</t>
+  </si>
+  <si>
+    <t>KTKBANK</t>
+  </si>
+  <si>
+    <t>SUPRIYA</t>
+  </si>
+  <si>
+    <t>ALIVUS</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>ASHAPURMIN</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>WAAREERTL</t>
+  </si>
+  <si>
+    <t>METROPOLIS</t>
+  </si>
+  <si>
+    <t>HAPPSTMNDS</t>
+  </si>
+  <si>
+    <t>SOUTHBANK</t>
+  </si>
+  <si>
+    <t>SWSOLAR</t>
+  </si>
+  <si>
+    <t>REDTAPE</t>
+  </si>
+  <si>
+    <t>PNGJL</t>
+  </si>
+  <si>
+    <t>SMLMAH</t>
+  </si>
+  <si>
+    <t>INOXGREEN</t>
+  </si>
+  <si>
+    <t>DBREALTY</t>
+  </si>
+  <si>
+    <t>BLACKBUCK</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>TDPOWERSYS</t>
+  </si>
+  <si>
+    <t>PRAJIND</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>BECTORFOOD</t>
+  </si>
+  <si>
+    <t>CAMPUS</t>
+  </si>
+  <si>
+    <t>GNFC</t>
+  </si>
+  <si>
+    <t>GODREJAGRO</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>HGINFRA</t>
+  </si>
+  <si>
+    <t>EDELWEISS</t>
+  </si>
+  <si>
+    <t>HEMIPROP</t>
+  </si>
+  <si>
+    <t>RALLIS</t>
+  </si>
+  <si>
+    <t>RTNPOWER</t>
+  </si>
+  <si>
+    <t>CAPILLARY</t>
+  </si>
+  <si>
+    <t>SUNTECK</t>
+  </si>
+  <si>
+    <t>VGUARD</t>
+  </si>
+  <si>
+    <t>AWFIS</t>
+  </si>
+  <si>
+    <t>BALUFORGE</t>
+  </si>
+  <si>
+    <t>BAJAJELEC</t>
+  </si>
+  <si>
+    <t>AVANTIFEED</t>
+  </si>
+  <si>
+    <t>RBA</t>
+  </si>
+  <si>
+    <t>NFL</t>
+  </si>
+  <si>
+    <t>KNRCON</t>
+  </si>
+  <si>
+    <t>RENUKA</t>
+  </si>
+  <si>
+    <t>CELLO</t>
+  </si>
+  <si>
+    <t>ALOKINDS</t>
+  </si>
+  <si>
+    <t>FINPIPE</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>SHARDACROP</t>
+  </si>
+  <si>
+    <t>NETWORK18</t>
+  </si>
+  <si>
+    <t>MTARTECH</t>
+  </si>
+  <si>
+    <t>THOMASCOOK</t>
+  </si>
+  <si>
+    <t>THANGAMAYL</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>JSLL</t>
+  </si>
+  <si>
+    <t>SKYGOLD</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>CERA</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>THYROCARE</t>
+  </si>
+  <si>
+    <t>JAYNECOIND</t>
+  </si>
+  <si>
+    <t>VIYASH</t>
   </si>
   <si>
     <t>GREAVESCOT</t>
   </si>
   <si>
+    <t>MIDHANI</t>
+  </si>
+  <si>
+    <t>VOLTAMP</t>
+  </si>
+  <si>
+    <t>UJJIVANSFB</t>
+  </si>
+  <si>
+    <t>RELIGARE</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>TIINDIA</t>
+  </si>
+  <si>
+    <t>V2RETAIL</t>
+  </si>
+  <si>
+    <t>SKIPPER</t>
+  </si>
+  <si>
+    <t>SHAILY</t>
+  </si>
+  <si>
+    <t>VIKRAMSOLR</t>
+  </si>
+  <si>
+    <t>WEBELSOLAR</t>
+  </si>
+  <si>
     <t>WABAG</t>
   </si>
   <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>PARAS</t>
-  </si>
-  <si>
-    <t>SKYGOLD</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
+    <t>SHAKTIPUMP</t>
+  </si>
+  <si>
+    <t>BLUESTONE</t>
+  </si>
+  <si>
+    <t>IIFLCAPS</t>
+  </si>
+  <si>
+    <t>KPIGREEN</t>
+  </si>
+  <si>
+    <t>NAZARA</t>
+  </si>
+  <si>
+    <t>QPOWER</t>
+  </si>
+  <si>
+    <t>AXISCADES</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>KITEX</t>
+  </si>
+  <si>
+    <t>ARVIND</t>
+  </si>
+  <si>
+    <t>SENCO</t>
+  </si>
+  <si>
+    <t>JKLAKSHMI</t>
+  </si>
+  <si>
+    <t>MANORAMA</t>
+  </si>
+  <si>
+    <t>ALKYLAMINE</t>
+  </si>
+  <si>
+    <t>TRANSRAILL</t>
+  </si>
+  <si>
+    <t>STAR</t>
+  </si>
+  <si>
+    <t>POWERMECH</t>
+  </si>
+  <si>
+    <t>GOKEX</t>
+  </si>
+  <si>
+    <t>GRWRHITECH</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>JSFB</t>
+  </si>
+  <si>
+    <t>KRN</t>
+  </si>
+  <si>
+    <t>IXIGO</t>
+  </si>
+  <si>
+    <t>TEXRAIL</t>
+  </si>
+  <si>
+    <t>REFEX</t>
   </si>
   <si>
     <t>AETHER</t>
   </si>
   <si>
+    <t>SANDUMA</t>
+  </si>
+  <si>
+    <t>UTLSOLAR</t>
+  </si>
+  <si>
+    <t>SURYAROSNI</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>OSWALPUMPS</t>
+  </si>
+  <si>
+    <t>TANLA</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>MOIL</t>
+  </si>
+  <si>
+    <t>LUMAXTECH</t>
+  </si>
+  <si>
+    <t>PFOCUS</t>
+  </si>
+  <si>
+    <t>TIPSMUSIC</t>
+  </si>
+  <si>
+    <t>GPPL</t>
+  </si>
+  <si>
+    <t>KIRLOSBROS</t>
+  </si>
+  <si>
+    <t>KSB</t>
+  </si>
+  <si>
+    <t>AARTIPHARM</t>
+  </si>
+  <si>
+    <t>SAMHI</t>
+  </si>
+  <si>
+    <t>IMFA</t>
+  </si>
+  <si>
+    <t>DYNAMATECH</t>
+  </si>
+  <si>
+    <t>GHCL</t>
+  </si>
+  <si>
+    <t>PRIVISCL</t>
+  </si>
+  <si>
+    <t>PRICOLLTD</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>GMRP&amp;UI</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>JAMNAAUTO</t>
+  </si>
+  <si>
+    <t>ICIL</t>
+  </si>
+  <si>
+    <t>RTNINDIA</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>PICCADIL</t>
+  </si>
+  <si>
+    <t>AURIONPRO</t>
+  </si>
+  <si>
+    <t>ZAGGLE</t>
+  </si>
+  <si>
+    <t>ELECTCAST</t>
+  </si>
+  <si>
+    <t>BANCOINDIA</t>
+  </si>
+  <si>
+    <t>IFBIND</t>
+  </si>
+  <si>
+    <t>FIEMIND</t>
+  </si>
+  <si>
+    <t>LOTUSDEV</t>
+  </si>
+  <si>
+    <t>WELENT</t>
+  </si>
+  <si>
+    <t>TSFINV</t>
+  </si>
+  <si>
+    <t>LXCHEM</t>
+  </si>
+  <si>
+    <t>TVSSCS</t>
+  </si>
+  <si>
+    <t>SUDARSCHEM</t>
+  </si>
+  <si>
+    <t>ASHOKA</t>
+  </si>
+  <si>
     <t>EIEL</t>
   </si>
   <si>
-    <t>QUESS</t>
-  </si>
-  <si>
-    <t>APOLLO</t>
-  </si>
-  <si>
-    <t>MARKSANS</t>
-  </si>
-  <si>
-    <t>DIACABS</t>
-  </si>
-  <si>
-    <t>REFEX</t>
+    <t>JYOTHYLAB</t>
+  </si>
+  <si>
+    <t>VMART</t>
+  </si>
+  <si>
+    <t>VIPIND</t>
+  </si>
+  <si>
+    <t>FEDFINA</t>
+  </si>
+  <si>
+    <t>ARVINDFASN</t>
+  </si>
+  <si>
+    <t>PGIL</t>
+  </si>
+  <si>
+    <t>GSFC</t>
+  </si>
+  <si>
+    <t>SHRIPISTON</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>JKPAPER</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>INDIGOPNTS</t>
+  </si>
+  <si>
+    <t>GOKULAGRO</t>
+  </si>
+  <si>
+    <t>EUREKAFORB</t>
+  </si>
+  <si>
+    <t>RAYMONDLSL</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>ADVENZYMES</t>
+  </si>
+  <si>
+    <t>EPL</t>
+  </si>
+  <si>
+    <t>KSCL</t>
+  </si>
+  <si>
+    <t>MANYAVAR</t>
+  </si>
+  <si>
+    <t>MEDPLUS</t>
+  </si>
+  <si>
+    <t>CRAMC</t>
+  </si>
+  <si>
+    <t>MAHSEAMLES</t>
   </si>
   <si>
     <t>IONEXCHANG</t>
   </si>
   <si>
-    <t>CCAVENUE</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>AZAD</t>
-  </si>
-  <si>
-    <t>GOKEX</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>SHRIPISTON</t>
-  </si>
-  <si>
-    <t>DATAMATICS</t>
-  </si>
-  <si>
-    <t>WELENT</t>
-  </si>
-  <si>
-    <t>SWSOLAR</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>WEBELSOLAR</t>
-  </si>
-  <si>
-    <t>TVSSCS</t>
-  </si>
-  <si>
-    <t>THYROCARE</t>
-  </si>
-  <si>
-    <t>APLLTD</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>UJJIVANSFB</t>
-  </si>
-  <si>
-    <t>SUDARSCHEM</t>
-  </si>
-  <si>
-    <t>PRIVISCL</t>
-  </si>
-  <si>
-    <t>TANLA</t>
-  </si>
-  <si>
-    <t>KTKBANK</t>
-  </si>
-  <si>
-    <t>SHAILY</t>
-  </si>
-  <si>
-    <t>HAPPSTMNDS</t>
-  </si>
-  <si>
-    <t>JSFB</t>
+    <t>EMIL</t>
+  </si>
+  <si>
+    <t>SAATVIKGL</t>
+  </si>
+  <si>
+    <t>SANOFICONR</t>
+  </si>
+  <si>
+    <t>STYRENIX</t>
+  </si>
+  <si>
+    <t>VAIBHAVGBL</t>
+  </si>
+  <si>
+    <t>PNCINFRA</t>
+  </si>
+  <si>
+    <t>ASKAUTOLTD</t>
+  </si>
+  <si>
+    <t>AKUMS</t>
+  </si>
+  <si>
+    <t>AVL</t>
+  </si>
+  <si>
+    <t>TARC</t>
+  </si>
+  <si>
+    <t>ETHOSLTD</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>RATNAMANI</t>
   </si>
   <si>
     <t>AGARWALEYE</t>
   </si>
   <si>
-    <t>SENCO</t>
-  </si>
-  <si>
-    <t>PRICOLLTD</t>
-  </si>
-  <si>
-    <t>PCJEWELLER</t>
-  </si>
-  <si>
-    <t>SHAKTIPUMP</t>
-  </si>
-  <si>
-    <t>MANORAMA</t>
-  </si>
-  <si>
-    <t>ASKAUTOLTD</t>
+    <t>WAKEFIT</t>
+  </si>
+  <si>
+    <t>MASTEK</t>
+  </si>
+  <si>
+    <t>KANSAINER</t>
+  </si>
+  <si>
+    <t>STYL</t>
+  </si>
+  <si>
+    <t>HERITGFOOD</t>
+  </si>
+  <si>
+    <t>CSBBANK</t>
+  </si>
+  <si>
+    <t>SHAREINDIA</t>
+  </si>
+  <si>
+    <t>CRIZAC</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
   </si>
   <si>
     <t>PURVA</t>
   </si>
   <si>
-    <t>OSWALPUMPS</t>
-  </si>
-  <si>
-    <t>EPL</t>
-  </si>
-  <si>
-    <t>GOKULAGRO</t>
-  </si>
-  <si>
-    <t>AARTIDRUGS</t>
+    <t>ANUP</t>
+  </si>
+  <si>
+    <t>MAHSCOOTER</t>
+  </si>
+  <si>
+    <t>PRSMJOHNSN</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>SMARTWORKS</t>
+  </si>
+  <si>
+    <t>DBL</t>
+  </si>
+  <si>
+    <t>VARROC</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>STARCEMENT</t>
+  </si>
+  <si>
+    <t>ELLEN</t>
+  </si>
+  <si>
+    <t>BIRLACORPN</t>
+  </si>
+  <si>
+    <t>ORIENTCEM</t>
+  </si>
+  <si>
+    <t>AHLUCONT</t>
+  </si>
+  <si>
+    <t>ORKLAINDIA</t>
+  </si>
+  <si>
+    <t>INDIASHLTR</t>
+  </si>
+  <si>
+    <t>CENTURYPLY</t>
+  </si>
+  <si>
+    <t>JAIBALAJI</t>
+  </si>
+  <si>
+    <t>SUBROS</t>
   </si>
   <si>
     <t>WESTLIFE</t>
   </si>
   <si>
-    <t>TDPOWERSYS</t>
-  </si>
-  <si>
-    <t>SOUTHBANK</t>
-  </si>
-  <si>
-    <t>JUSTDIAL</t>
-  </si>
-  <si>
-    <t>MIDHANI</t>
-  </si>
-  <si>
-    <t>INOXGREEN</t>
-  </si>
-  <si>
-    <t>MASTEK</t>
-  </si>
-  <si>
-    <t>ARVINDFASN</t>
-  </si>
-  <si>
-    <t>V2RETAIL</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>HERITGFOOD</t>
-  </si>
-  <si>
-    <t>PNGJL</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>KNRCON</t>
-  </si>
-  <si>
-    <t>VIKRAMSOLR</t>
-  </si>
-  <si>
-    <t>RTNINDIA</t>
-  </si>
-  <si>
-    <t>KPIGREEN</t>
-  </si>
-  <si>
-    <t>SUNTECK</t>
-  </si>
-  <si>
-    <t>JAYNECOIND</t>
-  </si>
-  <si>
-    <t>AWFIS</t>
-  </si>
-  <si>
-    <t>RTNPOWER</t>
-  </si>
-  <si>
-    <t>NFL</t>
-  </si>
-  <si>
-    <t>GODREJAGRO</t>
-  </si>
-  <si>
-    <t>GHCL</t>
-  </si>
-  <si>
-    <t>KITEX</t>
-  </si>
-  <si>
-    <t>CAMPUS</t>
-  </si>
-  <si>
-    <t>JSLL</t>
-  </si>
-  <si>
-    <t>RALLIS</t>
-  </si>
-  <si>
-    <t>NETWORK18</t>
-  </si>
-  <si>
-    <t>JAIBALAJI</t>
-  </si>
-  <si>
-    <t>WAKEFIT</t>
-  </si>
-  <si>
-    <t>TARC</t>
-  </si>
-  <si>
-    <t>CELLO</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>CRIZAC</t>
-  </si>
-  <si>
-    <t>RENUKA</t>
-  </si>
-  <si>
-    <t>PRSMJOHNSN</t>
-  </si>
-  <si>
-    <t>AXISCADES</t>
-  </si>
-  <si>
-    <t>JYOTHYLAB</t>
-  </si>
-  <si>
-    <t>JKLAKSHMI</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>AVANTIFEED</t>
-  </si>
-  <si>
-    <t>THOMASCOOK</t>
-  </si>
-  <si>
-    <t>THANGAMAYL</t>
-  </si>
-  <si>
-    <t>HGINFRA</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>BBOX</t>
-  </si>
-  <si>
-    <t>CERA</t>
-  </si>
-  <si>
-    <t>RAIN</t>
-  </si>
-  <si>
-    <t>EQUITASBNK</t>
-  </si>
-  <si>
-    <t>PRAJIND</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
-    <t>SFL</t>
-  </si>
-  <si>
-    <t>EDELWEISS</t>
-  </si>
-  <si>
-    <t>ASHAPURMIN</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>VOLTAMP</t>
-  </si>
-  <si>
-    <t>RELIGARE</t>
-  </si>
-  <si>
-    <t>TMB</t>
-  </si>
-  <si>
-    <t>AEQUS</t>
-  </si>
-  <si>
-    <t>BORORENEW</t>
-  </si>
-  <si>
-    <t>TIINDIA</t>
-  </si>
-  <si>
-    <t>SKIPPER</t>
-  </si>
-  <si>
-    <t>LLOYDSENGG</t>
-  </si>
-  <si>
-    <t>BLUESTONE</t>
-  </si>
-  <si>
-    <t>IIFLCAPS</t>
-  </si>
-  <si>
-    <t>WEWORK</t>
-  </si>
-  <si>
-    <t>NAZARA</t>
-  </si>
-  <si>
-    <t>QPOWER</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
-    <t>ARVIND</t>
-  </si>
-  <si>
-    <t>NEOGEN</t>
-  </si>
-  <si>
-    <t>RBA</t>
-  </si>
-  <si>
-    <t>ALKYLAMINE</t>
-  </si>
-  <si>
-    <t>MSTCLTD</t>
-  </si>
-  <si>
-    <t>TRANSRAILL</t>
-  </si>
-  <si>
-    <t>STAR</t>
-  </si>
-  <si>
-    <t>SUPRIYA</t>
-  </si>
-  <si>
-    <t>POWERMECH</t>
-  </si>
-  <si>
-    <t>GRWRHITECH</t>
-  </si>
-  <si>
-    <t>TIMETECHNO</t>
-  </si>
-  <si>
-    <t>KRN</t>
-  </si>
-  <si>
-    <t>IXIGO</t>
-  </si>
-  <si>
-    <t>TEXRAIL</t>
-  </si>
-  <si>
-    <t>WAAREERTL</t>
-  </si>
-  <si>
-    <t>BALUFORGE</t>
-  </si>
-  <si>
-    <t>SANDUMA</t>
-  </si>
-  <si>
-    <t>UTLSOLAR</t>
-  </si>
-  <si>
-    <t>SURYAROSNI</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>MOIL</t>
-  </si>
-  <si>
-    <t>LUMAXTECH</t>
-  </si>
-  <si>
-    <t>PFOCUS</t>
-  </si>
-  <si>
-    <t>TIPSMUSIC</t>
-  </si>
-  <si>
-    <t>SUDEEPPHRM</t>
-  </si>
-  <si>
-    <t>GPPL</t>
-  </si>
-  <si>
-    <t>KIRLOSBROS</t>
-  </si>
-  <si>
-    <t>KSB</t>
-  </si>
-  <si>
-    <t>AARTIPHARM</t>
-  </si>
-  <si>
-    <t>SAMHI</t>
-  </si>
-  <si>
-    <t>BLACKBUCK</t>
-  </si>
-  <si>
-    <t>ATLANTAELE</t>
-  </si>
-  <si>
-    <t>LLOYDSENT</t>
-  </si>
-  <si>
-    <t>IMFA</t>
-  </si>
-  <si>
-    <t>DYNAMATECH</t>
-  </si>
-  <si>
-    <t>SHARDACROP</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>GMRP&amp;UI</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>GNFC</t>
-  </si>
-  <si>
-    <t>JAMNAAUTO</t>
-  </si>
-  <si>
-    <t>ICIL</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>PICCADIL</t>
-  </si>
-  <si>
-    <t>AURIONPRO</t>
-  </si>
-  <si>
-    <t>ZAGGLE</t>
-  </si>
-  <si>
-    <t>ELECTCAST</t>
-  </si>
-  <si>
-    <t>BANCOINDIA</t>
-  </si>
-  <si>
-    <t>IFBIND</t>
-  </si>
-  <si>
-    <t>FIEMIND</t>
-  </si>
-  <si>
-    <t>LOTUSDEV</t>
-  </si>
-  <si>
-    <t>TSFINV</t>
-  </si>
-  <si>
-    <t>BECTORFOOD</t>
-  </si>
-  <si>
-    <t>LXCHEM</t>
-  </si>
-  <si>
-    <t>SMLMAH</t>
-  </si>
-  <si>
-    <t>ASHOKA</t>
-  </si>
-  <si>
-    <t>OPTIEMUS</t>
-  </si>
-  <si>
-    <t>ALOKINDS</t>
-  </si>
-  <si>
-    <t>VMART</t>
-  </si>
-  <si>
-    <t>VIPIND</t>
-  </si>
-  <si>
-    <t>FEDFINA</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>PGIL</t>
-  </si>
-  <si>
-    <t>GSFC</t>
-  </si>
-  <si>
-    <t>JKPAPER</t>
-  </si>
-  <si>
-    <t>HEMIPROP</t>
-  </si>
-  <si>
-    <t>SAFARI</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>INDIGOPNTS</t>
-  </si>
-  <si>
-    <t>EUREKAFORB</t>
-  </si>
-  <si>
-    <t>RAYMONDLSL</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>ADVENZYMES</t>
-  </si>
-  <si>
-    <t>ALIVUS</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>BAJAJELEC</t>
-  </si>
-  <si>
-    <t>KSCL</t>
-  </si>
-  <si>
-    <t>MANYAVAR</t>
-  </si>
-  <si>
-    <t>MEDPLUS</t>
-  </si>
-  <si>
-    <t>REDTAPE</t>
-  </si>
-  <si>
-    <t>CRAMC</t>
-  </si>
-  <si>
-    <t>MAHSEAMLES</t>
-  </si>
-  <si>
-    <t>EMIL</t>
-  </si>
-  <si>
-    <t>SAATVIKGL</t>
-  </si>
-  <si>
-    <t>FINPIPE</t>
-  </si>
-  <si>
-    <t>SANOFICONR</t>
-  </si>
-  <si>
-    <t>STYRENIX</t>
-  </si>
-  <si>
-    <t>VAIBHAVGBL</t>
-  </si>
-  <si>
-    <t>PNCINFRA</t>
-  </si>
-  <si>
-    <t>AKUMS</t>
-  </si>
-  <si>
-    <t>AVL</t>
-  </si>
-  <si>
-    <t>ROUTE</t>
-  </si>
-  <si>
-    <t>ETHOSLTD</t>
-  </si>
-  <si>
-    <t>METROPOLIS</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>RATNAMANI</t>
-  </si>
-  <si>
-    <t>JLHL</t>
-  </si>
-  <si>
-    <t>KANSAINER</t>
-  </si>
-  <si>
-    <t>DBREALTY</t>
-  </si>
-  <si>
-    <t>STYL</t>
-  </si>
-  <si>
-    <t>CSBBANK</t>
-  </si>
-  <si>
-    <t>INDIAGLYCO</t>
-  </si>
-  <si>
-    <t>SHAREINDIA</t>
-  </si>
-  <si>
-    <t>VGUARD</t>
-  </si>
-  <si>
-    <t>GMMPFAUDLR</t>
-  </si>
-  <si>
-    <t>RELAXO</t>
-  </si>
-  <si>
-    <t>ANUP</t>
-  </si>
-  <si>
-    <t>MAHSCOOTER</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>SMARTWORKS</t>
-  </si>
-  <si>
-    <t>DBL</t>
-  </si>
-  <si>
-    <t>VARROC</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>STARCEMENT</t>
-  </si>
-  <si>
-    <t>ELLEN</t>
-  </si>
-  <si>
-    <t>BIRLACORPN</t>
-  </si>
-  <si>
-    <t>ORIENTCEM</t>
-  </si>
-  <si>
-    <t>AHLUCONT</t>
-  </si>
-  <si>
-    <t>ORKLAINDIA</t>
-  </si>
-  <si>
-    <t>INDIASHLTR</t>
-  </si>
-  <si>
-    <t>CENTURYPLY</t>
-  </si>
-  <si>
-    <t>SUBROS</t>
-  </si>
-  <si>
-    <t>CAPILLARY</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -814,6 +814,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
     <t>2026-07-10</t>
   </si>
   <si>
@@ -821,9 +824,6 @@
   </si>
   <si>
     <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
   </si>
 </sst>
 </file>
@@ -1322,28 +1322,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>212.24</v>
+        <v>214.78</v>
       </c>
       <c r="C2" s="2">
-        <v>176.03</v>
+        <v>131.32</v>
       </c>
       <c r="D2" s="2">
-        <v>67.48999999999999</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2">
-        <v>28.76</v>
+        <v>19.46</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
       <c r="I2" s="2">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>260</v>
@@ -1354,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>543.05</v>
+        <v>2289.1</v>
       </c>
       <c r="C3" s="2">
-        <v>214.9</v>
+        <v>123.91</v>
       </c>
       <c r="D3" s="2">
-        <v>75.55</v>
+        <v>62.64</v>
       </c>
       <c r="E3" s="2">
-        <v>-10.8</v>
+        <v>8.33</v>
       </c>
       <c r="F3" s="2">
-        <v>98.97</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>260</v>
@@ -1386,28 +1386,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>264.6</v>
+        <v>520.4</v>
       </c>
       <c r="C4" s="2">
-        <v>110.13</v>
+        <v>188.89</v>
       </c>
       <c r="D4" s="2">
-        <v>89.41</v>
+        <v>31.85</v>
       </c>
       <c r="E4" s="2">
-        <v>15.53</v>
+        <v>-16.6</v>
       </c>
       <c r="F4" s="2">
-        <v>97.94</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>97.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>260</v>
@@ -1418,28 +1418,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>2414.9</v>
+        <v>588.95</v>
       </c>
       <c r="C5" s="2">
-        <v>127.45</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D5" s="2">
-        <v>66.73999999999999</v>
+        <v>36.92</v>
       </c>
       <c r="E5" s="2">
-        <v>15.12</v>
+        <v>33.25</v>
       </c>
       <c r="F5" s="2">
-        <v>96.91</v>
+        <v>96.47</v>
       </c>
       <c r="G5" s="2">
-        <v>97.2</v>
+        <v>88.8</v>
       </c>
       <c r="H5" s="2">
-        <v>97.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I5" s="2">
-        <v>97.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>260</v>
@@ -1450,28 +1450,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>263.6</v>
+        <v>767.3</v>
       </c>
       <c r="C6" s="2">
-        <v>74.65000000000001</v>
+        <v>42.46</v>
       </c>
       <c r="D6" s="2">
-        <v>57.22</v>
+        <v>42.67</v>
       </c>
       <c r="E6" s="2">
-        <v>37.69</v>
+        <v>39.74</v>
       </c>
       <c r="F6" s="2">
-        <v>95.88</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="I6" s="2">
-        <v>79.2</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>260</v>
@@ -1482,28 +1482,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>2221.2</v>
+        <v>1439.6</v>
       </c>
       <c r="C7" s="2">
-        <v>80.81999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="D7" s="2">
-        <v>47.06</v>
+        <v>51.31</v>
       </c>
       <c r="E7" s="2">
-        <v>36.35</v>
+        <v>4.58</v>
       </c>
       <c r="F7" s="2">
-        <v>94.84999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>93.2</v>
       </c>
       <c r="H7" s="2">
-        <v>98</v>
+        <v>90.8</v>
       </c>
       <c r="I7" s="2">
-        <v>95.2</v>
+        <v>97.2</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>260</v>
@@ -1514,28 +1514,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>1803.7</v>
+        <v>439.95</v>
       </c>
       <c r="C8" s="2">
-        <v>83.59999999999999</v>
+        <v>42.86</v>
       </c>
       <c r="D8" s="2">
-        <v>62.39</v>
+        <v>41.76</v>
       </c>
       <c r="E8" s="2">
-        <v>23.71</v>
+        <v>23.49</v>
       </c>
       <c r="F8" s="2">
-        <v>93.81</v>
+        <v>92.94</v>
       </c>
       <c r="G8" s="2">
-        <v>98.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H8" s="2">
-        <v>98.8</v>
+        <v>82</v>
       </c>
       <c r="I8" s="2">
-        <v>97.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>260</v>
@@ -1546,28 +1546,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>627.15</v>
+        <v>88.56</v>
       </c>
       <c r="C9" s="2">
-        <v>93.83</v>
+        <v>97.11</v>
       </c>
       <c r="D9" s="2">
-        <v>49.79</v>
+        <v>33.86</v>
       </c>
       <c r="E9" s="2">
-        <v>17.72</v>
+        <v>-1.92</v>
       </c>
       <c r="F9" s="2">
-        <v>92.78</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>94.8</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2">
-        <v>92.8</v>
+        <v>94</v>
       </c>
       <c r="I9" s="2">
-        <v>88.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>260</v>
@@ -1578,28 +1578,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1253.1</v>
+        <v>235.2</v>
       </c>
       <c r="C10" s="2">
-        <v>86.79000000000001</v>
+        <v>89.11</v>
       </c>
       <c r="D10" s="2">
-        <v>60.17</v>
+        <v>39.63</v>
       </c>
       <c r="E10" s="2">
-        <v>13.08</v>
+        <v>-1.19</v>
       </c>
       <c r="F10" s="2">
-        <v>91.75</v>
+        <v>90.59</v>
       </c>
       <c r="G10" s="2">
         <v>99.2</v>
       </c>
       <c r="H10" s="2">
-        <v>99.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>99.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>260</v>
@@ -1610,28 +1610,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>623.85</v>
+        <v>290.95</v>
       </c>
       <c r="C11" s="2">
-        <v>80.62</v>
+        <v>55.71</v>
       </c>
       <c r="D11" s="2">
-        <v>36.63</v>
+        <v>31.98</v>
       </c>
       <c r="E11" s="2">
-        <v>16.9</v>
+        <v>18.33</v>
       </c>
       <c r="F11" s="2">
-        <v>90.72</v>
+        <v>89.41</v>
       </c>
       <c r="G11" s="2">
-        <v>88</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H11" s="2">
-        <v>68</v>
+        <v>92.8</v>
       </c>
       <c r="I11" s="2">
-        <v>84</v>
+        <v>85.2</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>260</v>
@@ -1642,28 +1642,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1431.4</v>
+        <v>1724</v>
       </c>
       <c r="C12" s="2">
-        <v>85.08</v>
+        <v>81.28</v>
       </c>
       <c r="D12" s="2">
-        <v>46.58</v>
+        <v>28.66</v>
       </c>
       <c r="E12" s="2">
-        <v>6.47</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="2">
-        <v>89.69</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G12" s="2">
-        <v>90.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H12" s="2">
-        <v>97.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I12" s="2">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>260</v>
@@ -1674,28 +1674,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>1500.8</v>
+        <v>677.95</v>
       </c>
       <c r="C13" s="2">
-        <v>61</v>
+        <v>53.77</v>
       </c>
       <c r="D13" s="2">
-        <v>19.87</v>
+        <v>29.33</v>
       </c>
       <c r="E13" s="2">
-        <v>30.55</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F13" s="2">
-        <v>88.66</v>
+        <v>87.06</v>
       </c>
       <c r="G13" s="2">
-        <v>83.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H13" s="2">
-        <v>83.2</v>
+        <v>84</v>
       </c>
       <c r="I13" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>260</v>
@@ -1706,28 +1706,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>244.49</v>
+        <v>222.38</v>
       </c>
       <c r="C14" s="2">
-        <v>60.23</v>
+        <v>59.77</v>
       </c>
       <c r="D14" s="2">
-        <v>14.5</v>
+        <v>27.26</v>
       </c>
       <c r="E14" s="2">
-        <v>29.44</v>
+        <v>7.09</v>
       </c>
       <c r="F14" s="2">
-        <v>87.63</v>
+        <v>85.88</v>
       </c>
       <c r="G14" s="2">
         <v>89.2</v>
       </c>
       <c r="H14" s="2">
-        <v>80.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="I14" s="2">
-        <v>57.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>260</v>
@@ -1738,28 +1738,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>288.15</v>
+        <v>2175.6</v>
       </c>
       <c r="C15" s="2">
-        <v>52.25</v>
+        <v>46.09</v>
       </c>
       <c r="D15" s="2">
-        <v>37.98</v>
+        <v>24.9</v>
       </c>
       <c r="E15" s="2">
-        <v>17.35</v>
+        <v>13.61</v>
       </c>
       <c r="F15" s="2">
-        <v>86.59999999999999</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="G15" s="2">
-        <v>92.8</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2">
-        <v>85.2</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2">
-        <v>85.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>260</v>
@@ -1770,28 +1770,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>408.85</v>
+        <v>397.8</v>
       </c>
       <c r="C16" s="2">
-        <v>91.03</v>
+        <v>82.75</v>
       </c>
       <c r="D16" s="2">
-        <v>38.31</v>
+        <v>25.21</v>
       </c>
       <c r="E16" s="2">
-        <v>-3.04</v>
+        <v>-6.34</v>
       </c>
       <c r="F16" s="2">
-        <v>85.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="G16" s="2">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2">
         <v>95.2</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>84.40000000000001</v>
-      </c>
-      <c r="I16" s="2">
-        <v>94.40000000000001</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>260</v>
@@ -1802,28 +1802,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>272.4</v>
+        <v>228.38</v>
       </c>
       <c r="C17" s="2">
-        <v>58.98</v>
+        <v>80.41</v>
       </c>
       <c r="D17" s="2">
-        <v>43.91</v>
+        <v>20.6</v>
       </c>
       <c r="E17" s="2">
-        <v>9.06</v>
+        <v>-3.58</v>
       </c>
       <c r="F17" s="2">
-        <v>84.54000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G17" s="2">
-        <v>87.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2">
-        <v>87.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>89.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>260</v>
@@ -1834,28 +1834,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>229.01</v>
+        <v>267.1</v>
       </c>
       <c r="C18" s="2">
-        <v>67.16</v>
+        <v>53.45</v>
       </c>
       <c r="D18" s="2">
-        <v>37.94</v>
+        <v>31.4</v>
       </c>
       <c r="E18" s="2">
-        <v>6.35</v>
+        <v>4.31</v>
       </c>
       <c r="F18" s="2">
-        <v>83.51000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="G18" s="2">
-        <v>74.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H18" s="2">
-        <v>86.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I18" s="2">
-        <v>90.8</v>
+        <v>87.2</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>260</v>
@@ -1866,28 +1866,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>344.75</v>
+        <v>3218.8</v>
       </c>
       <c r="C19" s="2">
-        <v>60.42</v>
+        <v>47.34</v>
       </c>
       <c r="D19" s="2">
-        <v>32.29</v>
+        <v>30.04</v>
       </c>
       <c r="E19" s="2">
-        <v>9.76</v>
+        <v>7.6</v>
       </c>
       <c r="F19" s="2">
-        <v>82.47</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2">
-        <v>90</v>
+        <v>81.2</v>
       </c>
       <c r="I19" s="2">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>260</v>
@@ -1898,28 +1898,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>468.3</v>
+        <v>862.75</v>
       </c>
       <c r="C20" s="2">
-        <v>32.12</v>
+        <v>45.21</v>
       </c>
       <c r="D20" s="2">
-        <v>13.76</v>
+        <v>32.77</v>
       </c>
       <c r="E20" s="2">
-        <v>30.85</v>
+        <v>3.8</v>
       </c>
       <c r="F20" s="2">
-        <v>81.44</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="G20" s="2">
-        <v>70.8</v>
+        <v>69.2</v>
       </c>
       <c r="H20" s="2">
-        <v>56.4</v>
+        <v>85.2</v>
       </c>
       <c r="I20" s="2">
-        <v>9.6</v>
+        <v>70</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>260</v>
@@ -1930,28 +1930,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>18.1</v>
+        <v>761.1</v>
       </c>
       <c r="C21" s="2">
-        <v>11.94</v>
+        <v>47.14</v>
       </c>
       <c r="D21" s="2">
-        <v>31.83</v>
+        <v>31.02</v>
       </c>
       <c r="E21" s="2">
-        <v>31.25</v>
+        <v>2.75</v>
       </c>
       <c r="F21" s="2">
-        <v>80.41</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="G21" s="2">
-        <v>72.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="H21" s="2">
-        <v>51.2</v>
+        <v>86.8</v>
       </c>
       <c r="I21" s="2">
-        <v>33.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>260</v>
@@ -1962,28 +1962,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>3304</v>
+        <v>1159.3</v>
       </c>
       <c r="C22" s="2">
-        <v>48.17</v>
+        <v>35.31</v>
       </c>
       <c r="D22" s="2">
-        <v>32.7</v>
+        <v>4.37</v>
       </c>
       <c r="E22" s="2">
-        <v>12.38</v>
+        <v>21.27</v>
       </c>
       <c r="F22" s="2">
-        <v>79.38</v>
+        <v>76.47</v>
       </c>
       <c r="G22" s="2">
-        <v>81.2</v>
+        <v>60.8</v>
       </c>
       <c r="H22" s="2">
-        <v>88.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="I22" s="2">
-        <v>82.40000000000001</v>
+        <v>26.8</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>260</v>
@@ -1994,28 +1994,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>7101</v>
+        <v>1553</v>
       </c>
       <c r="C23" s="2">
-        <v>89.70999999999999</v>
+        <v>22.87</v>
       </c>
       <c r="D23" s="2">
-        <v>15.89</v>
+        <v>23.33</v>
       </c>
       <c r="E23" s="2">
-        <v>-3.31</v>
+        <v>14.4</v>
       </c>
       <c r="F23" s="2">
-        <v>78.34999999999999</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="G23" s="2">
-        <v>90.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="H23" s="2">
-        <v>98.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="I23" s="2">
-        <v>98.8</v>
+        <v>54.8</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>260</v>
@@ -2026,28 +2026,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>2479.5</v>
+        <v>1176.3</v>
       </c>
       <c r="C24" s="2">
-        <v>47.85</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="D24" s="2">
-        <v>14.7</v>
+        <v>36.32</v>
       </c>
       <c r="E24" s="2">
-        <v>16.85</v>
+        <v>-14.69</v>
       </c>
       <c r="F24" s="2">
-        <v>77.31999999999999</v>
+        <v>74.12</v>
       </c>
       <c r="G24" s="2">
-        <v>42.4</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H24" s="2">
-        <v>59.2</v>
+        <v>99.2</v>
       </c>
       <c r="I24" s="2">
-        <v>72.8</v>
+        <v>99.2</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>260</v>
@@ -2058,28 +2058,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>832.75</v>
+        <v>2329.7</v>
       </c>
       <c r="C25" s="2">
-        <v>28.65</v>
+        <v>42.41</v>
       </c>
       <c r="D25" s="2">
-        <v>20.28</v>
+        <v>6.86</v>
       </c>
       <c r="E25" s="2">
-        <v>15.38</v>
+        <v>11.88</v>
       </c>
       <c r="F25" s="2">
-        <v>76.29000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="G25" s="2">
-        <v>80.8</v>
+        <v>82</v>
       </c>
       <c r="H25" s="2">
-        <v>75.2</v>
+        <v>42.4</v>
       </c>
       <c r="I25" s="2">
-        <v>66</v>
+        <v>59.2</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>260</v>
@@ -2090,28 +2090,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>286.1</v>
+        <v>472.15</v>
       </c>
       <c r="C26" s="2">
-        <v>50.16</v>
+        <v>26.72</v>
       </c>
       <c r="D26" s="2">
-        <v>19.19</v>
+        <v>20.48</v>
       </c>
       <c r="E26" s="2">
-        <v>4.99</v>
+        <v>12.48</v>
       </c>
       <c r="F26" s="2">
-        <v>75.26000000000001</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="G26" s="2">
-        <v>79.2</v>
+        <v>70.8</v>
       </c>
       <c r="H26" s="2">
-        <v>86</v>
+        <v>76.8</v>
       </c>
       <c r="I26" s="2">
-        <v>86.8</v>
+        <v>58</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>260</v>
@@ -2122,28 +2122,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>4189.6</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="C27" s="2">
-        <v>36.2</v>
+        <v>58.06</v>
       </c>
       <c r="D27" s="2">
-        <v>17.35</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E27" s="2">
-        <v>11.96</v>
+        <v>0.34</v>
       </c>
       <c r="F27" s="2">
-        <v>74.23</v>
+        <v>70.59</v>
       </c>
       <c r="G27" s="2">
-        <v>87.2</v>
+        <v>83.2</v>
       </c>
       <c r="H27" s="2">
-        <v>82.8</v>
+        <v>80</v>
       </c>
       <c r="I27" s="2">
-        <v>69.2</v>
+        <v>72.8</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>260</v>
@@ -2154,28 +2154,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>900.45</v>
+        <v>17.06</v>
       </c>
       <c r="C28" s="2">
-        <v>22.83</v>
+        <v>12.91</v>
       </c>
       <c r="D28" s="2">
-        <v>23.4</v>
+        <v>22.29</v>
       </c>
       <c r="E28" s="2">
-        <v>13.61</v>
+        <v>13.73</v>
       </c>
       <c r="F28" s="2">
-        <v>73.2</v>
+        <v>69.41</v>
       </c>
       <c r="G28" s="2">
-        <v>47.2</v>
+        <v>86.8</v>
       </c>
       <c r="H28" s="2">
-        <v>48.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I28" s="2">
-        <v>50.4</v>
+        <v>51.2</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>260</v>
@@ -2186,28 +2186,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>614</v>
+        <v>204.03</v>
       </c>
       <c r="C29" s="2">
-        <v>31.32</v>
+        <v>19.33</v>
       </c>
       <c r="D29" s="2">
-        <v>16.99</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2">
-        <v>10.11</v>
+        <v>15.54</v>
       </c>
       <c r="F29" s="2">
-        <v>72.16</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="G29" s="2">
-        <v>74.40000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="H29" s="2">
-        <v>71.59999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="I29" s="2">
-        <v>74</v>
+        <v>29.6</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>260</v>
@@ -2218,28 +2218,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>236.55</v>
+        <v>422.3</v>
       </c>
       <c r="C30" s="2">
-        <v>24.51</v>
+        <v>19.48</v>
       </c>
       <c r="D30" s="2">
-        <v>11.54</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2">
-        <v>12.11</v>
+        <v>12.19</v>
       </c>
       <c r="F30" s="2">
-        <v>71.13</v>
+        <v>67.06</v>
       </c>
       <c r="G30" s="2">
-        <v>78</v>
+        <v>47.2</v>
       </c>
       <c r="H30" s="2">
-        <v>88.8</v>
+        <v>40.4</v>
       </c>
       <c r="I30" s="2">
-        <v>83.2</v>
+        <v>30</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>260</v>
@@ -2250,28 +2250,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>462.4</v>
+        <v>604.55</v>
       </c>
       <c r="C31" s="2">
-        <v>16.94</v>
+        <v>41.88</v>
       </c>
       <c r="D31" s="2">
-        <v>10.24</v>
+        <v>9.94</v>
       </c>
       <c r="E31" s="2">
-        <v>16.08</v>
+        <v>0.03</v>
       </c>
       <c r="F31" s="2">
-        <v>70.09999999999999</v>
+        <v>65.88</v>
       </c>
       <c r="G31" s="2">
-        <v>76.8</v>
+        <v>85.2</v>
       </c>
       <c r="H31" s="2">
-        <v>58</v>
+        <v>82.8</v>
       </c>
       <c r="I31" s="2">
-        <v>53.6</v>
+        <v>86.8</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>260</v>
@@ -2282,28 +2282,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>99.84999999999999</v>
+        <v>77.72</v>
       </c>
       <c r="C32" s="2">
-        <v>83.38</v>
+        <v>33.4</v>
       </c>
       <c r="D32" s="2">
-        <v>-14.06</v>
+        <v>11.35</v>
       </c>
       <c r="E32" s="2">
-        <v>-5.04</v>
+        <v>1.5</v>
       </c>
       <c r="F32" s="2">
-        <v>69.06999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G32" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H32" s="2">
-        <v>72.40000000000001</v>
+        <v>56</v>
       </c>
       <c r="I32" s="2">
-        <v>74.8</v>
+        <v>66</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>260</v>
@@ -2314,28 +2314,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>141.66</v>
+        <v>594.55</v>
       </c>
       <c r="C33" s="2">
-        <v>25.74</v>
+        <v>39.55</v>
       </c>
       <c r="D33" s="2">
-        <v>21.1</v>
+        <v>35.51</v>
       </c>
       <c r="E33" s="2">
-        <v>5.25</v>
+        <v>-13.86</v>
       </c>
       <c r="F33" s="2">
-        <v>68.04000000000001</v>
+        <v>63.53</v>
       </c>
       <c r="G33" s="2">
-        <v>68.8</v>
+        <v>88</v>
       </c>
       <c r="H33" s="2">
-        <v>70.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I33" s="2">
-        <v>84.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>260</v>
@@ -2346,28 +2346,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>515.7</v>
+        <v>1698.3</v>
       </c>
       <c r="C34" s="2">
-        <v>35.89</v>
+        <v>68.38</v>
       </c>
       <c r="D34" s="2">
-        <v>24.27</v>
+        <v>-1.74</v>
       </c>
       <c r="E34" s="2">
-        <v>-2.46</v>
+        <v>-12.05</v>
       </c>
       <c r="F34" s="2">
-        <v>67.01000000000001</v>
+        <v>62.35</v>
       </c>
       <c r="G34" s="2">
         <v>77.59999999999999</v>
       </c>
       <c r="H34" s="2">
-        <v>74</v>
+        <v>66.8</v>
       </c>
       <c r="I34" s="2">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>260</v>
@@ -2378,28 +2378,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>837.4</v>
+        <v>846</v>
       </c>
       <c r="C35" s="2">
-        <v>18.74</v>
+        <v>21.73</v>
       </c>
       <c r="D35" s="2">
-        <v>9.359999999999999</v>
+        <v>7.81</v>
       </c>
       <c r="E35" s="2">
-        <v>13.51</v>
+        <v>4.83</v>
       </c>
       <c r="F35" s="2">
-        <v>65.98</v>
+        <v>61.18</v>
       </c>
       <c r="G35" s="2">
-        <v>57.6</v>
+        <v>76</v>
       </c>
       <c r="H35" s="2">
-        <v>43.2</v>
+        <v>47.2</v>
       </c>
       <c r="I35" s="2">
-        <v>36</v>
+        <v>48.8</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>260</v>
@@ -2410,28 +2410,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>23.89</v>
+        <v>825.5</v>
       </c>
       <c r="C36" s="2">
-        <v>42.97</v>
+        <v>61.7</v>
       </c>
       <c r="D36" s="2">
-        <v>6.89</v>
+        <v>4.75</v>
       </c>
       <c r="E36" s="2">
-        <v>0.08</v>
+        <v>-15.94</v>
       </c>
       <c r="F36" s="2">
-        <v>64.95</v>
+        <v>60</v>
       </c>
       <c r="G36" s="2">
-        <v>75.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H36" s="2">
-        <v>90.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I36" s="2">
-        <v>91.2</v>
+        <v>93.2</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>260</v>
@@ -2442,28 +2442,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>65.27</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C37" s="2">
-        <v>13.95</v>
+        <v>10.23</v>
       </c>
       <c r="D37" s="2">
-        <v>6.35</v>
+        <v>7.42</v>
       </c>
       <c r="E37" s="2">
-        <v>14.61</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F37" s="2">
-        <v>63.92</v>
+        <v>58.82</v>
       </c>
       <c r="G37" s="2">
-        <v>51.2</v>
+        <v>53.6</v>
       </c>
       <c r="H37" s="2">
-        <v>30.4</v>
+        <v>63.6</v>
       </c>
       <c r="I37" s="2">
-        <v>27.2</v>
+        <v>4.4</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>260</v>
@@ -2474,28 +2474,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>999.25</v>
+        <v>825.1</v>
       </c>
       <c r="C38" s="2">
-        <v>16.33</v>
+        <v>15.83</v>
       </c>
       <c r="D38" s="2">
-        <v>5.97</v>
+        <v>4.55</v>
       </c>
       <c r="E38" s="2">
-        <v>11.26</v>
+        <v>5.68</v>
       </c>
       <c r="F38" s="2">
-        <v>62.89</v>
+        <v>57.65</v>
       </c>
       <c r="G38" s="2">
-        <v>39.2</v>
+        <v>66.8</v>
       </c>
       <c r="H38" s="2">
-        <v>33.6</v>
+        <v>57.6</v>
       </c>
       <c r="I38" s="2">
-        <v>14</v>
+        <v>43.2</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>260</v>
@@ -2506,28 +2506,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>3662.8</v>
+        <v>273.15</v>
       </c>
       <c r="C39" s="2">
-        <v>23.06</v>
+        <v>23.42</v>
       </c>
       <c r="D39" s="2">
-        <v>8.92</v>
+        <v>8.57</v>
       </c>
       <c r="E39" s="2">
-        <v>5.58</v>
+        <v>-0.4</v>
       </c>
       <c r="F39" s="2">
-        <v>61.86</v>
+        <v>56.47</v>
       </c>
       <c r="G39" s="2">
-        <v>73.2</v>
+        <v>60</v>
       </c>
       <c r="H39" s="2">
-        <v>71.2</v>
+        <v>59.2</v>
       </c>
       <c r="I39" s="2">
-        <v>70.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>260</v>
@@ -2538,28 +2538,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>550.2</v>
+        <v>828.7</v>
       </c>
       <c r="C40" s="2">
-        <v>26.01</v>
+        <v>37.02</v>
       </c>
       <c r="D40" s="2">
-        <v>4.42</v>
+        <v>15.41</v>
       </c>
       <c r="E40" s="2">
-        <v>5.46</v>
+        <v>-10.65</v>
       </c>
       <c r="F40" s="2">
-        <v>60.82</v>
+        <v>55.29</v>
       </c>
       <c r="G40" s="2">
-        <v>48</v>
+        <v>58.8</v>
       </c>
       <c r="H40" s="2">
-        <v>49.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I40" s="2">
-        <v>48</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>260</v>
@@ -2570,28 +2570,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>276.35</v>
+        <v>1133.3</v>
       </c>
       <c r="C41" s="2">
-        <v>36.11</v>
+        <v>20.48</v>
       </c>
       <c r="D41" s="2">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="E41" s="2">
-        <v>1.34</v>
+        <v>4.84</v>
       </c>
       <c r="F41" s="2">
-        <v>59.79</v>
+        <v>54.12</v>
       </c>
       <c r="G41" s="2">
-        <v>59.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H41" s="2">
-        <v>60.8</v>
+        <v>75.2</v>
       </c>
       <c r="I41" s="2">
-        <v>67.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>260</v>
@@ -2602,28 +2602,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>2767.4</v>
+        <v>561.3</v>
       </c>
       <c r="C42" s="2">
-        <v>42.08</v>
+        <v>16.85</v>
       </c>
       <c r="D42" s="2">
-        <v>7.31</v>
+        <v>4.81</v>
       </c>
       <c r="E42" s="2">
-        <v>-6.13</v>
+        <v>3.94</v>
       </c>
       <c r="F42" s="2">
-        <v>58.76</v>
+        <v>52.94</v>
       </c>
       <c r="G42" s="2">
-        <v>67.2</v>
+        <v>44.8</v>
       </c>
       <c r="H42" s="2">
-        <v>80</v>
+        <v>53.2</v>
       </c>
       <c r="I42" s="2">
-        <v>77.59999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>260</v>
@@ -2634,28 +2634,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>386.3</v>
+        <v>689.65</v>
       </c>
       <c r="C43" s="2">
-        <v>11.05</v>
+        <v>30.88</v>
       </c>
       <c r="D43" s="2">
-        <v>2.9</v>
+        <v>5.12</v>
       </c>
       <c r="E43" s="2">
-        <v>9.85</v>
+        <v>-3.23</v>
       </c>
       <c r="F43" s="2">
-        <v>57.73</v>
+        <v>51.76</v>
       </c>
       <c r="G43" s="2">
-        <v>14.4</v>
+        <v>32</v>
       </c>
       <c r="H43" s="2">
-        <v>4</v>
+        <v>44.4</v>
       </c>
       <c r="I43" s="2">
-        <v>4.8</v>
+        <v>50.4</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>260</v>
@@ -2666,28 +2666,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>474.1</v>
+        <v>1174</v>
       </c>
       <c r="C44" s="2">
-        <v>28.59</v>
+        <v>13.59</v>
       </c>
       <c r="D44" s="2">
-        <v>6.15</v>
+        <v>-4.8</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.57</v>
+        <v>7.3</v>
       </c>
       <c r="F44" s="2">
-        <v>56.7</v>
+        <v>50.59</v>
       </c>
       <c r="G44" s="2">
-        <v>44</v>
+        <v>55.2</v>
       </c>
       <c r="H44" s="2">
-        <v>46</v>
+        <v>52.4</v>
       </c>
       <c r="I44" s="2">
-        <v>54.8</v>
+        <v>37.2</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>260</v>
@@ -2698,28 +2698,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>481.55</v>
+        <v>999.2</v>
       </c>
       <c r="C45" s="2">
-        <v>7.44</v>
+        <v>25.33</v>
       </c>
       <c r="D45" s="2">
-        <v>6.41</v>
+        <v>-1.44</v>
       </c>
       <c r="E45" s="2">
-        <v>9.619999999999999</v>
+        <v>-0.59</v>
       </c>
       <c r="F45" s="2">
-        <v>55.67</v>
+        <v>49.41</v>
       </c>
       <c r="G45" s="2">
-        <v>50.4</v>
+        <v>54.4</v>
       </c>
       <c r="H45" s="2">
-        <v>42.8</v>
+        <v>52.8</v>
       </c>
       <c r="I45" s="2">
-        <v>37.6</v>
+        <v>46.8</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>260</v>
@@ -2730,28 +2730,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>362.15</v>
+        <v>545.3</v>
       </c>
       <c r="C46" s="2">
-        <v>17.96</v>
+        <v>20.16</v>
       </c>
       <c r="D46" s="2">
-        <v>8.01</v>
+        <v>-2.42</v>
       </c>
       <c r="E46" s="2">
-        <v>3.41</v>
+        <v>0.89</v>
       </c>
       <c r="F46" s="2">
-        <v>54.64</v>
+        <v>48.24</v>
       </c>
       <c r="G46" s="2">
-        <v>17.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H46" s="2">
-        <v>18</v>
+        <v>62.4</v>
       </c>
       <c r="I46" s="2">
-        <v>29.6</v>
+        <v>53.6</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>260</v>
@@ -2762,28 +2762,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>627.25</v>
+        <v>379.65</v>
       </c>
       <c r="C47" s="2">
-        <v>7.28</v>
+        <v>-4.28</v>
       </c>
       <c r="D47" s="2">
-        <v>8.82</v>
+        <v>0.79</v>
       </c>
       <c r="E47" s="2">
-        <v>7.9</v>
+        <v>10.02</v>
       </c>
       <c r="F47" s="2">
-        <v>53.61</v>
+        <v>47.06</v>
       </c>
       <c r="G47" s="2">
-        <v>50</v>
+        <v>57.6</v>
       </c>
       <c r="H47" s="2">
-        <v>35.6</v>
+        <v>14.4</v>
       </c>
       <c r="I47" s="2">
-        <v>21.6</v>
+        <v>4</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>260</v>
@@ -2794,28 +2794,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>9.99</v>
+        <v>44.6</v>
       </c>
       <c r="C48" s="2">
-        <v>6.73</v>
+        <v>12.06</v>
       </c>
       <c r="D48" s="2">
-        <v>5.83</v>
+        <v>11.44</v>
       </c>
       <c r="E48" s="2">
-        <v>8.94</v>
+        <v>-4.46</v>
       </c>
       <c r="F48" s="2">
-        <v>52.58</v>
+        <v>45.88</v>
       </c>
       <c r="G48" s="2">
-        <v>63.6</v>
+        <v>45.2</v>
       </c>
       <c r="H48" s="2">
-        <v>4.4</v>
+        <v>59.6</v>
       </c>
       <c r="I48" s="2">
-        <v>14.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>260</v>
@@ -2826,28 +2826,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>579.25</v>
+        <v>222.19</v>
       </c>
       <c r="C49" s="2">
-        <v>15.23</v>
+        <v>24.95</v>
       </c>
       <c r="D49" s="2">
-        <v>3.01</v>
+        <v>4.61</v>
       </c>
       <c r="E49" s="2">
-        <v>6.03</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="F49" s="2">
-        <v>51.55</v>
+        <v>44.71</v>
       </c>
       <c r="G49" s="2">
-        <v>48.4</v>
+        <v>71.2</v>
       </c>
       <c r="H49" s="2">
-        <v>59.6</v>
+        <v>78</v>
       </c>
       <c r="I49" s="2">
-        <v>42.8</v>
+        <v>88.8</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>260</v>
@@ -2858,28 +2858,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>1603.4</v>
+        <v>134.04</v>
       </c>
       <c r="C50" s="2">
-        <v>15.72</v>
+        <v>15.35</v>
       </c>
       <c r="D50" s="2">
-        <v>4.78</v>
+        <v>-0.73</v>
       </c>
       <c r="E50" s="2">
-        <v>4.68</v>
+        <v>-1.22</v>
       </c>
       <c r="F50" s="2">
-        <v>50.52</v>
+        <v>43.53</v>
       </c>
       <c r="G50" s="2">
         <v>47.6</v>
       </c>
       <c r="H50" s="2">
-        <v>64.8</v>
+        <v>51.6</v>
       </c>
       <c r="I50" s="2">
-        <v>66.40000000000001</v>
+        <v>43.6</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>260</v>
@@ -2890,28 +2890,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>471.85</v>
+        <v>591.75</v>
       </c>
       <c r="C51" s="2">
-        <v>17.93</v>
+        <v>5.1</v>
       </c>
       <c r="D51" s="2">
-        <v>2.34</v>
+        <v>-10.66</v>
       </c>
       <c r="E51" s="2">
-        <v>4.39</v>
+        <v>7.54</v>
       </c>
       <c r="F51" s="2">
-        <v>49.48</v>
+        <v>42.35</v>
       </c>
       <c r="G51" s="2">
-        <v>46</v>
+        <v>33.6</v>
       </c>
       <c r="H51" s="2">
-        <v>49.2</v>
+        <v>17.6</v>
       </c>
       <c r="I51" s="2">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>260</v>
@@ -2922,28 +2922,28 @@
         <v>59</v>
       </c>
       <c r="B52" s="1">
-        <v>224.06</v>
+        <v>4085.2</v>
       </c>
       <c r="C52" s="2">
-        <v>17.11</v>
+        <v>-0.63</v>
       </c>
       <c r="D52" s="2">
-        <v>1.9</v>
+        <v>9.18</v>
       </c>
       <c r="E52" s="2">
-        <v>4.83</v>
+        <v>0.23</v>
       </c>
       <c r="F52" s="2">
-        <v>48.45</v>
+        <v>41.18</v>
       </c>
       <c r="G52" s="2">
-        <v>41.6</v>
+        <v>37.6</v>
       </c>
       <c r="H52" s="2">
-        <v>19.6</v>
+        <v>24.8</v>
       </c>
       <c r="I52" s="2">
-        <v>30</v>
+        <v>35.2</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>260</v>
@@ -2954,28 +2954,28 @@
         <v>60</v>
       </c>
       <c r="B53" s="1">
-        <v>410.3</v>
+        <v>186</v>
       </c>
       <c r="C53" s="2">
-        <v>34.55</v>
+        <v>26.53</v>
       </c>
       <c r="D53" s="2">
-        <v>-0.93</v>
+        <v>-1.22</v>
       </c>
       <c r="E53" s="2">
-        <v>-2.9</v>
+        <v>-9.32</v>
       </c>
       <c r="F53" s="2">
-        <v>47.42</v>
+        <v>40</v>
       </c>
       <c r="G53" s="2">
-        <v>48.8</v>
+        <v>41.2</v>
       </c>
       <c r="H53" s="2">
-        <v>79.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I53" s="2">
-        <v>71.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>260</v>
@@ -2986,28 +2986,28 @@
         <v>61</v>
       </c>
       <c r="B54" s="1">
-        <v>237.56</v>
+        <v>119.5</v>
       </c>
       <c r="C54" s="2">
-        <v>12.36</v>
+        <v>15.44</v>
       </c>
       <c r="D54" s="2">
-        <v>5.59</v>
+        <v>-11.77</v>
       </c>
       <c r="E54" s="2">
-        <v>4.71</v>
+        <v>0.83</v>
       </c>
       <c r="F54" s="2">
-        <v>46.39</v>
+        <v>38.82</v>
       </c>
       <c r="G54" s="2">
-        <v>60.8</v>
+        <v>24.4</v>
       </c>
       <c r="H54" s="2">
-        <v>46.4</v>
+        <v>38</v>
       </c>
       <c r="I54" s="2">
-        <v>44.4</v>
+        <v>27.6</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>260</v>
@@ -3018,28 +3018,28 @@
         <v>62</v>
       </c>
       <c r="B55" s="1">
-        <v>217.71</v>
+        <v>579.6</v>
       </c>
       <c r="C55" s="2">
-        <v>35.67</v>
+        <v>-1.02</v>
       </c>
       <c r="D55" s="2">
-        <v>-7.53</v>
+        <v>3.1</v>
       </c>
       <c r="E55" s="2">
-        <v>-2.42</v>
+        <v>1.4</v>
       </c>
       <c r="F55" s="2">
-        <v>45.36</v>
+        <v>37.65</v>
       </c>
       <c r="G55" s="2">
-        <v>22.4</v>
+        <v>39.6</v>
       </c>
       <c r="H55" s="2">
-        <v>50.8</v>
+        <v>20.8</v>
       </c>
       <c r="I55" s="2">
-        <v>63.6</v>
+        <v>32</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>260</v>
@@ -3050,28 +3050,28 @@
         <v>63</v>
       </c>
       <c r="B56" s="1">
-        <v>396.8</v>
+        <v>63.04</v>
       </c>
       <c r="C56" s="2">
-        <v>11.06</v>
+        <v>14.33</v>
       </c>
       <c r="D56" s="2">
-        <v>0.24</v>
+        <v>-13.42</v>
       </c>
       <c r="E56" s="2">
-        <v>5.7</v>
+        <v>1.96</v>
       </c>
       <c r="F56" s="2">
-        <v>44.33</v>
+        <v>36.47</v>
       </c>
       <c r="G56" s="2">
-        <v>40.4</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H56" s="2">
-        <v>30</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I56" s="2">
-        <v>25.6</v>
+        <v>70.8</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>260</v>
@@ -3082,28 +3082,28 @@
         <v>64</v>
       </c>
       <c r="B57" s="1">
-        <v>507.6</v>
+        <v>1127.7</v>
       </c>
       <c r="C57" s="2">
-        <v>2.68</v>
+        <v>38.31</v>
       </c>
       <c r="D57" s="2">
-        <v>5.49</v>
+        <v>-4.33</v>
       </c>
       <c r="E57" s="2">
-        <v>7.22</v>
+        <v>-14.99</v>
       </c>
       <c r="F57" s="2">
-        <v>43.3</v>
+        <v>35.29</v>
       </c>
       <c r="G57" s="2">
-        <v>63.2</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2">
-        <v>52.8</v>
+        <v>26</v>
       </c>
       <c r="I57" s="2">
-        <v>24</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>260</v>
@@ -3114,28 +3114,28 @@
         <v>65</v>
       </c>
       <c r="B58" s="1">
-        <v>1150.2</v>
+        <v>346.95</v>
       </c>
       <c r="C58" s="2">
-        <v>29.26</v>
+        <v>10.49</v>
       </c>
       <c r="D58" s="2">
-        <v>-1.06</v>
+        <v>-12.87</v>
       </c>
       <c r="E58" s="2">
-        <v>-3.88</v>
+        <v>1.58</v>
       </c>
       <c r="F58" s="2">
-        <v>42.27</v>
+        <v>34.12</v>
       </c>
       <c r="G58" s="2">
-        <v>26</v>
+        <v>39.2</v>
       </c>
       <c r="H58" s="2">
-        <v>77.59999999999999</v>
+        <v>26.4</v>
       </c>
       <c r="I58" s="2">
-        <v>84.8</v>
+        <v>47.2</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>260</v>
@@ -3146,28 +3146,28 @@
         <v>66</v>
       </c>
       <c r="B59" s="1">
-        <v>45.81</v>
+        <v>22.37</v>
       </c>
       <c r="C59" s="2">
-        <v>12.83</v>
+        <v>38.94</v>
       </c>
       <c r="D59" s="2">
-        <v>11.57</v>
+        <v>-0.27</v>
       </c>
       <c r="E59" s="2">
-        <v>-2.37</v>
+        <v>-19.62</v>
       </c>
       <c r="F59" s="2">
-        <v>41.24</v>
+        <v>32.94</v>
       </c>
       <c r="G59" s="2">
-        <v>59.6</v>
+        <v>64.8</v>
       </c>
       <c r="H59" s="2">
-        <v>68.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I59" s="2">
-        <v>80.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>260</v>
@@ -3178,28 +3178,28 @@
         <v>67</v>
       </c>
       <c r="B60" s="1">
-        <v>564.05</v>
+        <v>188.63</v>
       </c>
       <c r="C60" s="2">
-        <v>2.72</v>
+        <v>0.7</v>
       </c>
       <c r="D60" s="2">
-        <v>7.14</v>
+        <v>-3.57</v>
       </c>
       <c r="E60" s="2">
-        <v>4.45</v>
+        <v>0.44</v>
       </c>
       <c r="F60" s="2">
-        <v>40.21</v>
+        <v>31.76</v>
       </c>
       <c r="G60" s="2">
-        <v>32</v>
+        <v>1.2</v>
       </c>
       <c r="H60" s="2">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="I60" s="2">
-        <v>10</v>
+        <v>22.4</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>260</v>
@@ -3210,28 +3210,28 @@
         <v>68</v>
       </c>
       <c r="B61" s="1">
-        <v>415.9</v>
+        <v>235.97</v>
       </c>
       <c r="C61" s="2">
-        <v>21.17</v>
+        <v>-0.08</v>
       </c>
       <c r="D61" s="2">
-        <v>5.42</v>
+        <v>-4.55</v>
       </c>
       <c r="E61" s="2">
-        <v>-4.69</v>
+        <v>-0.25</v>
       </c>
       <c r="F61" s="2">
-        <v>39.18</v>
+        <v>30.59</v>
       </c>
       <c r="G61" s="2">
-        <v>60.4</v>
+        <v>12.4</v>
       </c>
       <c r="H61" s="2">
-        <v>51.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I61" s="2">
-        <v>72</v>
+        <v>9.6</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>260</v>
@@ -3242,28 +3242,28 @@
         <v>69</v>
       </c>
       <c r="B62" s="1">
-        <v>191.66</v>
+        <v>502.7</v>
       </c>
       <c r="C62" s="2">
-        <v>18.13</v>
+        <v>15.87</v>
       </c>
       <c r="D62" s="2">
-        <v>1.42</v>
+        <v>3.65</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.83</v>
+        <v>-13.55</v>
       </c>
       <c r="F62" s="2">
-        <v>38.14</v>
+        <v>29.41</v>
       </c>
       <c r="G62" s="2">
-        <v>71.2</v>
+        <v>42</v>
       </c>
       <c r="H62" s="2">
-        <v>83.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="I62" s="2">
-        <v>72.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>260</v>
@@ -3274,28 +3274,28 @@
         <v>70</v>
       </c>
       <c r="B63" s="1">
-        <v>1680.1</v>
+        <v>567.8</v>
       </c>
       <c r="C63" s="2">
-        <v>7.78</v>
+        <v>-5.73</v>
       </c>
       <c r="D63" s="2">
-        <v>0.27</v>
+        <v>-2.55</v>
       </c>
       <c r="E63" s="2">
-        <v>3.91</v>
+        <v>-1.6</v>
       </c>
       <c r="F63" s="2">
-        <v>37.11</v>
+        <v>28.24</v>
       </c>
       <c r="G63" s="2">
-        <v>20</v>
+        <v>16.8</v>
       </c>
       <c r="H63" s="2">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="I63" s="2">
-        <v>9.199999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>260</v>
@@ -3306,28 +3306,28 @@
         <v>71</v>
       </c>
       <c r="B64" s="1">
-        <v>466</v>
+        <v>127.83</v>
       </c>
       <c r="C64" s="2">
-        <v>5.9</v>
+        <v>0.12</v>
       </c>
       <c r="D64" s="2">
-        <v>6.49</v>
+        <v>1.36</v>
       </c>
       <c r="E64" s="2">
-        <v>0.9399999999999999</v>
+        <v>-6.67</v>
       </c>
       <c r="F64" s="2">
-        <v>36.08</v>
+        <v>27.06</v>
       </c>
       <c r="G64" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H64" s="2">
-        <v>33.2</v>
+        <v>42.8</v>
       </c>
       <c r="I64" s="2">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>260</v>
@@ -3338,28 +3338,28 @@
         <v>72</v>
       </c>
       <c r="B65" s="1">
-        <v>220.23</v>
+        <v>549.85</v>
       </c>
       <c r="C65" s="2">
-        <v>13.5</v>
+        <v>12.09</v>
       </c>
       <c r="D65" s="2">
-        <v>8.300000000000001</v>
+        <v>-12.69</v>
       </c>
       <c r="E65" s="2">
-        <v>-4.93</v>
+        <v>-5.91</v>
       </c>
       <c r="F65" s="2">
-        <v>35.05</v>
+        <v>25.88</v>
       </c>
       <c r="G65" s="2">
-        <v>45.2</v>
+        <v>24.8</v>
       </c>
       <c r="H65" s="2">
-        <v>37.6</v>
+        <v>21.2</v>
       </c>
       <c r="I65" s="2">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>260</v>
@@ -3370,28 +3370,28 @@
         <v>73</v>
       </c>
       <c r="B66" s="1">
-        <v>188.67</v>
+        <v>118.85</v>
       </c>
       <c r="C66" s="2">
-        <v>4.91</v>
+        <v>8.59</v>
       </c>
       <c r="D66" s="2">
-        <v>2.47</v>
+        <v>-4.21</v>
       </c>
       <c r="E66" s="2">
-        <v>2.2</v>
+        <v>-8.77</v>
       </c>
       <c r="F66" s="2">
-        <v>34.02</v>
+        <v>24.71</v>
       </c>
       <c r="G66" s="2">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="H66" s="2">
-        <v>38</v>
+        <v>56.4</v>
       </c>
       <c r="I66" s="2">
-        <v>32.4</v>
+        <v>52</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>260</v>
@@ -3402,28 +3402,28 @@
         <v>74</v>
       </c>
       <c r="B67" s="1">
-        <v>336.65</v>
+        <v>137.18</v>
       </c>
       <c r="C67" s="2">
-        <v>8.06</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="2">
-        <v>-7</v>
+        <v>-12.43</v>
       </c>
       <c r="E67" s="2">
-        <v>4.79</v>
+        <v>-1.23</v>
       </c>
       <c r="F67" s="2">
-        <v>32.99</v>
+        <v>23.53</v>
       </c>
       <c r="G67" s="2">
-        <v>31.6</v>
+        <v>26.8</v>
       </c>
       <c r="H67" s="2">
-        <v>34.8</v>
+        <v>43.2</v>
       </c>
       <c r="I67" s="2">
-        <v>16</v>
+        <v>39.6</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>260</v>
@@ -3434,28 +3434,28 @@
         <v>75</v>
       </c>
       <c r="B68" s="1">
-        <v>588.05</v>
+        <v>233.94</v>
       </c>
       <c r="C68" s="2">
-        <v>11.25</v>
+        <v>-6.52</v>
       </c>
       <c r="D68" s="2">
-        <v>-12.86</v>
+        <v>-11.29</v>
       </c>
       <c r="E68" s="2">
-        <v>4.85</v>
+        <v>0.13</v>
       </c>
       <c r="F68" s="2">
-        <v>31.96</v>
+        <v>22.35</v>
       </c>
       <c r="G68" s="2">
-        <v>17.6</v>
+        <v>10</v>
       </c>
       <c r="H68" s="2">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="I68" s="2">
-        <v>25.2</v>
+        <v>5.2</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>260</v>
@@ -3466,28 +3466,28 @@
         <v>76</v>
       </c>
       <c r="B69" s="1">
-        <v>154.29</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="C69" s="2">
-        <v>10.9</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D69" s="2">
-        <v>-0.43</v>
+        <v>-11.03</v>
       </c>
       <c r="E69" s="2">
-        <v>-1.76</v>
+        <v>-7.64</v>
       </c>
       <c r="F69" s="2">
-        <v>30.93</v>
+        <v>21.18</v>
       </c>
       <c r="G69" s="2">
-        <v>50.8</v>
+        <v>20.8</v>
       </c>
       <c r="H69" s="2">
-        <v>54.4</v>
+        <v>18.4</v>
       </c>
       <c r="I69" s="2">
-        <v>51.2</v>
+        <v>25.2</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>260</v>
@@ -3498,28 +3498,28 @@
         <v>77</v>
       </c>
       <c r="B70" s="1">
-        <v>129.05</v>
+        <v>491.55</v>
       </c>
       <c r="C70" s="2">
-        <v>0.58</v>
+        <v>-4.6</v>
       </c>
       <c r="D70" s="2">
-        <v>2.82</v>
+        <v>-12.38</v>
       </c>
       <c r="E70" s="2">
-        <v>1.35</v>
+        <v>-0.92</v>
       </c>
       <c r="F70" s="2">
-        <v>29.9</v>
+        <v>20</v>
       </c>
       <c r="G70" s="2">
-        <v>35.2</v>
+        <v>23.2</v>
       </c>
       <c r="H70" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="I70" s="2">
-        <v>54.4</v>
+        <v>18.4</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>260</v>
@@ -3530,28 +3530,28 @@
         <v>78</v>
       </c>
       <c r="B71" s="1">
-        <v>203.35</v>
+        <v>314.05</v>
       </c>
       <c r="C71" s="2">
-        <v>21.69</v>
+        <v>-11.32</v>
       </c>
       <c r="D71" s="2">
-        <v>-7.79</v>
+        <v>-2.97</v>
       </c>
       <c r="E71" s="2">
-        <v>-4.46</v>
+        <v>-2.91</v>
       </c>
       <c r="F71" s="2">
-        <v>28.87</v>
+        <v>18.82</v>
       </c>
       <c r="G71" s="2">
-        <v>3.2</v>
+        <v>27.6</v>
       </c>
       <c r="H71" s="2">
-        <v>2.4</v>
+        <v>39.6</v>
       </c>
       <c r="I71" s="2">
-        <v>20.8</v>
+        <v>30.8</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>260</v>
@@ -3562,28 +3562,28 @@
         <v>79</v>
       </c>
       <c r="B72" s="1">
-        <v>33.57</v>
+        <v>300.15</v>
       </c>
       <c r="C72" s="2">
-        <v>22.52</v>
+        <v>-5.06</v>
       </c>
       <c r="D72" s="2">
-        <v>-8</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="E72" s="2">
-        <v>-5.52</v>
+        <v>-3.36</v>
       </c>
       <c r="F72" s="2">
-        <v>27.84</v>
+        <v>17.65</v>
       </c>
       <c r="G72" s="2">
-        <v>12</v>
+        <v>21.6</v>
       </c>
       <c r="H72" s="2">
-        <v>28.4</v>
+        <v>13.6</v>
       </c>
       <c r="I72" s="2">
-        <v>32.8</v>
+        <v>23.6</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>260</v>
@@ -3594,28 +3594,28 @@
         <v>80</v>
       </c>
       <c r="B73" s="1">
-        <v>404.6</v>
+        <v>288.3</v>
       </c>
       <c r="C73" s="2">
-        <v>11.83</v>
+        <v>12.79</v>
       </c>
       <c r="D73" s="2">
-        <v>-11.86</v>
+        <v>-25.82</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.17</v>
+        <v>-4.31</v>
       </c>
       <c r="F73" s="2">
-        <v>26.8</v>
+        <v>16.47</v>
       </c>
       <c r="G73" s="2">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="H73" s="2">
-        <v>15.6</v>
+        <v>12.4</v>
       </c>
       <c r="I73" s="2">
-        <v>17.6</v>
+        <v>10.4</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>260</v>
@@ -3626,28 +3626,28 @@
         <v>81</v>
       </c>
       <c r="B74" s="1">
-        <v>327.2</v>
+        <v>448.95</v>
       </c>
       <c r="C74" s="2">
-        <v>-16.33</v>
+        <v>-4.25</v>
       </c>
       <c r="D74" s="2">
-        <v>-3.48</v>
+        <v>-15.15</v>
       </c>
       <c r="E74" s="2">
-        <v>9.710000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="F74" s="2">
-        <v>25.77</v>
+        <v>15.29</v>
       </c>
       <c r="G74" s="2">
-        <v>39.6</v>
+        <v>19.6</v>
       </c>
       <c r="H74" s="2">
-        <v>30.8</v>
+        <v>23.6</v>
       </c>
       <c r="I74" s="2">
-        <v>30.8</v>
+        <v>22.8</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>260</v>
@@ -3658,28 +3658,28 @@
         <v>82</v>
       </c>
       <c r="B75" s="1">
-        <v>91.48</v>
+        <v>331.45</v>
       </c>
       <c r="C75" s="2">
-        <v>20.48</v>
+        <v>-11.31</v>
       </c>
       <c r="D75" s="2">
-        <v>-20.62</v>
+        <v>-15.92</v>
       </c>
       <c r="E75" s="2">
-        <v>-2.58</v>
+        <v>1.27</v>
       </c>
       <c r="F75" s="2">
-        <v>24.74</v>
+        <v>14.12</v>
       </c>
       <c r="G75" s="2">
-        <v>34</v>
+        <v>13.6</v>
       </c>
       <c r="H75" s="2">
-        <v>11.2</v>
+        <v>12.8</v>
       </c>
       <c r="I75" s="2">
-        <v>31.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>260</v>
@@ -3690,28 +3690,28 @@
         <v>83</v>
       </c>
       <c r="B76" s="1">
-        <v>303.2</v>
+        <v>1024.85</v>
       </c>
       <c r="C76" s="2">
-        <v>6.89</v>
+        <v>-14.89</v>
       </c>
       <c r="D76" s="2">
-        <v>-13.64</v>
+        <v>-27.03</v>
       </c>
       <c r="E76" s="2">
-        <v>-0.02</v>
+        <v>7.16</v>
       </c>
       <c r="F76" s="2">
-        <v>23.71</v>
+        <v>12.94</v>
       </c>
       <c r="G76" s="2">
-        <v>12.4</v>
+        <v>0.4</v>
       </c>
       <c r="H76" s="2">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="I76" s="2">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>260</v>
@@ -3722,28 +3722,28 @@
         <v>84</v>
       </c>
       <c r="B77" s="1">
-        <v>8.99</v>
+        <v>66.48</v>
       </c>
       <c r="C77" s="2">
-        <v>12.52</v>
+        <v>6.39</v>
       </c>
       <c r="D77" s="2">
-        <v>-11.43</v>
+        <v>-0.88</v>
       </c>
       <c r="E77" s="2">
-        <v>-5.47</v>
+        <v>-16.57</v>
       </c>
       <c r="F77" s="2">
-        <v>22.68</v>
+        <v>11.76</v>
       </c>
       <c r="G77" s="2">
-        <v>18.4</v>
+        <v>60.4</v>
       </c>
       <c r="H77" s="2">
-        <v>25.2</v>
+        <v>70</v>
       </c>
       <c r="I77" s="2">
-        <v>44</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>260</v>
@@ -3754,28 +3754,28 @@
         <v>85</v>
       </c>
       <c r="B78" s="1">
-        <v>73.75</v>
+        <v>72.56</v>
       </c>
       <c r="C78" s="2">
-        <v>0.77</v>
+        <v>-8.26</v>
       </c>
       <c r="D78" s="2">
-        <v>-5.73</v>
+        <v>-5.27</v>
       </c>
       <c r="E78" s="2">
-        <v>-2.55</v>
+        <v>-7.4</v>
       </c>
       <c r="F78" s="2">
-        <v>21.65</v>
+        <v>10.59</v>
       </c>
       <c r="G78" s="2">
+        <v>20.4</v>
+      </c>
+      <c r="H78" s="2">
         <v>29.6</v>
       </c>
-      <c r="H78" s="2">
+      <c r="I78" s="2">
         <v>24.8</v>
-      </c>
-      <c r="I78" s="2">
-        <v>34.4</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>260</v>
@@ -3786,28 +3786,28 @@
         <v>86</v>
       </c>
       <c r="B79" s="1">
-        <v>562.15</v>
+        <v>122.57</v>
       </c>
       <c r="C79" s="2">
-        <v>-7.53</v>
+        <v>-0.66</v>
       </c>
       <c r="D79" s="2">
-        <v>-4.44</v>
+        <v>-6.16</v>
       </c>
       <c r="E79" s="2">
-        <v>-1.52</v>
+        <v>-12.02</v>
       </c>
       <c r="F79" s="2">
-        <v>20.62</v>
+        <v>9.41</v>
       </c>
       <c r="G79" s="2">
-        <v>8</v>
+        <v>32.8</v>
       </c>
       <c r="H79" s="2">
-        <v>12.4</v>
+        <v>35.2</v>
       </c>
       <c r="I79" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>260</v>
@@ -3818,28 +3818,28 @@
         <v>87</v>
       </c>
       <c r="B80" s="1">
-        <v>436.05</v>
+        <v>22.37</v>
       </c>
       <c r="C80" s="2">
-        <v>-4.47</v>
+        <v>-10.7</v>
       </c>
       <c r="D80" s="2">
-        <v>-15.2</v>
+        <v>-13.93</v>
       </c>
       <c r="E80" s="2">
-        <v>0.44</v>
+        <v>-3.41</v>
       </c>
       <c r="F80" s="2">
-        <v>19.59</v>
+        <v>8.24</v>
       </c>
       <c r="G80" s="2">
-        <v>10.8</v>
+        <v>4</v>
       </c>
       <c r="H80" s="2">
-        <v>7.6</v>
+        <v>16.4</v>
       </c>
       <c r="I80" s="2">
-        <v>13.6</v>
+        <v>8.4</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>260</v>
@@ -3850,28 +3850,28 @@
         <v>88</v>
       </c>
       <c r="B81" s="1">
-        <v>153.35</v>
+        <v>364.85</v>
       </c>
       <c r="C81" s="2">
-        <v>-9.710000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D81" s="2">
-        <v>-8.630000000000001</v>
+        <v>-11.61</v>
       </c>
       <c r="E81" s="2">
-        <v>-0.25</v>
+        <v>-6.26</v>
       </c>
       <c r="F81" s="2">
-        <v>18.56</v>
+        <v>7.06</v>
       </c>
       <c r="G81" s="2">
         <v>6.8</v>
       </c>
       <c r="H81" s="2">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="I81" s="2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>260</v>
@@ -3882,28 +3882,28 @@
         <v>89</v>
       </c>
       <c r="B82" s="1">
-        <v>231.09</v>
+        <v>12.32</v>
       </c>
       <c r="C82" s="2">
-        <v>-7.58</v>
+        <v>-6.81</v>
       </c>
       <c r="D82" s="2">
-        <v>-6.31</v>
+        <v>-12.38</v>
       </c>
       <c r="E82" s="2">
-        <v>-2.78</v>
+        <v>-6.74</v>
       </c>
       <c r="F82" s="2">
-        <v>17.53</v>
+        <v>5.88</v>
       </c>
       <c r="G82" s="2">
-        <v>8.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="H82" s="2">
-        <v>9.6</v>
+        <v>28.8</v>
       </c>
       <c r="I82" s="2">
-        <v>21.2</v>
+        <v>17.2</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>260</v>
@@ -3914,28 +3914,28 @@
         <v>90</v>
       </c>
       <c r="B83" s="1">
-        <v>593</v>
+        <v>164.66</v>
       </c>
       <c r="C83" s="2">
-        <v>-2.17</v>
+        <v>-11.16</v>
       </c>
       <c r="D83" s="2">
-        <v>-13.56</v>
+        <v>-5.68</v>
       </c>
       <c r="E83" s="2">
-        <v>-2.63</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="F83" s="2">
-        <v>16.49</v>
+        <v>4.71</v>
       </c>
       <c r="G83" s="2">
-        <v>1.6</v>
+        <v>18.8</v>
       </c>
       <c r="H83" s="2">
-        <v>48.4</v>
+        <v>26.8</v>
       </c>
       <c r="I83" s="2">
-        <v>0.8</v>
+        <v>25.6</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>260</v>
@@ -3946,28 +3946,28 @@
         <v>91</v>
       </c>
       <c r="B84" s="1">
-        <v>229.07</v>
+        <v>169.08</v>
       </c>
       <c r="C84" s="2">
-        <v>-11.63</v>
+        <v>6.96</v>
       </c>
       <c r="D84" s="2">
-        <v>-11.38</v>
+        <v>-20.84</v>
       </c>
       <c r="E84" s="2">
-        <v>0.1</v>
+        <v>-10.99</v>
       </c>
       <c r="F84" s="2">
-        <v>15.46</v>
+        <v>3.53</v>
       </c>
       <c r="G84" s="2">
         <v>6</v>
       </c>
       <c r="H84" s="2">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="I84" s="2">
-        <v>3.6</v>
+        <v>28.8</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>260</v>
@@ -3978,28 +3978,28 @@
         <v>92</v>
       </c>
       <c r="B85" s="1">
-        <v>31.17</v>
+        <v>899.1</v>
       </c>
       <c r="C85" s="2">
-        <v>-6.51</v>
+        <v>-12.71</v>
       </c>
       <c r="D85" s="2">
-        <v>-9.42</v>
+        <v>-22.32</v>
       </c>
       <c r="E85" s="2">
-        <v>-4.21</v>
+        <v>-0.45</v>
       </c>
       <c r="F85" s="2">
-        <v>14.43</v>
+        <v>2.35</v>
       </c>
       <c r="G85" s="2">
-        <v>20.4</v>
+        <v>6.4</v>
       </c>
       <c r="H85" s="2">
-        <v>28</v>
+        <v>5.2</v>
       </c>
       <c r="I85" s="2">
-        <v>38.8</v>
+        <v>1.6</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>260</v>
@@ -4010,28 +4010,28 @@
         <v>93</v>
       </c>
       <c r="B86" s="1">
-        <v>66.06</v>
+        <v>30</v>
       </c>
       <c r="C86" s="2">
-        <v>0.59</v>
+        <v>-8.59</v>
       </c>
       <c r="D86" s="2">
-        <v>-20.02</v>
+        <v>-10.07</v>
       </c>
       <c r="E86" s="2">
-        <v>-3.45</v>
+        <v>-12.08</v>
       </c>
       <c r="F86" s="2">
-        <v>13.4</v>
+        <v>1.18</v>
       </c>
       <c r="G86" s="2">
-        <v>38.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H86" s="2">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="I86" s="2">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>260</v>
@@ -4041,29 +4041,14 @@
       <c r="A87" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B87" s="1">
-        <v>129.8</v>
-      </c>
-      <c r="C87" s="2">
-        <v>-29.48</v>
-      </c>
-      <c r="D87" s="2">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E87" s="2">
-        <v>4.19</v>
-      </c>
-      <c r="F87" s="2">
-        <v>12.37</v>
-      </c>
       <c r="G87" s="2">
-        <v>6.4</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H87" s="2">
-        <v>1.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I87" s="2">
-        <v>2.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>260</v>
@@ -4073,29 +4058,14 @@
       <c r="A88" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="1">
-        <v>124.21</v>
-      </c>
-      <c r="C88" s="2">
-        <v>-13.41</v>
-      </c>
-      <c r="D88" s="2">
-        <v>-10.12</v>
-      </c>
-      <c r="E88" s="2">
-        <v>-3.56</v>
-      </c>
-      <c r="F88" s="2">
-        <v>11.34</v>
-      </c>
       <c r="G88" s="2">
-        <v>10</v>
+        <v>29.2</v>
       </c>
       <c r="H88" s="2">
-        <v>3.6</v>
+        <v>25.6</v>
       </c>
       <c r="I88" s="2">
-        <v>8</v>
+        <v>65.2</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>260</v>
@@ -4105,29 +4075,14 @@
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="1">
-        <v>368.65</v>
-      </c>
-      <c r="C89" s="2">
-        <v>-12.92</v>
-      </c>
-      <c r="D89" s="2">
-        <v>-11.57</v>
-      </c>
-      <c r="E89" s="2">
-        <v>-3.2</v>
-      </c>
-      <c r="F89" s="2">
-        <v>10.31</v>
-      </c>
       <c r="G89" s="2">
-        <v>2.4</v>
+        <v>95.2</v>
       </c>
       <c r="H89" s="2">
-        <v>5.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I89" s="2">
-        <v>6.8</v>
+        <v>94</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>260</v>
@@ -4137,29 +4092,14 @@
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="1">
-        <v>172.46</v>
-      </c>
-      <c r="C90" s="2">
-        <v>5.96</v>
-      </c>
-      <c r="D90" s="2">
-        <v>-20.56</v>
-      </c>
-      <c r="E90" s="2">
-        <v>-9.52</v>
-      </c>
-      <c r="F90" s="2">
-        <v>9.279999999999999</v>
-      </c>
       <c r="G90" s="2">
-        <v>9.6</v>
+        <v>97.2</v>
       </c>
       <c r="H90" s="2">
-        <v>28.8</v>
+        <v>98.8</v>
       </c>
       <c r="I90" s="2">
-        <v>42.4</v>
+        <v>98.8</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>260</v>
@@ -4169,29 +4109,14 @@
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="1">
-        <v>200.02</v>
-      </c>
-      <c r="C91" s="2">
-        <v>-13.59</v>
-      </c>
-      <c r="D91" s="2">
-        <v>-6.57</v>
-      </c>
-      <c r="E91" s="2">
-        <v>-7.88</v>
-      </c>
-      <c r="F91" s="2">
-        <v>8.25</v>
-      </c>
       <c r="G91" s="2">
-        <v>4</v>
+        <v>91.2</v>
       </c>
       <c r="H91" s="2">
-        <v>4.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I91" s="2">
-        <v>12</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>260</v>
@@ -4201,29 +4126,14 @@
       <c r="A92" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="1">
-        <v>22.73</v>
-      </c>
-      <c r="C92" s="2">
-        <v>-3.19</v>
-      </c>
-      <c r="D92" s="2">
-        <v>-22</v>
-      </c>
-      <c r="E92" s="2">
-        <v>-5.53</v>
-      </c>
-      <c r="F92" s="2">
-        <v>7.22</v>
-      </c>
       <c r="G92" s="2">
-        <v>16.4</v>
+        <v>11.2</v>
       </c>
       <c r="H92" s="2">
-        <v>8.4</v>
+        <v>1.6</v>
       </c>
       <c r="I92" s="2">
-        <v>5.6</v>
+        <v>48.4</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>260</v>
@@ -4233,29 +4143,14 @@
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="1">
-        <v>112.7</v>
-      </c>
-      <c r="C93" s="2">
-        <v>-10.96</v>
-      </c>
-      <c r="D93" s="2">
-        <v>-15.91</v>
-      </c>
-      <c r="E93" s="2">
-        <v>-5.87</v>
-      </c>
-      <c r="F93" s="2">
-        <v>6.19</v>
-      </c>
       <c r="G93" s="2">
-        <v>7.6</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H93" s="2">
-        <v>14.4</v>
+        <v>88</v>
       </c>
       <c r="I93" s="2">
-        <v>27.6</v>
+        <v>68</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>260</v>
@@ -4265,29 +4160,14 @@
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="1">
-        <v>1603.3</v>
-      </c>
-      <c r="C94" s="2">
-        <v>11.87</v>
-      </c>
-      <c r="D94" s="2">
-        <v>-21.97</v>
-      </c>
-      <c r="E94" s="2">
-        <v>-15.87</v>
-      </c>
-      <c r="F94" s="2">
-        <v>5.15</v>
-      </c>
       <c r="G94" s="2">
-        <v>11.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H94" s="2">
-        <v>32.4</v>
+        <v>94.8</v>
       </c>
       <c r="I94" s="2">
-        <v>76.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>260</v>
@@ -4297,29 +4177,14 @@
       <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B95" s="1">
-        <v>200.54</v>
-      </c>
-      <c r="C95" s="2">
-        <v>-16.96</v>
-      </c>
-      <c r="D95" s="2">
-        <v>-23.81</v>
-      </c>
-      <c r="E95" s="2">
-        <v>-0.67</v>
-      </c>
-      <c r="F95" s="2">
-        <v>4.12</v>
-      </c>
       <c r="G95" s="2">
-        <v>0.8</v>
+        <v>68.8</v>
       </c>
       <c r="H95" s="2">
-        <v>6.4</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I95" s="2">
-        <v>5.2</v>
+        <v>76.8</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>260</v>
@@ -4329,29 +4194,14 @@
       <c r="A96" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B96" s="1">
-        <v>561.25</v>
-      </c>
-      <c r="C96" s="2">
-        <v>-18.26</v>
-      </c>
-      <c r="D96" s="2">
-        <v>-14.5</v>
-      </c>
-      <c r="E96" s="2">
-        <v>-5.93</v>
-      </c>
-      <c r="F96" s="2">
-        <v>3.09</v>
-      </c>
       <c r="G96" s="2">
-        <v>2.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H96" s="2">
-        <v>13.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I96" s="2">
-        <v>10.8</v>
+        <v>72</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>260</v>
@@ -4361,29 +4211,14 @@
       <c r="A97" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="1">
-        <v>262.4</v>
-      </c>
-      <c r="C97" s="2">
-        <v>-12.95</v>
-      </c>
-      <c r="D97" s="2">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="E97" s="2">
-        <v>-11.96</v>
-      </c>
-      <c r="F97" s="2">
-        <v>2.06</v>
-      </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>67.2</v>
       </c>
       <c r="H97" s="2">
-        <v>12.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I97" s="2">
-        <v>19.6</v>
+        <v>74</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>260</v>
@@ -4393,29 +4228,14 @@
       <c r="A98" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B98" s="1">
-        <v>924.75</v>
-      </c>
-      <c r="C98" s="2">
-        <v>-28.33</v>
-      </c>
-      <c r="D98" s="2">
-        <v>-30.33</v>
-      </c>
-      <c r="E98" s="2">
-        <v>-11.06</v>
-      </c>
-      <c r="F98" s="2">
-        <v>1.03</v>
-      </c>
       <c r="G98" s="2">
-        <v>0.4</v>
+        <v>24</v>
       </c>
       <c r="H98" s="2">
-        <v>0.4</v>
+        <v>34</v>
       </c>
       <c r="I98" s="2">
-        <v>0.4</v>
+        <v>11.2</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>260</v>
@@ -4426,13 +4246,13 @@
         <v>106</v>
       </c>
       <c r="G99" s="2">
-        <v>25.6</v>
+        <v>82.8</v>
       </c>
       <c r="H99" s="2">
-        <v>65.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I99" s="2">
-        <v>61.6</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>260</v>
@@ -4443,13 +4263,13 @@
         <v>107</v>
       </c>
       <c r="G100" s="2">
-        <v>93.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H100" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I100" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>260</v>
@@ -4460,13 +4280,13 @@
         <v>108</v>
       </c>
       <c r="G101" s="2">
-        <v>21.2</v>
+        <v>42.8</v>
       </c>
       <c r="H101" s="2">
-        <v>14</v>
+        <v>60.4</v>
       </c>
       <c r="I101" s="2">
-        <v>16.8</v>
+        <v>51.6</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>260</v>
@@ -4477,13 +4297,13 @@
         <v>109</v>
       </c>
       <c r="G102" s="2">
-        <v>88.40000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="H102" s="2">
-        <v>93.59999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="I102" s="2">
-        <v>95.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>260</v>
@@ -4494,13 +4314,13 @@
         <v>110</v>
       </c>
       <c r="G103" s="2">
-        <v>94.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="H103" s="2">
-        <v>93.2</v>
+        <v>51.2</v>
       </c>
       <c r="I103" s="2">
-        <v>96.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>260</v>
@@ -4511,13 +4331,13 @@
         <v>111</v>
       </c>
       <c r="G104" s="2">
-        <v>79.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="H104" s="2">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I104" s="2">
-        <v>76.8</v>
+        <v>78.8</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>260</v>
@@ -4528,13 +4348,13 @@
         <v>112</v>
       </c>
       <c r="G105" s="2">
-        <v>73.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="H105" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I105" s="2">
-        <v>82.8</v>
+        <v>55.6</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>260</v>
@@ -4545,13 +4365,13 @@
         <v>113</v>
       </c>
       <c r="G106" s="2">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="H106" s="2">
-        <v>66</v>
+        <v>37.2</v>
       </c>
       <c r="I106" s="2">
-        <v>74.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>260</v>
@@ -4562,13 +4382,13 @@
         <v>114</v>
       </c>
       <c r="G107" s="2">
-        <v>26.4</v>
+        <v>37.2</v>
       </c>
       <c r="H107" s="2">
-        <v>47.2</v>
+        <v>45.2</v>
       </c>
       <c r="I107" s="2">
-        <v>23.6</v>
+        <v>37.6</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>260</v>
@@ -4579,13 +4399,13 @@
         <v>115</v>
       </c>
       <c r="G108" s="2">
-        <v>86.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H108" s="2">
-        <v>78.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I108" s="2">
-        <v>63.2</v>
+        <v>73.2</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>260</v>
@@ -4596,13 +4416,13 @@
         <v>116</v>
       </c>
       <c r="G109" s="2">
-        <v>86.8</v>
+        <v>59.2</v>
       </c>
       <c r="H109" s="2">
-        <v>85.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I109" s="2">
-        <v>75.2</v>
+        <v>80</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>260</v>
@@ -4613,13 +4433,13 @@
         <v>117</v>
       </c>
       <c r="G110" s="2">
-        <v>56.4</v>
+        <v>32.4</v>
       </c>
       <c r="H110" s="2">
-        <v>52</v>
+        <v>3.2</v>
       </c>
       <c r="I110" s="2">
-        <v>64.8</v>
+        <v>2.4</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>260</v>
@@ -4630,13 +4450,13 @@
         <v>118</v>
       </c>
       <c r="G111" s="2">
-        <v>44.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H111" s="2">
-        <v>50.4</v>
+        <v>72</v>
       </c>
       <c r="I111" s="2">
-        <v>67.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>260</v>
@@ -4647,13 +4467,13 @@
         <v>119</v>
       </c>
       <c r="G112" s="2">
-        <v>95.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H112" s="2">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="I112" s="2">
-        <v>93.2</v>
+        <v>98</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>260</v>
@@ -4664,13 +4484,13 @@
         <v>120</v>
       </c>
       <c r="G113" s="2">
-        <v>31.2</v>
+        <v>53.2</v>
       </c>
       <c r="H113" s="2">
-        <v>69.2</v>
+        <v>48.4</v>
       </c>
       <c r="I113" s="2">
-        <v>70</v>
+        <v>59.6</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>260</v>
@@ -4681,13 +4501,13 @@
         <v>121</v>
       </c>
       <c r="G114" s="2">
-        <v>76.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H114" s="2">
-        <v>78.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I114" s="2">
-        <v>53.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>260</v>
@@ -4698,13 +4518,13 @@
         <v>122</v>
       </c>
       <c r="G115" s="2">
-        <v>62</v>
+        <v>38.4</v>
       </c>
       <c r="H115" s="2">
-        <v>55.6</v>
+        <v>38.8</v>
       </c>
       <c r="I115" s="2">
-        <v>77.2</v>
+        <v>40.8</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>260</v>
@@ -4715,13 +4535,13 @@
         <v>123</v>
       </c>
       <c r="G116" s="2">
-        <v>92.40000000000001</v>
+        <v>28</v>
       </c>
       <c r="H116" s="2">
-        <v>92.40000000000001</v>
+        <v>24</v>
       </c>
       <c r="I116" s="2">
-        <v>88.8</v>
+        <v>15.6</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>260</v>
@@ -4732,13 +4552,13 @@
         <v>124</v>
       </c>
       <c r="G117" s="2">
-        <v>82.8</v>
+        <v>61.2</v>
       </c>
       <c r="H117" s="2">
-        <v>86.8</v>
+        <v>68</v>
       </c>
       <c r="I117" s="2">
-        <v>79.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>260</v>
@@ -4749,13 +4569,13 @@
         <v>125</v>
       </c>
       <c r="G118" s="2">
-        <v>37.2</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2">
-        <v>54</v>
+        <v>36.4</v>
       </c>
       <c r="I118" s="2">
-        <v>78.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>260</v>
@@ -4766,13 +4586,13 @@
         <v>126</v>
       </c>
       <c r="G119" s="2">
-        <v>81.59999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="H119" s="2">
-        <v>73.2</v>
+        <v>11.6</v>
       </c>
       <c r="I119" s="2">
-        <v>86.40000000000001</v>
+        <v>32.4</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>260</v>
@@ -4783,13 +4603,13 @@
         <v>127</v>
       </c>
       <c r="G120" s="2">
-        <v>94</v>
+        <v>48.4</v>
       </c>
       <c r="H120" s="2">
-        <v>96</v>
+        <v>64.8</v>
       </c>
       <c r="I120" s="2">
-        <v>94.8</v>
+        <v>67.2</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>260</v>
@@ -4800,13 +4620,13 @@
         <v>128</v>
       </c>
       <c r="G121" s="2">
-        <v>67.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="H121" s="2">
-        <v>66.40000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="I121" s="2">
-        <v>60.8</v>
+        <v>14.8</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>260</v>
@@ -4817,13 +4637,13 @@
         <v>129</v>
       </c>
       <c r="G122" s="2">
-        <v>38.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H122" s="2">
-        <v>40.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I122" s="2">
-        <v>54</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>260</v>
@@ -4834,13 +4654,13 @@
         <v>130</v>
       </c>
       <c r="G123" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="H123" s="2">
-        <v>56</v>
+        <v>17.2</v>
       </c>
       <c r="I123" s="2">
-        <v>70.8</v>
+        <v>18</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>260</v>
@@ -4851,13 +4671,13 @@
         <v>131</v>
       </c>
       <c r="G124" s="2">
-        <v>68</v>
+        <v>1.6</v>
       </c>
       <c r="H124" s="2">
-        <v>62.8</v>
+        <v>2.8</v>
       </c>
       <c r="I124" s="2">
-        <v>58.4</v>
+        <v>13.6</v>
       </c>
       <c r="J124" s="4" t="s">
         <v>260</v>
@@ -4868,13 +4688,13 @@
         <v>132</v>
       </c>
       <c r="G125" s="2">
-        <v>36.4</v>
+        <v>52.8</v>
       </c>
       <c r="H125" s="2">
-        <v>84</v>
+        <v>47.6</v>
       </c>
       <c r="I125" s="2">
-        <v>92.8</v>
+        <v>64.8</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>260</v>
@@ -4885,13 +4705,13 @@
         <v>133</v>
       </c>
       <c r="G126" s="2">
-        <v>64.8</v>
+        <v>78.8</v>
       </c>
       <c r="H126" s="2">
-        <v>67.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I126" s="2">
-        <v>64.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>260</v>
@@ -4902,13 +4722,13 @@
         <v>134</v>
       </c>
       <c r="G127" s="2">
-        <v>91.59999999999999</v>
+        <v>14</v>
       </c>
       <c r="H127" s="2">
-        <v>90.40000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="I127" s="2">
-        <v>82</v>
+        <v>24.4</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>260</v>
@@ -4919,13 +4739,13 @@
         <v>135</v>
       </c>
       <c r="G128" s="2">
-        <v>74</v>
+        <v>56.4</v>
       </c>
       <c r="H128" s="2">
-        <v>80.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I128" s="2">
-        <v>87.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>260</v>
@@ -4936,13 +4756,13 @@
         <v>136</v>
       </c>
       <c r="G129" s="2">
-        <v>70</v>
+        <v>49.2</v>
       </c>
       <c r="H129" s="2">
-        <v>81.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="I129" s="2">
-        <v>65.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>260</v>
@@ -4953,13 +4773,13 @@
         <v>137</v>
       </c>
       <c r="G130" s="2">
-        <v>64.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="H130" s="2">
-        <v>76.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="I130" s="2">
-        <v>71.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="J130" s="4" t="s">
         <v>260</v>
@@ -4970,13 +4790,13 @@
         <v>138</v>
       </c>
       <c r="G131" s="2">
-        <v>98.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="H131" s="2">
-        <v>96.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I131" s="2">
-        <v>98.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>260</v>
@@ -4987,13 +4807,13 @@
         <v>139</v>
       </c>
       <c r="G132" s="2">
-        <v>21.6</v>
+        <v>33.2</v>
       </c>
       <c r="H132" s="2">
-        <v>24.4</v>
+        <v>50.8</v>
       </c>
       <c r="I132" s="2">
-        <v>12.4</v>
+        <v>54.4</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>260</v>
@@ -5004,13 +4824,13 @@
         <v>140</v>
       </c>
       <c r="G133" s="2">
-        <v>69.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="H133" s="2">
-        <v>58.8</v>
+        <v>44</v>
       </c>
       <c r="I133" s="2">
-        <v>52.4</v>
+        <v>46</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>260</v>
@@ -5021,13 +4841,13 @@
         <v>141</v>
       </c>
       <c r="G134" s="2">
-        <v>83.59999999999999</v>
+        <v>54</v>
       </c>
       <c r="H134" s="2">
-        <v>74.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="I134" s="2">
-        <v>89.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>260</v>
@@ -5038,13 +4858,13 @@
         <v>142</v>
       </c>
       <c r="G135" s="2">
-        <v>58.4</v>
+        <v>75.2</v>
       </c>
       <c r="H135" s="2">
-        <v>74.8</v>
+        <v>93.2</v>
       </c>
       <c r="I135" s="2">
-        <v>80</v>
+        <v>63.6</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>260</v>
@@ -5055,13 +4875,13 @@
         <v>143</v>
       </c>
       <c r="G136" s="2">
-        <v>96.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="H136" s="2">
-        <v>95.59999999999999</v>
+        <v>49.2</v>
       </c>
       <c r="I136" s="2">
-        <v>96</v>
+        <v>45.6</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>260</v>
@@ -5072,13 +4892,13 @@
         <v>144</v>
       </c>
       <c r="G137" s="2">
-        <v>32.4</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H137" s="2">
-        <v>29.6</v>
+        <v>92</v>
       </c>
       <c r="I137" s="2">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>260</v>
@@ -5089,13 +4909,13 @@
         <v>145</v>
       </c>
       <c r="G138" s="2">
-        <v>54</v>
+        <v>92.8</v>
       </c>
       <c r="H138" s="2">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="I138" s="2">
-        <v>90.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>260</v>
@@ -5106,13 +4926,13 @@
         <v>146</v>
       </c>
       <c r="G139" s="2">
-        <v>93.2</v>
+        <v>15.6</v>
       </c>
       <c r="H139" s="2">
-        <v>63.6</v>
+        <v>27.2</v>
       </c>
       <c r="I139" s="2">
-        <v>46.8</v>
+        <v>15.2</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>260</v>
@@ -5123,13 +4943,13 @@
         <v>147</v>
       </c>
       <c r="G140" s="2">
-        <v>49.2</v>
+        <v>96.8</v>
       </c>
       <c r="H140" s="2">
-        <v>45.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I140" s="2">
-        <v>29.2</v>
+        <v>78</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>260</v>
@@ -5140,13 +4960,13 @@
         <v>148</v>
       </c>
       <c r="G141" s="2">
-        <v>52.8</v>
+        <v>30.4</v>
       </c>
       <c r="H141" s="2">
-        <v>46.8</v>
+        <v>61.6</v>
       </c>
       <c r="I141" s="2">
-        <v>49.2</v>
+        <v>60.4</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>260</v>
@@ -5157,13 +4977,13 @@
         <v>149</v>
       </c>
       <c r="G142" s="2">
-        <v>23.6</v>
+        <v>81.2</v>
       </c>
       <c r="H142" s="2">
-        <v>22.8</v>
+        <v>88.8</v>
       </c>
       <c r="I142" s="2">
-        <v>12.8</v>
+        <v>94.8</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>260</v>
@@ -5174,13 +4994,13 @@
         <v>150</v>
       </c>
       <c r="G143" s="2">
-        <v>27.2</v>
+        <v>50.8</v>
       </c>
       <c r="H143" s="2">
-        <v>15.2</v>
+        <v>48.8</v>
       </c>
       <c r="I143" s="2">
-        <v>20</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>260</v>
@@ -5191,13 +5011,13 @@
         <v>151</v>
       </c>
       <c r="G144" s="2">
-        <v>84.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="H144" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="I144" s="2">
-        <v>87.2</v>
+        <v>49.6</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>260</v>
@@ -5208,13 +5028,13 @@
         <v>152</v>
       </c>
       <c r="G145" s="2">
-        <v>61.6</v>
+        <v>36.8</v>
       </c>
       <c r="H145" s="2">
-        <v>60.4</v>
+        <v>43.6</v>
       </c>
       <c r="I145" s="2">
-        <v>73.59999999999999</v>
+        <v>38</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>260</v>
@@ -5225,13 +5045,13 @@
         <v>153</v>
       </c>
       <c r="G146" s="2">
-        <v>88.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H146" s="2">
-        <v>94.8</v>
+        <v>79.2</v>
       </c>
       <c r="I146" s="2">
-        <v>93.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>260</v>
@@ -5242,13 +5062,13 @@
         <v>154</v>
       </c>
       <c r="G147" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="H147" s="2">
         <v>7.2</v>
       </c>
-      <c r="H147" s="2">
+      <c r="I147" s="2">
         <v>6</v>
-      </c>
-      <c r="I147" s="2">
-        <v>16.4</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>260</v>
@@ -5259,13 +5079,13 @@
         <v>155</v>
       </c>
       <c r="G148" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="H148" s="2">
         <v>5.6</v>
       </c>
-      <c r="H148" s="2">
+      <c r="I148" s="2">
         <v>2.8</v>
-      </c>
-      <c r="I148" s="2">
-        <v>38</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>260</v>
@@ -5276,13 +5096,13 @@
         <v>156</v>
       </c>
       <c r="G149" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="H149" s="2">
         <v>1.2</v>
       </c>
-      <c r="H149" s="2">
+      <c r="I149" s="2">
         <v>0.8</v>
-      </c>
-      <c r="I149" s="2">
-        <v>1.6</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>260</v>
@@ -5293,13 +5113,13 @@
         <v>157</v>
       </c>
       <c r="G150" s="2">
+        <v>72.8</v>
+      </c>
+      <c r="H150" s="2">
         <v>54.4</v>
       </c>
-      <c r="H150" s="2">
+      <c r="I150" s="2">
         <v>45.2</v>
-      </c>
-      <c r="I150" s="2">
-        <v>61.2</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>260</v>
@@ -5310,13 +5130,13 @@
         <v>158</v>
       </c>
       <c r="G151" s="2">
-        <v>85.2</v>
+        <v>16</v>
       </c>
       <c r="H151" s="2">
-        <v>70</v>
+        <v>14.8</v>
       </c>
       <c r="I151" s="2">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>260</v>
@@ -5327,13 +5147,13 @@
         <v>159</v>
       </c>
       <c r="G152" s="2">
-        <v>14.8</v>
+        <v>68</v>
       </c>
       <c r="H152" s="2">
-        <v>16</v>
+        <v>58.8</v>
       </c>
       <c r="I152" s="2">
-        <v>14.4</v>
+        <v>84.8</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>260</v>
@@ -5344,13 +5164,13 @@
         <v>160</v>
       </c>
       <c r="G153" s="2">
-        <v>58.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H153" s="2">
-        <v>84.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I153" s="2">
-        <v>80.8</v>
+        <v>77.2</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>260</v>
@@ -5361,13 +5181,13 @@
         <v>161</v>
       </c>
       <c r="G154" s="2">
-        <v>70.40000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="H154" s="2">
-        <v>77.2</v>
+        <v>57.2</v>
       </c>
       <c r="I154" s="2">
-        <v>65.2</v>
+        <v>41.6</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>260</v>
@@ -5378,13 +5198,13 @@
         <v>162</v>
       </c>
       <c r="G155" s="2">
-        <v>57.2</v>
+        <v>46.4</v>
       </c>
       <c r="H155" s="2">
-        <v>41.6</v>
+        <v>60</v>
       </c>
       <c r="I155" s="2">
-        <v>10.4</v>
+        <v>61.6</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>260</v>
@@ -5395,13 +5215,13 @@
         <v>163</v>
       </c>
       <c r="G156" s="2">
-        <v>60</v>
+        <v>31.6</v>
       </c>
       <c r="H156" s="2">
-        <v>61.6</v>
+        <v>19.2</v>
       </c>
       <c r="I156" s="2">
-        <v>56.4</v>
+        <v>8</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>260</v>
@@ -5412,13 +5232,13 @@
         <v>164</v>
       </c>
       <c r="G157" s="2">
-        <v>20.8</v>
+        <v>26</v>
       </c>
       <c r="H157" s="2">
-        <v>32</v>
+        <v>15.2</v>
       </c>
       <c r="I157" s="2">
-        <v>46</v>
+        <v>36.4</v>
       </c>
       <c r="J157" s="4" t="s">
         <v>260</v>
@@ -5429,13 +5249,13 @@
         <v>165</v>
       </c>
       <c r="G158" s="2">
-        <v>66.8</v>
+        <v>13.2</v>
       </c>
       <c r="H158" s="2">
-        <v>92</v>
+        <v>10.8</v>
       </c>
       <c r="I158" s="2">
-        <v>96.8</v>
+        <v>7.6</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>260</v>
@@ -5446,13 +5266,13 @@
         <v>166</v>
       </c>
       <c r="G159" s="2">
-        <v>80</v>
+        <v>62.4</v>
       </c>
       <c r="H159" s="2">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="I159" s="2">
-        <v>81.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>260</v>
@@ -5463,13 +5283,13 @@
         <v>167</v>
       </c>
       <c r="G160" s="2">
-        <v>19.2</v>
+        <v>54.8</v>
       </c>
       <c r="H160" s="2">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="I160" s="2">
-        <v>26.8</v>
+        <v>35.6</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>260</v>
@@ -5480,13 +5300,13 @@
         <v>168</v>
       </c>
       <c r="G161" s="2">
-        <v>15.2</v>
+        <v>31.2</v>
       </c>
       <c r="H161" s="2">
-        <v>36.4</v>
+        <v>45.6</v>
       </c>
       <c r="I161" s="2">
-        <v>47.2</v>
+        <v>64</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>260</v>
@@ -5500,10 +5320,10 @@
         <v>5.2</v>
       </c>
       <c r="H162" s="2">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="I162" s="2">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>260</v>
@@ -5514,13 +5334,13 @@
         <v>170</v>
       </c>
       <c r="G163" s="2">
-        <v>45.6</v>
+        <v>62</v>
       </c>
       <c r="H163" s="2">
-        <v>64</v>
+        <v>56.8</v>
       </c>
       <c r="I163" s="2">
-        <v>59.6</v>
+        <v>26.4</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>260</v>
@@ -5531,13 +5351,13 @@
         <v>171</v>
       </c>
       <c r="G164" s="2">
-        <v>42.8</v>
+        <v>48</v>
       </c>
       <c r="H164" s="2">
-        <v>42.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I164" s="2">
-        <v>47.6</v>
+        <v>34.4</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>260</v>
@@ -5548,13 +5368,13 @@
         <v>172</v>
       </c>
       <c r="G165" s="2">
-        <v>3.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H165" s="2">
-        <v>9.199999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I165" s="2">
-        <v>11.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>260</v>
@@ -5565,13 +5385,13 @@
         <v>173</v>
       </c>
       <c r="G166" s="2">
-        <v>56.8</v>
+        <v>30</v>
       </c>
       <c r="H166" s="2">
-        <v>26.4</v>
+        <v>12</v>
       </c>
       <c r="I166" s="2">
-        <v>38.4</v>
+        <v>28.4</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>260</v>
@@ -5582,13 +5402,13 @@
         <v>174</v>
       </c>
       <c r="G167" s="2">
-        <v>62.8</v>
+        <v>96</v>
       </c>
       <c r="H167" s="2">
-        <v>69.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I167" s="2">
-        <v>76</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>260</v>
@@ -5599,13 +5419,13 @@
         <v>175</v>
       </c>
       <c r="G168" s="2">
-        <v>65.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="H168" s="2">
-        <v>34.4</v>
+        <v>55.6</v>
       </c>
       <c r="I168" s="2">
-        <v>55.6</v>
+        <v>21.2</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>260</v>
@@ -5616,13 +5436,13 @@
         <v>176</v>
       </c>
       <c r="G169" s="2">
-        <v>96.8</v>
+        <v>28.8</v>
       </c>
       <c r="H169" s="2">
-        <v>94.40000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="I169" s="2">
-        <v>92.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>260</v>
@@ -5633,13 +5453,13 @@
         <v>177</v>
       </c>
       <c r="G170" s="2">
-        <v>98</v>
+        <v>8.4</v>
       </c>
       <c r="H170" s="2">
-        <v>91.59999999999999</v>
+        <v>16</v>
       </c>
       <c r="I170" s="2">
-        <v>92</v>
+        <v>3.2</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>260</v>
@@ -5650,13 +5470,13 @@
         <v>178</v>
       </c>
       <c r="G171" s="2">
-        <v>55.6</v>
+        <v>26.4</v>
       </c>
       <c r="H171" s="2">
-        <v>21.2</v>
+        <v>42</v>
       </c>
       <c r="I171" s="2">
-        <v>26.4</v>
+        <v>41.2</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>260</v>
@@ -5667,13 +5487,13 @@
         <v>179</v>
       </c>
       <c r="G172" s="2">
-        <v>55.2</v>
+        <v>49.6</v>
       </c>
       <c r="H172" s="2">
-        <v>53.2</v>
+        <v>58</v>
       </c>
       <c r="I172" s="2">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>260</v>
@@ -5684,13 +5504,13 @@
         <v>180</v>
       </c>
       <c r="G173" s="2">
-        <v>16</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H173" s="2">
-        <v>3.2</v>
+        <v>49.6</v>
       </c>
       <c r="I173" s="2">
-        <v>3.2</v>
+        <v>58.4</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>260</v>
@@ -5701,13 +5521,13 @@
         <v>181</v>
       </c>
       <c r="G174" s="2">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H174" s="2">
-        <v>41.2</v>
+        <v>28</v>
       </c>
       <c r="I174" s="2">
-        <v>40.8</v>
+        <v>31.2</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>260</v>
@@ -5718,13 +5538,13 @@
         <v>182</v>
       </c>
       <c r="G175" s="2">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H175" s="2">
-        <v>40</v>
+        <v>46.4</v>
       </c>
       <c r="I175" s="2">
-        <v>55.2</v>
+        <v>52.4</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>260</v>
@@ -5735,13 +5555,13 @@
         <v>183</v>
       </c>
       <c r="G176" s="2">
-        <v>49.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H176" s="2">
-        <v>58.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I176" s="2">
-        <v>75.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>260</v>
@@ -5752,13 +5572,13 @@
         <v>184</v>
       </c>
       <c r="G177" s="2">
-        <v>28</v>
+        <v>79.2</v>
       </c>
       <c r="H177" s="2">
-        <v>31.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I177" s="2">
-        <v>36.4</v>
+        <v>19.2</v>
       </c>
       <c r="J177" s="4" t="s">
         <v>260</v>
@@ -5769,13 +5589,13 @@
         <v>185</v>
       </c>
       <c r="G178" s="2">
-        <v>46.4</v>
+        <v>58</v>
       </c>
       <c r="H178" s="2">
-        <v>52.4</v>
+        <v>61.2</v>
       </c>
       <c r="I178" s="2">
-        <v>33.6</v>
+        <v>56.8</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>260</v>
@@ -5789,10 +5609,10 @@
         <v>68.40000000000001</v>
       </c>
       <c r="H179" s="2">
-        <v>19.2</v>
+        <v>68.8</v>
       </c>
       <c r="I179" s="2">
-        <v>13.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>260</v>
@@ -5803,13 +5623,13 @@
         <v>187</v>
       </c>
       <c r="G180" s="2">
-        <v>8.4</v>
+        <v>63.2</v>
       </c>
       <c r="H180" s="2">
-        <v>22.4</v>
+        <v>39.2</v>
       </c>
       <c r="I180" s="2">
-        <v>30.4</v>
+        <v>33.6</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>260</v>
@@ -5820,13 +5640,13 @@
         <v>188</v>
       </c>
       <c r="G181" s="2">
-        <v>61.2</v>
+        <v>25.2</v>
       </c>
       <c r="H181" s="2">
-        <v>56.8</v>
+        <v>37.6</v>
       </c>
       <c r="I181" s="2">
-        <v>49.6</v>
+        <v>34</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>260</v>
@@ -5837,13 +5657,13 @@
         <v>189</v>
       </c>
       <c r="G182" s="2">
-        <v>24.8</v>
+        <v>92</v>
       </c>
       <c r="H182" s="2">
-        <v>35.2</v>
+        <v>89.2</v>
       </c>
       <c r="I182" s="2">
-        <v>46.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>260</v>
@@ -5854,13 +5674,13 @@
         <v>190</v>
       </c>
       <c r="G183" s="2">
-        <v>37.6</v>
+        <v>2</v>
       </c>
       <c r="H183" s="2">
-        <v>34</v>
+        <v>0.8</v>
       </c>
       <c r="I183" s="2">
-        <v>43.6</v>
+        <v>6.4</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>260</v>
@@ -5871,13 +5691,13 @@
         <v>191</v>
       </c>
       <c r="G184" s="2">
-        <v>84.8</v>
+        <v>77.2</v>
       </c>
       <c r="H184" s="2">
-        <v>75.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="I184" s="2">
-        <v>52.8</v>
+        <v>76</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>260</v>
@@ -5888,13 +5708,13 @@
         <v>192</v>
       </c>
       <c r="G185" s="2">
-        <v>28.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H185" s="2">
-        <v>17.2</v>
+        <v>10.4</v>
       </c>
       <c r="I185" s="2">
-        <v>23.2</v>
+        <v>6.8</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>260</v>
@@ -5905,13 +5725,13 @@
         <v>193</v>
       </c>
       <c r="G186" s="2">
-        <v>86</v>
+        <v>52.4</v>
       </c>
       <c r="H186" s="2">
-        <v>76</v>
+        <v>36.8</v>
       </c>
       <c r="I186" s="2">
-        <v>86</v>
+        <v>29.2</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>260</v>
@@ -5922,13 +5742,13 @@
         <v>194</v>
       </c>
       <c r="G187" s="2">
-        <v>10.4</v>
+        <v>38.8</v>
       </c>
       <c r="H187" s="2">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="I187" s="2">
-        <v>22.4</v>
+        <v>33.2</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>260</v>
@@ -5939,13 +5759,13 @@
         <v>195</v>
       </c>
       <c r="G188" s="2">
-        <v>36.8</v>
+        <v>84</v>
       </c>
       <c r="H188" s="2">
-        <v>29.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I188" s="2">
-        <v>35.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>260</v>
@@ -5956,13 +5776,13 @@
         <v>196</v>
       </c>
       <c r="G189" s="2">
-        <v>52.4</v>
+        <v>17.2</v>
       </c>
       <c r="H189" s="2">
-        <v>37.2</v>
+        <v>16.8</v>
       </c>
       <c r="I189" s="2">
-        <v>2</v>
+        <v>21.6</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>260</v>
@@ -5973,13 +5793,13 @@
         <v>197</v>
       </c>
       <c r="G190" s="2">
-        <v>85.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H190" s="2">
-        <v>89.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I190" s="2">
-        <v>60.4</v>
+        <v>82.8</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>260</v>
@@ -5990,13 +5810,13 @@
         <v>198</v>
       </c>
       <c r="G191" s="2">
-        <v>16.8</v>
+        <v>0.8</v>
       </c>
       <c r="H191" s="2">
-        <v>21.6</v>
+        <v>2</v>
       </c>
       <c r="I191" s="2">
-        <v>22.8</v>
+        <v>12.8</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>260</v>
@@ -6007,13 +5827,13 @@
         <v>199</v>
       </c>
       <c r="G192" s="2">
+        <v>34.8</v>
+      </c>
+      <c r="H192" s="2">
         <v>22.8</v>
       </c>
-      <c r="H192" s="2">
+      <c r="I192" s="2">
         <v>16.4</v>
-      </c>
-      <c r="I192" s="2">
-        <v>17.2</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>260</v>
@@ -6024,13 +5844,13 @@
         <v>200</v>
       </c>
       <c r="G193" s="2">
-        <v>43.2</v>
+        <v>34</v>
       </c>
       <c r="H193" s="2">
-        <v>39.6</v>
+        <v>30.4</v>
       </c>
       <c r="I193" s="2">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>260</v>
@@ -6041,13 +5861,13 @@
         <v>201</v>
       </c>
       <c r="G194" s="2">
-        <v>30.4</v>
+        <v>16.4</v>
       </c>
       <c r="H194" s="2">
-        <v>24</v>
+        <v>25.2</v>
       </c>
       <c r="I194" s="2">
-        <v>40.4</v>
+        <v>11.6</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>260</v>
@@ -6058,13 +5878,13 @@
         <v>202</v>
       </c>
       <c r="G195" s="2">
-        <v>25.2</v>
+        <v>63.6</v>
       </c>
       <c r="H195" s="2">
-        <v>11.6</v>
+        <v>72.8</v>
       </c>
       <c r="I195" s="2">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>260</v>
@@ -6075,13 +5895,13 @@
         <v>203</v>
       </c>
       <c r="G196" s="2">
-        <v>72.8</v>
+        <v>48.8</v>
       </c>
       <c r="H196" s="2">
-        <v>50</v>
+        <v>22.4</v>
       </c>
       <c r="I196" s="2">
-        <v>56.8</v>
+        <v>50.8</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>260</v>
@@ -6092,13 +5912,13 @@
         <v>204</v>
       </c>
       <c r="G197" s="2">
+        <v>17.6</v>
+      </c>
+      <c r="H197" s="2">
         <v>33.2</v>
       </c>
-      <c r="H197" s="2">
+      <c r="I197" s="2">
         <v>16.8</v>
-      </c>
-      <c r="I197" s="2">
-        <v>18.8</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>260</v>
@@ -6109,13 +5929,13 @@
         <v>205</v>
       </c>
       <c r="G198" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H198" s="2">
         <v>18</v>
       </c>
-      <c r="H198" s="2">
+      <c r="I198" s="2">
         <v>27.2</v>
-      </c>
-      <c r="I198" s="2">
-        <v>35.6</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>260</v>
@@ -6126,13 +5946,13 @@
         <v>206</v>
       </c>
       <c r="G199" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H199" s="2">
         <v>23.2</v>
       </c>
-      <c r="H199" s="2">
+      <c r="I199" s="2">
         <v>12</v>
-      </c>
-      <c r="I199" s="2">
-        <v>7.6</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>260</v>
@@ -6143,13 +5963,13 @@
         <v>207</v>
       </c>
       <c r="G200" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="H200" s="2">
         <v>4.4</v>
       </c>
-      <c r="H200" s="2">
+      <c r="I200" s="2">
         <v>44.8</v>
-      </c>
-      <c r="I200" s="2">
-        <v>66.8</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>260</v>
@@ -6160,13 +5980,13 @@
         <v>208</v>
       </c>
       <c r="G201" s="2">
-        <v>75.2</v>
+        <v>50.4</v>
       </c>
       <c r="H201" s="2">
-        <v>62</v>
+        <v>60.8</v>
       </c>
       <c r="I201" s="2">
-        <v>52</v>
+        <v>46.4</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>260</v>
@@ -6177,13 +5997,13 @@
         <v>209</v>
       </c>
       <c r="G202" s="2">
-        <v>71.59999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="H202" s="2">
-        <v>70.8</v>
+        <v>52</v>
       </c>
       <c r="I202" s="2">
-        <v>41.2</v>
+        <v>48</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>260</v>
@@ -6194,13 +6014,13 @@
         <v>210</v>
       </c>
       <c r="G203" s="2">
-        <v>12.8</v>
+        <v>18.4</v>
       </c>
       <c r="H203" s="2">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="I203" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>260</v>
@@ -6211,13 +6031,13 @@
         <v>211</v>
       </c>
       <c r="G204" s="2">
-        <v>52</v>
+        <v>14.4</v>
       </c>
       <c r="H204" s="2">
-        <v>48</v>
+        <v>11.2</v>
       </c>
       <c r="I204" s="2">
-        <v>6.4</v>
+        <v>17.6</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>260</v>
@@ -6228,13 +6048,13 @@
         <v>212</v>
       </c>
       <c r="G205" s="2">
-        <v>14</v>
+        <v>30.8</v>
       </c>
       <c r="H205" s="2">
-        <v>26</v>
+        <v>28.4</v>
       </c>
       <c r="I205" s="2">
-        <v>18</v>
+        <v>20.4</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>260</v>
@@ -6245,13 +6065,13 @@
         <v>213</v>
       </c>
       <c r="G206" s="2">
-        <v>11.2</v>
+        <v>22.8</v>
       </c>
       <c r="H206" s="2">
-        <v>17.6</v>
+        <v>34.4</v>
       </c>
       <c r="I206" s="2">
-        <v>15.2</v>
+        <v>47.6</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>260</v>
@@ -6262,13 +6082,13 @@
         <v>214</v>
       </c>
       <c r="G207" s="2">
-        <v>51.6</v>
+        <v>87.2</v>
       </c>
       <c r="H207" s="2">
-        <v>43.6</v>
+        <v>70.8</v>
       </c>
       <c r="I207" s="2">
-        <v>45.2</v>
+        <v>56.4</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>260</v>
@@ -6279,13 +6099,13 @@
         <v>215</v>
       </c>
       <c r="G208" s="2">
-        <v>28.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H208" s="2">
-        <v>20.4</v>
+        <v>91.2</v>
       </c>
       <c r="I208" s="2">
-        <v>34</v>
+        <v>62.4</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>260</v>
@@ -6296,13 +6116,13 @@
         <v>216</v>
       </c>
       <c r="G209" s="2">
-        <v>34.4</v>
+        <v>36.4</v>
       </c>
       <c r="H209" s="2">
-        <v>47.6</v>
+        <v>18.8</v>
       </c>
       <c r="I209" s="2">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>260</v>
@@ -6313,13 +6133,13 @@
         <v>217</v>
       </c>
       <c r="G210" s="2">
-        <v>91.2</v>
+        <v>27.2</v>
       </c>
       <c r="H210" s="2">
-        <v>62.4</v>
+        <v>40</v>
       </c>
       <c r="I210" s="2">
-        <v>62.4</v>
+        <v>42</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>260</v>
@@ -6330,13 +6150,13 @@
         <v>218</v>
       </c>
       <c r="G211" s="2">
-        <v>18.8</v>
+        <v>51.2</v>
       </c>
       <c r="H211" s="2">
-        <v>57.2</v>
+        <v>54.8</v>
       </c>
       <c r="I211" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>260</v>
@@ -6347,13 +6167,13 @@
         <v>219</v>
       </c>
       <c r="G212" s="2">
-        <v>26.8</v>
+        <v>66</v>
       </c>
       <c r="H212" s="2">
-        <v>25.6</v>
+        <v>44.8</v>
       </c>
       <c r="I212" s="2">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>260</v>
@@ -6364,13 +6184,13 @@
         <v>220</v>
       </c>
       <c r="G213" s="2">
-        <v>40</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H213" s="2">
-        <v>42</v>
+        <v>65.2</v>
       </c>
       <c r="I213" s="2">
-        <v>59.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>260</v>
@@ -6381,13 +6201,13 @@
         <v>221</v>
       </c>
       <c r="G214" s="2">
-        <v>54.8</v>
+        <v>52</v>
       </c>
       <c r="H214" s="2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I214" s="2">
-        <v>64</v>
+        <v>49.2</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>260</v>
@@ -6398,13 +6218,13 @@
         <v>222</v>
       </c>
       <c r="G215" s="2">
-        <v>44.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H215" s="2">
-        <v>38.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I215" s="2">
-        <v>51.6</v>
+        <v>79.2</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>260</v>
@@ -6415,13 +6235,13 @@
         <v>223</v>
       </c>
       <c r="G216" s="2">
-        <v>65.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H216" s="2">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I216" s="2">
-        <v>57.2</v>
+        <v>89.2</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>260</v>
@@ -6432,13 +6252,13 @@
         <v>224</v>
       </c>
       <c r="G217" s="2">
-        <v>78.40000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="H217" s="2">
-        <v>79.2</v>
+        <v>10</v>
       </c>
       <c r="I217" s="2">
-        <v>81.2</v>
+        <v>3.6</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>260</v>
@@ -6449,13 +6269,13 @@
         <v>225</v>
       </c>
       <c r="G218" s="2">
-        <v>82.40000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="H218" s="2">
-        <v>89.2</v>
+        <v>34.8</v>
       </c>
       <c r="I218" s="2">
-        <v>85.2</v>
+        <v>40.4</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>260</v>
@@ -6466,13 +6286,13 @@
         <v>226</v>
       </c>
       <c r="G219" s="2">
-        <v>53.2</v>
+        <v>74.8</v>
       </c>
       <c r="H219" s="2">
-        <v>39.2</v>
+        <v>76</v>
       </c>
       <c r="I219" s="2">
-        <v>48.8</v>
+        <v>91.2</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>260</v>
@@ -6483,13 +6303,13 @@
         <v>227</v>
       </c>
       <c r="G220" s="2">
-        <v>34.8</v>
+        <v>45.6</v>
       </c>
       <c r="H220" s="2">
-        <v>40.4</v>
+        <v>15.6</v>
       </c>
       <c r="I220" s="2">
-        <v>15.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>260</v>
@@ -6500,13 +6320,13 @@
         <v>228</v>
       </c>
       <c r="G221" s="2">
-        <v>62.4</v>
+        <v>56.8</v>
       </c>
       <c r="H221" s="2">
-        <v>53.6</v>
+        <v>50.4</v>
       </c>
       <c r="I221" s="2">
-        <v>62.8</v>
+        <v>42.8</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>260</v>
@@ -6517,13 +6337,13 @@
         <v>229</v>
       </c>
       <c r="G222" s="2">
-        <v>76</v>
+        <v>7.6</v>
       </c>
       <c r="H222" s="2">
-        <v>91.2</v>
+        <v>6.4</v>
       </c>
       <c r="I222" s="2">
-        <v>78</v>
+        <v>1.2</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>260</v>
@@ -6534,13 +6354,13 @@
         <v>230</v>
       </c>
       <c r="G223" s="2">
-        <v>15.6</v>
+        <v>40.8</v>
       </c>
       <c r="H223" s="2">
-        <v>64.40000000000001</v>
+        <v>20</v>
       </c>
       <c r="I223" s="2">
-        <v>78.8</v>
+        <v>13.2</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>260</v>
@@ -6551,13 +6371,13 @@
         <v>231</v>
       </c>
       <c r="G224" s="2">
-        <v>66</v>
+        <v>25.6</v>
       </c>
       <c r="H224" s="2">
-        <v>54.8</v>
+        <v>41.2</v>
       </c>
       <c r="I224" s="2">
-        <v>45.6</v>
+        <v>36.8</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>260</v>
@@ -6568,13 +6388,13 @@
         <v>232</v>
       </c>
       <c r="G225" s="2">
-        <v>41.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H225" s="2">
-        <v>36.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I225" s="2">
-        <v>37.2</v>
+        <v>81.2</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>260</v>
@@ -6585,13 +6405,13 @@
         <v>233</v>
       </c>
       <c r="G226" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H226" s="2">
-        <v>27.6</v>
+        <v>31.6</v>
       </c>
       <c r="I226" s="2">
-        <v>41.6</v>
+        <v>34.8</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>260</v>
@@ -6602,13 +6422,13 @@
         <v>234</v>
       </c>
       <c r="G227" s="2">
-        <v>89.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="H227" s="2">
-        <v>81.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I227" s="2">
-        <v>69.59999999999999</v>
+        <v>2</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>260</v>
@@ -6619,13 +6439,13 @@
         <v>235</v>
       </c>
       <c r="G228" s="2">
-        <v>9.199999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="H228" s="2">
-        <v>2</v>
+        <v>32.8</v>
       </c>
       <c r="I228" s="2">
-        <v>11.6</v>
+        <v>20</v>
       </c>
       <c r="J228" s="4" t="s">
         <v>260</v>
@@ -6636,13 +6456,13 @@
         <v>236</v>
       </c>
       <c r="G229" s="2">
-        <v>64</v>
+        <v>4.4</v>
       </c>
       <c r="H229" s="2">
-        <v>26.8</v>
+        <v>4</v>
       </c>
       <c r="I229" s="2">
-        <v>28.4</v>
+        <v>4.8</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>260</v>
@@ -6653,13 +6473,13 @@
         <v>237</v>
       </c>
       <c r="G230" s="2">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="H230" s="2">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="I230" s="2">
-        <v>18.4</v>
+        <v>10.8</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>260</v>
@@ -6670,13 +6490,13 @@
         <v>238</v>
       </c>
       <c r="G231" s="2">
-        <v>13.6</v>
+        <v>51.6</v>
       </c>
       <c r="H231" s="2">
-        <v>23.6</v>
+        <v>41.6</v>
       </c>
       <c r="I231" s="2">
-        <v>24.8</v>
+        <v>19.6</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>260</v>
@@ -6687,13 +6507,13 @@
         <v>239</v>
       </c>
       <c r="G232" s="2">
-        <v>4.8</v>
+        <v>72</v>
       </c>
       <c r="H232" s="2">
-        <v>10.8</v>
+        <v>77.2</v>
       </c>
       <c r="I232" s="2">
-        <v>7.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>260</v>
@@ -6704,13 +6524,13 @@
         <v>240</v>
       </c>
       <c r="G233" s="2">
-        <v>82</v>
+        <v>43.2</v>
       </c>
       <c r="H233" s="2">
-        <v>87.59999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="I233" s="2">
-        <v>68.8</v>
+        <v>18.8</v>
       </c>
       <c r="J233" s="4" t="s">
         <v>260</v>
@@ -6721,13 +6541,13 @@
         <v>241</v>
       </c>
       <c r="G234" s="2">
-        <v>77.2</v>
+        <v>3.2</v>
       </c>
       <c r="H234" s="2">
-        <v>82.40000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I234" s="2">
-        <v>68</v>
+        <v>14.4</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>260</v>
@@ -6738,13 +6558,13 @@
         <v>242</v>
       </c>
       <c r="G235" s="2">
-        <v>40.8</v>
+        <v>55.6</v>
       </c>
       <c r="H235" s="2">
-        <v>18.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I235" s="2">
-        <v>20.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>260</v>
@@ -6755,13 +6575,13 @@
         <v>243</v>
       </c>
       <c r="G236" s="2">
-        <v>66.40000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="H236" s="2">
-        <v>65.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="I236" s="2">
-        <v>73.2</v>
+        <v>66.8</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>260</v>
@@ -6772,13 +6592,13 @@
         <v>244</v>
       </c>
       <c r="G237" s="2">
-        <v>53.6</v>
+        <v>19.2</v>
       </c>
       <c r="H237" s="2">
-        <v>66.8</v>
+        <v>29.2</v>
       </c>
       <c r="I237" s="2">
-        <v>48.4</v>
+        <v>55.2</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>260</v>
@@ -6789,13 +6609,13 @@
         <v>245</v>
       </c>
       <c r="G238" s="2">
-        <v>29.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H238" s="2">
-        <v>55.2</v>
+        <v>78.8</v>
       </c>
       <c r="I238" s="2">
-        <v>31.2</v>
+        <v>61.2</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>260</v>
@@ -6806,13 +6626,13 @@
         <v>246</v>
       </c>
       <c r="G239" s="2">
-        <v>78.8</v>
+        <v>80.8</v>
       </c>
       <c r="H239" s="2">
-        <v>61.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I239" s="2">
-        <v>62</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>260</v>
@@ -6823,13 +6643,13 @@
         <v>247</v>
       </c>
       <c r="G240" s="2">
-        <v>80.40000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="H240" s="2">
-        <v>73.59999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="I240" s="2">
-        <v>68.40000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>260</v>
@@ -6840,13 +6660,13 @@
         <v>248</v>
       </c>
       <c r="G241" s="2">
-        <v>24.4</v>
+        <v>10.4</v>
       </c>
       <c r="H241" s="2">
-        <v>31.6</v>
+        <v>13.2</v>
       </c>
       <c r="I241" s="2">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>260</v>
@@ -6857,13 +6677,13 @@
         <v>249</v>
       </c>
       <c r="G242" s="2">
-        <v>13.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H242" s="2">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="I242" s="2">
-        <v>26</v>
+        <v>63.2</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>260</v>
@@ -6874,13 +6694,13 @@
         <v>250</v>
       </c>
       <c r="G243" s="2">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="H243" s="2">
-        <v>63.2</v>
+        <v>30.8</v>
       </c>
       <c r="I243" s="2">
-        <v>58.8</v>
+        <v>36</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>260</v>
@@ -6891,13 +6711,13 @@
         <v>251</v>
       </c>
       <c r="G244" s="2">
-        <v>30.8</v>
+        <v>22.4</v>
       </c>
       <c r="H244" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I244" s="2">
-        <v>36.8</v>
+        <v>10</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>260</v>
@@ -6908,13 +6728,13 @@
         <v>252</v>
       </c>
       <c r="G245" s="2">
-        <v>30</v>
+        <v>42.4</v>
       </c>
       <c r="H245" s="2">
-        <v>10</v>
+        <v>35.6</v>
       </c>
       <c r="I245" s="2">
-        <v>8.4</v>
+        <v>57.6</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>260</v>
@@ -6925,13 +6745,13 @@
         <v>253</v>
       </c>
       <c r="G246" s="2">
-        <v>35.6</v>
+        <v>18</v>
       </c>
       <c r="H246" s="2">
-        <v>57.6</v>
+        <v>19.6</v>
       </c>
       <c r="I246" s="2">
-        <v>43.2</v>
+        <v>44.4</v>
       </c>
       <c r="J246" s="4" t="s">
         <v>260</v>
@@ -6942,13 +6762,13 @@
         <v>254</v>
       </c>
       <c r="G247" s="2">
-        <v>19.6</v>
+        <v>43.6</v>
       </c>
       <c r="H247" s="2">
-        <v>44.4</v>
+        <v>46.8</v>
       </c>
       <c r="I247" s="2">
-        <v>34.8</v>
+        <v>38.8</v>
       </c>
       <c r="J247" s="4" t="s">
         <v>260</v>
@@ -6959,13 +6779,13 @@
         <v>255</v>
       </c>
       <c r="G248" s="2">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
       <c r="H248" s="2">
-        <v>38.8</v>
+        <v>33.6</v>
       </c>
       <c r="I248" s="2">
-        <v>44.8</v>
+        <v>32.8</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>260</v>
@@ -6976,13 +6796,13 @@
         <v>256</v>
       </c>
       <c r="G249" s="2">
-        <v>33.6</v>
+        <v>8</v>
       </c>
       <c r="H249" s="2">
-        <v>32.8</v>
+        <v>38.4</v>
       </c>
       <c r="I249" s="2">
-        <v>28</v>
+        <v>20.8</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>260</v>
@@ -6993,13 +6813,13 @@
         <v>257</v>
       </c>
       <c r="G250" s="2">
+        <v>58.4</v>
+      </c>
+      <c r="H250" s="2">
         <v>69.2</v>
       </c>
-      <c r="H250" s="2">
+      <c r="I250" s="2">
         <v>68.8</v>
-      </c>
-      <c r="I250" s="2">
-        <v>28.8</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>260</v>
@@ -7010,13 +6830,13 @@
         <v>258</v>
       </c>
       <c r="G251" s="2">
-        <v>22</v>
+        <v>46.8</v>
       </c>
       <c r="H251" s="2">
-        <v>18.4</v>
+        <v>63.2</v>
       </c>
       <c r="I251" s="2">
-        <v>4.4</v>
+        <v>52.8</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>260</v>
@@ -7367,28 +7187,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>212.24</v>
+        <v>214.78</v>
       </c>
       <c r="C2" s="2">
-        <v>176.03</v>
+        <v>131.32</v>
       </c>
       <c r="D2" s="2">
-        <v>67.48999999999999</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2">
-        <v>28.76</v>
+        <v>19.46</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
       <c r="I2" s="2">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7396,28 +7216,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>543.05</v>
+        <v>2289.1</v>
       </c>
       <c r="C3" s="2">
-        <v>214.9</v>
+        <v>123.91</v>
       </c>
       <c r="D3" s="2">
-        <v>75.55</v>
+        <v>62.64</v>
       </c>
       <c r="E3" s="2">
-        <v>-10.8</v>
+        <v>8.33</v>
       </c>
       <c r="F3" s="2">
-        <v>98.97</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7425,54 +7245,54 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>264.6</v>
+        <v>520.4</v>
       </c>
       <c r="C4" s="2">
-        <v>110.13</v>
+        <v>188.89</v>
       </c>
       <c r="D4" s="2">
-        <v>89.41</v>
+        <v>31.85</v>
       </c>
       <c r="E4" s="2">
-        <v>15.53</v>
+        <v>-16.6</v>
       </c>
       <c r="F4" s="2">
-        <v>97.94</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>97.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>2414.9</v>
+        <v>1439.6</v>
       </c>
       <c r="C5" s="2">
-        <v>127.45</v>
+        <v>82.48</v>
       </c>
       <c r="D5" s="2">
-        <v>66.73999999999999</v>
+        <v>51.31</v>
       </c>
       <c r="E5" s="2">
-        <v>15.12</v>
+        <v>4.58</v>
       </c>
       <c r="F5" s="2">
-        <v>96.91</v>
+        <v>94.12</v>
       </c>
       <c r="G5" s="2">
-        <v>97.2</v>
+        <v>93.2</v>
       </c>
       <c r="H5" s="2">
-        <v>97.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I5" s="2">
         <v>97.2</v>
@@ -7480,118 +7300,118 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>2221.2</v>
+        <v>439.95</v>
       </c>
       <c r="C6" s="2">
-        <v>80.81999999999999</v>
+        <v>42.86</v>
       </c>
       <c r="D6" s="2">
-        <v>47.06</v>
+        <v>41.76</v>
       </c>
       <c r="E6" s="2">
-        <v>36.35</v>
+        <v>23.49</v>
       </c>
       <c r="F6" s="2">
-        <v>94.84999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="G6" s="2">
-        <v>96</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H6" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I6" s="2">
-        <v>95.2</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>1803.7</v>
+        <v>88.56</v>
       </c>
       <c r="C7" s="2">
-        <v>83.59999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="D7" s="2">
-        <v>62.39</v>
+        <v>33.86</v>
       </c>
       <c r="E7" s="2">
-        <v>23.71</v>
+        <v>-1.92</v>
       </c>
       <c r="F7" s="2">
-        <v>93.81</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2">
-        <v>98.8</v>
+        <v>94</v>
       </c>
       <c r="I7" s="2">
-        <v>97.59999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>627.15</v>
+        <v>235.2</v>
       </c>
       <c r="C8" s="2">
-        <v>93.83</v>
+        <v>89.11</v>
       </c>
       <c r="D8" s="2">
-        <v>49.79</v>
+        <v>39.63</v>
       </c>
       <c r="E8" s="2">
-        <v>17.72</v>
+        <v>-1.19</v>
       </c>
       <c r="F8" s="2">
-        <v>92.78</v>
+        <v>90.59</v>
       </c>
       <c r="G8" s="2">
-        <v>94.8</v>
+        <v>99.2</v>
       </c>
       <c r="H8" s="2">
-        <v>92.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>88.40000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>1253.1</v>
+        <v>290.95</v>
       </c>
       <c r="C9" s="2">
-        <v>86.79000000000001</v>
+        <v>55.71</v>
       </c>
       <c r="D9" s="2">
-        <v>60.17</v>
+        <v>31.98</v>
       </c>
       <c r="E9" s="2">
-        <v>13.08</v>
+        <v>18.33</v>
       </c>
       <c r="F9" s="2">
-        <v>91.75</v>
+        <v>89.41</v>
       </c>
       <c r="G9" s="2">
-        <v>99.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H9" s="2">
-        <v>99.2</v>
+        <v>92.8</v>
       </c>
       <c r="I9" s="2">
-        <v>99.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -7599,115 +7419,115 @@
         <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>1431.4</v>
+        <v>1724</v>
       </c>
       <c r="C10" s="2">
-        <v>85.08</v>
+        <v>81.28</v>
       </c>
       <c r="D10" s="2">
-        <v>46.58</v>
+        <v>28.66</v>
       </c>
       <c r="E10" s="2">
-        <v>6.47</v>
+        <v>0.06</v>
       </c>
       <c r="F10" s="2">
-        <v>89.69</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>90.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>97.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>288.15</v>
+        <v>397.8</v>
       </c>
       <c r="C11" s="2">
-        <v>52.25</v>
+        <v>82.75</v>
       </c>
       <c r="D11" s="2">
-        <v>37.98</v>
+        <v>25.21</v>
       </c>
       <c r="E11" s="2">
-        <v>17.35</v>
+        <v>-6.34</v>
       </c>
       <c r="F11" s="2">
-        <v>86.59999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="G11" s="2">
-        <v>92.8</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2">
-        <v>85.2</v>
+        <v>95.2</v>
       </c>
       <c r="I11" s="2">
-        <v>85.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1">
-        <v>408.85</v>
+        <v>228.38</v>
       </c>
       <c r="C12" s="2">
-        <v>91.03</v>
+        <v>80.41</v>
       </c>
       <c r="D12" s="2">
-        <v>38.31</v>
+        <v>20.6</v>
       </c>
       <c r="E12" s="2">
-        <v>-3.04</v>
+        <v>-3.58</v>
       </c>
       <c r="F12" s="2">
-        <v>85.56999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G12" s="2">
-        <v>95.2</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2">
-        <v>84.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>94.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1">
-        <v>272.4</v>
+        <v>267.1</v>
       </c>
       <c r="C13" s="2">
-        <v>58.98</v>
+        <v>53.45</v>
       </c>
       <c r="D13" s="2">
-        <v>43.91</v>
+        <v>31.4</v>
       </c>
       <c r="E13" s="2">
-        <v>9.06</v>
+        <v>4.31</v>
       </c>
       <c r="F13" s="2">
-        <v>84.54000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="G13" s="2">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H13" s="2">
         <v>87.59999999999999</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>87.2</v>
-      </c>
-      <c r="I13" s="2">
-        <v>89.2</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -7715,28 +7535,28 @@
         <v>26</v>
       </c>
       <c r="B14" s="1">
-        <v>344.75</v>
+        <v>3218.8</v>
       </c>
       <c r="C14" s="2">
-        <v>60.42</v>
+        <v>47.34</v>
       </c>
       <c r="D14" s="2">
-        <v>32.29</v>
+        <v>30.04</v>
       </c>
       <c r="E14" s="2">
-        <v>9.76</v>
+        <v>7.6</v>
       </c>
       <c r="F14" s="2">
-        <v>82.47</v>
+        <v>80</v>
       </c>
       <c r="G14" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2">
-        <v>90</v>
+        <v>81.2</v>
       </c>
       <c r="I14" s="2">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7790,7 +7610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -7832,28 +7652,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>212.24</v>
+        <v>214.78</v>
       </c>
       <c r="C2" s="2">
-        <v>176.03</v>
+        <v>131.32</v>
       </c>
       <c r="D2" s="2">
-        <v>67.48999999999999</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2">
-        <v>28.76</v>
+        <v>19.46</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
       <c r="I2" s="2">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7861,28 +7681,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>543.05</v>
+        <v>2289.1</v>
       </c>
       <c r="C3" s="2">
-        <v>214.9</v>
+        <v>123.91</v>
       </c>
       <c r="D3" s="2">
-        <v>75.55</v>
+        <v>62.64</v>
       </c>
       <c r="E3" s="2">
-        <v>-10.8</v>
+        <v>8.33</v>
       </c>
       <c r="F3" s="2">
-        <v>98.97</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="H3" s="2">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I3" s="2">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7890,28 +7710,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>264.6</v>
+        <v>520.4</v>
       </c>
       <c r="C4" s="2">
-        <v>110.13</v>
+        <v>188.89</v>
       </c>
       <c r="D4" s="2">
-        <v>89.41</v>
+        <v>31.85</v>
       </c>
       <c r="E4" s="2">
-        <v>15.53</v>
+        <v>-16.6</v>
       </c>
       <c r="F4" s="2">
-        <v>97.94</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>97.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7919,409 +7739,380 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>2414.9</v>
+        <v>588.95</v>
       </c>
       <c r="C5" s="2">
-        <v>127.45</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D5" s="2">
-        <v>66.73999999999999</v>
+        <v>36.92</v>
       </c>
       <c r="E5" s="2">
-        <v>15.12</v>
+        <v>33.25</v>
       </c>
       <c r="F5" s="2">
-        <v>96.91</v>
+        <v>96.47</v>
       </c>
       <c r="G5" s="2">
-        <v>97.2</v>
+        <v>88.8</v>
       </c>
       <c r="H5" s="2">
-        <v>97.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I5" s="2">
-        <v>97.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>263.6</v>
+        <v>1439.6</v>
       </c>
       <c r="C6" s="2">
-        <v>74.65000000000001</v>
+        <v>82.48</v>
       </c>
       <c r="D6" s="2">
-        <v>57.22</v>
+        <v>51.31</v>
       </c>
       <c r="E6" s="2">
-        <v>37.69</v>
+        <v>4.58</v>
       </c>
       <c r="F6" s="2">
-        <v>95.88</v>
+        <v>94.12</v>
       </c>
       <c r="G6" s="2">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="H6" s="2">
-        <v>88</v>
+        <v>90.8</v>
       </c>
       <c r="I6" s="2">
-        <v>79.2</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>2221.2</v>
+        <v>439.95</v>
       </c>
       <c r="C7" s="2">
-        <v>80.81999999999999</v>
+        <v>42.86</v>
       </c>
       <c r="D7" s="2">
-        <v>47.06</v>
+        <v>41.76</v>
       </c>
       <c r="E7" s="2">
-        <v>36.35</v>
+        <v>23.49</v>
       </c>
       <c r="F7" s="2">
-        <v>94.84999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="G7" s="2">
-        <v>96</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H7" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2">
-        <v>95.2</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>1803.7</v>
+        <v>88.56</v>
       </c>
       <c r="C8" s="2">
-        <v>83.59999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="D8" s="2">
-        <v>62.39</v>
+        <v>33.86</v>
       </c>
       <c r="E8" s="2">
-        <v>23.71</v>
+        <v>-1.92</v>
       </c>
       <c r="F8" s="2">
-        <v>93.81</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="H8" s="2">
-        <v>98.8</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2">
-        <v>97.59999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>627.15</v>
+        <v>235.2</v>
       </c>
       <c r="C9" s="2">
-        <v>93.83</v>
+        <v>89.11</v>
       </c>
       <c r="D9" s="2">
-        <v>49.79</v>
+        <v>39.63</v>
       </c>
       <c r="E9" s="2">
-        <v>17.72</v>
+        <v>-1.19</v>
       </c>
       <c r="F9" s="2">
-        <v>92.78</v>
+        <v>90.59</v>
       </c>
       <c r="G9" s="2">
-        <v>94.8</v>
+        <v>99.2</v>
       </c>
       <c r="H9" s="2">
-        <v>92.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>88.40000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1">
-        <v>1253.1</v>
+        <v>290.95</v>
       </c>
       <c r="C10" s="2">
-        <v>86.79000000000001</v>
+        <v>55.71</v>
       </c>
       <c r="D10" s="2">
-        <v>60.17</v>
+        <v>31.98</v>
       </c>
       <c r="E10" s="2">
-        <v>13.08</v>
+        <v>18.33</v>
       </c>
       <c r="F10" s="2">
-        <v>91.75</v>
+        <v>89.41</v>
       </c>
       <c r="G10" s="2">
-        <v>99.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>99.2</v>
+        <v>92.8</v>
       </c>
       <c r="I10" s="2">
-        <v>99.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1">
-        <v>623.85</v>
+        <v>1724</v>
       </c>
       <c r="C11" s="2">
-        <v>80.62</v>
+        <v>81.28</v>
       </c>
       <c r="D11" s="2">
-        <v>36.63</v>
+        <v>28.66</v>
       </c>
       <c r="E11" s="2">
-        <v>16.9</v>
+        <v>0.06</v>
       </c>
       <c r="F11" s="2">
-        <v>90.72</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G11" s="2">
-        <v>88</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H11" s="2">
-        <v>68</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I11" s="2">
-        <v>84</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1">
-        <v>1431.4</v>
+        <v>677.95</v>
       </c>
       <c r="C12" s="2">
-        <v>85.08</v>
+        <v>53.77</v>
       </c>
       <c r="D12" s="2">
-        <v>46.58</v>
+        <v>29.33</v>
       </c>
       <c r="E12" s="2">
-        <v>6.47</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F12" s="2">
-        <v>89.69</v>
+        <v>87.06</v>
       </c>
       <c r="G12" s="2">
-        <v>90.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H12" s="2">
-        <v>97.2</v>
+        <v>84</v>
       </c>
       <c r="I12" s="2">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1">
-        <v>1500.8</v>
+        <v>222.38</v>
       </c>
       <c r="C13" s="2">
-        <v>61</v>
+        <v>59.77</v>
       </c>
       <c r="D13" s="2">
-        <v>19.87</v>
+        <v>27.26</v>
       </c>
       <c r="E13" s="2">
-        <v>30.55</v>
+        <v>7.09</v>
       </c>
       <c r="F13" s="2">
-        <v>88.66</v>
+        <v>85.88</v>
       </c>
       <c r="G13" s="2">
-        <v>83.2</v>
+        <v>89.2</v>
       </c>
       <c r="H13" s="2">
-        <v>83.2</v>
+        <v>74.8</v>
       </c>
       <c r="I13" s="2">
-        <v>58</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>244.49</v>
+        <v>397.8</v>
       </c>
       <c r="C14" s="2">
-        <v>60.23</v>
+        <v>82.75</v>
       </c>
       <c r="D14" s="2">
-        <v>14.5</v>
+        <v>25.21</v>
       </c>
       <c r="E14" s="2">
-        <v>29.44</v>
+        <v>-6.34</v>
       </c>
       <c r="F14" s="2">
-        <v>87.63</v>
+        <v>83.53</v>
       </c>
       <c r="G14" s="2">
-        <v>89.2</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2">
-        <v>80.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I14" s="2">
-        <v>57.6</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>288.15</v>
+        <v>228.38</v>
       </c>
       <c r="C15" s="2">
-        <v>52.25</v>
+        <v>80.41</v>
       </c>
       <c r="D15" s="2">
-        <v>37.98</v>
+        <v>20.6</v>
       </c>
       <c r="E15" s="2">
-        <v>17.35</v>
+        <v>-3.58</v>
       </c>
       <c r="F15" s="2">
-        <v>86.59999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G15" s="2">
-        <v>92.8</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2">
-        <v>85.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>85.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>408.85</v>
+        <v>267.1</v>
       </c>
       <c r="C16" s="2">
-        <v>91.03</v>
+        <v>53.45</v>
       </c>
       <c r="D16" s="2">
-        <v>38.31</v>
+        <v>31.4</v>
       </c>
       <c r="E16" s="2">
-        <v>-3.04</v>
+        <v>4.31</v>
       </c>
       <c r="F16" s="2">
-        <v>85.56999999999999</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="G16" s="2">
-        <v>95.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H16" s="2">
-        <v>84.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I16" s="2">
-        <v>94.40000000000001</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>272.4</v>
+        <v>3218.8</v>
       </c>
       <c r="C17" s="2">
-        <v>58.98</v>
+        <v>47.34</v>
       </c>
       <c r="D17" s="2">
-        <v>43.91</v>
+        <v>30.04</v>
       </c>
       <c r="E17" s="2">
-        <v>9.06</v>
+        <v>7.6</v>
       </c>
       <c r="F17" s="2">
-        <v>84.54000000000001</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2">
-        <v>87.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2">
-        <v>87.2</v>
+        <v>81.2</v>
       </c>
       <c r="I17" s="2">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1">
-        <v>344.75</v>
-      </c>
-      <c r="C18" s="2">
-        <v>60.42</v>
-      </c>
-      <c r="D18" s="2">
-        <v>32.29</v>
-      </c>
-      <c r="E18" s="2">
-        <v>9.76</v>
-      </c>
-      <c r="F18" s="2">
-        <v>82.47</v>
-      </c>
-      <c r="G18" s="2">
-        <v>92</v>
-      </c>
-      <c r="H18" s="2">
-        <v>90</v>
-      </c>
-      <c r="I18" s="2">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8329,7 +8120,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8337,7 +8128,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8345,22 +8136,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -8396,13 +8187,13 @@
         <v>265</v>
       </c>
       <c r="B2" s="2">
-        <v>25.2</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2">
-        <v>26.4</v>
+        <v>20.8</v>
       </c>
       <c r="D2" s="2">
-        <v>24</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8410,13 +8201,13 @@
         <v>266</v>
       </c>
       <c r="B3" s="2">
-        <v>71.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D3" s="2">
-        <v>62.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8424,13 +8215,13 @@
         <v>267</v>
       </c>
       <c r="B4" s="2">
-        <v>57.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C4" s="2">
-        <v>66</v>
+        <v>70.8</v>
       </c>
       <c r="D4" s="2">
-        <v>59.2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8438,13 +8229,13 @@
         <v>268</v>
       </c>
       <c r="B5" s="2">
-        <v>75.2</v>
+        <v>57.2</v>
       </c>
       <c r="C5" s="2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2">
-        <v>56.8</v>
+        <v>58.8</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_250_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_250_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="269">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-17</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-17</t>
+    <t>Price_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-24</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-24</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-24</t>
   </si>
   <si>
     <t>RS_Score_2026-07-17</t>
@@ -43,759 +46,756 @@
     <t>RS_Score_2026-07-03</t>
   </si>
   <si>
-    <t>RS_Score_2026-06-26</t>
-  </si>
-  <si>
     <t>CUPID</t>
   </si>
   <si>
+    <t>DIACABS</t>
+  </si>
+  <si>
+    <t>STLTECH</t>
+  </si>
+  <si>
+    <t>THANGAMAYL</t>
+  </si>
+  <si>
+    <t>UTLSOLAR</t>
+  </si>
+  <si>
+    <t>BLUESTONE</t>
+  </si>
+  <si>
+    <t>SKYGOLD</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>JUSTDIAL</t>
+  </si>
+  <si>
+    <t>AZAD</t>
+  </si>
+  <si>
+    <t>WABAG</t>
+  </si>
+  <si>
+    <t>LOTUSDEV</t>
+  </si>
+  <si>
+    <t>UJJIVANSFB</t>
+  </si>
+  <si>
+    <t>LXCHEM</t>
+  </si>
+  <si>
+    <t>APOLLO</t>
+  </si>
+  <si>
+    <t>PFOCUS</t>
+  </si>
+  <si>
+    <t>SPARC</t>
+  </si>
+  <si>
+    <t>AEQUS</t>
+  </si>
+  <si>
+    <t>NEOGEN</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>SENCO</t>
+  </si>
+  <si>
+    <t>EMIL</t>
+  </si>
+  <si>
+    <t>SHRIPISTON</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
+  </si>
+  <si>
+    <t>EQUITASBNK</t>
+  </si>
+  <si>
+    <t>ELLEN</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>REFEX</t>
+  </si>
+  <si>
+    <t>BECTORFOOD</t>
+  </si>
+  <si>
+    <t>PNCINFRA</t>
+  </si>
+  <si>
+    <t>SOUTHBANK</t>
+  </si>
+  <si>
+    <t>ETHOSLTD</t>
+  </si>
+  <si>
+    <t>SAMHI</t>
+  </si>
+  <si>
+    <t>PCJEWELLER</t>
+  </si>
+  <si>
+    <t>FIEMIND</t>
+  </si>
+  <si>
+    <t>CRAMC</t>
+  </si>
+  <si>
+    <t>CCAVENUE</t>
+  </si>
+  <si>
+    <t>HAPPSTMNDS</t>
+  </si>
+  <si>
+    <t>NAZARA</t>
+  </si>
+  <si>
+    <t>QPOWER</t>
+  </si>
+  <si>
+    <t>KIRLOSBROS</t>
+  </si>
+  <si>
+    <t>FEDFINA</t>
+  </si>
+  <si>
+    <t>MIDHANI</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>RTNINDIA</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>BAJAJELEC</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>VOLTAMP</t>
+  </si>
+  <si>
+    <t>SUNTECK</t>
+  </si>
+  <si>
+    <t>GPPL</t>
+  </si>
+  <si>
+    <t>KANSAINER</t>
+  </si>
+  <si>
+    <t>ASHOKA</t>
+  </si>
+  <si>
+    <t>NFL</t>
+  </si>
+  <si>
+    <t>HEMIPROP</t>
+  </si>
+  <si>
+    <t>KNRCON</t>
+  </si>
+  <si>
+    <t>FINPIPE</t>
+  </si>
+  <si>
+    <t>SANDUMA</t>
+  </si>
+  <si>
+    <t>JKLAKSHMI</t>
+  </si>
+  <si>
+    <t>KITEX</t>
+  </si>
+  <si>
+    <t>CAMPUS</t>
+  </si>
+  <si>
+    <t>RALLIS</t>
+  </si>
+  <si>
+    <t>MOIL</t>
+  </si>
+  <si>
+    <t>JSLL</t>
+  </si>
+  <si>
+    <t>MEDPLUS</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>MTARTECH</t>
+  </si>
+  <si>
+    <t>PARAS</t>
+  </si>
+  <si>
+    <t>THOMASCOOK</t>
+  </si>
+  <si>
+    <t>HGINFRA</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>TDPOWERSYS</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
     <t>BALAMINES</t>
   </si>
   <si>
-    <t>STLTECH</t>
+    <t>BBOX</t>
+  </si>
+  <si>
+    <t>CERA</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>NETWORK18</t>
+  </si>
+  <si>
+    <t>THYROCARE</t>
+  </si>
+  <si>
+    <t>PRAJIND</t>
+  </si>
+  <si>
+    <t>JAYNECOIND</t>
+  </si>
+  <si>
+    <t>MARKSANS</t>
+  </si>
+  <si>
+    <t>VIYASH</t>
+  </si>
+  <si>
+    <t>SFL</t>
+  </si>
+  <si>
+    <t>EDELWEISS</t>
+  </si>
+  <si>
+    <t>ASHAPURMIN</t>
+  </si>
+  <si>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>RELIGARE</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>BORORENEW</t>
+  </si>
+  <si>
+    <t>TIINDIA</t>
+  </si>
+  <si>
+    <t>V2RETAIL</t>
+  </si>
+  <si>
+    <t>SKIPPER</t>
+  </si>
+  <si>
+    <t>SHAILY</t>
+  </si>
+  <si>
+    <t>VIKRAMSOLR</t>
+  </si>
+  <si>
+    <t>WEBELSOLAR</t>
+  </si>
+  <si>
+    <t>SHAKTIPUMP</t>
+  </si>
+  <si>
+    <t>LLOYDSENGG</t>
+  </si>
+  <si>
+    <t>IIFLCAPS</t>
+  </si>
+  <si>
+    <t>SWSOLAR</t>
+  </si>
+  <si>
+    <t>KPIGREEN</t>
+  </si>
+  <si>
+    <t>WEWORK</t>
+  </si>
+  <si>
+    <t>AVANTIFEED</t>
+  </si>
+  <si>
+    <t>KTKBANK</t>
+  </si>
+  <si>
+    <t>AXISCADES</t>
+  </si>
+  <si>
+    <t>APLLTD</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>ARVIND</t>
+  </si>
+  <si>
+    <t>RBA</t>
+  </si>
+  <si>
+    <t>MANORAMA</t>
+  </si>
+  <si>
+    <t>ALKYLAMINE</t>
+  </si>
+  <si>
+    <t>TRANSRAILL</t>
+  </si>
+  <si>
+    <t>STAR</t>
+  </si>
+  <si>
+    <t>SUPRIYA</t>
+  </si>
+  <si>
+    <t>POWERMECH</t>
+  </si>
+  <si>
+    <t>GOKEX</t>
+  </si>
+  <si>
+    <t>GRWRHITECH</t>
+  </si>
+  <si>
+    <t>TIMETECHNO</t>
+  </si>
+  <si>
+    <t>JSFB</t>
+  </si>
+  <si>
+    <t>KRN</t>
+  </si>
+  <si>
+    <t>IXIGO</t>
+  </si>
+  <si>
+    <t>RENUKA</t>
+  </si>
+  <si>
+    <t>TEXRAIL</t>
+  </si>
+  <si>
+    <t>WAAREERTL</t>
+  </si>
+  <si>
+    <t>AETHER</t>
+  </si>
+  <si>
+    <t>BALUFORGE</t>
+  </si>
+  <si>
+    <t>SURYAROSNI</t>
+  </si>
+  <si>
+    <t>OSWALPUMPS</t>
+  </si>
+  <si>
+    <t>TANLA</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>LUMAXTECH</t>
+  </si>
+  <si>
+    <t>TIPSMUSIC</t>
+  </si>
+  <si>
+    <t>SUDEEPPHRM</t>
+  </si>
+  <si>
+    <t>KSB</t>
+  </si>
+  <si>
+    <t>AARTIPHARM</t>
+  </si>
+  <si>
+    <t>BLACKBUCK</t>
+  </si>
+  <si>
+    <t>ATLANTAELE</t>
+  </si>
+  <si>
+    <t>LLOYDSENT</t>
+  </si>
+  <si>
+    <t>IMFA</t>
+  </si>
+  <si>
+    <t>DYNAMATECH</t>
+  </si>
+  <si>
+    <t>SHARDACROP</t>
+  </si>
+  <si>
+    <t>GHCL</t>
+  </si>
+  <si>
+    <t>PRIVISCL</t>
+  </si>
+  <si>
+    <t>RTNPOWER</t>
+  </si>
+  <si>
+    <t>PRICOLLTD</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>GMRP&amp;UI</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>GNFC</t>
+  </si>
+  <si>
+    <t>JAMNAAUTO</t>
+  </si>
+  <si>
+    <t>ICIL</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>PICCADIL</t>
+  </si>
+  <si>
+    <t>AURIONPRO</t>
+  </si>
+  <si>
+    <t>ZAGGLE</t>
+  </si>
+  <si>
+    <t>ELECTCAST</t>
+  </si>
+  <si>
+    <t>INOXGREEN</t>
+  </si>
+  <si>
+    <t>BANCOINDIA</t>
+  </si>
+  <si>
+    <t>PNGJL</t>
+  </si>
+  <si>
+    <t>IFBIND</t>
+  </si>
+  <si>
+    <t>WELENT</t>
+  </si>
+  <si>
+    <t>TSFINV</t>
+  </si>
+  <si>
+    <t>SMLMAH</t>
+  </si>
+  <si>
+    <t>TVSSCS</t>
+  </si>
+  <si>
+    <t>SUDARSCHEM</t>
+  </si>
+  <si>
+    <t>EIEL</t>
   </si>
   <si>
     <t>OPTIEMUS</t>
   </si>
   <si>
-    <t>JUSTDIAL</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
+    <t>ALOKINDS</t>
+  </si>
+  <si>
+    <t>JYOTHYLAB</t>
+  </si>
+  <si>
+    <t>VMART</t>
+  </si>
+  <si>
+    <t>AWFIS</t>
+  </si>
+  <si>
+    <t>VIPIND</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>ARVINDFASN</t>
+  </si>
+  <si>
+    <t>PGIL</t>
+  </si>
+  <si>
+    <t>GSFC</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>JKPAPER</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>INDIGOPNTS</t>
+  </si>
+  <si>
+    <t>GOKULAGRO</t>
+  </si>
+  <si>
+    <t>EUREKAFORB</t>
+  </si>
+  <si>
+    <t>RAYMONDLSL</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>ADVENZYMES</t>
+  </si>
+  <si>
+    <t>ALIVUS</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>EPL</t>
+  </si>
+  <si>
+    <t>KSCL</t>
+  </si>
+  <si>
+    <t>MANYAVAR</t>
+  </si>
+  <si>
+    <t>REDTAPE</t>
+  </si>
+  <si>
+    <t>MAHSEAMLES</t>
+  </si>
+  <si>
+    <t>IONEXCHANG</t>
+  </si>
+  <si>
+    <t>SAATVIKGL</t>
+  </si>
+  <si>
+    <t>SANOFICONR</t>
+  </si>
+  <si>
+    <t>STYRENIX</t>
+  </si>
+  <si>
+    <t>VAIBHAVGBL</t>
+  </si>
+  <si>
+    <t>GODREJAGRO</t>
+  </si>
+  <si>
+    <t>ASKAUTOLTD</t>
+  </si>
+  <si>
+    <t>AKUMS</t>
+  </si>
+  <si>
+    <t>DATAMATICS</t>
+  </si>
+  <si>
+    <t>AVL</t>
+  </si>
+  <si>
+    <t>TARC</t>
+  </si>
+  <si>
+    <t>METROPOLIS</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>RATNAMANI</t>
+  </si>
+  <si>
+    <t>AGARWALEYE</t>
+  </si>
+  <si>
+    <t>WAKEFIT</t>
+  </si>
+  <si>
+    <t>JLHL</t>
+  </si>
+  <si>
+    <t>MASTEK</t>
+  </si>
+  <si>
+    <t>CELLO</t>
+  </si>
+  <si>
+    <t>DBREALTY</t>
+  </si>
+  <si>
+    <t>STYL</t>
+  </si>
+  <si>
+    <t>HERITGFOOD</t>
+  </si>
+  <si>
+    <t>CSBBANK</t>
+  </si>
+  <si>
+    <t>INDIAGLYCO</t>
+  </si>
+  <si>
+    <t>SHAREINDIA</t>
+  </si>
+  <si>
+    <t>VGUARD</t>
+  </si>
+  <si>
+    <t>CRIZAC</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
   </si>
   <si>
     <t>RELAXO</t>
   </si>
   <si>
-    <t>LLOYDSENGG</t>
-  </si>
-  <si>
-    <t>SPARC</t>
-  </si>
-  <si>
-    <t>QUESS</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>WEWORK</t>
-  </si>
-  <si>
-    <t>DIACABS</t>
-  </si>
-  <si>
-    <t>NEOGEN</t>
-  </si>
-  <si>
-    <t>APOLLO</t>
-  </si>
-  <si>
-    <t>AEQUS</t>
-  </si>
-  <si>
-    <t>MARKSANS</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>SUDEEPPHRM</t>
-  </si>
-  <si>
-    <t>SFL</t>
-  </si>
-  <si>
-    <t>INDIAGLYCO</t>
-  </si>
-  <si>
-    <t>JLHL</t>
-  </si>
-  <si>
-    <t>PARAS</t>
-  </si>
-  <si>
-    <t>AZAD</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>LLOYDSENT</t>
-  </si>
-  <si>
-    <t>CCAVENUE</t>
-  </si>
-  <si>
-    <t>TIMETECHNO</t>
+    <t>PURVA</t>
+  </si>
+  <si>
+    <t>ANUP</t>
   </si>
   <si>
     <t>AARTIDRUGS</t>
   </si>
   <si>
-    <t>BORORENEW</t>
-  </si>
-  <si>
-    <t>EQUITASBNK</t>
-  </si>
-  <si>
-    <t>MSTCLTD</t>
-  </si>
-  <si>
-    <t>ATLANTAELE</t>
-  </si>
-  <si>
-    <t>DATAMATICS</t>
-  </si>
-  <si>
-    <t>BBOX</t>
-  </si>
-  <si>
-    <t>PCJEWELLER</t>
-  </si>
-  <si>
-    <t>APLLTD</t>
-  </si>
-  <si>
-    <t>KTKBANK</t>
-  </si>
-  <si>
-    <t>SUPRIYA</t>
-  </si>
-  <si>
-    <t>ALIVUS</t>
-  </si>
-  <si>
-    <t>ROUTE</t>
-  </si>
-  <si>
-    <t>ASHAPURMIN</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>WAAREERTL</t>
-  </si>
-  <si>
-    <t>METROPOLIS</t>
-  </si>
-  <si>
-    <t>HAPPSTMNDS</t>
-  </si>
-  <si>
-    <t>SOUTHBANK</t>
-  </si>
-  <si>
-    <t>SWSOLAR</t>
-  </si>
-  <si>
-    <t>REDTAPE</t>
-  </si>
-  <si>
-    <t>PNGJL</t>
-  </si>
-  <si>
-    <t>SMLMAH</t>
-  </si>
-  <si>
-    <t>INOXGREEN</t>
-  </si>
-  <si>
-    <t>DBREALTY</t>
-  </si>
-  <si>
-    <t>BLACKBUCK</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>TDPOWERSYS</t>
-  </si>
-  <si>
-    <t>PRAJIND</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>BECTORFOOD</t>
-  </si>
-  <si>
-    <t>CAMPUS</t>
-  </si>
-  <si>
-    <t>GNFC</t>
-  </si>
-  <si>
-    <t>GODREJAGRO</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>HGINFRA</t>
-  </si>
-  <si>
-    <t>EDELWEISS</t>
-  </si>
-  <si>
-    <t>HEMIPROP</t>
-  </si>
-  <si>
-    <t>RALLIS</t>
-  </si>
-  <si>
-    <t>RTNPOWER</t>
+    <t>MAHSCOOTER</t>
+  </si>
+  <si>
+    <t>PRSMJOHNSN</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>SMARTWORKS</t>
+  </si>
+  <si>
+    <t>DBL</t>
+  </si>
+  <si>
+    <t>VARROC</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>STARCEMENT</t>
+  </si>
+  <si>
+    <t>BIRLACORPN</t>
+  </si>
+  <si>
+    <t>ORIENTCEM</t>
+  </si>
+  <si>
+    <t>AHLUCONT</t>
+  </si>
+  <si>
+    <t>ORKLAINDIA</t>
+  </si>
+  <si>
+    <t>INDIASHLTR</t>
+  </si>
+  <si>
+    <t>CENTURYPLY</t>
+  </si>
+  <si>
+    <t>JAIBALAJI</t>
+  </si>
+  <si>
+    <t>SUBROS</t>
+  </si>
+  <si>
+    <t>WESTLIFE</t>
   </si>
   <si>
     <t>CAPILLARY</t>
   </si>
   <si>
-    <t>SUNTECK</t>
-  </si>
-  <si>
-    <t>VGUARD</t>
-  </si>
-  <si>
-    <t>AWFIS</t>
-  </si>
-  <si>
-    <t>BALUFORGE</t>
-  </si>
-  <si>
-    <t>BAJAJELEC</t>
-  </si>
-  <si>
-    <t>AVANTIFEED</t>
-  </si>
-  <si>
-    <t>RBA</t>
-  </si>
-  <si>
-    <t>NFL</t>
-  </si>
-  <si>
-    <t>KNRCON</t>
-  </si>
-  <si>
-    <t>RENUKA</t>
-  </si>
-  <si>
-    <t>CELLO</t>
-  </si>
-  <si>
-    <t>ALOKINDS</t>
-  </si>
-  <si>
-    <t>FINPIPE</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>SHARDACROP</t>
-  </si>
-  <si>
-    <t>NETWORK18</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>THOMASCOOK</t>
-  </si>
-  <si>
-    <t>THANGAMAYL</t>
-  </si>
-  <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>JSLL</t>
-  </si>
-  <si>
-    <t>SKYGOLD</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>CERA</t>
-  </si>
-  <si>
-    <t>RAIN</t>
-  </si>
-  <si>
-    <t>THYROCARE</t>
-  </si>
-  <si>
-    <t>JAYNECOIND</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>MIDHANI</t>
-  </si>
-  <si>
-    <t>VOLTAMP</t>
-  </si>
-  <si>
-    <t>UJJIVANSFB</t>
-  </si>
-  <si>
-    <t>RELIGARE</t>
-  </si>
-  <si>
-    <t>TMB</t>
-  </si>
-  <si>
-    <t>TIINDIA</t>
-  </si>
-  <si>
-    <t>V2RETAIL</t>
-  </si>
-  <si>
-    <t>SKIPPER</t>
-  </si>
-  <si>
-    <t>SHAILY</t>
-  </si>
-  <si>
-    <t>VIKRAMSOLR</t>
-  </si>
-  <si>
-    <t>WEBELSOLAR</t>
-  </si>
-  <si>
-    <t>WABAG</t>
-  </si>
-  <si>
-    <t>SHAKTIPUMP</t>
-  </si>
-  <si>
-    <t>BLUESTONE</t>
-  </si>
-  <si>
-    <t>IIFLCAPS</t>
-  </si>
-  <si>
-    <t>KPIGREEN</t>
-  </si>
-  <si>
-    <t>NAZARA</t>
-  </si>
-  <si>
-    <t>QPOWER</t>
-  </si>
-  <si>
-    <t>AXISCADES</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
-    <t>KITEX</t>
-  </si>
-  <si>
-    <t>ARVIND</t>
-  </si>
-  <si>
-    <t>SENCO</t>
-  </si>
-  <si>
-    <t>JKLAKSHMI</t>
-  </si>
-  <si>
-    <t>MANORAMA</t>
-  </si>
-  <si>
-    <t>ALKYLAMINE</t>
-  </si>
-  <si>
-    <t>TRANSRAILL</t>
-  </si>
-  <si>
-    <t>STAR</t>
-  </si>
-  <si>
-    <t>POWERMECH</t>
-  </si>
-  <si>
-    <t>GOKEX</t>
-  </si>
-  <si>
-    <t>GRWRHITECH</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>JSFB</t>
-  </si>
-  <si>
-    <t>KRN</t>
-  </si>
-  <si>
-    <t>IXIGO</t>
-  </si>
-  <si>
-    <t>TEXRAIL</t>
-  </si>
-  <si>
-    <t>REFEX</t>
-  </si>
-  <si>
-    <t>AETHER</t>
-  </si>
-  <si>
-    <t>SANDUMA</t>
-  </si>
-  <si>
-    <t>UTLSOLAR</t>
-  </si>
-  <si>
-    <t>SURYAROSNI</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>OSWALPUMPS</t>
-  </si>
-  <si>
-    <t>TANLA</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>MOIL</t>
-  </si>
-  <si>
-    <t>LUMAXTECH</t>
-  </si>
-  <si>
-    <t>PFOCUS</t>
-  </si>
-  <si>
-    <t>TIPSMUSIC</t>
-  </si>
-  <si>
-    <t>GPPL</t>
-  </si>
-  <si>
-    <t>KIRLOSBROS</t>
-  </si>
-  <si>
-    <t>KSB</t>
-  </si>
-  <si>
-    <t>AARTIPHARM</t>
-  </si>
-  <si>
-    <t>SAMHI</t>
-  </si>
-  <si>
-    <t>IMFA</t>
-  </si>
-  <si>
-    <t>DYNAMATECH</t>
-  </si>
-  <si>
-    <t>GHCL</t>
-  </si>
-  <si>
-    <t>PRIVISCL</t>
-  </si>
-  <si>
-    <t>PRICOLLTD</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>GMRP&amp;UI</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>JAMNAAUTO</t>
-  </si>
-  <si>
-    <t>ICIL</t>
-  </si>
-  <si>
-    <t>RTNINDIA</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>PICCADIL</t>
-  </si>
-  <si>
-    <t>AURIONPRO</t>
-  </si>
-  <si>
-    <t>ZAGGLE</t>
-  </si>
-  <si>
-    <t>ELECTCAST</t>
-  </si>
-  <si>
-    <t>BANCOINDIA</t>
-  </si>
-  <si>
-    <t>IFBIND</t>
-  </si>
-  <si>
-    <t>FIEMIND</t>
-  </si>
-  <si>
-    <t>LOTUSDEV</t>
-  </si>
-  <si>
-    <t>WELENT</t>
-  </si>
-  <si>
-    <t>TSFINV</t>
-  </si>
-  <si>
-    <t>LXCHEM</t>
-  </si>
-  <si>
-    <t>TVSSCS</t>
-  </si>
-  <si>
-    <t>SUDARSCHEM</t>
-  </si>
-  <si>
-    <t>ASHOKA</t>
-  </si>
-  <si>
-    <t>EIEL</t>
-  </si>
-  <si>
-    <t>JYOTHYLAB</t>
-  </si>
-  <si>
-    <t>VMART</t>
-  </si>
-  <si>
-    <t>VIPIND</t>
-  </si>
-  <si>
-    <t>FEDFINA</t>
-  </si>
-  <si>
-    <t>ARVINDFASN</t>
-  </si>
-  <si>
-    <t>PGIL</t>
-  </si>
-  <si>
-    <t>GSFC</t>
-  </si>
-  <si>
-    <t>SHRIPISTON</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>JKPAPER</t>
-  </si>
-  <si>
-    <t>SAFARI</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>INDIGOPNTS</t>
-  </si>
-  <si>
-    <t>GOKULAGRO</t>
-  </si>
-  <si>
-    <t>EUREKAFORB</t>
-  </si>
-  <si>
-    <t>RAYMONDLSL</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>ADVENZYMES</t>
-  </si>
-  <si>
-    <t>EPL</t>
-  </si>
-  <si>
-    <t>KSCL</t>
-  </si>
-  <si>
-    <t>MANYAVAR</t>
-  </si>
-  <si>
-    <t>MEDPLUS</t>
-  </si>
-  <si>
-    <t>CRAMC</t>
-  </si>
-  <si>
-    <t>MAHSEAMLES</t>
-  </si>
-  <si>
-    <t>IONEXCHANG</t>
-  </si>
-  <si>
-    <t>EMIL</t>
-  </si>
-  <si>
-    <t>SAATVIKGL</t>
-  </si>
-  <si>
-    <t>SANOFICONR</t>
-  </si>
-  <si>
-    <t>STYRENIX</t>
-  </si>
-  <si>
-    <t>VAIBHAVGBL</t>
-  </si>
-  <si>
-    <t>PNCINFRA</t>
-  </si>
-  <si>
-    <t>ASKAUTOLTD</t>
-  </si>
-  <si>
-    <t>AKUMS</t>
-  </si>
-  <si>
-    <t>AVL</t>
-  </si>
-  <si>
-    <t>TARC</t>
-  </si>
-  <si>
-    <t>ETHOSLTD</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>RATNAMANI</t>
-  </si>
-  <si>
-    <t>AGARWALEYE</t>
-  </si>
-  <si>
-    <t>WAKEFIT</t>
-  </si>
-  <si>
-    <t>MASTEK</t>
-  </si>
-  <si>
-    <t>KANSAINER</t>
-  </si>
-  <si>
-    <t>STYL</t>
-  </si>
-  <si>
-    <t>HERITGFOOD</t>
-  </si>
-  <si>
-    <t>CSBBANK</t>
-  </si>
-  <si>
-    <t>SHAREINDIA</t>
-  </si>
-  <si>
-    <t>CRIZAC</t>
-  </si>
-  <si>
-    <t>GMMPFAUDLR</t>
-  </si>
-  <si>
-    <t>PURVA</t>
-  </si>
-  <si>
-    <t>ANUP</t>
-  </si>
-  <si>
-    <t>MAHSCOOTER</t>
-  </si>
-  <si>
-    <t>PRSMJOHNSN</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>SMARTWORKS</t>
-  </si>
-  <si>
-    <t>DBL</t>
-  </si>
-  <si>
-    <t>VARROC</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>STARCEMENT</t>
-  </si>
-  <si>
-    <t>ELLEN</t>
-  </si>
-  <si>
-    <t>BIRLACORPN</t>
-  </si>
-  <si>
-    <t>ORIENTCEM</t>
-  </si>
-  <si>
-    <t>AHLUCONT</t>
-  </si>
-  <si>
-    <t>ORKLAINDIA</t>
-  </si>
-  <si>
-    <t>INDIASHLTR</t>
-  </si>
-  <si>
-    <t>CENTURYPLY</t>
-  </si>
-  <si>
-    <t>JAIBALAJI</t>
-  </si>
-  <si>
-    <t>SUBROS</t>
-  </si>
-  <si>
-    <t>WESTLIFE</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -814,6 +814,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
     <t>2026-07-17</t>
   </si>
   <si>
@@ -821,9 +824,6 @@
   </si>
   <si>
     <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
   </si>
 </sst>
 </file>
@@ -1322,16 +1322,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>214.78</v>
+        <v>213.43</v>
       </c>
       <c r="C2" s="2">
-        <v>131.32</v>
+        <v>169.99</v>
       </c>
       <c r="D2" s="2">
-        <v>64</v>
+        <v>76.62</v>
       </c>
       <c r="E2" s="2">
-        <v>19.46</v>
+        <v>13.29</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -1340,7 +1340,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>99.59999999999999</v>
@@ -1354,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>2289.1</v>
+        <v>295.15</v>
       </c>
       <c r="C3" s="2">
-        <v>123.91</v>
+        <v>135.22</v>
       </c>
       <c r="D3" s="2">
-        <v>62.64</v>
+        <v>53.87</v>
       </c>
       <c r="E3" s="2">
-        <v>8.33</v>
+        <v>41.53</v>
       </c>
       <c r="F3" s="2">
-        <v>98.81999999999999</v>
+        <v>98.55</v>
       </c>
       <c r="G3" s="2">
-        <v>98.8</v>
+        <v>90</v>
       </c>
       <c r="H3" s="2">
-        <v>97.2</v>
+        <v>89.2</v>
       </c>
       <c r="I3" s="2">
-        <v>97.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>260</v>
@@ -1386,25 +1386,25 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>520.4</v>
+        <v>564.15</v>
       </c>
       <c r="C4" s="2">
-        <v>188.89</v>
+        <v>220.25</v>
       </c>
       <c r="D4" s="2">
-        <v>31.85</v>
+        <v>33.72</v>
       </c>
       <c r="E4" s="2">
-        <v>-16.6</v>
+        <v>-9.67</v>
       </c>
       <c r="F4" s="2">
-        <v>97.65000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="H4" s="2">
         <v>99.59999999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>100</v>
       </c>
       <c r="I4" s="2">
         <v>100</v>
@@ -1418,28 +1418,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>588.95</v>
+        <v>6906.5</v>
       </c>
       <c r="C5" s="2">
-        <v>64.76000000000001</v>
+        <v>98.16</v>
       </c>
       <c r="D5" s="2">
-        <v>36.92</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>33.25</v>
+        <v>17.88</v>
       </c>
       <c r="F5" s="2">
-        <v>96.47</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>88.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H5" s="2">
-        <v>84.8</v>
+        <v>95.2</v>
       </c>
       <c r="I5" s="2">
-        <v>75.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>260</v>
@@ -1450,28 +1450,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>767.3</v>
+        <v>383.8</v>
       </c>
       <c r="C6" s="2">
-        <v>42.46</v>
+        <v>106.07</v>
       </c>
       <c r="D6" s="2">
-        <v>42.67</v>
+        <v>45.63</v>
       </c>
       <c r="E6" s="2">
-        <v>39.74</v>
+        <v>24.71</v>
       </c>
       <c r="F6" s="2">
-        <v>95.29000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="G6" s="2">
-        <v>44</v>
+        <v>97.2</v>
       </c>
       <c r="H6" s="2">
-        <v>32</v>
+        <v>96.8</v>
       </c>
       <c r="I6" s="2">
-        <v>22</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>260</v>
@@ -1482,28 +1482,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>1439.6</v>
+        <v>772.4</v>
       </c>
       <c r="C7" s="2">
-        <v>82.48</v>
+        <v>44.77</v>
       </c>
       <c r="D7" s="2">
-        <v>51.31</v>
+        <v>66.39</v>
       </c>
       <c r="E7" s="2">
-        <v>4.58</v>
+        <v>43.45</v>
       </c>
       <c r="F7" s="2">
-        <v>94.12</v>
+        <v>92.75</v>
       </c>
       <c r="G7" s="2">
-        <v>93.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H7" s="2">
-        <v>90.8</v>
+        <v>73.2</v>
       </c>
       <c r="I7" s="2">
-        <v>97.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>260</v>
@@ -1514,28 +1514,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>439.95</v>
+        <v>653.7</v>
       </c>
       <c r="C8" s="2">
-        <v>42.86</v>
+        <v>93.09</v>
       </c>
       <c r="D8" s="2">
-        <v>41.76</v>
+        <v>47.75</v>
       </c>
       <c r="E8" s="2">
-        <v>23.49</v>
+        <v>27.65</v>
       </c>
       <c r="F8" s="2">
-        <v>92.94</v>
+        <v>91.3</v>
       </c>
       <c r="G8" s="2">
-        <v>80.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H8" s="2">
-        <v>82</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>87.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>260</v>
@@ -1546,28 +1546,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>88.56</v>
+        <v>246.32</v>
       </c>
       <c r="C9" s="2">
-        <v>97.11</v>
+        <v>83.14</v>
       </c>
       <c r="D9" s="2">
-        <v>33.86</v>
+        <v>53.49</v>
       </c>
       <c r="E9" s="2">
-        <v>-1.92</v>
+        <v>17.54</v>
       </c>
       <c r="F9" s="2">
-        <v>91.76000000000001</v>
+        <v>89.86</v>
       </c>
       <c r="G9" s="2">
-        <v>98</v>
+        <v>95.2</v>
       </c>
       <c r="H9" s="2">
-        <v>94</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>260</v>
@@ -1578,28 +1578,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>235.2</v>
+        <v>1520.2</v>
       </c>
       <c r="C10" s="2">
-        <v>89.11</v>
+        <v>102.1</v>
       </c>
       <c r="D10" s="2">
-        <v>39.63</v>
+        <v>52.42</v>
       </c>
       <c r="E10" s="2">
-        <v>-1.19</v>
+        <v>7.09</v>
       </c>
       <c r="F10" s="2">
-        <v>90.59</v>
+        <v>88.41</v>
       </c>
       <c r="G10" s="2">
-        <v>99.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H10" s="2">
-        <v>97.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I10" s="2">
-        <v>95.2</v>
+        <v>90.8</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>260</v>
@@ -1610,28 +1610,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>290.95</v>
+        <v>1813.4</v>
       </c>
       <c r="C11" s="2">
-        <v>55.71</v>
+        <v>88.02</v>
       </c>
       <c r="D11" s="2">
-        <v>31.98</v>
+        <v>66.8</v>
       </c>
       <c r="E11" s="2">
-        <v>18.33</v>
+        <v>4.98</v>
       </c>
       <c r="F11" s="2">
-        <v>89.41</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G11" s="2">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="H11" s="2">
-        <v>92.8</v>
+        <v>97.2</v>
       </c>
       <c r="I11" s="2">
-        <v>85.2</v>
+        <v>98.8</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>260</v>
@@ -1642,28 +1642,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1724</v>
+        <v>728.95</v>
       </c>
       <c r="C12" s="2">
-        <v>81.28</v>
+        <v>42.25</v>
       </c>
       <c r="D12" s="2">
-        <v>28.66</v>
+        <v>40.68</v>
       </c>
       <c r="E12" s="2">
-        <v>0.06</v>
+        <v>38.69</v>
       </c>
       <c r="F12" s="2">
-        <v>88.23999999999999</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="G12" s="2">
-        <v>92.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2">
-        <v>95.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="I12" s="2">
-        <v>96.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>260</v>
@@ -1674,28 +1674,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>677.95</v>
+        <v>2439</v>
       </c>
       <c r="C13" s="2">
-        <v>53.77</v>
+        <v>62.46</v>
       </c>
       <c r="D13" s="2">
-        <v>29.33</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2">
-        <v>9.369999999999999</v>
+        <v>22.93</v>
       </c>
       <c r="F13" s="2">
-        <v>87.06</v>
+        <v>84.06</v>
       </c>
       <c r="G13" s="2">
-        <v>88.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="H13" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I13" s="2">
-        <v>56</v>
+        <v>42.4</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>260</v>
@@ -1706,28 +1706,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>222.38</v>
+        <v>2041.2</v>
       </c>
       <c r="C14" s="2">
-        <v>59.77</v>
+        <v>66.33</v>
       </c>
       <c r="D14" s="2">
-        <v>27.26</v>
+        <v>48.7</v>
       </c>
       <c r="E14" s="2">
-        <v>7.09</v>
+        <v>2.41</v>
       </c>
       <c r="F14" s="2">
-        <v>85.88</v>
+        <v>82.61</v>
       </c>
       <c r="G14" s="2">
         <v>89.2</v>
       </c>
       <c r="H14" s="2">
-        <v>74.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I14" s="2">
-        <v>86.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>260</v>
@@ -1738,28 +1738,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>2175.6</v>
+        <v>180.39</v>
       </c>
       <c r="C15" s="2">
-        <v>46.09</v>
+        <v>50.32</v>
       </c>
       <c r="D15" s="2">
-        <v>24.9</v>
+        <v>30.41</v>
       </c>
       <c r="E15" s="2">
-        <v>13.61</v>
+        <v>18.43</v>
       </c>
       <c r="F15" s="2">
-        <v>84.70999999999999</v>
+        <v>81.16</v>
       </c>
       <c r="G15" s="2">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="I15" s="2">
-        <v>80.8</v>
+        <v>46.4</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>260</v>
@@ -1770,28 +1770,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>397.8</v>
+        <v>70.72</v>
       </c>
       <c r="C16" s="2">
-        <v>82.75</v>
+        <v>37.96</v>
       </c>
       <c r="D16" s="2">
-        <v>25.21</v>
+        <v>30.6</v>
       </c>
       <c r="E16" s="2">
-        <v>-6.34</v>
+        <v>24.27</v>
       </c>
       <c r="F16" s="2">
-        <v>83.53</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="G16" s="2">
-        <v>90</v>
+        <v>75.2</v>
       </c>
       <c r="H16" s="2">
-        <v>95.2</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2">
-        <v>84.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>260</v>
@@ -1802,28 +1802,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>228.38</v>
+        <v>182.28</v>
       </c>
       <c r="C17" s="2">
-        <v>80.41</v>
+        <v>58.48</v>
       </c>
       <c r="D17" s="2">
-        <v>20.6</v>
+        <v>20.85</v>
       </c>
       <c r="E17" s="2">
-        <v>-3.58</v>
+        <v>18.43</v>
       </c>
       <c r="F17" s="2">
-        <v>82.34999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="G17" s="2">
-        <v>94</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H17" s="2">
-        <v>92.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="I17" s="2">
-        <v>92.40000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>260</v>
@@ -1834,28 +1834,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>267.1</v>
+        <v>394.3</v>
       </c>
       <c r="C18" s="2">
-        <v>53.45</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D18" s="2">
-        <v>31.4</v>
+        <v>26.78</v>
       </c>
       <c r="E18" s="2">
-        <v>4.31</v>
+        <v>-3.16</v>
       </c>
       <c r="F18" s="2">
-        <v>81.18000000000001</v>
+        <v>76.81</v>
       </c>
       <c r="G18" s="2">
-        <v>89.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H18" s="2">
-        <v>87.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2">
-        <v>87.2</v>
+        <v>95.2</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>260</v>
@@ -1866,28 +1866,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>3218.8</v>
+        <v>289.29</v>
       </c>
       <c r="C19" s="2">
-        <v>47.34</v>
+        <v>12.89</v>
       </c>
       <c r="D19" s="2">
-        <v>30.04</v>
+        <v>22.92</v>
       </c>
       <c r="E19" s="2">
-        <v>7.6</v>
+        <v>37.44</v>
       </c>
       <c r="F19" s="2">
-        <v>80</v>
+        <v>75.36</v>
       </c>
       <c r="G19" s="2">
-        <v>86</v>
+        <v>77.2</v>
       </c>
       <c r="H19" s="2">
-        <v>81.2</v>
+        <v>21.2</v>
       </c>
       <c r="I19" s="2">
-        <v>88.40000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>260</v>
@@ -1898,28 +1898,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>862.75</v>
+        <v>216.23</v>
       </c>
       <c r="C20" s="2">
-        <v>45.21</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="D20" s="2">
-        <v>32.77</v>
+        <v>33.29</v>
       </c>
       <c r="E20" s="2">
-        <v>3.8</v>
+        <v>-6.47</v>
       </c>
       <c r="F20" s="2">
-        <v>78.81999999999999</v>
+        <v>73.91</v>
       </c>
       <c r="G20" s="2">
-        <v>69.2</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2">
-        <v>85.2</v>
+        <v>99.2</v>
       </c>
       <c r="I20" s="2">
-        <v>70</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>260</v>
@@ -1930,28 +1930,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>761.1</v>
+        <v>229.23</v>
       </c>
       <c r="C21" s="2">
-        <v>47.14</v>
+        <v>88.12</v>
       </c>
       <c r="D21" s="2">
-        <v>31.02</v>
+        <v>17.34</v>
       </c>
       <c r="E21" s="2">
-        <v>2.75</v>
+        <v>-4.31</v>
       </c>
       <c r="F21" s="2">
-        <v>77.65000000000001</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="G21" s="2">
-        <v>84.8</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2">
-        <v>86.8</v>
+        <v>94</v>
       </c>
       <c r="I21" s="2">
-        <v>85.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>260</v>
@@ -1962,28 +1962,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>1159.3</v>
+        <v>2062.8</v>
       </c>
       <c r="C22" s="2">
-        <v>35.31</v>
+        <v>51.75</v>
       </c>
       <c r="D22" s="2">
-        <v>4.37</v>
+        <v>21.98</v>
       </c>
       <c r="E22" s="2">
-        <v>21.27</v>
+        <v>9.59</v>
       </c>
       <c r="F22" s="2">
-        <v>76.47</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="G22" s="2">
-        <v>60.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H22" s="2">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I22" s="2">
-        <v>26.8</v>
+        <v>74</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>260</v>
@@ -1994,28 +1994,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>1553</v>
+        <v>3184.7</v>
       </c>
       <c r="C23" s="2">
-        <v>22.87</v>
+        <v>52.86</v>
       </c>
       <c r="D23" s="2">
-        <v>23.33</v>
+        <v>33.11</v>
       </c>
       <c r="E23" s="2">
-        <v>14.4</v>
+        <v>1.43</v>
       </c>
       <c r="F23" s="2">
-        <v>75.29000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="G23" s="2">
-        <v>65.2</v>
+        <v>87.2</v>
       </c>
       <c r="H23" s="2">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2">
-        <v>54.8</v>
+        <v>81.2</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>260</v>
@@ -2026,28 +2026,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>1176.3</v>
+        <v>382.85</v>
       </c>
       <c r="C24" s="2">
-        <v>67.29000000000001</v>
+        <v>29.38</v>
       </c>
       <c r="D24" s="2">
-        <v>36.32</v>
+        <v>15.84</v>
       </c>
       <c r="E24" s="2">
-        <v>-14.69</v>
+        <v>17.03</v>
       </c>
       <c r="F24" s="2">
-        <v>74.12</v>
+        <v>68.12</v>
       </c>
       <c r="G24" s="2">
-        <v>95.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="H24" s="2">
-        <v>99.2</v>
+        <v>56</v>
       </c>
       <c r="I24" s="2">
-        <v>99.2</v>
+        <v>17.2</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>260</v>
@@ -2058,28 +2058,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>2329.7</v>
+        <v>129.64</v>
       </c>
       <c r="C25" s="2">
-        <v>42.41</v>
+        <v>42.1</v>
       </c>
       <c r="D25" s="2">
-        <v>6.86</v>
+        <v>10.39</v>
       </c>
       <c r="E25" s="2">
-        <v>11.88</v>
+        <v>11.46</v>
       </c>
       <c r="F25" s="2">
-        <v>72.94</v>
+        <v>66.67</v>
       </c>
       <c r="G25" s="2">
-        <v>82</v>
+        <v>76.8</v>
       </c>
       <c r="H25" s="2">
-        <v>42.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I25" s="2">
-        <v>59.2</v>
+        <v>91.2</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>260</v>
@@ -2090,28 +2090,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>472.15</v>
+        <v>4159.9</v>
       </c>
       <c r="C26" s="2">
-        <v>26.72</v>
+        <v>39.54</v>
       </c>
       <c r="D26" s="2">
-        <v>20.48</v>
+        <v>23.84</v>
       </c>
       <c r="E26" s="2">
-        <v>12.48</v>
+        <v>3.89</v>
       </c>
       <c r="F26" s="2">
-        <v>71.76000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="G26" s="2">
-        <v>70.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H26" s="2">
-        <v>76.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I26" s="2">
-        <v>58</v>
+        <v>87.2</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>260</v>
@@ -2122,28 +2122,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>77.90000000000001</v>
+        <v>607.2</v>
       </c>
       <c r="C27" s="2">
-        <v>58.06</v>
+        <v>47.27</v>
       </c>
       <c r="D27" s="2">
-        <v>9.039999999999999</v>
+        <v>45.54</v>
       </c>
       <c r="E27" s="2">
-        <v>0.34</v>
+        <v>-12.11</v>
       </c>
       <c r="F27" s="2">
-        <v>70.59</v>
+        <v>63.77</v>
       </c>
       <c r="G27" s="2">
-        <v>83.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H27" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I27" s="2">
-        <v>72.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>260</v>
@@ -2154,28 +2154,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>17.06</v>
+        <v>78.34</v>
       </c>
       <c r="C28" s="2">
-        <v>12.91</v>
+        <v>40.27</v>
       </c>
       <c r="D28" s="2">
-        <v>22.29</v>
+        <v>17.38</v>
       </c>
       <c r="E28" s="2">
-        <v>13.73</v>
+        <v>5.01</v>
       </c>
       <c r="F28" s="2">
-        <v>69.41</v>
+        <v>62.32</v>
       </c>
       <c r="G28" s="2">
-        <v>86.8</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2">
-        <v>72.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I28" s="2">
-        <v>51.2</v>
+        <v>56</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>260</v>
@@ -2186,28 +2186,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>204.03</v>
+        <v>281.2</v>
       </c>
       <c r="C29" s="2">
-        <v>19.33</v>
+        <v>43.84</v>
       </c>
       <c r="D29" s="2">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="E29" s="2">
-        <v>15.54</v>
+        <v>7.45</v>
       </c>
       <c r="F29" s="2">
-        <v>68.23999999999999</v>
+        <v>60.87</v>
       </c>
       <c r="G29" s="2">
-        <v>34.4</v>
+        <v>56</v>
       </c>
       <c r="H29" s="2">
-        <v>32.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I29" s="2">
-        <v>29.6</v>
+        <v>27.6</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>260</v>
@@ -2218,28 +2218,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>422.3</v>
+        <v>568.55</v>
       </c>
       <c r="C30" s="2">
-        <v>19.48</v>
+        <v>27.63</v>
       </c>
       <c r="D30" s="2">
-        <v>10</v>
+        <v>13.53</v>
       </c>
       <c r="E30" s="2">
-        <v>12.19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F30" s="2">
-        <v>67.06</v>
+        <v>59.42</v>
       </c>
       <c r="G30" s="2">
-        <v>47.2</v>
+        <v>58.4</v>
       </c>
       <c r="H30" s="2">
-        <v>40.4</v>
+        <v>44.8</v>
       </c>
       <c r="I30" s="2">
-        <v>30</v>
+        <v>53.2</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>260</v>
@@ -2250,28 +2250,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>604.55</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2">
-        <v>41.88</v>
+        <v>61.34</v>
       </c>
       <c r="D31" s="2">
-        <v>9.94</v>
+        <v>18.09</v>
       </c>
       <c r="E31" s="2">
-        <v>0.03</v>
+        <v>-10.9</v>
       </c>
       <c r="F31" s="2">
-        <v>65.88</v>
+        <v>57.97</v>
       </c>
       <c r="G31" s="2">
-        <v>85.2</v>
+        <v>68</v>
       </c>
       <c r="H31" s="2">
-        <v>82.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I31" s="2">
-        <v>86.8</v>
+        <v>92</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>260</v>
@@ -2282,28 +2282,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>77.72</v>
+        <v>206.63</v>
       </c>
       <c r="C32" s="2">
-        <v>33.4</v>
+        <v>13.43</v>
       </c>
       <c r="D32" s="2">
-        <v>11.35</v>
+        <v>13.71</v>
       </c>
       <c r="E32" s="2">
-        <v>1.5</v>
+        <v>14.84</v>
       </c>
       <c r="F32" s="2">
-        <v>64.70999999999999</v>
+        <v>56.52</v>
       </c>
       <c r="G32" s="2">
-        <v>70</v>
+        <v>31.6</v>
       </c>
       <c r="H32" s="2">
-        <v>56</v>
+        <v>1.2</v>
       </c>
       <c r="I32" s="2">
-        <v>66</v>
+        <v>8.4</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>260</v>
@@ -2314,28 +2314,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>594.55</v>
+        <v>238.21</v>
       </c>
       <c r="C33" s="2">
-        <v>39.55</v>
+        <v>28.95</v>
       </c>
       <c r="D33" s="2">
-        <v>35.51</v>
+        <v>12.44</v>
       </c>
       <c r="E33" s="2">
-        <v>-13.86</v>
+        <v>5.23</v>
       </c>
       <c r="F33" s="2">
-        <v>63.53</v>
+        <v>55.07</v>
       </c>
       <c r="G33" s="2">
-        <v>88</v>
+        <v>66.8</v>
       </c>
       <c r="H33" s="2">
-        <v>98.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I33" s="2">
-        <v>96.8</v>
+        <v>65.2</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>260</v>
@@ -2346,28 +2346,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>1698.3</v>
+        <v>46.52</v>
       </c>
       <c r="C34" s="2">
-        <v>68.38</v>
+        <v>25.87</v>
       </c>
       <c r="D34" s="2">
-        <v>-1.74</v>
+        <v>21.62</v>
       </c>
       <c r="E34" s="2">
-        <v>-12.05</v>
+        <v>1.48</v>
       </c>
       <c r="F34" s="2">
-        <v>62.35</v>
+        <v>53.62</v>
       </c>
       <c r="G34" s="2">
-        <v>77.59999999999999</v>
+        <v>47.2</v>
       </c>
       <c r="H34" s="2">
-        <v>66.8</v>
+        <v>45.2</v>
       </c>
       <c r="I34" s="2">
-        <v>92</v>
+        <v>59.6</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>260</v>
@@ -2378,28 +2378,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>846</v>
+        <v>2562.8</v>
       </c>
       <c r="C35" s="2">
-        <v>21.73</v>
+        <v>25.57</v>
       </c>
       <c r="D35" s="2">
-        <v>7.81</v>
+        <v>12.61</v>
       </c>
       <c r="E35" s="2">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="F35" s="2">
-        <v>61.18</v>
+        <v>52.17</v>
       </c>
       <c r="G35" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H35" s="2">
-        <v>47.2</v>
+        <v>35.6</v>
       </c>
       <c r="I35" s="2">
-        <v>48.8</v>
+        <v>34.8</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>260</v>
@@ -2410,28 +2410,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>825.5</v>
+        <v>177.66</v>
       </c>
       <c r="C36" s="2">
-        <v>61.7</v>
+        <v>18.52</v>
       </c>
       <c r="D36" s="2">
-        <v>4.75</v>
+        <v>23.63</v>
       </c>
       <c r="E36" s="2">
-        <v>-15.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F36" s="2">
+        <v>50.72</v>
+      </c>
+      <c r="G36" s="2">
+        <v>32.8</v>
+      </c>
+      <c r="H36" s="2">
+        <v>46.4</v>
+      </c>
+      <c r="I36" s="2">
         <v>60</v>
-      </c>
-      <c r="G36" s="2">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="H36" s="2">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="I36" s="2">
-        <v>93.2</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>260</v>
@@ -2442,28 +2442,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>9.699999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="C37" s="2">
-        <v>10.23</v>
+        <v>11.81</v>
       </c>
       <c r="D37" s="2">
-        <v>7.42</v>
+        <v>13.73</v>
       </c>
       <c r="E37" s="2">
-        <v>8.380000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F37" s="2">
-        <v>58.82</v>
+        <v>49.28</v>
       </c>
       <c r="G37" s="2">
+        <v>62.4</v>
+      </c>
+      <c r="H37" s="2">
         <v>53.6</v>
       </c>
-      <c r="H37" s="2">
+      <c r="I37" s="2">
         <v>63.6</v>
-      </c>
-      <c r="I37" s="2">
-        <v>4.4</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>260</v>
@@ -2474,28 +2474,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>825.1</v>
+        <v>2331.9</v>
       </c>
       <c r="C38" s="2">
-        <v>15.83</v>
+        <v>18.42</v>
       </c>
       <c r="D38" s="2">
-        <v>4.55</v>
+        <v>10.17</v>
       </c>
       <c r="E38" s="2">
         <v>5.68</v>
       </c>
       <c r="F38" s="2">
-        <v>57.65</v>
+        <v>47.83</v>
       </c>
       <c r="G38" s="2">
-        <v>66.8</v>
+        <v>38</v>
       </c>
       <c r="H38" s="2">
-        <v>57.6</v>
+        <v>22</v>
       </c>
       <c r="I38" s="2">
-        <v>43.2</v>
+        <v>28</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>260</v>
@@ -2506,28 +2506,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>273.15</v>
+        <v>259.95</v>
       </c>
       <c r="C39" s="2">
-        <v>23.42</v>
+        <v>12.06</v>
       </c>
       <c r="D39" s="2">
-        <v>8.57</v>
+        <v>13.66</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.4</v>
+        <v>6.29</v>
       </c>
       <c r="F39" s="2">
-        <v>56.47</v>
+        <v>46.38</v>
       </c>
       <c r="G39" s="2">
-        <v>60</v>
+        <v>52.4</v>
       </c>
       <c r="H39" s="2">
-        <v>59.2</v>
+        <v>30.8</v>
       </c>
       <c r="I39" s="2">
-        <v>60.8</v>
+        <v>28.4</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>260</v>
@@ -2538,28 +2538,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>828.7</v>
+        <v>16.34</v>
       </c>
       <c r="C40" s="2">
-        <v>37.02</v>
+        <v>16.13</v>
       </c>
       <c r="D40" s="2">
-        <v>15.41</v>
+        <v>20.5</v>
       </c>
       <c r="E40" s="2">
-        <v>-10.65</v>
+        <v>-2.68</v>
       </c>
       <c r="F40" s="2">
-        <v>55.29</v>
+        <v>44.93</v>
       </c>
       <c r="G40" s="2">
-        <v>58.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H40" s="2">
-        <v>83.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I40" s="2">
-        <v>74.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>260</v>
@@ -2570,28 +2570,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>1133.3</v>
+        <v>372.55</v>
       </c>
       <c r="C41" s="2">
-        <v>20.48</v>
+        <v>-1.2</v>
       </c>
       <c r="D41" s="2">
-        <v>0.65</v>
+        <v>5</v>
       </c>
       <c r="E41" s="2">
-        <v>4.84</v>
+        <v>11.4</v>
       </c>
       <c r="F41" s="2">
-        <v>54.12</v>
+        <v>43.48</v>
       </c>
       <c r="G41" s="2">
-        <v>67.59999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="H41" s="2">
-        <v>75.2</v>
+        <v>57.6</v>
       </c>
       <c r="I41" s="2">
-        <v>62</v>
+        <v>14.4</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>260</v>
@@ -2602,28 +2602,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>561.3</v>
+        <v>302.3</v>
       </c>
       <c r="C42" s="2">
-        <v>16.85</v>
+        <v>26.33</v>
       </c>
       <c r="D42" s="2">
-        <v>4.81</v>
+        <v>1.12</v>
       </c>
       <c r="E42" s="2">
-        <v>3.94</v>
+        <v>-0.48</v>
       </c>
       <c r="F42" s="2">
-        <v>52.94</v>
+        <v>42.03</v>
       </c>
       <c r="G42" s="2">
-        <v>44.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H42" s="2">
-        <v>53.2</v>
+        <v>61.2</v>
       </c>
       <c r="I42" s="2">
-        <v>39.2</v>
+        <v>68</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>260</v>
@@ -2634,28 +2634,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>689.65</v>
+        <v>1105.4</v>
       </c>
       <c r="C43" s="2">
-        <v>30.88</v>
+        <v>36.62</v>
       </c>
       <c r="D43" s="2">
-        <v>5.12</v>
+        <v>4.99</v>
       </c>
       <c r="E43" s="2">
-        <v>-3.23</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="F43" s="2">
-        <v>51.76</v>
+        <v>40.58</v>
       </c>
       <c r="G43" s="2">
-        <v>32</v>
+        <v>44.4</v>
       </c>
       <c r="H43" s="2">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="I43" s="2">
-        <v>50.4</v>
+        <v>36.4</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>260</v>
@@ -2666,28 +2666,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1174</v>
+        <v>1836.1</v>
       </c>
       <c r="C44" s="2">
-        <v>13.59</v>
+        <v>21.43</v>
       </c>
       <c r="D44" s="2">
-        <v>-4.8</v>
+        <v>12.77</v>
       </c>
       <c r="E44" s="2">
-        <v>7.3</v>
+        <v>-6.15</v>
       </c>
       <c r="F44" s="2">
-        <v>50.59</v>
+        <v>39.13</v>
       </c>
       <c r="G44" s="2">
-        <v>55.2</v>
+        <v>44</v>
       </c>
       <c r="H44" s="2">
-        <v>52.4</v>
+        <v>68</v>
       </c>
       <c r="I44" s="2">
-        <v>37.2</v>
+        <v>58.8</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>260</v>
@@ -2698,28 +2698,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>999.2</v>
+        <v>150.53</v>
       </c>
       <c r="C45" s="2">
-        <v>25.33</v>
+        <v>15.39</v>
       </c>
       <c r="D45" s="2">
-        <v>-1.44</v>
+        <v>0.1</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.59</v>
+        <v>2.33</v>
       </c>
       <c r="F45" s="2">
-        <v>49.41</v>
+        <v>37.68</v>
       </c>
       <c r="G45" s="2">
-        <v>54.4</v>
+        <v>64</v>
       </c>
       <c r="H45" s="2">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="I45" s="2">
-        <v>46.8</v>
+        <v>36.8</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>260</v>
@@ -2730,28 +2730,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>545.3</v>
+        <v>392.7</v>
       </c>
       <c r="C46" s="2">
-        <v>20.16</v>
+        <v>22.8</v>
       </c>
       <c r="D46" s="2">
-        <v>-2.42</v>
+        <v>-1.28</v>
       </c>
       <c r="E46" s="2">
-        <v>0.89</v>
+        <v>-5.28</v>
       </c>
       <c r="F46" s="2">
-        <v>48.24</v>
+        <v>36.23</v>
       </c>
       <c r="G46" s="2">
-        <v>66.40000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="H46" s="2">
-        <v>62.4</v>
+        <v>42.8</v>
       </c>
       <c r="I46" s="2">
-        <v>53.6</v>
+        <v>60.4</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>260</v>
@@ -2762,28 +2762,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>379.65</v>
+        <v>21.43</v>
       </c>
       <c r="C47" s="2">
-        <v>-4.28</v>
+        <v>41.45</v>
       </c>
       <c r="D47" s="2">
-        <v>0.79</v>
+        <v>1.18</v>
       </c>
       <c r="E47" s="2">
-        <v>10.02</v>
+        <v>-16.58</v>
       </c>
       <c r="F47" s="2">
-        <v>47.06</v>
+        <v>34.78</v>
       </c>
       <c r="G47" s="2">
-        <v>57.6</v>
+        <v>32.4</v>
       </c>
       <c r="H47" s="2">
-        <v>14.4</v>
+        <v>64.8</v>
       </c>
       <c r="I47" s="2">
-        <v>4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>260</v>
@@ -2794,28 +2794,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>44.6</v>
+        <v>31.6</v>
       </c>
       <c r="C48" s="2">
-        <v>12.06</v>
+        <v>20.8</v>
       </c>
       <c r="D48" s="2">
-        <v>11.44</v>
+        <v>-5.81</v>
       </c>
       <c r="E48" s="2">
-        <v>-4.46</v>
+        <v>-3.89</v>
       </c>
       <c r="F48" s="2">
-        <v>45.88</v>
+        <v>33.33</v>
       </c>
       <c r="G48" s="2">
-        <v>45.2</v>
+        <v>22</v>
       </c>
       <c r="H48" s="2">
-        <v>59.6</v>
+        <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>68.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>260</v>
@@ -2826,25 +2826,25 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>222.19</v>
+        <v>1497.1</v>
       </c>
       <c r="C49" s="2">
-        <v>24.95</v>
+        <v>43.14</v>
       </c>
       <c r="D49" s="2">
-        <v>4.61</v>
+        <v>-1.46</v>
       </c>
       <c r="E49" s="2">
-        <v>-8.529999999999999</v>
+        <v>-21.08</v>
       </c>
       <c r="F49" s="2">
-        <v>44.71</v>
+        <v>31.88</v>
       </c>
       <c r="G49" s="2">
-        <v>71.2</v>
+        <v>56.4</v>
       </c>
       <c r="H49" s="2">
-        <v>78</v>
+        <v>81.2</v>
       </c>
       <c r="I49" s="2">
         <v>88.8</v>
@@ -2858,28 +2858,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>134.04</v>
+        <v>328.9</v>
       </c>
       <c r="C50" s="2">
-        <v>15.35</v>
+        <v>-3.09</v>
       </c>
       <c r="D50" s="2">
-        <v>-0.73</v>
+        <v>-6.99</v>
       </c>
       <c r="E50" s="2">
-        <v>-1.22</v>
+        <v>4.66</v>
       </c>
       <c r="F50" s="2">
-        <v>43.53</v>
+        <v>30.43</v>
       </c>
       <c r="G50" s="2">
-        <v>47.6</v>
+        <v>13.6</v>
       </c>
       <c r="H50" s="2">
-        <v>51.6</v>
+        <v>13.6</v>
       </c>
       <c r="I50" s="2">
-        <v>43.6</v>
+        <v>12.8</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>260</v>
@@ -2890,28 +2890,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>591.75</v>
+        <v>124.22</v>
       </c>
       <c r="C51" s="2">
-        <v>5.1</v>
+        <v>5.81</v>
       </c>
       <c r="D51" s="2">
-        <v>-10.66</v>
+        <v>2.1</v>
       </c>
       <c r="E51" s="2">
-        <v>7.54</v>
+        <v>-4.36</v>
       </c>
       <c r="F51" s="2">
-        <v>42.35</v>
+        <v>28.99</v>
       </c>
       <c r="G51" s="2">
-        <v>33.6</v>
+        <v>26.4</v>
       </c>
       <c r="H51" s="2">
-        <v>17.6</v>
+        <v>38</v>
       </c>
       <c r="I51" s="2">
-        <v>7.2</v>
+        <v>42.8</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>260</v>
@@ -2922,28 +2922,28 @@
         <v>59</v>
       </c>
       <c r="B52" s="1">
-        <v>4085.2</v>
+        <v>151.64</v>
       </c>
       <c r="C52" s="2">
-        <v>-0.63</v>
+        <v>16.56</v>
       </c>
       <c r="D52" s="2">
-        <v>9.18</v>
+        <v>-6.38</v>
       </c>
       <c r="E52" s="2">
-        <v>0.23</v>
+        <v>-6.32</v>
       </c>
       <c r="F52" s="2">
-        <v>41.18</v>
+        <v>27.54</v>
       </c>
       <c r="G52" s="2">
-        <v>37.6</v>
+        <v>16.4</v>
       </c>
       <c r="H52" s="2">
-        <v>24.8</v>
+        <v>33.2</v>
       </c>
       <c r="I52" s="2">
-        <v>35.2</v>
+        <v>50.8</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>260</v>
@@ -2954,28 +2954,28 @@
         <v>60</v>
       </c>
       <c r="B53" s="1">
-        <v>186</v>
+        <v>9180</v>
       </c>
       <c r="C53" s="2">
-        <v>26.53</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D53" s="2">
-        <v>-1.22</v>
+        <v>0.58</v>
       </c>
       <c r="E53" s="2">
-        <v>-9.32</v>
+        <v>-7.94</v>
       </c>
       <c r="F53" s="2">
-        <v>40</v>
+        <v>26.09</v>
       </c>
       <c r="G53" s="2">
-        <v>41.2</v>
+        <v>27.6</v>
       </c>
       <c r="H53" s="2">
-        <v>71.2</v>
+        <v>10.8</v>
       </c>
       <c r="I53" s="2">
-        <v>83.59999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>260</v>
@@ -2986,28 +2986,28 @@
         <v>61</v>
       </c>
       <c r="B54" s="1">
-        <v>119.5</v>
+        <v>306.25</v>
       </c>
       <c r="C54" s="2">
-        <v>15.44</v>
+        <v>-2.67</v>
       </c>
       <c r="D54" s="2">
-        <v>-11.77</v>
+        <v>1.52</v>
       </c>
       <c r="E54" s="2">
-        <v>0.83</v>
+        <v>-2.99</v>
       </c>
       <c r="F54" s="2">
-        <v>38.82</v>
+        <v>24.64</v>
       </c>
       <c r="G54" s="2">
-        <v>24.4</v>
+        <v>17.2</v>
       </c>
       <c r="H54" s="2">
-        <v>38</v>
+        <v>27.6</v>
       </c>
       <c r="I54" s="2">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>260</v>
@@ -3018,28 +3018,28 @@
         <v>62</v>
       </c>
       <c r="B55" s="1">
-        <v>579.6</v>
+        <v>149.23</v>
       </c>
       <c r="C55" s="2">
-        <v>-1.02</v>
+        <v>-1.92</v>
       </c>
       <c r="D55" s="2">
-        <v>3.1</v>
+        <v>-2.36</v>
       </c>
       <c r="E55" s="2">
-        <v>1.4</v>
+        <v>-1.82</v>
       </c>
       <c r="F55" s="2">
-        <v>37.65</v>
+        <v>23.19</v>
       </c>
       <c r="G55" s="2">
-        <v>39.6</v>
+        <v>21.2</v>
       </c>
       <c r="H55" s="2">
-        <v>20.8</v>
+        <v>16</v>
       </c>
       <c r="I55" s="2">
-        <v>32</v>
+        <v>14.8</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>260</v>
@@ -3050,28 +3050,28 @@
         <v>63</v>
       </c>
       <c r="B56" s="1">
-        <v>63.04</v>
+        <v>193.19</v>
       </c>
       <c r="C56" s="2">
-        <v>14.33</v>
+        <v>12.53</v>
       </c>
       <c r="D56" s="2">
-        <v>-13.42</v>
+        <v>-10.21</v>
       </c>
       <c r="E56" s="2">
-        <v>1.96</v>
+        <v>-5.71</v>
       </c>
       <c r="F56" s="2">
-        <v>36.47</v>
+        <v>21.74</v>
       </c>
       <c r="G56" s="2">
-        <v>71.59999999999999</v>
+        <v>28.8</v>
       </c>
       <c r="H56" s="2">
-        <v>71.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="I56" s="2">
-        <v>70.8</v>
+        <v>41.2</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>260</v>
@@ -3082,28 +3082,28 @@
         <v>64</v>
       </c>
       <c r="B57" s="1">
-        <v>1127.7</v>
+        <v>120.87</v>
       </c>
       <c r="C57" s="2">
-        <v>38.31</v>
+        <v>7.44</v>
       </c>
       <c r="D57" s="2">
-        <v>-4.33</v>
+        <v>-3.37</v>
       </c>
       <c r="E57" s="2">
-        <v>-14.99</v>
+        <v>-8.56</v>
       </c>
       <c r="F57" s="2">
-        <v>35.29</v>
+        <v>20.29</v>
       </c>
       <c r="G57" s="2">
-        <v>46</v>
+        <v>16.8</v>
       </c>
       <c r="H57" s="2">
-        <v>26</v>
+        <v>25.2</v>
       </c>
       <c r="I57" s="2">
-        <v>77.59999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>260</v>
@@ -3114,28 +3114,28 @@
         <v>65</v>
       </c>
       <c r="B58" s="1">
-        <v>346.95</v>
+        <v>70.31</v>
       </c>
       <c r="C58" s="2">
-        <v>10.49</v>
+        <v>1.94</v>
       </c>
       <c r="D58" s="2">
-        <v>-12.87</v>
+        <v>-4.22</v>
       </c>
       <c r="E58" s="2">
-        <v>1.58</v>
+        <v>-5.55</v>
       </c>
       <c r="F58" s="2">
-        <v>34.12</v>
+        <v>18.84</v>
       </c>
       <c r="G58" s="2">
-        <v>39.2</v>
+        <v>11.6</v>
       </c>
       <c r="H58" s="2">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="I58" s="2">
-        <v>47.2</v>
+        <v>29.6</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>260</v>
@@ -3146,28 +3146,28 @@
         <v>66</v>
       </c>
       <c r="B59" s="1">
-        <v>22.37</v>
+        <v>133.37</v>
       </c>
       <c r="C59" s="2">
-        <v>38.94</v>
+        <v>1.21</v>
       </c>
       <c r="D59" s="2">
-        <v>-0.27</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="E59" s="2">
-        <v>-19.62</v>
+        <v>-3.71</v>
       </c>
       <c r="F59" s="2">
-        <v>32.94</v>
+        <v>17.39</v>
       </c>
       <c r="G59" s="2">
-        <v>64.8</v>
+        <v>22.8</v>
       </c>
       <c r="H59" s="2">
-        <v>75.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="I59" s="2">
-        <v>90.8</v>
+        <v>43.2</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>260</v>
@@ -3178,28 +3178,28 @@
         <v>67</v>
       </c>
       <c r="B60" s="1">
-        <v>188.63</v>
+        <v>121.22</v>
       </c>
       <c r="C60" s="2">
-        <v>0.7</v>
+        <v>2.02</v>
       </c>
       <c r="D60" s="2">
-        <v>-3.57</v>
+        <v>-2.99</v>
       </c>
       <c r="E60" s="2">
-        <v>0.44</v>
+        <v>-9.06</v>
       </c>
       <c r="F60" s="2">
-        <v>31.76</v>
+        <v>15.94</v>
       </c>
       <c r="G60" s="2">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H60" s="2">
-        <v>8.4</v>
+        <v>32.8</v>
       </c>
       <c r="I60" s="2">
-        <v>22.4</v>
+        <v>35.2</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>260</v>
@@ -3210,28 +3210,28 @@
         <v>68</v>
       </c>
       <c r="B61" s="1">
-        <v>235.97</v>
+        <v>163.67</v>
       </c>
       <c r="C61" s="2">
-        <v>-0.08</v>
+        <v>-7.05</v>
       </c>
       <c r="D61" s="2">
-        <v>-4.55</v>
+        <v>0.04</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.25</v>
+        <v>-6.22</v>
       </c>
       <c r="F61" s="2">
-        <v>30.59</v>
+        <v>14.49</v>
       </c>
       <c r="G61" s="2">
-        <v>12.4</v>
+        <v>6.8</v>
       </c>
       <c r="H61" s="2">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="I61" s="2">
-        <v>9.6</v>
+        <v>26.8</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>260</v>
@@ -3242,28 +3242,28 @@
         <v>69</v>
       </c>
       <c r="B62" s="1">
-        <v>502.7</v>
+        <v>195.04</v>
       </c>
       <c r="C62" s="2">
-        <v>15.87</v>
+        <v>3.5</v>
       </c>
       <c r="D62" s="2">
-        <v>3.65</v>
+        <v>-11.5</v>
       </c>
       <c r="E62" s="2">
-        <v>-13.55</v>
+        <v>-6.21</v>
       </c>
       <c r="F62" s="2">
-        <v>29.41</v>
+        <v>13.04</v>
       </c>
       <c r="G62" s="2">
-        <v>42</v>
+        <v>6.4</v>
       </c>
       <c r="H62" s="2">
-        <v>62.8</v>
+        <v>15.6</v>
       </c>
       <c r="I62" s="2">
-        <v>69.59999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>260</v>
@@ -3274,28 +3274,28 @@
         <v>70</v>
       </c>
       <c r="B63" s="1">
-        <v>567.8</v>
+        <v>572.5</v>
       </c>
       <c r="C63" s="2">
-        <v>-5.73</v>
+        <v>-3.8</v>
       </c>
       <c r="D63" s="2">
-        <v>-2.55</v>
+        <v>-10.34</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.6</v>
+        <v>-3.97</v>
       </c>
       <c r="F63" s="2">
-        <v>28.24</v>
+        <v>11.59</v>
       </c>
       <c r="G63" s="2">
-        <v>16.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H63" s="2">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="I63" s="2">
-        <v>12.4</v>
+        <v>2.8</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>260</v>
@@ -3306,28 +3306,28 @@
         <v>71</v>
       </c>
       <c r="B64" s="1">
-        <v>127.83</v>
+        <v>147.04</v>
       </c>
       <c r="C64" s="2">
-        <v>0.12</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="D64" s="2">
-        <v>1.36</v>
+        <v>-4.53</v>
       </c>
       <c r="E64" s="2">
-        <v>-6.67</v>
+        <v>-5.69</v>
       </c>
       <c r="F64" s="2">
-        <v>27.06</v>
+        <v>10.14</v>
       </c>
       <c r="G64" s="2">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="H64" s="2">
-        <v>42.8</v>
+        <v>12.8</v>
       </c>
       <c r="I64" s="2">
-        <v>42.4</v>
+        <v>6.8</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>260</v>
@@ -3338,28 +3338,28 @@
         <v>72</v>
       </c>
       <c r="B65" s="1">
-        <v>549.85</v>
+        <v>216.55</v>
       </c>
       <c r="C65" s="2">
-        <v>12.09</v>
+        <v>-5.68</v>
       </c>
       <c r="D65" s="2">
-        <v>-12.69</v>
+        <v>-6.24</v>
       </c>
       <c r="E65" s="2">
-        <v>-5.91</v>
+        <v>-6.8</v>
       </c>
       <c r="F65" s="2">
-        <v>25.88</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G65" s="2">
-        <v>24.8</v>
+        <v>29.2</v>
       </c>
       <c r="H65" s="2">
-        <v>21.2</v>
+        <v>12.4</v>
       </c>
       <c r="I65" s="2">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>260</v>
@@ -3370,28 +3370,28 @@
         <v>73</v>
       </c>
       <c r="B66" s="1">
-        <v>118.85</v>
+        <v>218.72</v>
       </c>
       <c r="C66" s="2">
-        <v>8.59</v>
+        <v>-7.02</v>
       </c>
       <c r="D66" s="2">
-        <v>-4.21</v>
+        <v>-13.33</v>
       </c>
       <c r="E66" s="2">
-        <v>-8.77</v>
+        <v>-2.61</v>
       </c>
       <c r="F66" s="2">
-        <v>24.71</v>
+        <v>7.25</v>
       </c>
       <c r="G66" s="2">
-        <v>44.4</v>
+        <v>20.8</v>
       </c>
       <c r="H66" s="2">
-        <v>56.4</v>
+        <v>10</v>
       </c>
       <c r="I66" s="2">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>260</v>
@@ -3402,28 +3402,28 @@
         <v>74</v>
       </c>
       <c r="B67" s="1">
-        <v>137.18</v>
+        <v>268.85</v>
       </c>
       <c r="C67" s="2">
-        <v>0.01</v>
+        <v>-9.68</v>
       </c>
       <c r="D67" s="2">
-        <v>-12.43</v>
+        <v>-10.65</v>
       </c>
       <c r="E67" s="2">
-        <v>-1.23</v>
+        <v>-4</v>
       </c>
       <c r="F67" s="2">
-        <v>23.53</v>
+        <v>5.8</v>
       </c>
       <c r="G67" s="2">
-        <v>26.8</v>
+        <v>9.6</v>
       </c>
       <c r="H67" s="2">
-        <v>43.2</v>
+        <v>5.6</v>
       </c>
       <c r="I67" s="2">
-        <v>39.6</v>
+        <v>7.2</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>260</v>
@@ -3434,28 +3434,28 @@
         <v>75</v>
       </c>
       <c r="B68" s="1">
-        <v>233.94</v>
+        <v>554.8</v>
       </c>
       <c r="C68" s="2">
-        <v>-6.52</v>
+        <v>-6.94</v>
       </c>
       <c r="D68" s="2">
-        <v>-11.29</v>
+        <v>-12.13</v>
       </c>
       <c r="E68" s="2">
-        <v>0.13</v>
+        <v>-5.47</v>
       </c>
       <c r="F68" s="2">
-        <v>22.35</v>
+        <v>4.35</v>
       </c>
       <c r="G68" s="2">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="H68" s="2">
-        <v>6</v>
+        <v>11.2</v>
       </c>
       <c r="I68" s="2">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>260</v>
@@ -3466,28 +3466,28 @@
         <v>76</v>
       </c>
       <c r="B69" s="1">
-        <v>8.710000000000001</v>
+        <v>720.55</v>
       </c>
       <c r="C69" s="2">
-        <v>8.470000000000001</v>
+        <v>-12.13</v>
       </c>
       <c r="D69" s="2">
-        <v>-11.03</v>
+        <v>-22.35</v>
       </c>
       <c r="E69" s="2">
-        <v>-7.64</v>
+        <v>-10.11</v>
       </c>
       <c r="F69" s="2">
-        <v>21.18</v>
+        <v>2.9</v>
       </c>
       <c r="G69" s="2">
-        <v>20.8</v>
+        <v>18</v>
       </c>
       <c r="H69" s="2">
-        <v>18.4</v>
+        <v>14.4</v>
       </c>
       <c r="I69" s="2">
-        <v>25.2</v>
+        <v>11.2</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>260</v>
@@ -3498,28 +3498,28 @@
         <v>77</v>
       </c>
       <c r="B70" s="1">
-        <v>491.55</v>
+        <v>248.7</v>
       </c>
       <c r="C70" s="2">
-        <v>-4.6</v>
+        <v>-26.05</v>
       </c>
       <c r="D70" s="2">
-        <v>-12.38</v>
+        <v>-32.57</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.92</v>
+        <v>-39.68</v>
       </c>
       <c r="F70" s="2">
-        <v>20</v>
+        <v>1.45</v>
       </c>
       <c r="G70" s="2">
-        <v>23.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H70" s="2">
-        <v>22</v>
+        <v>70.8</v>
       </c>
       <c r="I70" s="2">
-        <v>18.4</v>
+        <v>76.8</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>260</v>
@@ -3529,29 +3529,14 @@
       <c r="A71" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="1">
-        <v>314.05</v>
-      </c>
-      <c r="C71" s="2">
-        <v>-11.32</v>
-      </c>
-      <c r="D71" s="2">
-        <v>-2.97</v>
-      </c>
-      <c r="E71" s="2">
-        <v>-2.91</v>
-      </c>
-      <c r="F71" s="2">
-        <v>18.82</v>
-      </c>
       <c r="G71" s="2">
-        <v>27.6</v>
+        <v>34.8</v>
       </c>
       <c r="H71" s="2">
-        <v>39.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I71" s="2">
-        <v>30.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>260</v>
@@ -3561,29 +3546,14 @@
       <c r="A72" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="1">
-        <v>300.15</v>
-      </c>
-      <c r="C72" s="2">
-        <v>-5.06</v>
-      </c>
-      <c r="D72" s="2">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E72" s="2">
-        <v>-3.36</v>
-      </c>
-      <c r="F72" s="2">
-        <v>17.65</v>
-      </c>
       <c r="G72" s="2">
-        <v>21.6</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H72" s="2">
-        <v>13.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I72" s="2">
-        <v>23.6</v>
+        <v>99.2</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>260</v>
@@ -3593,29 +3563,14 @@
       <c r="A73" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="1">
-        <v>288.3</v>
-      </c>
-      <c r="C73" s="2">
-        <v>12.79</v>
-      </c>
-      <c r="D73" s="2">
-        <v>-25.82</v>
-      </c>
-      <c r="E73" s="2">
-        <v>-4.31</v>
-      </c>
-      <c r="F73" s="2">
-        <v>16.47</v>
-      </c>
       <c r="G73" s="2">
-        <v>23.6</v>
+        <v>32</v>
       </c>
       <c r="H73" s="2">
-        <v>12.4</v>
+        <v>29.2</v>
       </c>
       <c r="I73" s="2">
-        <v>10.4</v>
+        <v>25.6</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>260</v>
@@ -3625,29 +3580,14 @@
       <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="1">
-        <v>448.95</v>
-      </c>
-      <c r="C74" s="2">
-        <v>-4.25</v>
-      </c>
-      <c r="D74" s="2">
-        <v>-15.15</v>
-      </c>
-      <c r="E74" s="2">
-        <v>-2.02</v>
-      </c>
-      <c r="F74" s="2">
-        <v>15.29</v>
-      </c>
       <c r="G74" s="2">
-        <v>19.6</v>
+        <v>26</v>
       </c>
       <c r="H74" s="2">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
       <c r="I74" s="2">
-        <v>22.8</v>
+        <v>21.2</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>260</v>
@@ -3657,29 +3597,14 @@
       <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B75" s="1">
-        <v>331.45</v>
-      </c>
-      <c r="C75" s="2">
-        <v>-11.31</v>
-      </c>
-      <c r="D75" s="2">
-        <v>-15.92</v>
-      </c>
-      <c r="E75" s="2">
-        <v>1.27</v>
-      </c>
-      <c r="F75" s="2">
-        <v>14.12</v>
-      </c>
       <c r="G75" s="2">
-        <v>13.6</v>
+        <v>88.8</v>
       </c>
       <c r="H75" s="2">
-        <v>12.8</v>
+        <v>91.2</v>
       </c>
       <c r="I75" s="2">
-        <v>8.800000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>260</v>
@@ -3689,29 +3614,14 @@
       <c r="A76" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="1">
-        <v>1024.85</v>
-      </c>
-      <c r="C76" s="2">
-        <v>-14.89</v>
-      </c>
-      <c r="D76" s="2">
-        <v>-27.03</v>
-      </c>
-      <c r="E76" s="2">
-        <v>7.16</v>
-      </c>
-      <c r="F76" s="2">
-        <v>12.94</v>
-      </c>
       <c r="G76" s="2">
-        <v>0.4</v>
+        <v>36</v>
       </c>
       <c r="H76" s="2">
-        <v>0.4</v>
+        <v>46</v>
       </c>
       <c r="I76" s="2">
-        <v>0.4</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>260</v>
@@ -3721,29 +3631,14 @@
       <c r="A77" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="1">
-        <v>66.48</v>
-      </c>
-      <c r="C77" s="2">
-        <v>6.39</v>
-      </c>
-      <c r="D77" s="2">
-        <v>-0.88</v>
-      </c>
-      <c r="E77" s="2">
-        <v>-16.57</v>
-      </c>
-      <c r="F77" s="2">
-        <v>11.76</v>
-      </c>
       <c r="G77" s="2">
-        <v>60.4</v>
+        <v>96</v>
       </c>
       <c r="H77" s="2">
-        <v>70</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I77" s="2">
-        <v>81.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>260</v>
@@ -3753,29 +3648,14 @@
       <c r="A78" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="1">
-        <v>72.56</v>
-      </c>
-      <c r="C78" s="2">
-        <v>-8.26</v>
-      </c>
-      <c r="D78" s="2">
-        <v>-5.27</v>
-      </c>
-      <c r="E78" s="2">
-        <v>-7.4</v>
-      </c>
-      <c r="F78" s="2">
-        <v>10.59</v>
-      </c>
       <c r="G78" s="2">
-        <v>20.4</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H78" s="2">
-        <v>29.6</v>
+        <v>98.8</v>
       </c>
       <c r="I78" s="2">
-        <v>24.8</v>
+        <v>97.2</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>260</v>
@@ -3785,29 +3665,14 @@
       <c r="A79" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B79" s="1">
-        <v>122.57</v>
-      </c>
-      <c r="C79" s="2">
-        <v>-0.66</v>
-      </c>
-      <c r="D79" s="2">
-        <v>-6.16</v>
-      </c>
-      <c r="E79" s="2">
-        <v>-12.02</v>
-      </c>
-      <c r="F79" s="2">
-        <v>9.41</v>
-      </c>
       <c r="G79" s="2">
-        <v>32.8</v>
+        <v>62.8</v>
       </c>
       <c r="H79" s="2">
-        <v>35.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I79" s="2">
-        <v>44</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>260</v>
@@ -3817,29 +3682,14 @@
       <c r="A80" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B80" s="1">
-        <v>22.37</v>
-      </c>
-      <c r="C80" s="2">
-        <v>-10.7</v>
-      </c>
-      <c r="D80" s="2">
-        <v>-13.93</v>
-      </c>
-      <c r="E80" s="2">
-        <v>-3.41</v>
-      </c>
-      <c r="F80" s="2">
-        <v>8.24</v>
-      </c>
       <c r="G80" s="2">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H80" s="2">
-        <v>16.4</v>
+        <v>68.8</v>
       </c>
       <c r="I80" s="2">
-        <v>8.4</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>260</v>
@@ -3849,29 +3699,14 @@
       <c r="A81" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="1">
-        <v>364.85</v>
-      </c>
-      <c r="C81" s="2">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="D81" s="2">
-        <v>-11.61</v>
-      </c>
-      <c r="E81" s="2">
-        <v>-6.26</v>
-      </c>
-      <c r="F81" s="2">
-        <v>7.06</v>
-      </c>
       <c r="G81" s="2">
-        <v>6.8</v>
+        <v>92.8</v>
       </c>
       <c r="H81" s="2">
-        <v>2.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I81" s="2">
-        <v>5.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>260</v>
@@ -3881,29 +3716,14 @@
       <c r="A82" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="1">
-        <v>12.32</v>
-      </c>
-      <c r="C82" s="2">
-        <v>-6.81</v>
-      </c>
-      <c r="D82" s="2">
-        <v>-12.38</v>
-      </c>
-      <c r="E82" s="2">
-        <v>-6.74</v>
-      </c>
-      <c r="F82" s="2">
-        <v>5.88</v>
-      </c>
       <c r="G82" s="2">
-        <v>11.6</v>
+        <v>3.2</v>
       </c>
       <c r="H82" s="2">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I82" s="2">
-        <v>17.2</v>
+        <v>20.4</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>260</v>
@@ -3913,29 +3733,14 @@
       <c r="A83" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="1">
-        <v>164.66</v>
-      </c>
-      <c r="C83" s="2">
-        <v>-11.16</v>
-      </c>
-      <c r="D83" s="2">
-        <v>-5.68</v>
-      </c>
-      <c r="E83" s="2">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="F83" s="2">
-        <v>4.71</v>
-      </c>
       <c r="G83" s="2">
-        <v>18.8</v>
+        <v>67.2</v>
       </c>
       <c r="H83" s="2">
-        <v>26.8</v>
+        <v>67.2</v>
       </c>
       <c r="I83" s="2">
-        <v>25.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>260</v>
@@ -3945,29 +3750,14 @@
       <c r="A84" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="1">
-        <v>169.08</v>
-      </c>
-      <c r="C84" s="2">
-        <v>6.96</v>
-      </c>
-      <c r="D84" s="2">
-        <v>-20.84</v>
-      </c>
-      <c r="E84" s="2">
-        <v>-10.99</v>
-      </c>
-      <c r="F84" s="2">
-        <v>3.53</v>
-      </c>
       <c r="G84" s="2">
-        <v>6</v>
+        <v>34.4</v>
       </c>
       <c r="H84" s="2">
-        <v>9.6</v>
+        <v>39.2</v>
       </c>
       <c r="I84" s="2">
-        <v>28.8</v>
+        <v>26.4</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>260</v>
@@ -3977,29 +3767,14 @@
       <c r="A85" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B85" s="1">
-        <v>899.1</v>
-      </c>
-      <c r="C85" s="2">
-        <v>-12.71</v>
-      </c>
-      <c r="D85" s="2">
-        <v>-22.32</v>
-      </c>
-      <c r="E85" s="2">
-        <v>-0.45</v>
-      </c>
-      <c r="F85" s="2">
-        <v>2.35</v>
-      </c>
       <c r="G85" s="2">
-        <v>6.4</v>
+        <v>40.8</v>
       </c>
       <c r="H85" s="2">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="I85" s="2">
-        <v>1.6</v>
+        <v>34</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>260</v>
@@ -4009,29 +3784,14 @@
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B86" s="1">
-        <v>30</v>
-      </c>
-      <c r="C86" s="2">
-        <v>-8.59</v>
-      </c>
-      <c r="D86" s="2">
-        <v>-10.07</v>
-      </c>
-      <c r="E86" s="2">
-        <v>-12.08</v>
-      </c>
-      <c r="F86" s="2">
-        <v>1.18</v>
-      </c>
       <c r="G86" s="2">
-        <v>8.800000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H86" s="2">
-        <v>20.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I86" s="2">
-        <v>28</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>260</v>
@@ -4042,13 +3802,13 @@
         <v>94</v>
       </c>
       <c r="G87" s="2">
-        <v>83.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H87" s="2">
-        <v>90.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I87" s="2">
-        <v>98.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>260</v>
@@ -4059,13 +3819,13 @@
         <v>95</v>
       </c>
       <c r="G88" s="2">
-        <v>29.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H88" s="2">
-        <v>25.6</v>
+        <v>84.8</v>
       </c>
       <c r="I88" s="2">
-        <v>65.2</v>
+        <v>86.8</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>260</v>
@@ -4076,13 +3836,13 @@
         <v>96</v>
       </c>
       <c r="G89" s="2">
-        <v>95.2</v>
+        <v>25.6</v>
       </c>
       <c r="H89" s="2">
-        <v>93.59999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="I89" s="2">
-        <v>94</v>
+        <v>56.4</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>260</v>
@@ -4093,13 +3853,13 @@
         <v>97</v>
       </c>
       <c r="G90" s="2">
-        <v>97.2</v>
+        <v>58</v>
       </c>
       <c r="H90" s="2">
-        <v>98.8</v>
+        <v>32</v>
       </c>
       <c r="I90" s="2">
-        <v>98.8</v>
+        <v>44.4</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>260</v>
@@ -4110,13 +3870,13 @@
         <v>98</v>
       </c>
       <c r="G91" s="2">
-        <v>91.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H91" s="2">
-        <v>88.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I91" s="2">
-        <v>93.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>260</v>
@@ -4127,13 +3887,13 @@
         <v>99</v>
       </c>
       <c r="G92" s="2">
-        <v>11.2</v>
+        <v>92</v>
       </c>
       <c r="H92" s="2">
-        <v>1.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I92" s="2">
-        <v>48.4</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>260</v>
@@ -4144,13 +3904,13 @@
         <v>100</v>
       </c>
       <c r="G93" s="2">
-        <v>94.40000000000001</v>
+        <v>6</v>
       </c>
       <c r="H93" s="2">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="I93" s="2">
-        <v>68</v>
+        <v>9.6</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>260</v>
@@ -4161,13 +3921,13 @@
         <v>101</v>
       </c>
       <c r="G94" s="2">
-        <v>96.40000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="H94" s="2">
-        <v>94.8</v>
+        <v>76.8</v>
       </c>
       <c r="I94" s="2">
-        <v>92.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>260</v>
@@ -4178,13 +3938,13 @@
         <v>102</v>
       </c>
       <c r="G95" s="2">
-        <v>68.8</v>
+        <v>74</v>
       </c>
       <c r="H95" s="2">
-        <v>79.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="I95" s="2">
-        <v>76.8</v>
+        <v>62</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>260</v>
@@ -4195,13 +3955,13 @@
         <v>103</v>
       </c>
       <c r="G96" s="2">
-        <v>86.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H96" s="2">
-        <v>73.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I96" s="2">
-        <v>72</v>
+        <v>82.8</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>260</v>
@@ -4212,13 +3972,13 @@
         <v>104</v>
       </c>
       <c r="G97" s="2">
-        <v>67.2</v>
+        <v>18.4</v>
       </c>
       <c r="H97" s="2">
-        <v>77.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="I97" s="2">
-        <v>74</v>
+        <v>37.2</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>260</v>
@@ -4229,13 +3989,13 @@
         <v>105</v>
       </c>
       <c r="G98" s="2">
-        <v>24</v>
+        <v>33.6</v>
       </c>
       <c r="H98" s="2">
-        <v>34</v>
+        <v>37.2</v>
       </c>
       <c r="I98" s="2">
-        <v>11.2</v>
+        <v>45.2</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>260</v>
@@ -4246,13 +4006,13 @@
         <v>106</v>
       </c>
       <c r="G99" s="2">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="H99" s="2">
-        <v>86.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I99" s="2">
-        <v>78.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>260</v>
@@ -4263,13 +4023,13 @@
         <v>107</v>
       </c>
       <c r="G100" s="2">
-        <v>98.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H100" s="2">
-        <v>90</v>
+        <v>59.2</v>
       </c>
       <c r="I100" s="2">
-        <v>88</v>
+        <v>67.2</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>260</v>
@@ -4280,13 +4040,13 @@
         <v>108</v>
       </c>
       <c r="G101" s="2">
-        <v>42.8</v>
+        <v>24.4</v>
       </c>
       <c r="H101" s="2">
-        <v>60.4</v>
+        <v>32.4</v>
       </c>
       <c r="I101" s="2">
-        <v>51.6</v>
+        <v>3.2</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>260</v>
@@ -4297,13 +4057,13 @@
         <v>109</v>
       </c>
       <c r="G102" s="2">
-        <v>10.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H102" s="2">
-        <v>31.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I102" s="2">
-        <v>69.2</v>
+        <v>72</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>260</v>
@@ -4314,13 +4074,13 @@
         <v>110</v>
       </c>
       <c r="G103" s="2">
-        <v>64</v>
+        <v>41.6</v>
       </c>
       <c r="H103" s="2">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="I103" s="2">
-        <v>30.4</v>
+        <v>48.4</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>260</v>
@@ -4331,13 +4091,13 @@
         <v>111</v>
       </c>
       <c r="G104" s="2">
-        <v>76.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H104" s="2">
-        <v>76.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="I104" s="2">
-        <v>78.8</v>
+        <v>94</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>260</v>
@@ -4348,13 +4108,13 @@
         <v>112</v>
       </c>
       <c r="G105" s="2">
-        <v>59.6</v>
+        <v>35.6</v>
       </c>
       <c r="H105" s="2">
-        <v>62</v>
+        <v>38.4</v>
       </c>
       <c r="I105" s="2">
-        <v>55.6</v>
+        <v>38.8</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>260</v>
@@ -4365,13 +4125,13 @@
         <v>113</v>
       </c>
       <c r="G106" s="2">
-        <v>20</v>
+        <v>46.8</v>
       </c>
       <c r="H106" s="2">
-        <v>37.2</v>
+        <v>71.2</v>
       </c>
       <c r="I106" s="2">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>260</v>
@@ -4382,13 +4142,13 @@
         <v>114</v>
       </c>
       <c r="G107" s="2">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="H107" s="2">
-        <v>45.2</v>
+        <v>28</v>
       </c>
       <c r="I107" s="2">
-        <v>37.6</v>
+        <v>24</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>260</v>
@@ -4399,13 +4159,13 @@
         <v>115</v>
       </c>
       <c r="G108" s="2">
-        <v>72.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H108" s="2">
-        <v>81.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I108" s="2">
-        <v>73.2</v>
+        <v>84</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>260</v>
@@ -4416,13 +4176,13 @@
         <v>116</v>
       </c>
       <c r="G109" s="2">
-        <v>59.2</v>
+        <v>12.4</v>
       </c>
       <c r="H109" s="2">
-        <v>67.2</v>
+        <v>0.4</v>
       </c>
       <c r="I109" s="2">
-        <v>80</v>
+        <v>0.4</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>260</v>
@@ -4433,13 +4193,13 @@
         <v>117</v>
       </c>
       <c r="G110" s="2">
-        <v>32.4</v>
+        <v>59.6</v>
       </c>
       <c r="H110" s="2">
-        <v>3.2</v>
+        <v>60</v>
       </c>
       <c r="I110" s="2">
-        <v>2.4</v>
+        <v>59.2</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>260</v>
@@ -4450,13 +4210,13 @@
         <v>118</v>
       </c>
       <c r="G111" s="2">
-        <v>70.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H111" s="2">
-        <v>72</v>
+        <v>2.4</v>
       </c>
       <c r="I111" s="2">
-        <v>72.40000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>260</v>
@@ -4467,13 +4227,13 @@
         <v>119</v>
       </c>
       <c r="G112" s="2">
-        <v>97.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="H112" s="2">
-        <v>96</v>
+        <v>66.8</v>
       </c>
       <c r="I112" s="2">
-        <v>98</v>
+        <v>57.6</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>260</v>
@@ -4484,13 +4244,13 @@
         <v>120</v>
       </c>
       <c r="G113" s="2">
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="H113" s="2">
         <v>48.4</v>
       </c>
       <c r="I113" s="2">
-        <v>59.6</v>
+        <v>64.8</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>260</v>
@@ -4501,13 +4261,13 @@
         <v>121</v>
       </c>
       <c r="G114" s="2">
-        <v>73.2</v>
+        <v>86.8</v>
       </c>
       <c r="H114" s="2">
-        <v>67.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I114" s="2">
-        <v>66.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>260</v>
@@ -4518,13 +4278,13 @@
         <v>122</v>
       </c>
       <c r="G115" s="2">
-        <v>38.4</v>
+        <v>12</v>
       </c>
       <c r="H115" s="2">
-        <v>38.8</v>
+        <v>60.4</v>
       </c>
       <c r="I115" s="2">
-        <v>40.8</v>
+        <v>70</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>260</v>
@@ -4535,13 +4295,13 @@
         <v>123</v>
       </c>
       <c r="G116" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="H116" s="2">
-        <v>24</v>
+        <v>52.8</v>
       </c>
       <c r="I116" s="2">
-        <v>15.6</v>
+        <v>47.6</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>260</v>
@@ -4552,13 +4312,13 @@
         <v>124</v>
       </c>
       <c r="G117" s="2">
-        <v>61.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H117" s="2">
-        <v>68</v>
+        <v>78.8</v>
       </c>
       <c r="I117" s="2">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>260</v>
@@ -4569,13 +4329,13 @@
         <v>125</v>
       </c>
       <c r="G118" s="2">
-        <v>50</v>
+        <v>18.8</v>
       </c>
       <c r="H118" s="2">
-        <v>36.4</v>
+        <v>14</v>
       </c>
       <c r="I118" s="2">
-        <v>84</v>
+        <v>21.6</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>260</v>
@@ -4586,13 +4346,13 @@
         <v>126</v>
       </c>
       <c r="G119" s="2">
-        <v>2.4</v>
+        <v>42.4</v>
       </c>
       <c r="H119" s="2">
-        <v>11.6</v>
+        <v>56.4</v>
       </c>
       <c r="I119" s="2">
-        <v>32.4</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>260</v>
@@ -4603,13 +4363,13 @@
         <v>127</v>
       </c>
       <c r="G120" s="2">
-        <v>48.4</v>
+        <v>59.2</v>
       </c>
       <c r="H120" s="2">
-        <v>64.8</v>
+        <v>58.8</v>
       </c>
       <c r="I120" s="2">
-        <v>67.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>260</v>
@@ -4620,13 +4380,13 @@
         <v>128</v>
       </c>
       <c r="G121" s="2">
-        <v>12.8</v>
+        <v>39.6</v>
       </c>
       <c r="H121" s="2">
-        <v>6.8</v>
+        <v>49.2</v>
       </c>
       <c r="I121" s="2">
-        <v>14.8</v>
+        <v>58.4</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>260</v>
@@ -4637,13 +4397,13 @@
         <v>129</v>
       </c>
       <c r="G122" s="2">
-        <v>82.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="H122" s="2">
-        <v>91.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="I122" s="2">
-        <v>90.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>260</v>
@@ -4654,13 +4414,13 @@
         <v>130</v>
       </c>
       <c r="G123" s="2">
-        <v>56</v>
+        <v>91.2</v>
       </c>
       <c r="H123" s="2">
-        <v>17.2</v>
+        <v>94.8</v>
       </c>
       <c r="I123" s="2">
-        <v>18</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>260</v>
@@ -4671,13 +4431,13 @@
         <v>131</v>
       </c>
       <c r="G124" s="2">
-        <v>1.6</v>
+        <v>78</v>
       </c>
       <c r="H124" s="2">
-        <v>2.8</v>
+        <v>34.4</v>
       </c>
       <c r="I124" s="2">
-        <v>13.6</v>
+        <v>32.4</v>
       </c>
       <c r="J124" s="4" t="s">
         <v>260</v>
@@ -4688,13 +4448,13 @@
         <v>132</v>
       </c>
       <c r="G125" s="2">
-        <v>52.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H125" s="2">
-        <v>47.6</v>
+        <v>57.2</v>
       </c>
       <c r="I125" s="2">
-        <v>64.8</v>
+        <v>44</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>260</v>
@@ -4705,13 +4465,13 @@
         <v>133</v>
       </c>
       <c r="G126" s="2">
-        <v>78.8</v>
+        <v>61.2</v>
       </c>
       <c r="H126" s="2">
-        <v>64.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="I126" s="2">
-        <v>76.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>260</v>
@@ -4722,13 +4482,13 @@
         <v>134</v>
       </c>
       <c r="G127" s="2">
-        <v>14</v>
+        <v>68.8</v>
       </c>
       <c r="H127" s="2">
-        <v>21.6</v>
+        <v>75.2</v>
       </c>
       <c r="I127" s="2">
-        <v>24.4</v>
+        <v>93.2</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>260</v>
@@ -4739,13 +4499,13 @@
         <v>135</v>
       </c>
       <c r="G128" s="2">
-        <v>56.4</v>
+        <v>8.4</v>
       </c>
       <c r="H128" s="2">
-        <v>69.59999999999999</v>
+        <v>4</v>
       </c>
       <c r="I128" s="2">
-        <v>58.8</v>
+        <v>16.4</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>260</v>
@@ -4756,13 +4516,13 @@
         <v>136</v>
       </c>
       <c r="G129" s="2">
+        <v>54.4</v>
+      </c>
+      <c r="H129" s="2">
+        <v>62.8</v>
+      </c>
+      <c r="I129" s="2">
         <v>49.2</v>
-      </c>
-      <c r="H129" s="2">
-        <v>58.4</v>
-      </c>
-      <c r="I129" s="2">
-        <v>74.8</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>260</v>
@@ -4773,13 +4533,13 @@
         <v>137</v>
       </c>
       <c r="G130" s="2">
-        <v>80</v>
+        <v>53.2</v>
       </c>
       <c r="H130" s="2">
-        <v>80.8</v>
+        <v>54.4</v>
       </c>
       <c r="I130" s="2">
-        <v>75.2</v>
+        <v>52.8</v>
       </c>
       <c r="J130" s="4" t="s">
         <v>260</v>
@@ -4790,13 +4550,13 @@
         <v>138</v>
       </c>
       <c r="G131" s="2">
-        <v>94.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H131" s="2">
-        <v>96.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="I131" s="2">
-        <v>95.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>260</v>
@@ -4807,13 +4567,13 @@
         <v>139</v>
       </c>
       <c r="G132" s="2">
-        <v>33.2</v>
+        <v>14.8</v>
       </c>
       <c r="H132" s="2">
-        <v>50.8</v>
+        <v>19.6</v>
       </c>
       <c r="I132" s="2">
-        <v>54.4</v>
+        <v>23.6</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>260</v>
@@ -4824,13 +4584,13 @@
         <v>140</v>
       </c>
       <c r="G133" s="2">
-        <v>57.2</v>
+        <v>35.2</v>
       </c>
       <c r="H133" s="2">
-        <v>44</v>
+        <v>30.4</v>
       </c>
       <c r="I133" s="2">
-        <v>46</v>
+        <v>61.6</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>260</v>
@@ -4841,13 +4601,13 @@
         <v>141</v>
       </c>
       <c r="G134" s="2">
-        <v>54</v>
+        <v>47.6</v>
       </c>
       <c r="H134" s="2">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="I134" s="2">
-        <v>82</v>
+        <v>48.8</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>260</v>
@@ -4858,13 +4618,13 @@
         <v>142</v>
       </c>
       <c r="G135" s="2">
-        <v>75.2</v>
+        <v>78.8</v>
       </c>
       <c r="H135" s="2">
-        <v>93.2</v>
+        <v>61.6</v>
       </c>
       <c r="I135" s="2">
-        <v>63.6</v>
+        <v>48</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>260</v>
@@ -4875,13 +4635,13 @@
         <v>143</v>
       </c>
       <c r="G136" s="2">
-        <v>62.8</v>
+        <v>52.8</v>
       </c>
       <c r="H136" s="2">
-        <v>49.2</v>
+        <v>36.8</v>
       </c>
       <c r="I136" s="2">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>260</v>
@@ -4892,13 +4652,13 @@
         <v>144</v>
       </c>
       <c r="G137" s="2">
-        <v>87.59999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="H137" s="2">
-        <v>92</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I137" s="2">
-        <v>90</v>
+        <v>79.2</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>260</v>
@@ -4909,13 +4669,13 @@
         <v>145</v>
       </c>
       <c r="G138" s="2">
-        <v>92.8</v>
+        <v>1.6</v>
       </c>
       <c r="H138" s="2">
-        <v>83.2</v>
+        <v>3.6</v>
       </c>
       <c r="I138" s="2">
-        <v>83.2</v>
+        <v>5.6</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>260</v>
@@ -4926,13 +4686,13 @@
         <v>146</v>
       </c>
       <c r="G139" s="2">
-        <v>15.6</v>
+        <v>63.6</v>
       </c>
       <c r="H139" s="2">
-        <v>27.2</v>
+        <v>72.8</v>
       </c>
       <c r="I139" s="2">
-        <v>15.2</v>
+        <v>54.4</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>260</v>
@@ -4943,13 +4703,13 @@
         <v>147</v>
       </c>
       <c r="G140" s="2">
-        <v>96.8</v>
+        <v>86</v>
       </c>
       <c r="H140" s="2">
-        <v>84.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I140" s="2">
-        <v>78</v>
+        <v>85.2</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>260</v>
@@ -4960,13 +4720,13 @@
         <v>148</v>
       </c>
       <c r="G141" s="2">
-        <v>30.4</v>
+        <v>45.6</v>
       </c>
       <c r="H141" s="2">
-        <v>61.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I141" s="2">
-        <v>60.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>260</v>
@@ -4977,13 +4737,13 @@
         <v>149</v>
       </c>
       <c r="G142" s="2">
-        <v>81.2</v>
+        <v>40.4</v>
       </c>
       <c r="H142" s="2">
-        <v>88.8</v>
+        <v>35.2</v>
       </c>
       <c r="I142" s="2">
-        <v>94.8</v>
+        <v>57.2</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>260</v>
@@ -4994,13 +4754,13 @@
         <v>150</v>
       </c>
       <c r="G143" s="2">
-        <v>50.8</v>
+        <v>37.6</v>
       </c>
       <c r="H143" s="2">
-        <v>48.8</v>
+        <v>39.6</v>
       </c>
       <c r="I143" s="2">
-        <v>79.59999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>260</v>
@@ -5011,13 +4771,13 @@
         <v>151</v>
       </c>
       <c r="G144" s="2">
-        <v>61.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H144" s="2">
-        <v>48</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I144" s="2">
-        <v>49.6</v>
+        <v>66.8</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>260</v>
@@ -5028,13 +4788,13 @@
         <v>152</v>
       </c>
       <c r="G145" s="2">
-        <v>36.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H145" s="2">
-        <v>43.6</v>
+        <v>83.2</v>
       </c>
       <c r="I145" s="2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>260</v>
@@ -5045,13 +4805,13 @@
         <v>153</v>
       </c>
       <c r="G146" s="2">
-        <v>79.59999999999999</v>
+        <v>28</v>
       </c>
       <c r="H146" s="2">
-        <v>79.2</v>
+        <v>31.6</v>
       </c>
       <c r="I146" s="2">
-        <v>86</v>
+        <v>19.2</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>260</v>
@@ -5062,13 +4822,13 @@
         <v>154</v>
       </c>
       <c r="G147" s="2">
-        <v>5.6</v>
+        <v>14.4</v>
       </c>
       <c r="H147" s="2">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="I147" s="2">
-        <v>6</v>
+        <v>15.2</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>260</v>
@@ -5079,13 +4839,13 @@
         <v>155</v>
       </c>
       <c r="G148" s="2">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="H148" s="2">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="I148" s="2">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>260</v>
@@ -5096,13 +4856,13 @@
         <v>156</v>
       </c>
       <c r="G149" s="2">
-        <v>21.2</v>
+        <v>22.4</v>
       </c>
       <c r="H149" s="2">
-        <v>1.2</v>
+        <v>13.2</v>
       </c>
       <c r="I149" s="2">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>260</v>
@@ -5113,13 +4873,13 @@
         <v>157</v>
       </c>
       <c r="G150" s="2">
-        <v>72.8</v>
+        <v>60.4</v>
       </c>
       <c r="H150" s="2">
-        <v>54.4</v>
+        <v>62.4</v>
       </c>
       <c r="I150" s="2">
-        <v>45.2</v>
+        <v>73.2</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>260</v>
@@ -5130,13 +4890,13 @@
         <v>158</v>
       </c>
       <c r="G151" s="2">
-        <v>16</v>
+        <v>20.4</v>
       </c>
       <c r="H151" s="2">
-        <v>14.8</v>
+        <v>20.8</v>
       </c>
       <c r="I151" s="2">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>260</v>
@@ -5147,13 +4907,13 @@
         <v>159</v>
       </c>
       <c r="G152" s="2">
-        <v>68</v>
+        <v>55.2</v>
       </c>
       <c r="H152" s="2">
-        <v>58.8</v>
+        <v>54.8</v>
       </c>
       <c r="I152" s="2">
-        <v>84.8</v>
+        <v>50</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>260</v>
@@ -5164,13 +4924,13 @@
         <v>160</v>
       </c>
       <c r="G153" s="2">
-        <v>65.59999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="H153" s="2">
-        <v>70.40000000000001</v>
+        <v>31.2</v>
       </c>
       <c r="I153" s="2">
-        <v>77.2</v>
+        <v>45.6</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>260</v>
@@ -5181,13 +4941,13 @@
         <v>161</v>
       </c>
       <c r="G154" s="2">
-        <v>35.2</v>
+        <v>12.8</v>
       </c>
       <c r="H154" s="2">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="I154" s="2">
-        <v>41.6</v>
+        <v>3.6</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>260</v>
@@ -5198,13 +4958,13 @@
         <v>162</v>
       </c>
       <c r="G155" s="2">
-        <v>46.4</v>
+        <v>60.8</v>
       </c>
       <c r="H155" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I155" s="2">
-        <v>61.6</v>
+        <v>56.8</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>260</v>
@@ -5215,13 +4975,13 @@
         <v>163</v>
       </c>
       <c r="G156" s="2">
-        <v>31.6</v>
+        <v>28.4</v>
       </c>
       <c r="H156" s="2">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="I156" s="2">
-        <v>8</v>
+        <v>62.8</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>260</v>
@@ -5232,13 +4992,13 @@
         <v>164</v>
       </c>
       <c r="G157" s="2">
-        <v>26</v>
+        <v>39.2</v>
       </c>
       <c r="H157" s="2">
-        <v>15.2</v>
+        <v>48</v>
       </c>
       <c r="I157" s="2">
-        <v>36.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J157" s="4" t="s">
         <v>260</v>
@@ -5249,13 +5009,13 @@
         <v>165</v>
       </c>
       <c r="G158" s="2">
-        <v>13.2</v>
+        <v>85.2</v>
       </c>
       <c r="H158" s="2">
-        <v>10.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I158" s="2">
-        <v>7.6</v>
+        <v>96.8</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>260</v>
@@ -5266,13 +5026,13 @@
         <v>166</v>
       </c>
       <c r="G159" s="2">
-        <v>62.4</v>
+        <v>96.8</v>
       </c>
       <c r="H159" s="2">
-        <v>73.2</v>
+        <v>96</v>
       </c>
       <c r="I159" s="2">
-        <v>71.2</v>
+        <v>98</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>260</v>
@@ -5283,13 +5043,13 @@
         <v>167</v>
       </c>
       <c r="G160" s="2">
-        <v>54.8</v>
+        <v>90.8</v>
       </c>
       <c r="H160" s="2">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I160" s="2">
-        <v>35.6</v>
+        <v>55.6</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>260</v>
@@ -5300,13 +5060,13 @@
         <v>168</v>
       </c>
       <c r="G161" s="2">
-        <v>31.2</v>
+        <v>24</v>
       </c>
       <c r="H161" s="2">
-        <v>45.6</v>
+        <v>28.8</v>
       </c>
       <c r="I161" s="2">
-        <v>64</v>
+        <v>55.2</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>260</v>
@@ -5317,13 +5077,13 @@
         <v>169</v>
       </c>
       <c r="G162" s="2">
-        <v>5.2</v>
+        <v>10.8</v>
       </c>
       <c r="H162" s="2">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="I162" s="2">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>260</v>
@@ -5334,13 +5094,13 @@
         <v>170</v>
       </c>
       <c r="G163" s="2">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="H163" s="2">
-        <v>56.8</v>
+        <v>26.4</v>
       </c>
       <c r="I163" s="2">
-        <v>26.4</v>
+        <v>42</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>260</v>
@@ -5351,13 +5111,13 @@
         <v>171</v>
       </c>
       <c r="G164" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H164" s="2">
-        <v>65.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="I164" s="2">
-        <v>34.4</v>
+        <v>71.2</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>260</v>
@@ -5368,13 +5128,13 @@
         <v>172</v>
       </c>
       <c r="G165" s="2">
-        <v>91.59999999999999</v>
+        <v>50.8</v>
       </c>
       <c r="H165" s="2">
-        <v>96.8</v>
+        <v>49.6</v>
       </c>
       <c r="I165" s="2">
-        <v>94.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>260</v>
@@ -5385,13 +5145,13 @@
         <v>173</v>
       </c>
       <c r="G166" s="2">
-        <v>30</v>
+        <v>43.2</v>
       </c>
       <c r="H166" s="2">
-        <v>12</v>
+        <v>33.6</v>
       </c>
       <c r="I166" s="2">
-        <v>28.4</v>
+        <v>17.6</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>260</v>
@@ -5402,13 +5162,13 @@
         <v>174</v>
       </c>
       <c r="G167" s="2">
-        <v>96</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H167" s="2">
-        <v>98</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I167" s="2">
-        <v>91.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>260</v>
@@ -5419,13 +5179,13 @@
         <v>175</v>
       </c>
       <c r="G168" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H168" s="2">
-        <v>55.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I168" s="2">
-        <v>21.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>260</v>
@@ -5436,13 +5196,13 @@
         <v>176</v>
       </c>
       <c r="G169" s="2">
-        <v>28.8</v>
+        <v>83.2</v>
       </c>
       <c r="H169" s="2">
-        <v>55.2</v>
+        <v>79.2</v>
       </c>
       <c r="I169" s="2">
-        <v>53.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>260</v>
@@ -5453,13 +5213,13 @@
         <v>177</v>
       </c>
       <c r="G170" s="2">
-        <v>8.4</v>
+        <v>42.8</v>
       </c>
       <c r="H170" s="2">
-        <v>16</v>
+        <v>37.6</v>
       </c>
       <c r="I170" s="2">
-        <v>3.2</v>
+        <v>24.8</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>260</v>
@@ -5470,13 +5230,13 @@
         <v>178</v>
       </c>
       <c r="G171" s="2">
-        <v>26.4</v>
+        <v>64.8</v>
       </c>
       <c r="H171" s="2">
-        <v>42</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I171" s="2">
-        <v>41.2</v>
+        <v>68.8</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>260</v>
@@ -5487,13 +5247,13 @@
         <v>179</v>
       </c>
       <c r="G172" s="2">
-        <v>49.6</v>
+        <v>79.2</v>
       </c>
       <c r="H172" s="2">
-        <v>58</v>
+        <v>63.2</v>
       </c>
       <c r="I172" s="2">
-        <v>40</v>
+        <v>39.2</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>260</v>
@@ -5504,13 +5264,13 @@
         <v>180</v>
       </c>
       <c r="G173" s="2">
-        <v>69.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="H173" s="2">
-        <v>49.6</v>
+        <v>92</v>
       </c>
       <c r="I173" s="2">
-        <v>58.4</v>
+        <v>89.2</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>260</v>
@@ -5521,13 +5281,13 @@
         <v>181</v>
       </c>
       <c r="G174" s="2">
-        <v>22</v>
+        <v>98.8</v>
       </c>
       <c r="H174" s="2">
-        <v>28</v>
+        <v>88.8</v>
       </c>
       <c r="I174" s="2">
-        <v>31.2</v>
+        <v>84.8</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>260</v>
@@ -5538,13 +5298,13 @@
         <v>182</v>
       </c>
       <c r="G175" s="2">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="H175" s="2">
-        <v>46.4</v>
+        <v>11.6</v>
       </c>
       <c r="I175" s="2">
-        <v>52.4</v>
+        <v>28.8</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>260</v>
@@ -5555,13 +5315,13 @@
         <v>183</v>
       </c>
       <c r="G176" s="2">
-        <v>74.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H176" s="2">
-        <v>74.40000000000001</v>
+        <v>2</v>
       </c>
       <c r="I176" s="2">
-        <v>71.59999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>260</v>
@@ -5572,13 +5332,13 @@
         <v>184</v>
       </c>
       <c r="G177" s="2">
-        <v>79.2</v>
+        <v>71.2</v>
       </c>
       <c r="H177" s="2">
-        <v>68.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I177" s="2">
-        <v>19.2</v>
+        <v>86</v>
       </c>
       <c r="J177" s="4" t="s">
         <v>260</v>
@@ -5589,13 +5349,13 @@
         <v>185</v>
       </c>
       <c r="G178" s="2">
-        <v>58</v>
+        <v>15.6</v>
       </c>
       <c r="H178" s="2">
-        <v>61.2</v>
+        <v>23.6</v>
       </c>
       <c r="I178" s="2">
-        <v>56.8</v>
+        <v>12.4</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>260</v>
@@ -5606,13 +5366,13 @@
         <v>186</v>
       </c>
       <c r="G179" s="2">
-        <v>68.40000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H179" s="2">
-        <v>68.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I179" s="2">
-        <v>70.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>260</v>
@@ -5623,13 +5383,13 @@
         <v>187</v>
       </c>
       <c r="G180" s="2">
-        <v>63.2</v>
+        <v>53.6</v>
       </c>
       <c r="H180" s="2">
-        <v>39.2</v>
+        <v>55.2</v>
       </c>
       <c r="I180" s="2">
-        <v>33.6</v>
+        <v>52.4</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>260</v>
@@ -5640,13 +5400,13 @@
         <v>188</v>
       </c>
       <c r="G181" s="2">
-        <v>25.2</v>
+        <v>45.2</v>
       </c>
       <c r="H181" s="2">
-        <v>37.6</v>
+        <v>38.8</v>
       </c>
       <c r="I181" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>260</v>
@@ -5657,13 +5417,13 @@
         <v>189</v>
       </c>
       <c r="G182" s="2">
-        <v>92</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H182" s="2">
-        <v>89.2</v>
+        <v>84</v>
       </c>
       <c r="I182" s="2">
-        <v>80.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>260</v>
@@ -5674,13 +5434,13 @@
         <v>190</v>
       </c>
       <c r="G183" s="2">
-        <v>2</v>
+        <v>19.6</v>
       </c>
       <c r="H183" s="2">
-        <v>0.8</v>
+        <v>17.2</v>
       </c>
       <c r="I183" s="2">
-        <v>6.4</v>
+        <v>16.8</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>260</v>
@@ -5691,13 +5451,13 @@
         <v>191</v>
       </c>
       <c r="G184" s="2">
-        <v>77.2</v>
+        <v>10</v>
       </c>
       <c r="H184" s="2">
-        <v>86</v>
+        <v>0.8</v>
       </c>
       <c r="I184" s="2">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>260</v>
@@ -5708,13 +5468,13 @@
         <v>192</v>
       </c>
       <c r="G185" s="2">
-        <v>9.199999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="H185" s="2">
-        <v>10.4</v>
+        <v>34.8</v>
       </c>
       <c r="I185" s="2">
-        <v>6.8</v>
+        <v>22.8</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>260</v>
@@ -5725,13 +5485,13 @@
         <v>193</v>
       </c>
       <c r="G186" s="2">
-        <v>52.4</v>
+        <v>42</v>
       </c>
       <c r="H186" s="2">
-        <v>36.8</v>
+        <v>34</v>
       </c>
       <c r="I186" s="2">
-        <v>29.2</v>
+        <v>30.4</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>260</v>
@@ -5742,13 +5502,13 @@
         <v>194</v>
       </c>
       <c r="G187" s="2">
-        <v>38.8</v>
+        <v>17.6</v>
       </c>
       <c r="H187" s="2">
-        <v>36</v>
+        <v>16.4</v>
       </c>
       <c r="I187" s="2">
-        <v>33.2</v>
+        <v>25.2</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>260</v>
@@ -5759,13 +5519,13 @@
         <v>195</v>
       </c>
       <c r="G188" s="2">
-        <v>84</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H188" s="2">
-        <v>85.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="I188" s="2">
-        <v>89.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>260</v>
@@ -5776,13 +5536,13 @@
         <v>196</v>
       </c>
       <c r="G189" s="2">
-        <v>17.2</v>
+        <v>44.8</v>
       </c>
       <c r="H189" s="2">
-        <v>16.8</v>
+        <v>48.8</v>
       </c>
       <c r="I189" s="2">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>260</v>
@@ -5793,13 +5553,13 @@
         <v>197</v>
       </c>
       <c r="G190" s="2">
-        <v>78.40000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="H190" s="2">
-        <v>87.2</v>
+        <v>17.6</v>
       </c>
       <c r="I190" s="2">
-        <v>82.8</v>
+        <v>33.2</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>260</v>
@@ -5810,13 +5570,13 @@
         <v>198</v>
       </c>
       <c r="G191" s="2">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="H191" s="2">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="I191" s="2">
-        <v>12.8</v>
+        <v>18</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>260</v>
@@ -5827,13 +5587,13 @@
         <v>199</v>
       </c>
       <c r="G192" s="2">
-        <v>34.8</v>
+        <v>30.4</v>
       </c>
       <c r="H192" s="2">
-        <v>22.8</v>
+        <v>9.6</v>
       </c>
       <c r="I192" s="2">
-        <v>16.4</v>
+        <v>23.2</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>260</v>
@@ -5844,13 +5604,13 @@
         <v>200</v>
       </c>
       <c r="G193" s="2">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="H193" s="2">
-        <v>30.4</v>
+        <v>15.2</v>
       </c>
       <c r="I193" s="2">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>260</v>
@@ -5861,13 +5621,13 @@
         <v>201</v>
       </c>
       <c r="G194" s="2">
-        <v>16.4</v>
+        <v>58.8</v>
       </c>
       <c r="H194" s="2">
-        <v>25.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I194" s="2">
-        <v>11.6</v>
+        <v>75.2</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>260</v>
@@ -5878,13 +5638,13 @@
         <v>202</v>
       </c>
       <c r="G195" s="2">
-        <v>63.6</v>
+        <v>37.2</v>
       </c>
       <c r="H195" s="2">
-        <v>72.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I195" s="2">
-        <v>50</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>260</v>
@@ -5895,13 +5655,13 @@
         <v>203</v>
       </c>
       <c r="G196" s="2">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="H196" s="2">
-        <v>22.4</v>
+        <v>50.4</v>
       </c>
       <c r="I196" s="2">
-        <v>50.8</v>
+        <v>60.8</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>260</v>
@@ -5912,13 +5672,13 @@
         <v>204</v>
       </c>
       <c r="G197" s="2">
-        <v>17.6</v>
+        <v>8</v>
       </c>
       <c r="H197" s="2">
-        <v>33.2</v>
+        <v>29.6</v>
       </c>
       <c r="I197" s="2">
-        <v>16.8</v>
+        <v>52</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>260</v>
@@ -5929,13 +5689,13 @@
         <v>205</v>
       </c>
       <c r="G198" s="2">
-        <v>4.8</v>
+        <v>23.6</v>
       </c>
       <c r="H198" s="2">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="I198" s="2">
-        <v>27.2</v>
+        <v>14</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>260</v>
@@ -5946,13 +5706,13 @@
         <v>206</v>
       </c>
       <c r="G199" s="2">
-        <v>9.6</v>
+        <v>46</v>
       </c>
       <c r="H199" s="2">
-        <v>23.2</v>
+        <v>47.6</v>
       </c>
       <c r="I199" s="2">
-        <v>12</v>
+        <v>51.6</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>260</v>
@@ -5963,13 +5723,13 @@
         <v>207</v>
       </c>
       <c r="G200" s="2">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="H200" s="2">
-        <v>4.4</v>
+        <v>22.8</v>
       </c>
       <c r="I200" s="2">
-        <v>44.8</v>
+        <v>34.4</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>260</v>
@@ -5980,13 +5740,13 @@
         <v>208</v>
       </c>
       <c r="G201" s="2">
-        <v>50.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H201" s="2">
-        <v>60.8</v>
+        <v>87.2</v>
       </c>
       <c r="I201" s="2">
-        <v>46.4</v>
+        <v>70.8</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>260</v>
@@ -5997,13 +5757,13 @@
         <v>209</v>
       </c>
       <c r="G202" s="2">
-        <v>29.6</v>
+        <v>62</v>
       </c>
       <c r="H202" s="2">
-        <v>52</v>
+        <v>36.4</v>
       </c>
       <c r="I202" s="2">
-        <v>48</v>
+        <v>18.8</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>260</v>
@@ -6014,13 +5774,13 @@
         <v>210</v>
       </c>
       <c r="G203" s="2">
-        <v>18.4</v>
+        <v>29.6</v>
       </c>
       <c r="H203" s="2">
-        <v>14</v>
+        <v>27.2</v>
       </c>
       <c r="I203" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>260</v>
@@ -6031,13 +5791,13 @@
         <v>211</v>
       </c>
       <c r="G204" s="2">
-        <v>14.4</v>
+        <v>34</v>
       </c>
       <c r="H204" s="2">
-        <v>11.2</v>
+        <v>51.2</v>
       </c>
       <c r="I204" s="2">
-        <v>17.6</v>
+        <v>54.8</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>260</v>
@@ -6048,13 +5808,13 @@
         <v>212</v>
       </c>
       <c r="G205" s="2">
-        <v>30.8</v>
+        <v>76</v>
       </c>
       <c r="H205" s="2">
-        <v>28.4</v>
+        <v>66</v>
       </c>
       <c r="I205" s="2">
-        <v>20.4</v>
+        <v>44.8</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>260</v>
@@ -6065,13 +5825,13 @@
         <v>213</v>
       </c>
       <c r="G206" s="2">
-        <v>22.8</v>
+        <v>26.8</v>
       </c>
       <c r="H206" s="2">
-        <v>34.4</v>
+        <v>16.8</v>
       </c>
       <c r="I206" s="2">
-        <v>47.6</v>
+        <v>8</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>260</v>
@@ -6082,13 +5842,13 @@
         <v>214</v>
       </c>
       <c r="G207" s="2">
-        <v>87.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H207" s="2">
-        <v>70.8</v>
+        <v>52</v>
       </c>
       <c r="I207" s="2">
-        <v>56.4</v>
+        <v>46</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>260</v>
@@ -6099,13 +5859,13 @@
         <v>215</v>
       </c>
       <c r="G208" s="2">
-        <v>81.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="H208" s="2">
-        <v>91.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I208" s="2">
-        <v>62.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>260</v>
@@ -6116,13 +5876,13 @@
         <v>216</v>
       </c>
       <c r="G209" s="2">
-        <v>36.4</v>
+        <v>65.2</v>
       </c>
       <c r="H209" s="2">
-        <v>18.8</v>
+        <v>76</v>
       </c>
       <c r="I209" s="2">
-        <v>57.2</v>
+        <v>47.2</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>260</v>
@@ -6133,13 +5893,13 @@
         <v>217</v>
       </c>
       <c r="G210" s="2">
-        <v>27.2</v>
+        <v>73.2</v>
       </c>
       <c r="H210" s="2">
-        <v>40</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I210" s="2">
-        <v>42</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>260</v>
@@ -6150,13 +5910,13 @@
         <v>218</v>
       </c>
       <c r="G211" s="2">
-        <v>51.2</v>
+        <v>2.8</v>
       </c>
       <c r="H211" s="2">
-        <v>54.8</v>
+        <v>7.2</v>
       </c>
       <c r="I211" s="2">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>260</v>
@@ -6167,13 +5927,13 @@
         <v>219</v>
       </c>
       <c r="G212" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H212" s="2">
-        <v>44.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I212" s="2">
-        <v>38.4</v>
+        <v>62.4</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>260</v>
@@ -6184,13 +5944,13 @@
         <v>220</v>
       </c>
       <c r="G213" s="2">
-        <v>73.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H213" s="2">
-        <v>65.2</v>
+        <v>74.8</v>
       </c>
       <c r="I213" s="2">
-        <v>67.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>260</v>
@@ -6201,13 +5961,13 @@
         <v>221</v>
       </c>
       <c r="G214" s="2">
-        <v>52</v>
+        <v>23.2</v>
       </c>
       <c r="H214" s="2">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="I214" s="2">
-        <v>49.2</v>
+        <v>15.6</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>260</v>
@@ -6218,13 +5978,13 @@
         <v>222</v>
       </c>
       <c r="G215" s="2">
-        <v>85.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="H215" s="2">
-        <v>78.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="I215" s="2">
-        <v>79.2</v>
+        <v>50.4</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>260</v>
@@ -6235,13 +5995,13 @@
         <v>223</v>
       </c>
       <c r="G216" s="2">
-        <v>76.40000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="H216" s="2">
-        <v>82.40000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I216" s="2">
-        <v>89.2</v>
+        <v>6.4</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>260</v>
@@ -6252,13 +6012,13 @@
         <v>224</v>
       </c>
       <c r="G217" s="2">
-        <v>7.2</v>
+        <v>82.8</v>
       </c>
       <c r="H217" s="2">
-        <v>10</v>
+        <v>65.2</v>
       </c>
       <c r="I217" s="2">
-        <v>3.6</v>
+        <v>66</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>260</v>
@@ -6269,13 +6029,13 @@
         <v>225</v>
       </c>
       <c r="G218" s="2">
-        <v>35.6</v>
+        <v>66</v>
       </c>
       <c r="H218" s="2">
-        <v>34.8</v>
+        <v>40.8</v>
       </c>
       <c r="I218" s="2">
-        <v>40.4</v>
+        <v>20</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>260</v>
@@ -6286,13 +6046,13 @@
         <v>226</v>
       </c>
       <c r="G219" s="2">
-        <v>74.8</v>
+        <v>7.6</v>
       </c>
       <c r="H219" s="2">
-        <v>76</v>
+        <v>6.8</v>
       </c>
       <c r="I219" s="2">
-        <v>91.2</v>
+        <v>2.4</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>260</v>
@@ -6303,13 +6063,13 @@
         <v>227</v>
       </c>
       <c r="G220" s="2">
-        <v>45.6</v>
+        <v>38.4</v>
       </c>
       <c r="H220" s="2">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="I220" s="2">
-        <v>64.40000000000001</v>
+        <v>38</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>260</v>
@@ -6320,13 +6080,13 @@
         <v>228</v>
       </c>
       <c r="G221" s="2">
-        <v>56.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H221" s="2">
-        <v>50.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I221" s="2">
-        <v>42.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>260</v>
@@ -6337,13 +6097,13 @@
         <v>229</v>
       </c>
       <c r="G222" s="2">
-        <v>7.6</v>
+        <v>33.2</v>
       </c>
       <c r="H222" s="2">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="I222" s="2">
-        <v>1.2</v>
+        <v>31.6</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>260</v>
@@ -6354,13 +6114,13 @@
         <v>230</v>
       </c>
       <c r="G223" s="2">
-        <v>40.8</v>
+        <v>43.6</v>
       </c>
       <c r="H223" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I223" s="2">
-        <v>13.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>260</v>
@@ -6371,13 +6131,13 @@
         <v>231</v>
       </c>
       <c r="G224" s="2">
-        <v>25.6</v>
+        <v>84.8</v>
       </c>
       <c r="H224" s="2">
-        <v>41.2</v>
+        <v>60.8</v>
       </c>
       <c r="I224" s="2">
-        <v>36.8</v>
+        <v>64</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>260</v>
@@ -6388,13 +6148,13 @@
         <v>232</v>
       </c>
       <c r="G225" s="2">
-        <v>93.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H225" s="2">
-        <v>89.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I225" s="2">
-        <v>81.2</v>
+        <v>32.8</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>260</v>
@@ -6405,13 +6165,13 @@
         <v>233</v>
       </c>
       <c r="G226" s="2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H226" s="2">
-        <v>31.6</v>
+        <v>21.6</v>
       </c>
       <c r="I226" s="2">
-        <v>34.8</v>
+        <v>13.6</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>260</v>
@@ -6422,13 +6182,13 @@
         <v>234</v>
       </c>
       <c r="G227" s="2">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="H227" s="2">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="I227" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>260</v>
@@ -6439,13 +6199,13 @@
         <v>235</v>
       </c>
       <c r="G228" s="2">
-        <v>90.8</v>
+        <v>13.2</v>
       </c>
       <c r="H228" s="2">
-        <v>32.8</v>
+        <v>2.8</v>
       </c>
       <c r="I228" s="2">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="J228" s="4" t="s">
         <v>260</v>
@@ -6456,13 +6216,13 @@
         <v>236</v>
       </c>
       <c r="G229" s="2">
-        <v>4.4</v>
+        <v>94.8</v>
       </c>
       <c r="H229" s="2">
-        <v>4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I229" s="2">
-        <v>4.8</v>
+        <v>82</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>260</v>
@@ -6473,13 +6233,13 @@
         <v>237</v>
       </c>
       <c r="G230" s="2">
-        <v>2.8</v>
+        <v>54</v>
       </c>
       <c r="H230" s="2">
-        <v>4.8</v>
+        <v>51.6</v>
       </c>
       <c r="I230" s="2">
-        <v>10.8</v>
+        <v>41.6</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>260</v>
@@ -6490,13 +6250,13 @@
         <v>238</v>
       </c>
       <c r="G231" s="2">
-        <v>51.6</v>
+        <v>63.2</v>
       </c>
       <c r="H231" s="2">
-        <v>41.6</v>
+        <v>72</v>
       </c>
       <c r="I231" s="2">
-        <v>19.6</v>
+        <v>77.2</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>260</v>
@@ -6507,13 +6267,13 @@
         <v>239</v>
       </c>
       <c r="G232" s="2">
-        <v>72</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H232" s="2">
-        <v>77.2</v>
+        <v>47.2</v>
       </c>
       <c r="I232" s="2">
-        <v>82.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>260</v>
@@ -6524,13 +6284,13 @@
         <v>240</v>
       </c>
       <c r="G233" s="2">
+        <v>46.4</v>
+      </c>
+      <c r="H233" s="2">
         <v>43.2</v>
       </c>
-      <c r="H233" s="2">
+      <c r="I233" s="2">
         <v>40.8</v>
-      </c>
-      <c r="I233" s="2">
-        <v>18.8</v>
       </c>
       <c r="J233" s="4" t="s">
         <v>260</v>
@@ -6541,13 +6301,13 @@
         <v>241</v>
       </c>
       <c r="G234" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="H234" s="2">
         <v>3.2</v>
       </c>
-      <c r="H234" s="2">
+      <c r="I234" s="2">
         <v>7.6</v>
-      </c>
-      <c r="I234" s="2">
-        <v>14.4</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>260</v>
@@ -6558,13 +6318,13 @@
         <v>242</v>
       </c>
       <c r="G235" s="2">
+        <v>54.8</v>
+      </c>
+      <c r="H235" s="2">
         <v>55.6</v>
       </c>
-      <c r="H235" s="2">
+      <c r="I235" s="2">
         <v>66.40000000000001</v>
-      </c>
-      <c r="I235" s="2">
-        <v>65.59999999999999</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>260</v>
@@ -6575,13 +6335,13 @@
         <v>243</v>
       </c>
       <c r="G236" s="2">
+        <v>41.2</v>
+      </c>
+      <c r="H236" s="2">
         <v>41.6</v>
       </c>
-      <c r="H236" s="2">
+      <c r="I236" s="2">
         <v>53.6</v>
-      </c>
-      <c r="I236" s="2">
-        <v>66.8</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>260</v>
@@ -6592,13 +6352,13 @@
         <v>244</v>
       </c>
       <c r="G237" s="2">
+        <v>2</v>
+      </c>
+      <c r="H237" s="2">
         <v>19.2</v>
       </c>
-      <c r="H237" s="2">
+      <c r="I237" s="2">
         <v>29.2</v>
-      </c>
-      <c r="I237" s="2">
-        <v>55.2</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>260</v>
@@ -6609,13 +6369,13 @@
         <v>245</v>
       </c>
       <c r="G238" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="H238" s="2">
         <v>75.59999999999999</v>
       </c>
-      <c r="H238" s="2">
+      <c r="I238" s="2">
         <v>78.8</v>
-      </c>
-      <c r="I238" s="2">
-        <v>61.2</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>260</v>
@@ -6626,13 +6386,13 @@
         <v>246</v>
       </c>
       <c r="G239" s="2">
+        <v>80</v>
+      </c>
+      <c r="H239" s="2">
         <v>80.8</v>
       </c>
-      <c r="H239" s="2">
+      <c r="I239" s="2">
         <v>80.40000000000001</v>
-      </c>
-      <c r="I239" s="2">
-        <v>73.59999999999999</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>260</v>
@@ -6643,13 +6403,13 @@
         <v>247</v>
       </c>
       <c r="G240" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="H240" s="2">
         <v>14.8</v>
       </c>
-      <c r="H240" s="2">
+      <c r="I240" s="2">
         <v>24.4</v>
-      </c>
-      <c r="I240" s="2">
-        <v>31.6</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>260</v>
@@ -6660,13 +6420,13 @@
         <v>248</v>
       </c>
       <c r="G241" s="2">
+        <v>24.8</v>
+      </c>
+      <c r="H241" s="2">
         <v>10.4</v>
       </c>
-      <c r="H241" s="2">
+      <c r="I241" s="2">
         <v>13.2</v>
-      </c>
-      <c r="I241" s="2">
-        <v>23.2</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>260</v>
@@ -6677,13 +6437,13 @@
         <v>249</v>
       </c>
       <c r="G242" s="2">
-        <v>64.40000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="H242" s="2">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="I242" s="2">
-        <v>63.2</v>
+        <v>30.8</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>260</v>
@@ -6694,13 +6454,13 @@
         <v>250</v>
       </c>
       <c r="G243" s="2">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="H243" s="2">
-        <v>30.8</v>
+        <v>22.4</v>
       </c>
       <c r="I243" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>260</v>
@@ -6711,13 +6471,13 @@
         <v>251</v>
       </c>
       <c r="G244" s="2">
-        <v>22.4</v>
+        <v>49.2</v>
       </c>
       <c r="H244" s="2">
-        <v>30</v>
+        <v>42.4</v>
       </c>
       <c r="I244" s="2">
-        <v>10</v>
+        <v>35.6</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>260</v>
@@ -6728,13 +6488,13 @@
         <v>252</v>
       </c>
       <c r="G245" s="2">
-        <v>42.4</v>
+        <v>27.2</v>
       </c>
       <c r="H245" s="2">
-        <v>35.6</v>
+        <v>18</v>
       </c>
       <c r="I245" s="2">
-        <v>57.6</v>
+        <v>19.6</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>260</v>
@@ -6745,13 +6505,13 @@
         <v>253</v>
       </c>
       <c r="G246" s="2">
-        <v>18</v>
+        <v>55.6</v>
       </c>
       <c r="H246" s="2">
-        <v>19.6</v>
+        <v>43.6</v>
       </c>
       <c r="I246" s="2">
-        <v>44.4</v>
+        <v>46.8</v>
       </c>
       <c r="J246" s="4" t="s">
         <v>260</v>
@@ -6762,13 +6522,13 @@
         <v>254</v>
       </c>
       <c r="G247" s="2">
-        <v>43.6</v>
+        <v>57.2</v>
       </c>
       <c r="H247" s="2">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
       <c r="I247" s="2">
-        <v>38.8</v>
+        <v>33.6</v>
       </c>
       <c r="J247" s="4" t="s">
         <v>260</v>
@@ -6779,13 +6539,13 @@
         <v>255</v>
       </c>
       <c r="G248" s="2">
-        <v>40.4</v>
+        <v>3.6</v>
       </c>
       <c r="H248" s="2">
-        <v>33.6</v>
+        <v>8</v>
       </c>
       <c r="I248" s="2">
-        <v>32.8</v>
+        <v>38.4</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>260</v>
@@ -6796,13 +6556,13 @@
         <v>256</v>
       </c>
       <c r="G249" s="2">
-        <v>8</v>
+        <v>38.8</v>
       </c>
       <c r="H249" s="2">
-        <v>38.4</v>
+        <v>58.4</v>
       </c>
       <c r="I249" s="2">
-        <v>20.8</v>
+        <v>69.2</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>260</v>
@@ -6813,13 +6573,13 @@
         <v>257</v>
       </c>
       <c r="G250" s="2">
-        <v>58.4</v>
+        <v>15.2</v>
       </c>
       <c r="H250" s="2">
-        <v>69.2</v>
+        <v>46.8</v>
       </c>
       <c r="I250" s="2">
-        <v>68.8</v>
+        <v>63.2</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>260</v>
@@ -6830,13 +6590,13 @@
         <v>258</v>
       </c>
       <c r="G251" s="2">
-        <v>46.8</v>
+        <v>19.2</v>
       </c>
       <c r="H251" s="2">
-        <v>63.2</v>
+        <v>23.2</v>
       </c>
       <c r="I251" s="2">
-        <v>52.8</v>
+        <v>22</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>260</v>
@@ -7145,6 +6905,355 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="14.7109375" style="2" customWidth="1"/>
+    <col min="6" max="9" width="16.7109375" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1">
+        <v>213.43</v>
+      </c>
+      <c r="C2" s="2">
+        <v>169.99</v>
+      </c>
+      <c r="D2" s="2">
+        <v>76.62</v>
+      </c>
+      <c r="E2" s="2">
+        <v>13.29</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>564.15</v>
+      </c>
+      <c r="C3" s="2">
+        <v>220.25</v>
+      </c>
+      <c r="D3" s="2">
+        <v>33.72</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-9.67</v>
+      </c>
+      <c r="F3" s="2">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="H3" s="2">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I3" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>6906.5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>98.16</v>
+      </c>
+      <c r="D4" s="2">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>17.88</v>
+      </c>
+      <c r="F4" s="2">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H4" s="2">
+        <v>95.2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>93.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1">
+        <v>383.8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>106.07</v>
+      </c>
+      <c r="D5" s="2">
+        <v>45.63</v>
+      </c>
+      <c r="E5" s="2">
+        <v>24.71</v>
+      </c>
+      <c r="F5" s="2">
+        <v>94.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="H5" s="2">
+        <v>96.8</v>
+      </c>
+      <c r="I5" s="2">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1">
+        <v>653.7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>93.09</v>
+      </c>
+      <c r="D6" s="2">
+        <v>47.75</v>
+      </c>
+      <c r="E6" s="2">
+        <v>27.65</v>
+      </c>
+      <c r="F6" s="2">
+        <v>91.3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="I6" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>246.32</v>
+      </c>
+      <c r="C7" s="2">
+        <v>83.14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>53.49</v>
+      </c>
+      <c r="E7" s="2">
+        <v>17.54</v>
+      </c>
+      <c r="F7" s="2">
+        <v>89.86</v>
+      </c>
+      <c r="G7" s="2">
+        <v>95.2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1520.2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>102.1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>52.42</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7.09</v>
+      </c>
+      <c r="F8" s="2">
+        <v>88.41</v>
+      </c>
+      <c r="G8" s="2">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H8" s="2">
+        <v>93.2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1813.4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>88.02</v>
+      </c>
+      <c r="D9" s="2">
+        <v>66.8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.98</v>
+      </c>
+      <c r="F9" s="2">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="G9" s="2">
+        <v>93.2</v>
+      </c>
+      <c r="H9" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="I9" s="2">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2041.2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>66.33</v>
+      </c>
+      <c r="D10" s="2">
+        <v>48.7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.41</v>
+      </c>
+      <c r="F10" s="2">
+        <v>82.61</v>
+      </c>
+      <c r="G10" s="2">
+        <v>89.2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I10" s="2">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C10">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F10">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G10">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H10">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7187,16 +7296,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>214.78</v>
+        <v>213.43</v>
       </c>
       <c r="C2" s="2">
-        <v>131.32</v>
+        <v>169.99</v>
       </c>
       <c r="D2" s="2">
-        <v>64</v>
+        <v>76.62</v>
       </c>
       <c r="E2" s="2">
-        <v>19.46</v>
+        <v>13.29</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
@@ -7205,7 +7314,7 @@
         <v>100</v>
       </c>
       <c r="H2" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <v>99.59999999999999</v>
@@ -7216,28 +7325,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>2289.1</v>
+        <v>295.15</v>
       </c>
       <c r="C3" s="2">
-        <v>123.91</v>
+        <v>135.22</v>
       </c>
       <c r="D3" s="2">
-        <v>62.64</v>
+        <v>53.87</v>
       </c>
       <c r="E3" s="2">
-        <v>8.33</v>
+        <v>41.53</v>
       </c>
       <c r="F3" s="2">
-        <v>98.81999999999999</v>
+        <v>98.55</v>
       </c>
       <c r="G3" s="2">
-        <v>98.8</v>
+        <v>90</v>
       </c>
       <c r="H3" s="2">
-        <v>97.2</v>
+        <v>89.2</v>
       </c>
       <c r="I3" s="2">
-        <v>97.59999999999999</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7245,25 +7354,25 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>520.4</v>
+        <v>564.15</v>
       </c>
       <c r="C4" s="2">
-        <v>188.89</v>
+        <v>220.25</v>
       </c>
       <c r="D4" s="2">
-        <v>31.85</v>
+        <v>33.72</v>
       </c>
       <c r="E4" s="2">
-        <v>-16.6</v>
+        <v>-9.67</v>
       </c>
       <c r="F4" s="2">
-        <v>97.65000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="H4" s="2">
         <v>99.59999999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>100</v>
       </c>
       <c r="I4" s="2">
         <v>100</v>
@@ -7271,292 +7380,292 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>1439.6</v>
+        <v>6906.5</v>
       </c>
       <c r="C5" s="2">
-        <v>82.48</v>
+        <v>98.16</v>
       </c>
       <c r="D5" s="2">
-        <v>51.31</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>4.58</v>
+        <v>17.88</v>
       </c>
       <c r="F5" s="2">
-        <v>94.12</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>93.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H5" s="2">
-        <v>90.8</v>
+        <v>95.2</v>
       </c>
       <c r="I5" s="2">
-        <v>97.2</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>439.95</v>
+        <v>383.8</v>
       </c>
       <c r="C6" s="2">
-        <v>42.86</v>
+        <v>106.07</v>
       </c>
       <c r="D6" s="2">
-        <v>41.76</v>
+        <v>45.63</v>
       </c>
       <c r="E6" s="2">
-        <v>23.49</v>
+        <v>24.71</v>
       </c>
       <c r="F6" s="2">
-        <v>92.94</v>
+        <v>94.2</v>
       </c>
       <c r="G6" s="2">
-        <v>80.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H6" s="2">
-        <v>82</v>
+        <v>96.8</v>
       </c>
       <c r="I6" s="2">
-        <v>87.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>88.56</v>
+        <v>772.4</v>
       </c>
       <c r="C7" s="2">
-        <v>97.11</v>
+        <v>44.77</v>
       </c>
       <c r="D7" s="2">
-        <v>33.86</v>
+        <v>66.39</v>
       </c>
       <c r="E7" s="2">
-        <v>-1.92</v>
+        <v>43.45</v>
       </c>
       <c r="F7" s="2">
-        <v>91.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="G7" s="2">
-        <v>98</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H7" s="2">
-        <v>94</v>
+        <v>73.2</v>
       </c>
       <c r="I7" s="2">
-        <v>96</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>235.2</v>
+        <v>653.7</v>
       </c>
       <c r="C8" s="2">
-        <v>89.11</v>
+        <v>93.09</v>
       </c>
       <c r="D8" s="2">
-        <v>39.63</v>
+        <v>47.75</v>
       </c>
       <c r="E8" s="2">
-        <v>-1.19</v>
+        <v>27.65</v>
       </c>
       <c r="F8" s="2">
-        <v>90.59</v>
+        <v>91.3</v>
       </c>
       <c r="G8" s="2">
-        <v>99.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H8" s="2">
-        <v>97.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>95.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>290.95</v>
+        <v>246.32</v>
       </c>
       <c r="C9" s="2">
-        <v>55.71</v>
+        <v>83.14</v>
       </c>
       <c r="D9" s="2">
-        <v>31.98</v>
+        <v>53.49</v>
       </c>
       <c r="E9" s="2">
-        <v>18.33</v>
+        <v>17.54</v>
       </c>
       <c r="F9" s="2">
-        <v>89.41</v>
+        <v>89.86</v>
       </c>
       <c r="G9" s="2">
-        <v>90.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H9" s="2">
-        <v>92.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>85.2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1724</v>
+        <v>1520.2</v>
       </c>
       <c r="C10" s="2">
-        <v>81.28</v>
+        <v>102.1</v>
       </c>
       <c r="D10" s="2">
-        <v>28.66</v>
+        <v>52.42</v>
       </c>
       <c r="E10" s="2">
-        <v>0.06</v>
+        <v>7.09</v>
       </c>
       <c r="F10" s="2">
-        <v>88.23999999999999</v>
+        <v>88.41</v>
       </c>
       <c r="G10" s="2">
-        <v>92.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H10" s="2">
-        <v>95.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I10" s="2">
-        <v>96.40000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>397.8</v>
+        <v>1813.4</v>
       </c>
       <c r="C11" s="2">
-        <v>82.75</v>
+        <v>88.02</v>
       </c>
       <c r="D11" s="2">
-        <v>25.21</v>
+        <v>66.8</v>
       </c>
       <c r="E11" s="2">
-        <v>-6.34</v>
+        <v>4.98</v>
       </c>
       <c r="F11" s="2">
-        <v>83.53</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G11" s="2">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="H11" s="2">
-        <v>95.2</v>
+        <v>97.2</v>
       </c>
       <c r="I11" s="2">
-        <v>84.40000000000001</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>228.38</v>
+        <v>728.95</v>
       </c>
       <c r="C12" s="2">
-        <v>80.41</v>
+        <v>42.25</v>
       </c>
       <c r="D12" s="2">
-        <v>20.6</v>
+        <v>40.68</v>
       </c>
       <c r="E12" s="2">
-        <v>-3.58</v>
+        <v>38.69</v>
       </c>
       <c r="F12" s="2">
-        <v>82.34999999999999</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="G12" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2">
-        <v>92.40000000000001</v>
+        <v>44</v>
       </c>
       <c r="I12" s="2">
-        <v>92.40000000000001</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>267.1</v>
+        <v>2439</v>
       </c>
       <c r="C13" s="2">
-        <v>53.45</v>
+        <v>62.46</v>
       </c>
       <c r="D13" s="2">
-        <v>31.4</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2">
-        <v>4.31</v>
+        <v>22.93</v>
       </c>
       <c r="F13" s="2">
-        <v>81.18000000000001</v>
+        <v>84.06</v>
       </c>
       <c r="G13" s="2">
-        <v>89.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H13" s="2">
-        <v>87.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="I13" s="2">
-        <v>87.2</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>3218.8</v>
+        <v>2041.2</v>
       </c>
       <c r="C14" s="2">
-        <v>47.34</v>
+        <v>66.33</v>
       </c>
       <c r="D14" s="2">
-        <v>30.04</v>
+        <v>48.7</v>
       </c>
       <c r="E14" s="2">
-        <v>7.6</v>
+        <v>2.41</v>
       </c>
       <c r="F14" s="2">
-        <v>80</v>
+        <v>82.61</v>
       </c>
       <c r="G14" s="2">
-        <v>86</v>
+        <v>89.2</v>
       </c>
       <c r="H14" s="2">
-        <v>81.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I14" s="2">
-        <v>88.40000000000001</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -7608,558 +7717,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
-    <col min="3" max="5" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6" max="9" width="16.7109375" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1">
-        <v>214.78</v>
-      </c>
-      <c r="C2" s="2">
-        <v>131.32</v>
-      </c>
-      <c r="D2" s="2">
-        <v>64</v>
-      </c>
-      <c r="E2" s="2">
-        <v>19.46</v>
-      </c>
-      <c r="F2" s="2">
-        <v>100</v>
-      </c>
-      <c r="G2" s="2">
-        <v>100</v>
-      </c>
-      <c r="H2" s="2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I2" s="2">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2289.1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>123.91</v>
-      </c>
-      <c r="D3" s="2">
-        <v>62.64</v>
-      </c>
-      <c r="E3" s="2">
-        <v>8.33</v>
-      </c>
-      <c r="F3" s="2">
-        <v>98.81999999999999</v>
-      </c>
-      <c r="G3" s="2">
-        <v>98.8</v>
-      </c>
-      <c r="H3" s="2">
-        <v>97.2</v>
-      </c>
-      <c r="I3" s="2">
-        <v>97.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1">
-        <v>520.4</v>
-      </c>
-      <c r="C4" s="2">
-        <v>188.89</v>
-      </c>
-      <c r="D4" s="2">
-        <v>31.85</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-16.6</v>
-      </c>
-      <c r="F4" s="2">
-        <v>97.65000000000001</v>
-      </c>
-      <c r="G4" s="2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>100</v>
-      </c>
-      <c r="I4" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1">
-        <v>588.95</v>
-      </c>
-      <c r="C5" s="2">
-        <v>64.76000000000001</v>
-      </c>
-      <c r="D5" s="2">
-        <v>36.92</v>
-      </c>
-      <c r="E5" s="2">
-        <v>33.25</v>
-      </c>
-      <c r="F5" s="2">
-        <v>96.47</v>
-      </c>
-      <c r="G5" s="2">
-        <v>88.8</v>
-      </c>
-      <c r="H5" s="2">
-        <v>84.8</v>
-      </c>
-      <c r="I5" s="2">
-        <v>75.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1439.6</v>
-      </c>
-      <c r="C6" s="2">
-        <v>82.48</v>
-      </c>
-      <c r="D6" s="2">
-        <v>51.31</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4.58</v>
-      </c>
-      <c r="F6" s="2">
-        <v>94.12</v>
-      </c>
-      <c r="G6" s="2">
-        <v>93.2</v>
-      </c>
-      <c r="H6" s="2">
-        <v>90.8</v>
-      </c>
-      <c r="I6" s="2">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1">
-        <v>439.95</v>
-      </c>
-      <c r="C7" s="2">
-        <v>42.86</v>
-      </c>
-      <c r="D7" s="2">
-        <v>41.76</v>
-      </c>
-      <c r="E7" s="2">
-        <v>23.49</v>
-      </c>
-      <c r="F7" s="2">
-        <v>92.94</v>
-      </c>
-      <c r="G7" s="2">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H7" s="2">
-        <v>82</v>
-      </c>
-      <c r="I7" s="2">
-        <v>87.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1">
-        <v>88.56</v>
-      </c>
-      <c r="C8" s="2">
-        <v>97.11</v>
-      </c>
-      <c r="D8" s="2">
-        <v>33.86</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-1.92</v>
-      </c>
-      <c r="F8" s="2">
-        <v>91.76000000000001</v>
-      </c>
-      <c r="G8" s="2">
-        <v>98</v>
-      </c>
-      <c r="H8" s="2">
-        <v>94</v>
-      </c>
-      <c r="I8" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1">
-        <v>235.2</v>
-      </c>
-      <c r="C9" s="2">
-        <v>89.11</v>
-      </c>
-      <c r="D9" s="2">
-        <v>39.63</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-1.19</v>
-      </c>
-      <c r="F9" s="2">
-        <v>90.59</v>
-      </c>
-      <c r="G9" s="2">
-        <v>99.2</v>
-      </c>
-      <c r="H9" s="2">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="I9" s="2">
-        <v>95.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>290.95</v>
-      </c>
-      <c r="C10" s="2">
-        <v>55.71</v>
-      </c>
-      <c r="D10" s="2">
-        <v>31.98</v>
-      </c>
-      <c r="E10" s="2">
-        <v>18.33</v>
-      </c>
-      <c r="F10" s="2">
-        <v>89.41</v>
-      </c>
-      <c r="G10" s="2">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="H10" s="2">
-        <v>92.8</v>
-      </c>
-      <c r="I10" s="2">
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1724</v>
-      </c>
-      <c r="C11" s="2">
-        <v>81.28</v>
-      </c>
-      <c r="D11" s="2">
-        <v>28.66</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="F11" s="2">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="G11" s="2">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="H11" s="2">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="I11" s="2">
-        <v>96.40000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1">
-        <v>677.95</v>
-      </c>
-      <c r="C12" s="2">
-        <v>53.77</v>
-      </c>
-      <c r="D12" s="2">
-        <v>29.33</v>
-      </c>
-      <c r="E12" s="2">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="F12" s="2">
-        <v>87.06</v>
-      </c>
-      <c r="G12" s="2">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="H12" s="2">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1">
-        <v>222.38</v>
-      </c>
-      <c r="C13" s="2">
-        <v>59.77</v>
-      </c>
-      <c r="D13" s="2">
-        <v>27.26</v>
-      </c>
-      <c r="E13" s="2">
-        <v>7.09</v>
-      </c>
-      <c r="F13" s="2">
-        <v>85.88</v>
-      </c>
-      <c r="G13" s="2">
-        <v>89.2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>74.8</v>
-      </c>
-      <c r="I13" s="2">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1">
-        <v>397.8</v>
-      </c>
-      <c r="C14" s="2">
-        <v>82.75</v>
-      </c>
-      <c r="D14" s="2">
-        <v>25.21</v>
-      </c>
-      <c r="E14" s="2">
-        <v>-6.34</v>
-      </c>
-      <c r="F14" s="2">
-        <v>83.53</v>
-      </c>
-      <c r="G14" s="2">
-        <v>90</v>
-      </c>
-      <c r="H14" s="2">
-        <v>95.2</v>
-      </c>
-      <c r="I14" s="2">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1">
-        <v>228.38</v>
-      </c>
-      <c r="C15" s="2">
-        <v>80.41</v>
-      </c>
-      <c r="D15" s="2">
-        <v>20.6</v>
-      </c>
-      <c r="E15" s="2">
-        <v>-3.58</v>
-      </c>
-      <c r="F15" s="2">
-        <v>82.34999999999999</v>
-      </c>
-      <c r="G15" s="2">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="I15" s="2">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1">
-        <v>267.1</v>
-      </c>
-      <c r="C16" s="2">
-        <v>53.45</v>
-      </c>
-      <c r="D16" s="2">
-        <v>31.4</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4.31</v>
-      </c>
-      <c r="F16" s="2">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="G16" s="2">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="H16" s="2">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="I16" s="2">
-        <v>87.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3218.8</v>
-      </c>
-      <c r="C17" s="2">
-        <v>47.34</v>
-      </c>
-      <c r="D17" s="2">
-        <v>30.04</v>
-      </c>
-      <c r="E17" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="F17" s="2">
-        <v>80</v>
-      </c>
-      <c r="G17" s="2">
-        <v>86</v>
-      </c>
-      <c r="H17" s="2">
-        <v>81.2</v>
-      </c>
-      <c r="I17" s="2">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C2:C17">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
@@ -8187,13 +7744,13 @@
         <v>265</v>
       </c>
       <c r="B2" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
         <v>16</v>
       </c>
-      <c r="C2" s="2">
-        <v>20.8</v>
-      </c>
       <c r="D2" s="2">
-        <v>21.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8201,13 +7758,13 @@
         <v>266</v>
       </c>
       <c r="B3" s="2">
-        <v>64.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2">
-        <v>69.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D3" s="2">
-        <v>63.6</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8215,13 +7772,13 @@
         <v>267</v>
       </c>
       <c r="B4" s="2">
-        <v>71.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C4" s="2">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D4" s="2">
-        <v>62</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8229,13 +7786,13 @@
         <v>268</v>
       </c>
       <c r="B5" s="2">
-        <v>57.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C5" s="2">
-        <v>66</v>
+        <v>70.8</v>
       </c>
       <c r="D5" s="2">
-        <v>58.8</v>
+        <v>62.4</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_250_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_250_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-24</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-24</t>
+    <t>Price_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-07-31</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-07-31</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-07-31</t>
   </si>
   <si>
     <t>RS_Score_2026-07-24</t>
@@ -43,759 +46,756 @@
     <t>RS_Score_2026-07-10</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-03</t>
+    <t>DIACABS</t>
+  </si>
+  <si>
+    <t>STLTECH</t>
+  </si>
+  <si>
+    <t>BLUESTONE</t>
+  </si>
+  <si>
+    <t>SMLMAH</t>
+  </si>
+  <si>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>SKYGOLD</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>LLOYDSENGG</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>PARAS</t>
+  </si>
+  <si>
+    <t>BALAMINES</t>
+  </si>
+  <si>
+    <t>UJJIVANSFB</t>
+  </si>
+  <si>
+    <t>LLOYDSENT</t>
+  </si>
+  <si>
+    <t>WEWORK</t>
+  </si>
+  <si>
+    <t>SENCO</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>LXCHEM</t>
+  </si>
+  <si>
+    <t>WABAG</t>
+  </si>
+  <si>
+    <t>THYROCARE</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>VAIBHAVGBL</t>
+  </si>
+  <si>
+    <t>PNGJL</t>
+  </si>
+  <si>
+    <t>APOLLO</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
+  </si>
+  <si>
+    <t>IFBIND</t>
+  </si>
+  <si>
+    <t>BECTORFOOD</t>
+  </si>
+  <si>
+    <t>VARROC</t>
+  </si>
+  <si>
+    <t>AARTIDRUGS</t>
+  </si>
+  <si>
+    <t>KTKBANK</t>
+  </si>
+  <si>
+    <t>SKIPPER</t>
+  </si>
+  <si>
+    <t>EMIL</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>SOUTHBANK</t>
+  </si>
+  <si>
+    <t>TVSSCS</t>
+  </si>
+  <si>
+    <t>MANORAMA</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
+  </si>
+  <si>
+    <t>IONEXCHANG</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>IMFA</t>
+  </si>
+  <si>
+    <t>ALIVUS</t>
+  </si>
+  <si>
+    <t>SPARC</t>
+  </si>
+  <si>
+    <t>WESTLIFE</t>
+  </si>
+  <si>
+    <t>CENTURYPLY</t>
+  </si>
+  <si>
+    <t>ETHOSLTD</t>
+  </si>
+  <si>
+    <t>GNFC</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>THOMASCOOK</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>PCJEWELLER</t>
+  </si>
+  <si>
+    <t>SAATVIKGL</t>
+  </si>
+  <si>
+    <t>SANDUMA</t>
+  </si>
+  <si>
+    <t>JAMNAAUTO</t>
+  </si>
+  <si>
+    <t>AGARWALEYE</t>
+  </si>
+  <si>
+    <t>TEXRAIL</t>
+  </si>
+  <si>
+    <t>LUMAXTECH</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>VIYASH</t>
+  </si>
+  <si>
+    <t>GODREJAGRO</t>
+  </si>
+  <si>
+    <t>EDELWEISS</t>
+  </si>
+  <si>
+    <t>KSB</t>
+  </si>
+  <si>
+    <t>SWSOLAR</t>
+  </si>
+  <si>
+    <t>TRANSRAILL</t>
+  </si>
+  <si>
+    <t>ASHOKA</t>
+  </si>
+  <si>
+    <t>CAPILLARY</t>
+  </si>
+  <si>
+    <t>RTNINDIA</t>
+  </si>
+  <si>
+    <t>MOIL</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>BALUFORGE</t>
+  </si>
+  <si>
+    <t>GMRP&amp;UI</t>
+  </si>
+  <si>
+    <t>KNRCON</t>
+  </si>
+  <si>
+    <t>BBOX</t>
+  </si>
+  <si>
+    <t>CRIZAC</t>
+  </si>
+  <si>
+    <t>JKLAKSHMI</t>
+  </si>
+  <si>
+    <t>TIINDIA</t>
+  </si>
+  <si>
+    <t>SUNTECK</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>ALOKINDS</t>
+  </si>
+  <si>
+    <t>RENUKA</t>
+  </si>
+  <si>
+    <t>ELECTCAST</t>
+  </si>
+  <si>
+    <t>PRAJIND</t>
+  </si>
+  <si>
+    <t>JAIBALAJI</t>
+  </si>
+  <si>
+    <t>AVANTIFEED</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>VGUARD</t>
+  </si>
+  <si>
+    <t>TDPOWERSYS</t>
   </si>
   <si>
     <t>CUPID</t>
   </si>
   <si>
-    <t>DIACABS</t>
-  </si>
-  <si>
-    <t>STLTECH</t>
+    <t>MTARTECH</t>
   </si>
   <si>
     <t>THANGAMAYL</t>
   </si>
   <si>
+    <t>AZAD</t>
+  </si>
+  <si>
+    <t>BLACKBUCK</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>PRIVISCL</t>
+  </si>
+  <si>
+    <t>PRICOLLTD</t>
+  </si>
+  <si>
+    <t>LOTUSDEV</t>
+  </si>
+  <si>
+    <t>AEQUS</t>
+  </si>
+  <si>
+    <t>GOKULAGRO</t>
+  </si>
+  <si>
+    <t>TIMETECHNO</t>
+  </si>
+  <si>
+    <t>TANLA</t>
+  </si>
+  <si>
+    <t>NAZARA</t>
+  </si>
+  <si>
+    <t>AETHER</t>
+  </si>
+  <si>
+    <t>JSFB</t>
+  </si>
+  <si>
+    <t>ASHAPURMIN</t>
+  </si>
+  <si>
+    <t>HAPPSTMNDS</t>
+  </si>
+  <si>
+    <t>VIKRAMSOLR</t>
+  </si>
+  <si>
+    <t>SUDARSCHEM</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>INOXGREEN</t>
+  </si>
+  <si>
+    <t>REFEX</t>
+  </si>
+  <si>
+    <t>BORORENEW</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>MASTEK</t>
+  </si>
+  <si>
+    <t>SAMHI</t>
+  </si>
+  <si>
+    <t>SHAILY</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>METROPOLIS</t>
+  </si>
+  <si>
+    <t>EIEL</t>
+  </si>
+  <si>
+    <t>JUSTDIAL</t>
+  </si>
+  <si>
+    <t>AXISCADES</t>
+  </si>
+  <si>
+    <t>RAYMONDLSL</t>
+  </si>
+  <si>
+    <t>GRWRHITECH</t>
+  </si>
+  <si>
+    <t>SHAKTIPUMP</t>
+  </si>
+  <si>
+    <t>WAKEFIT</t>
+  </si>
+  <si>
+    <t>RELAXO</t>
+  </si>
+  <si>
+    <t>SHARDACROP</t>
+  </si>
+  <si>
+    <t>CSBBANK</t>
+  </si>
+  <si>
+    <t>RATNAMANI</t>
+  </si>
+  <si>
+    <t>GPPL</t>
+  </si>
+  <si>
+    <t>EQUITASBNK</t>
+  </si>
+  <si>
+    <t>CCAVENUE</t>
+  </si>
+  <si>
+    <t>WAAREERTL</t>
+  </si>
+  <si>
+    <t>NEOGEN</t>
+  </si>
+  <si>
+    <t>TIPSMUSIC</t>
+  </si>
+  <si>
+    <t>MANYAVAR</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>MARKSANS</t>
+  </si>
+  <si>
+    <t>OSWALPUMPS</t>
+  </si>
+  <si>
+    <t>ARVIND</t>
+  </si>
+  <si>
+    <t>KIRLOSBROS</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>JKPAPER</t>
+  </si>
+  <si>
+    <t>MEDPLUS</t>
+  </si>
+  <si>
+    <t>VOLTAMP</t>
+  </si>
+  <si>
+    <t>JAYNECOIND</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>STAR</t>
+  </si>
+  <si>
+    <t>AURIONPRO</t>
+  </si>
+  <si>
+    <t>ICIL</t>
+  </si>
+  <si>
+    <t>SUPRIYA</t>
+  </si>
+  <si>
+    <t>RALLIS</t>
+  </si>
+  <si>
+    <t>WEBELSOLAR</t>
+  </si>
+  <si>
+    <t>INDIAGLYCO</t>
+  </si>
+  <si>
+    <t>ELLEN</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>SHRIPISTON</t>
+  </si>
+  <si>
+    <t>INDIASHLTR</t>
+  </si>
+  <si>
+    <t>KPIGREEN</t>
+  </si>
+  <si>
+    <t>JSLL</t>
+  </si>
+  <si>
+    <t>ASKAUTOLTD</t>
+  </si>
+  <si>
+    <t>KRN</t>
+  </si>
+  <si>
+    <t>CAMPUS</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>VMART</t>
+  </si>
+  <si>
+    <t>AKUMS</t>
+  </si>
+  <si>
+    <t>SHAREINDIA</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>GHCL</t>
+  </si>
+  <si>
+    <t>GOKEX</t>
+  </si>
+  <si>
+    <t>ATLANTAELE</t>
+  </si>
+  <si>
+    <t>CRAMC</t>
+  </si>
+  <si>
+    <t>RBA</t>
+  </si>
+  <si>
+    <t>HERITGFOOD</t>
+  </si>
+  <si>
+    <t>FIEMIND</t>
+  </si>
+  <si>
+    <t>AVL</t>
+  </si>
+  <si>
     <t>UTLSOLAR</t>
   </si>
   <si>
-    <t>BLUESTONE</t>
-  </si>
-  <si>
-    <t>SKYGOLD</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
-  </si>
-  <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>JUSTDIAL</t>
-  </si>
-  <si>
-    <t>AZAD</t>
-  </si>
-  <si>
-    <t>WABAG</t>
-  </si>
-  <si>
-    <t>LOTUSDEV</t>
-  </si>
-  <si>
-    <t>UJJIVANSFB</t>
-  </si>
-  <si>
-    <t>LXCHEM</t>
-  </si>
-  <si>
-    <t>APOLLO</t>
-  </si>
-  <si>
-    <t>PFOCUS</t>
-  </si>
-  <si>
-    <t>SPARC</t>
-  </si>
-  <si>
-    <t>AEQUS</t>
-  </si>
-  <si>
-    <t>NEOGEN</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>SENCO</t>
-  </si>
-  <si>
-    <t>EMIL</t>
-  </si>
-  <si>
-    <t>SHRIPISTON</t>
-  </si>
-  <si>
-    <t>MSTCLTD</t>
-  </si>
-  <si>
-    <t>EQUITASBNK</t>
-  </si>
-  <si>
-    <t>ELLEN</t>
-  </si>
-  <si>
-    <t>ROUTE</t>
-  </si>
-  <si>
-    <t>REFEX</t>
-  </si>
-  <si>
-    <t>BECTORFOOD</t>
+    <t>SUDEEPPHRM</t>
+  </si>
+  <si>
+    <t>V2RETAIL</t>
+  </si>
+  <si>
+    <t>JLHL</t>
+  </si>
+  <si>
+    <t>FEDFINA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>POWERMECH</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>DYNAMATECH</t>
+  </si>
+  <si>
+    <t>STYRENIX</t>
+  </si>
+  <si>
+    <t>PGIL</t>
+  </si>
+  <si>
+    <t>SFL</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>MIDHANI</t>
+  </si>
+  <si>
+    <t>GSFC</t>
+  </si>
+  <si>
+    <t>JYOTHYLAB</t>
+  </si>
+  <si>
+    <t>SMARTWORKS</t>
+  </si>
+  <si>
+    <t>ARVINDFASN</t>
+  </si>
+  <si>
+    <t>INDIGOPNTS</t>
   </si>
   <si>
     <t>PNCINFRA</t>
   </si>
   <si>
-    <t>SOUTHBANK</t>
-  </si>
-  <si>
-    <t>ETHOSLTD</t>
-  </si>
-  <si>
-    <t>SAMHI</t>
-  </si>
-  <si>
-    <t>PCJEWELLER</t>
-  </si>
-  <si>
-    <t>FIEMIND</t>
-  </si>
-  <si>
-    <t>CRAMC</t>
-  </si>
-  <si>
-    <t>CCAVENUE</t>
-  </si>
-  <si>
-    <t>HAPPSTMNDS</t>
-  </si>
-  <si>
-    <t>NAZARA</t>
+    <t>OPTIEMUS</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>ZAGGLE</t>
   </si>
   <si>
     <t>QPOWER</t>
   </si>
   <si>
-    <t>KIRLOSBROS</t>
-  </si>
-  <si>
-    <t>FEDFINA</t>
-  </si>
-  <si>
-    <t>MIDHANI</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>RTNINDIA</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
+    <t>RELIGARE</t>
+  </si>
+  <si>
+    <t>STYL</t>
+  </si>
+  <si>
+    <t>NETWORK18</t>
+  </si>
+  <si>
+    <t>RTNPOWER</t>
+  </si>
+  <si>
+    <t>PICCADIL</t>
+  </si>
+  <si>
+    <t>KSCL</t>
+  </si>
+  <si>
+    <t>MAHSCOOTER</t>
+  </si>
+  <si>
+    <t>IIFLCAPS</t>
+  </si>
+  <si>
+    <t>BIRLACORPN</t>
+  </si>
+  <si>
+    <t>DATAMATICS</t>
+  </si>
+  <si>
+    <t>AARTIPHARM</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>WELENT</t>
+  </si>
+  <si>
+    <t>CELLO</t>
+  </si>
+  <si>
+    <t>ANUP</t>
+  </si>
+  <si>
+    <t>IXIGO</t>
+  </si>
+  <si>
+    <t>REDTAPE</t>
+  </si>
+  <si>
+    <t>KANSAINER</t>
+  </si>
+  <si>
+    <t>ORKLAINDIA</t>
+  </si>
+  <si>
+    <t>DBL</t>
+  </si>
+  <si>
+    <t>TARC</t>
+  </si>
+  <si>
+    <t>FINPIPE</t>
+  </si>
+  <si>
+    <t>ORIENTCEM</t>
+  </si>
+  <si>
+    <t>ADVENZYMES</t>
+  </si>
+  <si>
+    <t>AWFIS</t>
+  </si>
+  <si>
+    <t>APLLTD</t>
+  </si>
+  <si>
+    <t>KITEX</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>EPL</t>
+  </si>
+  <si>
+    <t>BANCOINDIA</t>
+  </si>
+  <si>
+    <t>EUREKAFORB</t>
+  </si>
+  <si>
+    <t>SURYAROSNI</t>
+  </si>
+  <si>
+    <t>PRSMJOHNSN</t>
+  </si>
+  <si>
+    <t>PURVA</t>
+  </si>
+  <si>
+    <t>ALKYLAMINE</t>
+  </si>
+  <si>
+    <t>MAHSEAMLES</t>
+  </si>
+  <si>
+    <t>CERA</t>
   </si>
   <si>
     <t>BAJAJELEC</t>
   </si>
   <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>VOLTAMP</t>
-  </si>
-  <si>
-    <t>SUNTECK</t>
-  </si>
-  <si>
-    <t>GPPL</t>
-  </si>
-  <si>
-    <t>KANSAINER</t>
-  </si>
-  <si>
-    <t>ASHOKA</t>
+    <t>STARCEMENT</t>
+  </si>
+  <si>
+    <t>DBREALTY</t>
+  </si>
+  <si>
+    <t>VIPIND</t>
+  </si>
+  <si>
+    <t>HGINFRA</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>HEMIPROP</t>
   </si>
   <si>
     <t>NFL</t>
   </si>
   <si>
-    <t>HEMIPROP</t>
-  </si>
-  <si>
-    <t>KNRCON</t>
-  </si>
-  <si>
-    <t>FINPIPE</t>
-  </si>
-  <si>
-    <t>SANDUMA</t>
-  </si>
-  <si>
-    <t>JKLAKSHMI</t>
-  </si>
-  <si>
-    <t>KITEX</t>
-  </si>
-  <si>
-    <t>CAMPUS</t>
-  </si>
-  <si>
-    <t>RALLIS</t>
-  </si>
-  <si>
-    <t>MOIL</t>
-  </si>
-  <si>
-    <t>JSLL</t>
-  </si>
-  <si>
-    <t>MEDPLUS</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>PARAS</t>
-  </si>
-  <si>
-    <t>THOMASCOOK</t>
-  </si>
-  <si>
-    <t>HGINFRA</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>TDPOWERSYS</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>BALAMINES</t>
-  </si>
-  <si>
-    <t>BBOX</t>
-  </si>
-  <si>
-    <t>CERA</t>
-  </si>
-  <si>
-    <t>RAIN</t>
-  </si>
-  <si>
-    <t>NETWORK18</t>
-  </si>
-  <si>
-    <t>THYROCARE</t>
-  </si>
-  <si>
-    <t>PRAJIND</t>
-  </si>
-  <si>
-    <t>JAYNECOIND</t>
-  </si>
-  <si>
-    <t>MARKSANS</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
-    <t>SFL</t>
-  </si>
-  <si>
-    <t>EDELWEISS</t>
-  </si>
-  <si>
-    <t>ASHAPURMIN</t>
-  </si>
-  <si>
-    <t>QUESS</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>RELIGARE</t>
-  </si>
-  <si>
-    <t>TMB</t>
-  </si>
-  <si>
-    <t>BORORENEW</t>
-  </si>
-  <si>
-    <t>TIINDIA</t>
-  </si>
-  <si>
-    <t>V2RETAIL</t>
-  </si>
-  <si>
-    <t>SKIPPER</t>
-  </si>
-  <si>
-    <t>SHAILY</t>
-  </si>
-  <si>
-    <t>VIKRAMSOLR</t>
-  </si>
-  <si>
-    <t>WEBELSOLAR</t>
-  </si>
-  <si>
-    <t>SHAKTIPUMP</t>
-  </si>
-  <si>
-    <t>LLOYDSENGG</t>
-  </si>
-  <si>
-    <t>IIFLCAPS</t>
-  </si>
-  <si>
-    <t>SWSOLAR</t>
-  </si>
-  <si>
-    <t>KPIGREEN</t>
-  </si>
-  <si>
-    <t>WEWORK</t>
-  </si>
-  <si>
-    <t>AVANTIFEED</t>
-  </si>
-  <si>
-    <t>KTKBANK</t>
-  </si>
-  <si>
-    <t>AXISCADES</t>
-  </si>
-  <si>
-    <t>APLLTD</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
-    <t>ARVIND</t>
-  </si>
-  <si>
-    <t>RBA</t>
-  </si>
-  <si>
-    <t>MANORAMA</t>
-  </si>
-  <si>
-    <t>ALKYLAMINE</t>
-  </si>
-  <si>
-    <t>TRANSRAILL</t>
-  </si>
-  <si>
-    <t>STAR</t>
-  </si>
-  <si>
-    <t>SUPRIYA</t>
-  </si>
-  <si>
-    <t>POWERMECH</t>
-  </si>
-  <si>
-    <t>GOKEX</t>
-  </si>
-  <si>
-    <t>GRWRHITECH</t>
-  </si>
-  <si>
-    <t>TIMETECHNO</t>
-  </si>
-  <si>
-    <t>JSFB</t>
-  </si>
-  <si>
-    <t>KRN</t>
-  </si>
-  <si>
-    <t>IXIGO</t>
-  </si>
-  <si>
-    <t>RENUKA</t>
-  </si>
-  <si>
-    <t>TEXRAIL</t>
-  </si>
-  <si>
-    <t>WAAREERTL</t>
-  </si>
-  <si>
-    <t>AETHER</t>
-  </si>
-  <si>
-    <t>BALUFORGE</t>
-  </si>
-  <si>
-    <t>SURYAROSNI</t>
-  </si>
-  <si>
-    <t>OSWALPUMPS</t>
-  </si>
-  <si>
-    <t>TANLA</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>LUMAXTECH</t>
-  </si>
-  <si>
-    <t>TIPSMUSIC</t>
-  </si>
-  <si>
-    <t>SUDEEPPHRM</t>
-  </si>
-  <si>
-    <t>KSB</t>
-  </si>
-  <si>
-    <t>AARTIPHARM</t>
-  </si>
-  <si>
-    <t>BLACKBUCK</t>
-  </si>
-  <si>
-    <t>ATLANTAELE</t>
-  </si>
-  <si>
-    <t>LLOYDSENT</t>
-  </si>
-  <si>
-    <t>IMFA</t>
-  </si>
-  <si>
-    <t>DYNAMATECH</t>
-  </si>
-  <si>
-    <t>SHARDACROP</t>
-  </si>
-  <si>
-    <t>GHCL</t>
-  </si>
-  <si>
-    <t>PRIVISCL</t>
-  </si>
-  <si>
-    <t>RTNPOWER</t>
-  </si>
-  <si>
-    <t>PRICOLLTD</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>GMRP&amp;UI</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>GNFC</t>
-  </si>
-  <si>
-    <t>JAMNAAUTO</t>
-  </si>
-  <si>
-    <t>ICIL</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>PICCADIL</t>
-  </si>
-  <si>
-    <t>AURIONPRO</t>
-  </si>
-  <si>
-    <t>ZAGGLE</t>
-  </si>
-  <si>
-    <t>ELECTCAST</t>
-  </si>
-  <si>
-    <t>INOXGREEN</t>
-  </si>
-  <si>
-    <t>BANCOINDIA</t>
-  </si>
-  <si>
-    <t>PNGJL</t>
-  </si>
-  <si>
-    <t>IFBIND</t>
-  </si>
-  <si>
-    <t>WELENT</t>
-  </si>
-  <si>
     <t>TSFINV</t>
   </si>
   <si>
-    <t>SMLMAH</t>
-  </si>
-  <si>
-    <t>TVSSCS</t>
-  </si>
-  <si>
-    <t>SUDARSCHEM</t>
-  </si>
-  <si>
-    <t>EIEL</t>
-  </si>
-  <si>
-    <t>OPTIEMUS</t>
-  </si>
-  <si>
-    <t>ALOKINDS</t>
-  </si>
-  <si>
-    <t>JYOTHYLAB</t>
-  </si>
-  <si>
-    <t>VMART</t>
-  </si>
-  <si>
-    <t>AWFIS</t>
-  </si>
-  <si>
-    <t>VIPIND</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>ARVINDFASN</t>
-  </si>
-  <si>
-    <t>PGIL</t>
-  </si>
-  <si>
-    <t>GSFC</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>JKPAPER</t>
-  </si>
-  <si>
-    <t>SAFARI</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>INDIGOPNTS</t>
-  </si>
-  <si>
-    <t>GOKULAGRO</t>
-  </si>
-  <si>
-    <t>EUREKAFORB</t>
-  </si>
-  <si>
-    <t>RAYMONDLSL</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>ADVENZYMES</t>
-  </si>
-  <si>
-    <t>ALIVUS</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>EPL</t>
-  </si>
-  <si>
-    <t>KSCL</t>
-  </si>
-  <si>
-    <t>MANYAVAR</t>
-  </si>
-  <si>
-    <t>REDTAPE</t>
-  </si>
-  <si>
-    <t>MAHSEAMLES</t>
-  </si>
-  <si>
-    <t>IONEXCHANG</t>
-  </si>
-  <si>
-    <t>SAATVIKGL</t>
+    <t>AHLUCONT</t>
   </si>
   <si>
     <t>SANOFICONR</t>
   </si>
   <si>
-    <t>STYRENIX</t>
-  </si>
-  <si>
-    <t>VAIBHAVGBL</t>
-  </si>
-  <si>
-    <t>GODREJAGRO</t>
-  </si>
-  <si>
-    <t>ASKAUTOLTD</t>
-  </si>
-  <si>
-    <t>AKUMS</t>
-  </si>
-  <si>
-    <t>DATAMATICS</t>
-  </si>
-  <si>
-    <t>AVL</t>
-  </si>
-  <si>
-    <t>TARC</t>
-  </si>
-  <si>
-    <t>METROPOLIS</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>RATNAMANI</t>
-  </si>
-  <si>
-    <t>AGARWALEYE</t>
-  </si>
-  <si>
-    <t>WAKEFIT</t>
-  </si>
-  <si>
-    <t>JLHL</t>
-  </si>
-  <si>
-    <t>MASTEK</t>
-  </si>
-  <si>
-    <t>CELLO</t>
-  </si>
-  <si>
-    <t>DBREALTY</t>
-  </si>
-  <si>
-    <t>STYL</t>
-  </si>
-  <si>
-    <t>HERITGFOOD</t>
-  </si>
-  <si>
-    <t>CSBBANK</t>
-  </si>
-  <si>
-    <t>INDIAGLYCO</t>
-  </si>
-  <si>
-    <t>SHAREINDIA</t>
-  </si>
-  <si>
-    <t>VGUARD</t>
-  </si>
-  <si>
-    <t>CRIZAC</t>
-  </si>
-  <si>
-    <t>GMMPFAUDLR</t>
-  </si>
-  <si>
-    <t>RELAXO</t>
-  </si>
-  <si>
-    <t>PURVA</t>
-  </si>
-  <si>
-    <t>ANUP</t>
-  </si>
-  <si>
-    <t>AARTIDRUGS</t>
-  </si>
-  <si>
-    <t>MAHSCOOTER</t>
-  </si>
-  <si>
-    <t>PRSMJOHNSN</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>SMARTWORKS</t>
-  </si>
-  <si>
-    <t>DBL</t>
-  </si>
-  <si>
-    <t>VARROC</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>STARCEMENT</t>
-  </si>
-  <si>
-    <t>BIRLACORPN</t>
-  </si>
-  <si>
-    <t>ORIENTCEM</t>
-  </si>
-  <si>
-    <t>AHLUCONT</t>
-  </si>
-  <si>
-    <t>ORKLAINDIA</t>
-  </si>
-  <si>
-    <t>INDIASHLTR</t>
-  </si>
-  <si>
-    <t>CENTURYPLY</t>
-  </si>
-  <si>
-    <t>JAIBALAJI</t>
-  </si>
-  <si>
     <t>SUBROS</t>
   </si>
   <si>
-    <t>WESTLIFE</t>
-  </si>
-  <si>
-    <t>CAPILLARY</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -814,6 +814,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -821,9 +824,6 @@
   </si>
   <si>
     <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
   </si>
 </sst>
 </file>
@@ -1322,28 +1322,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>213.43</v>
+        <v>323.97</v>
       </c>
       <c r="C2" s="2">
-        <v>169.99</v>
+        <v>167.74</v>
       </c>
       <c r="D2" s="2">
-        <v>76.62</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>13.29</v>
+        <v>48.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I2" s="2">
-        <v>99.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>260</v>
@@ -1354,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>295.15</v>
+        <v>557.05</v>
       </c>
       <c r="C3" s="2">
-        <v>135.22</v>
+        <v>209.44</v>
       </c>
       <c r="D3" s="2">
-        <v>53.87</v>
+        <v>20.26</v>
       </c>
       <c r="E3" s="2">
-        <v>41.53</v>
+        <v>-4.8</v>
       </c>
       <c r="F3" s="2">
-        <v>98.55</v>
+        <v>98.84</v>
       </c>
       <c r="G3" s="2">
-        <v>90</v>
+        <v>99.2</v>
       </c>
       <c r="H3" s="2">
-        <v>89.2</v>
+        <v>99.2</v>
       </c>
       <c r="I3" s="2">
-        <v>74.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>260</v>
@@ -1386,28 +1386,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>564.15</v>
+        <v>816.2</v>
       </c>
       <c r="C4" s="2">
-        <v>220.25</v>
+        <v>57.57</v>
       </c>
       <c r="D4" s="2">
-        <v>33.72</v>
+        <v>68.48</v>
       </c>
       <c r="E4" s="2">
-        <v>-9.67</v>
+        <v>40.11</v>
       </c>
       <c r="F4" s="2">
-        <v>97.09999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="G4" s="2">
-        <v>99.2</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>99.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I4" s="2">
-        <v>100</v>
+        <v>73.2</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>260</v>
@@ -1418,28 +1418,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>6906.5</v>
+        <v>5685.6</v>
       </c>
       <c r="C5" s="2">
-        <v>98.16</v>
+        <v>43.72</v>
       </c>
       <c r="D5" s="2">
-        <v>95.26000000000001</v>
+        <v>48.03</v>
       </c>
       <c r="E5" s="2">
-        <v>17.88</v>
+        <v>46.07</v>
       </c>
       <c r="F5" s="2">
-        <v>95.65000000000001</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>98.40000000000001</v>
+        <v>33.2</v>
       </c>
       <c r="H5" s="2">
-        <v>95.2</v>
+        <v>42.8</v>
       </c>
       <c r="I5" s="2">
-        <v>93.59999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>260</v>
@@ -1450,28 +1450,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>383.8</v>
+        <v>332.55</v>
       </c>
       <c r="C6" s="2">
-        <v>106.07</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>45.63</v>
+        <v>61.29</v>
       </c>
       <c r="E6" s="2">
-        <v>24.71</v>
+        <v>13.29</v>
       </c>
       <c r="F6" s="2">
-        <v>94.2</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>97.2</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
-        <v>96.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>84.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>260</v>
@@ -1482,28 +1482,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>772.4</v>
+        <v>222.95</v>
       </c>
       <c r="C7" s="2">
-        <v>44.77</v>
+        <v>112.52</v>
       </c>
       <c r="D7" s="2">
-        <v>66.39</v>
+        <v>24.57</v>
       </c>
       <c r="E7" s="2">
-        <v>43.45</v>
+        <v>13.24</v>
       </c>
       <c r="F7" s="2">
-        <v>92.75</v>
+        <v>94.19</v>
       </c>
       <c r="G7" s="2">
-        <v>83.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H7" s="2">
-        <v>73.2</v>
+        <v>92.8</v>
       </c>
       <c r="I7" s="2">
-        <v>67.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>260</v>
@@ -1514,28 +1514,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>653.7</v>
+        <v>643.7</v>
       </c>
       <c r="C8" s="2">
-        <v>93.09</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D8" s="2">
-        <v>47.75</v>
+        <v>32.9</v>
       </c>
       <c r="E8" s="2">
-        <v>27.65</v>
+        <v>15.86</v>
       </c>
       <c r="F8" s="2">
-        <v>91.3</v>
+        <v>93.02</v>
       </c>
       <c r="G8" s="2">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H8" s="2">
         <v>96.40000000000001</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>94.40000000000001</v>
-      </c>
-      <c r="I8" s="2">
-        <v>88</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>260</v>
@@ -1546,28 +1546,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>246.32</v>
+        <v>1861.6</v>
       </c>
       <c r="C9" s="2">
-        <v>83.14</v>
+        <v>103.82</v>
       </c>
       <c r="D9" s="2">
-        <v>53.49</v>
+        <v>50.66</v>
       </c>
       <c r="E9" s="2">
-        <v>17.54</v>
+        <v>0.63</v>
       </c>
       <c r="F9" s="2">
-        <v>89.86</v>
+        <v>91.86</v>
       </c>
       <c r="G9" s="2">
-        <v>95.2</v>
+        <v>94.8</v>
       </c>
       <c r="H9" s="2">
-        <v>98.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I9" s="2">
-        <v>90</v>
+        <v>97.2</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>260</v>
@@ -1578,28 +1578,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>1520.2</v>
+        <v>88.66</v>
       </c>
       <c r="C10" s="2">
-        <v>102.1</v>
+        <v>127.1</v>
       </c>
       <c r="D10" s="2">
-        <v>52.42</v>
+        <v>18.8</v>
       </c>
       <c r="E10" s="2">
-        <v>7.09</v>
+        <v>-1.9</v>
       </c>
       <c r="F10" s="2">
-        <v>88.41</v>
+        <v>90.7</v>
       </c>
       <c r="G10" s="2">
-        <v>95.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="H10" s="2">
-        <v>93.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>90.8</v>
+        <v>98</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>260</v>
@@ -1610,28 +1610,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>1813.4</v>
+        <v>238.05</v>
       </c>
       <c r="C11" s="2">
-        <v>88.02</v>
+        <v>82.37</v>
       </c>
       <c r="D11" s="2">
-        <v>66.8</v>
+        <v>39.83</v>
       </c>
       <c r="E11" s="2">
-        <v>4.98</v>
+        <v>7.07</v>
       </c>
       <c r="F11" s="2">
-        <v>86.95999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="G11" s="2">
-        <v>93.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H11" s="2">
-        <v>97.2</v>
+        <v>95.2</v>
       </c>
       <c r="I11" s="2">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>260</v>
@@ -1642,28 +1642,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>728.95</v>
+        <v>1256.5</v>
       </c>
       <c r="C12" s="2">
-        <v>42.25</v>
+        <v>102.86</v>
       </c>
       <c r="D12" s="2">
-        <v>40.68</v>
+        <v>46.83</v>
       </c>
       <c r="E12" s="2">
-        <v>38.69</v>
+        <v>-7.5</v>
       </c>
       <c r="F12" s="2">
-        <v>85.51000000000001</v>
+        <v>88.37</v>
       </c>
       <c r="G12" s="2">
-        <v>98</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H12" s="2">
-        <v>44</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>32</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>260</v>
@@ -1674,28 +1674,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>2439</v>
+        <v>2133.3</v>
       </c>
       <c r="C13" s="2">
-        <v>62.46</v>
+        <v>105</v>
       </c>
       <c r="D13" s="2">
-        <v>27</v>
+        <v>11.61</v>
       </c>
       <c r="E13" s="2">
-        <v>22.93</v>
+        <v>-0.53</v>
       </c>
       <c r="F13" s="2">
-        <v>84.06</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="G13" s="2">
-        <v>80.8</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2">
-        <v>82</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I13" s="2">
-        <v>42.4</v>
+        <v>98.8</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>260</v>
@@ -1706,28 +1706,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>2041.2</v>
+        <v>71.75</v>
       </c>
       <c r="C14" s="2">
-        <v>66.33</v>
+        <v>39.75</v>
       </c>
       <c r="D14" s="2">
-        <v>48.7</v>
+        <v>30.76</v>
       </c>
       <c r="E14" s="2">
-        <v>2.41</v>
+        <v>20.02</v>
       </c>
       <c r="F14" s="2">
-        <v>82.61</v>
+        <v>86.05</v>
       </c>
       <c r="G14" s="2">
-        <v>89.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H14" s="2">
-        <v>97.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="I14" s="2">
-        <v>96</v>
+        <v>63.6</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>260</v>
@@ -1738,28 +1738,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>180.39</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="C15" s="2">
-        <v>50.32</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="D15" s="2">
-        <v>30.41</v>
+        <v>12.19</v>
       </c>
       <c r="E15" s="2">
-        <v>18.43</v>
+        <v>2.88</v>
       </c>
       <c r="F15" s="2">
-        <v>81.16</v>
+        <v>84.88</v>
       </c>
       <c r="G15" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2">
-        <v>40</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>46.4</v>
+        <v>83.2</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>260</v>
@@ -1770,28 +1770,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>70.72</v>
+        <v>743.5</v>
       </c>
       <c r="C16" s="2">
-        <v>37.96</v>
+        <v>67.02</v>
       </c>
       <c r="D16" s="2">
-        <v>30.6</v>
+        <v>29.62</v>
       </c>
       <c r="E16" s="2">
-        <v>24.27</v>
+        <v>0.86</v>
       </c>
       <c r="F16" s="2">
-        <v>79.70999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="G16" s="2">
-        <v>75.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H16" s="2">
-        <v>64</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I16" s="2">
-        <v>51.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>260</v>
@@ -1802,28 +1802,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>182.28</v>
+        <v>403.2</v>
       </c>
       <c r="C17" s="2">
-        <v>58.48</v>
+        <v>37.14</v>
       </c>
       <c r="D17" s="2">
-        <v>20.85</v>
+        <v>13.96</v>
       </c>
       <c r="E17" s="2">
-        <v>18.43</v>
+        <v>23.49</v>
       </c>
       <c r="F17" s="2">
-        <v>78.26000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="G17" s="2">
-        <v>75.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H17" s="2">
-        <v>58</v>
+        <v>69.2</v>
       </c>
       <c r="I17" s="2">
-        <v>61.2</v>
+        <v>55.6</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>260</v>
@@ -1834,28 +1834,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>394.3</v>
+        <v>1908</v>
       </c>
       <c r="C18" s="2">
-        <v>95.09999999999999</v>
+        <v>58.85</v>
       </c>
       <c r="D18" s="2">
-        <v>26.78</v>
+        <v>32.66</v>
       </c>
       <c r="E18" s="2">
-        <v>-3.16</v>
+        <v>1.88</v>
       </c>
       <c r="F18" s="2">
-        <v>76.81</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G18" s="2">
-        <v>88.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H18" s="2">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="I18" s="2">
-        <v>95.2</v>
+        <v>91.2</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>260</v>
@@ -1866,28 +1866,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>289.29</v>
+        <v>178.48</v>
       </c>
       <c r="C19" s="2">
-        <v>12.89</v>
+        <v>51.51</v>
       </c>
       <c r="D19" s="2">
-        <v>22.92</v>
+        <v>15.79</v>
       </c>
       <c r="E19" s="2">
-        <v>37.44</v>
+        <v>13.3</v>
       </c>
       <c r="F19" s="2">
-        <v>75.36</v>
+        <v>80.23</v>
       </c>
       <c r="G19" s="2">
-        <v>77.2</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2">
-        <v>21.2</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2">
-        <v>1.2</v>
+        <v>57.6</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>260</v>
@@ -1898,25 +1898,25 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>216.23</v>
+        <v>1977.2</v>
       </c>
       <c r="C20" s="2">
-        <v>88.34999999999999</v>
+        <v>63.98</v>
       </c>
       <c r="D20" s="2">
-        <v>33.29</v>
+        <v>36.43</v>
       </c>
       <c r="E20" s="2">
-        <v>-6.47</v>
+        <v>-3.57</v>
       </c>
       <c r="F20" s="2">
-        <v>73.91</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G20" s="2">
-        <v>94</v>
+        <v>89.2</v>
       </c>
       <c r="H20" s="2">
-        <v>99.2</v>
+        <v>89.2</v>
       </c>
       <c r="I20" s="2">
         <v>97.59999999999999</v>
@@ -1930,28 +1930,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>229.23</v>
+        <v>579</v>
       </c>
       <c r="C21" s="2">
-        <v>88.12</v>
+        <v>60.06</v>
       </c>
       <c r="D21" s="2">
-        <v>17.34</v>
+        <v>18.94</v>
       </c>
       <c r="E21" s="2">
-        <v>-4.31</v>
+        <v>6.2</v>
       </c>
       <c r="F21" s="2">
-        <v>72.45999999999999</v>
+        <v>77.91</v>
       </c>
       <c r="G21" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H21" s="2">
-        <v>94</v>
+        <v>67.2</v>
       </c>
       <c r="I21" s="2">
-        <v>92.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>260</v>
@@ -1962,28 +1962,28 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>2062.8</v>
+        <v>3346.9</v>
       </c>
       <c r="C22" s="2">
-        <v>51.75</v>
+        <v>58.18</v>
       </c>
       <c r="D22" s="2">
-        <v>21.98</v>
+        <v>15.2</v>
       </c>
       <c r="E22" s="2">
-        <v>9.59</v>
+        <v>4.9</v>
       </c>
       <c r="F22" s="2">
-        <v>71.01000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="G22" s="2">
-        <v>89.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="H22" s="2">
-        <v>78</v>
+        <v>87.2</v>
       </c>
       <c r="I22" s="2">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>260</v>
@@ -1994,28 +1994,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>3184.7</v>
+        <v>266.36</v>
       </c>
       <c r="C23" s="2">
-        <v>52.86</v>
+        <v>36.47</v>
       </c>
       <c r="D23" s="2">
-        <v>33.11</v>
+        <v>16.93</v>
       </c>
       <c r="E23" s="2">
-        <v>1.43</v>
+        <v>13.6</v>
       </c>
       <c r="F23" s="2">
-        <v>69.56999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="G23" s="2">
-        <v>87.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H23" s="2">
-        <v>86</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I23" s="2">
-        <v>81.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>260</v>
@@ -2026,28 +2026,28 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>382.85</v>
+        <v>670.3</v>
       </c>
       <c r="C24" s="2">
-        <v>29.38</v>
+        <v>19.58</v>
       </c>
       <c r="D24" s="2">
-        <v>15.84</v>
+        <v>26.94</v>
       </c>
       <c r="E24" s="2">
-        <v>17.03</v>
+        <v>15.62</v>
       </c>
       <c r="F24" s="2">
-        <v>68.12</v>
+        <v>74.42</v>
       </c>
       <c r="G24" s="2">
-        <v>69.2</v>
+        <v>81.2</v>
       </c>
       <c r="H24" s="2">
-        <v>56</v>
+        <v>43.2</v>
       </c>
       <c r="I24" s="2">
-        <v>17.2</v>
+        <v>33.2</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>260</v>
@@ -2058,28 +2058,28 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>129.64</v>
+        <v>389.9</v>
       </c>
       <c r="C25" s="2">
-        <v>42.1</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="D25" s="2">
-        <v>10.39</v>
+        <v>-4.48</v>
       </c>
       <c r="E25" s="2">
-        <v>11.46</v>
+        <v>-8.01</v>
       </c>
       <c r="F25" s="2">
-        <v>66.67</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="G25" s="2">
-        <v>76.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H25" s="2">
-        <v>81.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I25" s="2">
-        <v>91.2</v>
+        <v>90</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>260</v>
@@ -2090,28 +2090,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>4159.9</v>
+        <v>618.2</v>
       </c>
       <c r="C26" s="2">
-        <v>39.54</v>
+        <v>55.5</v>
       </c>
       <c r="D26" s="2">
-        <v>23.84</v>
+        <v>43.75</v>
       </c>
       <c r="E26" s="2">
-        <v>3.89</v>
+        <v>-14.95</v>
       </c>
       <c r="F26" s="2">
-        <v>65.22</v>
+        <v>72.09</v>
       </c>
       <c r="G26" s="2">
-        <v>81.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H26" s="2">
-        <v>78.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I26" s="2">
-        <v>87.2</v>
+        <v>88</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>260</v>
@@ -2122,28 +2122,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>607.2</v>
+        <v>1315.7</v>
       </c>
       <c r="C27" s="2">
-        <v>47.27</v>
+        <v>34.17</v>
       </c>
       <c r="D27" s="2">
-        <v>45.54</v>
+        <v>25.04</v>
       </c>
       <c r="E27" s="2">
-        <v>-12.11</v>
+        <v>3.22</v>
       </c>
       <c r="F27" s="2">
-        <v>63.77</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="G27" s="2">
-        <v>69.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="H27" s="2">
-        <v>88</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I27" s="2">
-        <v>98.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>260</v>
@@ -2154,28 +2154,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>78.34</v>
+        <v>206.46</v>
       </c>
       <c r="C28" s="2">
-        <v>40.27</v>
+        <v>13.96</v>
       </c>
       <c r="D28" s="2">
-        <v>17.38</v>
+        <v>15.42</v>
       </c>
       <c r="E28" s="2">
-        <v>5.01</v>
+        <v>16.47</v>
       </c>
       <c r="F28" s="2">
-        <v>62.32</v>
+        <v>69.77</v>
       </c>
       <c r="G28" s="2">
-        <v>70</v>
+        <v>71.2</v>
       </c>
       <c r="H28" s="2">
-        <v>70</v>
+        <v>31.6</v>
       </c>
       <c r="I28" s="2">
-        <v>56</v>
+        <v>1.2</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>260</v>
@@ -2186,28 +2186,28 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>281.2</v>
+        <v>679.2</v>
       </c>
       <c r="C29" s="2">
-        <v>43.84</v>
+        <v>38.84</v>
       </c>
       <c r="D29" s="2">
-        <v>2.65</v>
+        <v>16.73</v>
       </c>
       <c r="E29" s="2">
-        <v>7.45</v>
+        <v>2.77</v>
       </c>
       <c r="F29" s="2">
-        <v>60.87</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G29" s="2">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H29" s="2">
-        <v>64.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="I29" s="2">
-        <v>27.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>260</v>
@@ -2218,28 +2218,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>568.55</v>
+        <v>422.75</v>
       </c>
       <c r="C30" s="2">
-        <v>27.63</v>
+        <v>26.02</v>
       </c>
       <c r="D30" s="2">
-        <v>13.53</v>
+        <v>7.17</v>
       </c>
       <c r="E30" s="2">
-        <v>9.800000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="F30" s="2">
-        <v>59.42</v>
+        <v>67.44</v>
       </c>
       <c r="G30" s="2">
-        <v>58.4</v>
+        <v>64</v>
       </c>
       <c r="H30" s="2">
-        <v>44.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I30" s="2">
-        <v>53.2</v>
+        <v>46.8</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>260</v>
@@ -2250,28 +2250,28 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>316</v>
+        <v>284.75</v>
       </c>
       <c r="C31" s="2">
-        <v>61.34</v>
+        <v>30.55</v>
       </c>
       <c r="D31" s="2">
-        <v>18.09</v>
+        <v>7.76</v>
       </c>
       <c r="E31" s="2">
-        <v>-10.9</v>
+        <v>8.19</v>
       </c>
       <c r="F31" s="2">
-        <v>57.97</v>
+        <v>66.28</v>
       </c>
       <c r="G31" s="2">
-        <v>68</v>
+        <v>63.2</v>
       </c>
       <c r="H31" s="2">
-        <v>87.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="I31" s="2">
-        <v>92</v>
+        <v>59.6</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>260</v>
@@ -2282,28 +2282,28 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>206.63</v>
+        <v>527.75</v>
       </c>
       <c r="C32" s="2">
-        <v>13.43</v>
+        <v>55.82</v>
       </c>
       <c r="D32" s="2">
-        <v>13.71</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E32" s="2">
-        <v>14.84</v>
+        <v>-6.02</v>
       </c>
       <c r="F32" s="2">
-        <v>56.52</v>
+        <v>65.12</v>
       </c>
       <c r="G32" s="2">
-        <v>31.6</v>
+        <v>78.8</v>
       </c>
       <c r="H32" s="2">
-        <v>1.2</v>
+        <v>81.2</v>
       </c>
       <c r="I32" s="2">
-        <v>8.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>260</v>
@@ -2314,28 +2314,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>238.21</v>
+        <v>130.16</v>
       </c>
       <c r="C33" s="2">
-        <v>28.95</v>
+        <v>45.9</v>
       </c>
       <c r="D33" s="2">
-        <v>12.44</v>
+        <v>11.47</v>
       </c>
       <c r="E33" s="2">
-        <v>5.23</v>
+        <v>-2.84</v>
       </c>
       <c r="F33" s="2">
-        <v>55.07</v>
+        <v>63.95</v>
       </c>
       <c r="G33" s="2">
-        <v>66.8</v>
+        <v>80</v>
       </c>
       <c r="H33" s="2">
-        <v>73.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I33" s="2">
-        <v>65.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>260</v>
@@ -2346,28 +2346,28 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>46.52</v>
+        <v>292.65</v>
       </c>
       <c r="C34" s="2">
-        <v>25.87</v>
+        <v>42.51</v>
       </c>
       <c r="D34" s="2">
-        <v>21.62</v>
+        <v>4.86</v>
       </c>
       <c r="E34" s="2">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="F34" s="2">
-        <v>53.62</v>
+        <v>62.79</v>
       </c>
       <c r="G34" s="2">
-        <v>47.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H34" s="2">
-        <v>45.2</v>
+        <v>57.6</v>
       </c>
       <c r="I34" s="2">
-        <v>59.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>260</v>
@@ -2378,28 +2378,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>2562.8</v>
+        <v>172.11</v>
       </c>
       <c r="C35" s="2">
-        <v>25.57</v>
+        <v>33.72</v>
       </c>
       <c r="D35" s="2">
-        <v>12.61</v>
+        <v>5.61</v>
       </c>
       <c r="E35" s="2">
-        <v>5.14</v>
+        <v>5.65</v>
       </c>
       <c r="F35" s="2">
-        <v>52.17</v>
+        <v>61.63</v>
       </c>
       <c r="G35" s="2">
-        <v>72</v>
+        <v>28.4</v>
       </c>
       <c r="H35" s="2">
-        <v>35.6</v>
+        <v>16.4</v>
       </c>
       <c r="I35" s="2">
-        <v>34.8</v>
+        <v>32.8</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>260</v>
@@ -2410,28 +2410,28 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>177.66</v>
+        <v>46.7</v>
       </c>
       <c r="C36" s="2">
-        <v>18.52</v>
+        <v>34.43</v>
       </c>
       <c r="D36" s="2">
-        <v>23.63</v>
+        <v>13.9</v>
       </c>
       <c r="E36" s="2">
-        <v>0.6899999999999999</v>
+        <v>-0.34</v>
       </c>
       <c r="F36" s="2">
-        <v>50.72</v>
+        <v>60.47</v>
       </c>
       <c r="G36" s="2">
-        <v>32.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H36" s="2">
-        <v>46.4</v>
+        <v>47.2</v>
       </c>
       <c r="I36" s="2">
-        <v>60</v>
+        <v>44.8</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>260</v>
@@ -2442,28 +2442,28 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>9.279999999999999</v>
+        <v>135.11</v>
       </c>
       <c r="C37" s="2">
-        <v>11.81</v>
+        <v>38.59</v>
       </c>
       <c r="D37" s="2">
-        <v>13.73</v>
+        <v>11.84</v>
       </c>
       <c r="E37" s="2">
-        <v>8.789999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="F37" s="2">
-        <v>49.28</v>
+        <v>59.3</v>
       </c>
       <c r="G37" s="2">
-        <v>62.4</v>
+        <v>69.2</v>
       </c>
       <c r="H37" s="2">
-        <v>53.6</v>
+        <v>64.8</v>
       </c>
       <c r="I37" s="2">
-        <v>63.6</v>
+        <v>68</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>260</v>
@@ -2474,28 +2474,28 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>2331.9</v>
+        <v>1604.5</v>
       </c>
       <c r="C38" s="2">
-        <v>18.42</v>
+        <v>26.85</v>
       </c>
       <c r="D38" s="2">
-        <v>10.17</v>
+        <v>13.99</v>
       </c>
       <c r="E38" s="2">
-        <v>5.68</v>
+        <v>1.81</v>
       </c>
       <c r="F38" s="2">
-        <v>47.83</v>
+        <v>58.14</v>
       </c>
       <c r="G38" s="2">
-        <v>38</v>
+        <v>57.2</v>
       </c>
       <c r="H38" s="2">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="I38" s="2">
-        <v>28</v>
+        <v>52.4</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>260</v>
@@ -2506,28 +2506,28 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>259.95</v>
+        <v>864.4</v>
       </c>
       <c r="C39" s="2">
-        <v>12.06</v>
+        <v>4.09</v>
       </c>
       <c r="D39" s="2">
-        <v>13.66</v>
+        <v>7.37</v>
       </c>
       <c r="E39" s="2">
-        <v>6.29</v>
+        <v>12.44</v>
       </c>
       <c r="F39" s="2">
-        <v>46.38</v>
+        <v>56.98</v>
       </c>
       <c r="G39" s="2">
-        <v>52.4</v>
+        <v>22</v>
       </c>
       <c r="H39" s="2">
-        <v>30.8</v>
+        <v>13.2</v>
       </c>
       <c r="I39" s="2">
-        <v>28.4</v>
+        <v>2.8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>260</v>
@@ -2538,28 +2538,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>16.34</v>
+        <v>420.7</v>
       </c>
       <c r="C40" s="2">
-        <v>16.13</v>
+        <v>27.04</v>
       </c>
       <c r="D40" s="2">
-        <v>20.5</v>
+        <v>3.04</v>
       </c>
       <c r="E40" s="2">
-        <v>-2.68</v>
+        <v>3.06</v>
       </c>
       <c r="F40" s="2">
-        <v>44.93</v>
+        <v>55.81</v>
       </c>
       <c r="G40" s="2">
-        <v>78.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="H40" s="2">
-        <v>86.8</v>
+        <v>76.8</v>
       </c>
       <c r="I40" s="2">
-        <v>72.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>260</v>
@@ -2570,28 +2570,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>372.55</v>
+        <v>61.14</v>
       </c>
       <c r="C41" s="2">
-        <v>-1.2</v>
+        <v>41.72</v>
       </c>
       <c r="D41" s="2">
-        <v>5</v>
+        <v>-2.75</v>
       </c>
       <c r="E41" s="2">
-        <v>11.4</v>
+        <v>-2.46</v>
       </c>
       <c r="F41" s="2">
-        <v>43.48</v>
+        <v>54.65</v>
       </c>
       <c r="G41" s="2">
-        <v>48.4</v>
+        <v>38.8</v>
       </c>
       <c r="H41" s="2">
-        <v>57.6</v>
+        <v>37.2</v>
       </c>
       <c r="I41" s="2">
-        <v>14.4</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>260</v>
@@ -2602,28 +2602,28 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>302.3</v>
+        <v>1448.6</v>
       </c>
       <c r="C42" s="2">
-        <v>26.33</v>
+        <v>21.48</v>
       </c>
       <c r="D42" s="2">
-        <v>1.12</v>
+        <v>-2.65</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.48</v>
+        <v>7.08</v>
       </c>
       <c r="F42" s="2">
-        <v>42.03</v>
+        <v>53.49</v>
       </c>
       <c r="G42" s="2">
-        <v>65.59999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="H42" s="2">
-        <v>61.2</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2">
-        <v>68</v>
+        <v>31.2</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>260</v>
@@ -2634,28 +2634,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1105.4</v>
+        <v>1160</v>
       </c>
       <c r="C43" s="2">
-        <v>36.62</v>
+        <v>19.61</v>
       </c>
       <c r="D43" s="2">
-        <v>4.99</v>
+        <v>10.51</v>
       </c>
       <c r="E43" s="2">
-        <v>-8.449999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="F43" s="2">
-        <v>40.58</v>
+        <v>52.33</v>
       </c>
       <c r="G43" s="2">
-        <v>44.4</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="I43" s="2">
-        <v>36.4</v>
+        <v>67.2</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>260</v>
@@ -2666,28 +2666,28 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1836.1</v>
+        <v>206.21</v>
       </c>
       <c r="C44" s="2">
-        <v>21.43</v>
+        <v>84.3</v>
       </c>
       <c r="D44" s="2">
-        <v>12.77</v>
+        <v>-11.49</v>
       </c>
       <c r="E44" s="2">
-        <v>-6.15</v>
+        <v>-21.21</v>
       </c>
       <c r="F44" s="2">
-        <v>39.13</v>
+        <v>51.16</v>
       </c>
       <c r="G44" s="2">
-        <v>44</v>
+        <v>87.2</v>
       </c>
       <c r="H44" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="I44" s="2">
-        <v>58.8</v>
+        <v>99.2</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>260</v>
@@ -2698,28 +2698,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>150.53</v>
+        <v>507.1</v>
       </c>
       <c r="C45" s="2">
-        <v>15.39</v>
+        <v>19.37</v>
       </c>
       <c r="D45" s="2">
-        <v>0.1</v>
+        <v>8.59</v>
       </c>
       <c r="E45" s="2">
-        <v>2.33</v>
+        <v>0.75</v>
       </c>
       <c r="F45" s="2">
-        <v>37.68</v>
+        <v>50</v>
       </c>
       <c r="G45" s="2">
-        <v>64</v>
+        <v>29.6</v>
       </c>
       <c r="H45" s="2">
-        <v>52.4</v>
+        <v>15.2</v>
       </c>
       <c r="I45" s="2">
-        <v>36.8</v>
+        <v>46.4</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>260</v>
@@ -2730,28 +2730,28 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>392.7</v>
+        <v>799.5</v>
       </c>
       <c r="C46" s="2">
-        <v>22.8</v>
+        <v>17.78</v>
       </c>
       <c r="D46" s="2">
-        <v>-1.28</v>
+        <v>2.76</v>
       </c>
       <c r="E46" s="2">
-        <v>-5.28</v>
+        <v>2.8</v>
       </c>
       <c r="F46" s="2">
-        <v>36.23</v>
+        <v>48.84</v>
       </c>
       <c r="G46" s="2">
-        <v>36.8</v>
+        <v>56.8</v>
       </c>
       <c r="H46" s="2">
-        <v>42.8</v>
+        <v>57.2</v>
       </c>
       <c r="I46" s="2">
-        <v>60.4</v>
+        <v>40</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>260</v>
@@ -2762,28 +2762,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>21.43</v>
+        <v>2575.4</v>
       </c>
       <c r="C47" s="2">
-        <v>41.45</v>
+        <v>16.76</v>
       </c>
       <c r="D47" s="2">
-        <v>1.18</v>
+        <v>6.06</v>
       </c>
       <c r="E47" s="2">
-        <v>-16.58</v>
+        <v>1.51</v>
       </c>
       <c r="F47" s="2">
-        <v>34.78</v>
+        <v>47.67</v>
       </c>
       <c r="G47" s="2">
-        <v>32.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H47" s="2">
-        <v>64.8</v>
+        <v>72</v>
       </c>
       <c r="I47" s="2">
-        <v>75.59999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>260</v>
@@ -2794,28 +2794,28 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>31.6</v>
+        <v>510.3</v>
       </c>
       <c r="C48" s="2">
-        <v>20.8</v>
+        <v>30.48</v>
       </c>
       <c r="D48" s="2">
-        <v>-5.81</v>
+        <v>-0.92</v>
       </c>
       <c r="E48" s="2">
-        <v>-3.89</v>
+        <v>-2.05</v>
       </c>
       <c r="F48" s="2">
-        <v>33.33</v>
+        <v>46.51</v>
       </c>
       <c r="G48" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H48" s="2">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="I48" s="2">
-        <v>12</v>
+        <v>41.6</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>260</v>
@@ -2826,28 +2826,28 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>1497.1</v>
+        <v>818.45</v>
       </c>
       <c r="C49" s="2">
-        <v>43.14</v>
+        <v>26.43</v>
       </c>
       <c r="D49" s="2">
-        <v>-1.46</v>
+        <v>-0.26</v>
       </c>
       <c r="E49" s="2">
-        <v>-21.08</v>
+        <v>-2.86</v>
       </c>
       <c r="F49" s="2">
-        <v>31.88</v>
+        <v>45.35</v>
       </c>
       <c r="G49" s="2">
-        <v>56.4</v>
+        <v>53.2</v>
       </c>
       <c r="H49" s="2">
-        <v>81.2</v>
+        <v>51.2</v>
       </c>
       <c r="I49" s="2">
-        <v>88.8</v>
+        <v>48</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>260</v>
@@ -2858,28 +2858,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>328.9</v>
+        <v>104.27</v>
       </c>
       <c r="C50" s="2">
-        <v>-3.09</v>
+        <v>10.02</v>
       </c>
       <c r="D50" s="2">
-        <v>-6.99</v>
+        <v>11.91</v>
       </c>
       <c r="E50" s="2">
-        <v>4.66</v>
+        <v>-2.41</v>
       </c>
       <c r="F50" s="2">
-        <v>30.43</v>
+        <v>44.19</v>
       </c>
       <c r="G50" s="2">
-        <v>13.6</v>
+        <v>27.2</v>
       </c>
       <c r="H50" s="2">
-        <v>13.6</v>
+        <v>32</v>
       </c>
       <c r="I50" s="2">
-        <v>12.8</v>
+        <v>28.8</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>260</v>
@@ -2890,28 +2890,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>124.22</v>
+        <v>21.44</v>
       </c>
       <c r="C51" s="2">
-        <v>5.81</v>
+        <v>45.95</v>
       </c>
       <c r="D51" s="2">
-        <v>2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="E51" s="2">
-        <v>-4.36</v>
+        <v>-12.85</v>
       </c>
       <c r="F51" s="2">
-        <v>28.99</v>
+        <v>43.02</v>
       </c>
       <c r="G51" s="2">
-        <v>26.4</v>
+        <v>40.4</v>
       </c>
       <c r="H51" s="2">
-        <v>38</v>
+        <v>32.4</v>
       </c>
       <c r="I51" s="2">
-        <v>42.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>260</v>
@@ -2922,28 +2922,28 @@
         <v>59</v>
       </c>
       <c r="B52" s="1">
-        <v>151.64</v>
+        <v>9.26</v>
       </c>
       <c r="C52" s="2">
-        <v>16.56</v>
+        <v>15.75</v>
       </c>
       <c r="D52" s="2">
-        <v>-6.38</v>
+        <v>3.81</v>
       </c>
       <c r="E52" s="2">
-        <v>-6.32</v>
+        <v>-2.11</v>
       </c>
       <c r="F52" s="2">
-        <v>27.54</v>
+        <v>41.86</v>
       </c>
       <c r="G52" s="2">
-        <v>16.4</v>
+        <v>61.2</v>
       </c>
       <c r="H52" s="2">
-        <v>33.2</v>
+        <v>62.4</v>
       </c>
       <c r="I52" s="2">
-        <v>50.8</v>
+        <v>53.2</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>260</v>
@@ -2954,28 +2954,28 @@
         <v>60</v>
       </c>
       <c r="B53" s="1">
-        <v>9180</v>
+        <v>433.55</v>
       </c>
       <c r="C53" s="2">
-        <v>9.130000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="D53" s="2">
-        <v>0.58</v>
+        <v>-2.46</v>
       </c>
       <c r="E53" s="2">
-        <v>-7.94</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2">
-        <v>26.09</v>
+        <v>40.7</v>
       </c>
       <c r="G53" s="2">
-        <v>27.6</v>
+        <v>46.4</v>
       </c>
       <c r="H53" s="2">
-        <v>10.8</v>
+        <v>62</v>
       </c>
       <c r="I53" s="2">
-        <v>31.2</v>
+        <v>36</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>260</v>
@@ -2986,28 +2986,28 @@
         <v>61</v>
       </c>
       <c r="B54" s="1">
-        <v>306.25</v>
+        <v>212.84</v>
       </c>
       <c r="C54" s="2">
-        <v>-2.67</v>
+        <v>20.36</v>
       </c>
       <c r="D54" s="2">
-        <v>1.52</v>
+        <v>-8.42</v>
       </c>
       <c r="E54" s="2">
-        <v>-2.99</v>
+        <v>0.89</v>
       </c>
       <c r="F54" s="2">
-        <v>24.64</v>
+        <v>39.53</v>
       </c>
       <c r="G54" s="2">
-        <v>17.2</v>
+        <v>12.4</v>
       </c>
       <c r="H54" s="2">
-        <v>27.6</v>
+        <v>6.4</v>
       </c>
       <c r="I54" s="2">
-        <v>39.6</v>
+        <v>15.6</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>260</v>
@@ -3018,28 +3018,28 @@
         <v>62</v>
       </c>
       <c r="B55" s="1">
-        <v>149.23</v>
+        <v>131.18</v>
       </c>
       <c r="C55" s="2">
-        <v>-1.92</v>
+        <v>11.36</v>
       </c>
       <c r="D55" s="2">
-        <v>-2.36</v>
+        <v>11.51</v>
       </c>
       <c r="E55" s="2">
-        <v>-1.82</v>
+        <v>-4.73</v>
       </c>
       <c r="F55" s="2">
-        <v>23.19</v>
+        <v>38.37</v>
       </c>
       <c r="G55" s="2">
-        <v>21.2</v>
+        <v>54.4</v>
       </c>
       <c r="H55" s="2">
-        <v>16</v>
+        <v>39.2</v>
       </c>
       <c r="I55" s="2">
-        <v>14.8</v>
+        <v>47.6</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>260</v>
@@ -3050,28 +3050,28 @@
         <v>63</v>
       </c>
       <c r="B56" s="1">
-        <v>193.19</v>
+        <v>478</v>
       </c>
       <c r="C56" s="2">
-        <v>12.53</v>
+        <v>14.29</v>
       </c>
       <c r="D56" s="2">
-        <v>-10.21</v>
+        <v>-0.35</v>
       </c>
       <c r="E56" s="2">
-        <v>-5.71</v>
+        <v>-0.67</v>
       </c>
       <c r="F56" s="2">
-        <v>21.74</v>
+        <v>37.21</v>
       </c>
       <c r="G56" s="2">
-        <v>28.8</v>
+        <v>48</v>
       </c>
       <c r="H56" s="2">
-        <v>25.6</v>
+        <v>49.6</v>
       </c>
       <c r="I56" s="2">
-        <v>41.2</v>
+        <v>56.4</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>260</v>
@@ -3082,28 +3082,28 @@
         <v>64</v>
       </c>
       <c r="B57" s="1">
-        <v>120.87</v>
+        <v>111.39</v>
       </c>
       <c r="C57" s="2">
-        <v>7.44</v>
+        <v>25.81</v>
       </c>
       <c r="D57" s="2">
-        <v>-3.37</v>
+        <v>-1.67</v>
       </c>
       <c r="E57" s="2">
-        <v>-8.56</v>
+        <v>-7.97</v>
       </c>
       <c r="F57" s="2">
-        <v>20.29</v>
+        <v>36.05</v>
       </c>
       <c r="G57" s="2">
-        <v>16.8</v>
+        <v>51.2</v>
       </c>
       <c r="H57" s="2">
-        <v>25.2</v>
+        <v>54.4</v>
       </c>
       <c r="I57" s="2">
-        <v>37.6</v>
+        <v>62.4</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>260</v>
@@ -3114,28 +3114,28 @@
         <v>65</v>
       </c>
       <c r="B58" s="1">
-        <v>70.31</v>
+        <v>1568.3</v>
       </c>
       <c r="C58" s="2">
-        <v>1.94</v>
+        <v>-0.22</v>
       </c>
       <c r="D58" s="2">
-        <v>-4.22</v>
+        <v>-1.43</v>
       </c>
       <c r="E58" s="2">
-        <v>-5.55</v>
+        <v>3.43</v>
       </c>
       <c r="F58" s="2">
-        <v>18.84</v>
+        <v>34.88</v>
       </c>
       <c r="G58" s="2">
         <v>11.6</v>
       </c>
       <c r="H58" s="2">
-        <v>20.4</v>
+        <v>1.6</v>
       </c>
       <c r="I58" s="2">
-        <v>29.6</v>
+        <v>3.6</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>260</v>
@@ -3146,28 +3146,28 @@
         <v>66</v>
       </c>
       <c r="B59" s="1">
-        <v>133.37</v>
+        <v>127.4</v>
       </c>
       <c r="C59" s="2">
-        <v>1.21</v>
+        <v>11.77</v>
       </c>
       <c r="D59" s="2">
-        <v>-8.800000000000001</v>
+        <v>-2.52</v>
       </c>
       <c r="E59" s="2">
-        <v>-3.71</v>
+        <v>-2.41</v>
       </c>
       <c r="F59" s="2">
-        <v>17.39</v>
+        <v>33.72</v>
       </c>
       <c r="G59" s="2">
-        <v>22.8</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="I59" s="2">
-        <v>43.2</v>
+        <v>37.6</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>260</v>
@@ -3178,28 +3178,28 @@
         <v>67</v>
       </c>
       <c r="B60" s="1">
-        <v>121.22</v>
+        <v>252</v>
       </c>
       <c r="C60" s="2">
-        <v>2.02</v>
+        <v>33.49</v>
       </c>
       <c r="D60" s="2">
-        <v>-2.99</v>
+        <v>-3.43</v>
       </c>
       <c r="E60" s="2">
-        <v>-9.06</v>
+        <v>-13.06</v>
       </c>
       <c r="F60" s="2">
-        <v>15.94</v>
+        <v>32.56</v>
       </c>
       <c r="G60" s="2">
-        <v>8.800000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="H60" s="2">
-        <v>32.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I60" s="2">
-        <v>35.2</v>
+        <v>82.8</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>260</v>
@@ -3210,28 +3210,28 @@
         <v>68</v>
       </c>
       <c r="B61" s="1">
-        <v>163.67</v>
+        <v>556.8</v>
       </c>
       <c r="C61" s="2">
-        <v>-7.05</v>
+        <v>1.87</v>
       </c>
       <c r="D61" s="2">
-        <v>0.04</v>
+        <v>-0.79</v>
       </c>
       <c r="E61" s="2">
-        <v>-6.22</v>
+        <v>-0.08</v>
       </c>
       <c r="F61" s="2">
-        <v>14.49</v>
+        <v>31.4</v>
       </c>
       <c r="G61" s="2">
-        <v>6.8</v>
+        <v>37.2</v>
       </c>
       <c r="H61" s="2">
-        <v>18.8</v>
+        <v>26.8</v>
       </c>
       <c r="I61" s="2">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>260</v>
@@ -3242,28 +3242,28 @@
         <v>69</v>
       </c>
       <c r="B62" s="1">
-        <v>195.04</v>
+        <v>115.47</v>
       </c>
       <c r="C62" s="2">
-        <v>3.5</v>
+        <v>11.29</v>
       </c>
       <c r="D62" s="2">
-        <v>-11.5</v>
+        <v>3.14</v>
       </c>
       <c r="E62" s="2">
-        <v>-6.21</v>
+        <v>-8.44</v>
       </c>
       <c r="F62" s="2">
-        <v>13.04</v>
+        <v>30.23</v>
       </c>
       <c r="G62" s="2">
-        <v>6.4</v>
+        <v>38.4</v>
       </c>
       <c r="H62" s="2">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="I62" s="2">
-        <v>27.2</v>
+        <v>44</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>260</v>
@@ -3274,28 +3274,28 @@
         <v>70</v>
       </c>
       <c r="B63" s="1">
-        <v>572.5</v>
+        <v>855.9</v>
       </c>
       <c r="C63" s="2">
-        <v>-3.8</v>
+        <v>7.62</v>
       </c>
       <c r="D63" s="2">
-        <v>-10.34</v>
+        <v>4.74</v>
       </c>
       <c r="E63" s="2">
-        <v>-3.97</v>
+        <v>-8.43</v>
       </c>
       <c r="F63" s="2">
-        <v>11.59</v>
+        <v>29.07</v>
       </c>
       <c r="G63" s="2">
-        <v>9.199999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="H63" s="2">
-        <v>1.6</v>
+        <v>45.6</v>
       </c>
       <c r="I63" s="2">
-        <v>2.8</v>
+        <v>65.2</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>260</v>
@@ -3306,28 +3306,28 @@
         <v>71</v>
       </c>
       <c r="B64" s="1">
-        <v>147.04</v>
+        <v>203.96</v>
       </c>
       <c r="C64" s="2">
-        <v>-8.550000000000001</v>
+        <v>25.34</v>
       </c>
       <c r="D64" s="2">
-        <v>-4.53</v>
+        <v>3.51</v>
       </c>
       <c r="E64" s="2">
-        <v>-5.69</v>
+        <v>-16.79</v>
       </c>
       <c r="F64" s="2">
-        <v>10.14</v>
+        <v>27.91</v>
       </c>
       <c r="G64" s="2">
-        <v>5.2</v>
+        <v>31.6</v>
       </c>
       <c r="H64" s="2">
-        <v>12.8</v>
+        <v>46.8</v>
       </c>
       <c r="I64" s="2">
-        <v>6.8</v>
+        <v>70.8</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>260</v>
@@ -3338,28 +3338,28 @@
         <v>72</v>
       </c>
       <c r="B65" s="1">
-        <v>216.55</v>
+        <v>502.95</v>
       </c>
       <c r="C65" s="2">
-        <v>-5.68</v>
+        <v>0.98</v>
       </c>
       <c r="D65" s="2">
-        <v>-6.24</v>
+        <v>-1.47</v>
       </c>
       <c r="E65" s="2">
-        <v>-6.8</v>
+        <v>-3.32</v>
       </c>
       <c r="F65" s="2">
-        <v>8.699999999999999</v>
+        <v>26.74</v>
       </c>
       <c r="G65" s="2">
-        <v>29.2</v>
+        <v>12</v>
       </c>
       <c r="H65" s="2">
-        <v>12.4</v>
+        <v>18.8</v>
       </c>
       <c r="I65" s="2">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>260</v>
@@ -3370,28 +3370,28 @@
         <v>73</v>
       </c>
       <c r="B66" s="1">
-        <v>218.72</v>
+        <v>121.09</v>
       </c>
       <c r="C66" s="2">
-        <v>-7.02</v>
+        <v>9.52</v>
       </c>
       <c r="D66" s="2">
-        <v>-13.33</v>
+        <v>-1.77</v>
       </c>
       <c r="E66" s="2">
-        <v>-2.61</v>
+        <v>-7.53</v>
       </c>
       <c r="F66" s="2">
-        <v>7.25</v>
+        <v>25.58</v>
       </c>
       <c r="G66" s="2">
         <v>20.8</v>
       </c>
       <c r="H66" s="2">
-        <v>10</v>
+        <v>16.8</v>
       </c>
       <c r="I66" s="2">
-        <v>6</v>
+        <v>24.8</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>260</v>
@@ -3402,28 +3402,28 @@
         <v>74</v>
       </c>
       <c r="B67" s="1">
-        <v>268.85</v>
+        <v>497.35</v>
       </c>
       <c r="C67" s="2">
-        <v>-9.68</v>
+        <v>4.23</v>
       </c>
       <c r="D67" s="2">
-        <v>-10.65</v>
+        <v>-4.74</v>
       </c>
       <c r="E67" s="2">
-        <v>-4</v>
+        <v>-3.59</v>
       </c>
       <c r="F67" s="2">
-        <v>5.8</v>
+        <v>24.42</v>
       </c>
       <c r="G67" s="2">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="H67" s="2">
-        <v>5.6</v>
+        <v>19.2</v>
       </c>
       <c r="I67" s="2">
-        <v>7.2</v>
+        <v>22.8</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>260</v>
@@ -3434,28 +3434,28 @@
         <v>75</v>
       </c>
       <c r="B68" s="1">
-        <v>554.8</v>
+        <v>31.34</v>
       </c>
       <c r="C68" s="2">
-        <v>-6.94</v>
+        <v>14.09</v>
       </c>
       <c r="D68" s="2">
-        <v>-12.13</v>
+        <v>-10.35</v>
       </c>
       <c r="E68" s="2">
-        <v>-5.47</v>
+        <v>-5.94</v>
       </c>
       <c r="F68" s="2">
-        <v>4.35</v>
+        <v>23.26</v>
       </c>
       <c r="G68" s="2">
-        <v>0.8</v>
+        <v>38</v>
       </c>
       <c r="H68" s="2">
-        <v>11.2</v>
+        <v>22</v>
       </c>
       <c r="I68" s="2">
-        <v>1.6</v>
+        <v>29.6</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>260</v>
@@ -3466,28 +3466,28 @@
         <v>76</v>
       </c>
       <c r="B69" s="1">
-        <v>720.55</v>
+        <v>281.05</v>
       </c>
       <c r="C69" s="2">
-        <v>-12.13</v>
+        <v>-2.97</v>
       </c>
       <c r="D69" s="2">
-        <v>-22.35</v>
+        <v>-7.17</v>
       </c>
       <c r="E69" s="2">
-        <v>-10.11</v>
+        <v>0.48</v>
       </c>
       <c r="F69" s="2">
-        <v>2.9</v>
+        <v>22.09</v>
       </c>
       <c r="G69" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H69" s="2">
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
       <c r="I69" s="2">
-        <v>11.2</v>
+        <v>5.6</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>260</v>
@@ -3498,28 +3498,28 @@
         <v>77</v>
       </c>
       <c r="B70" s="1">
-        <v>248.7</v>
+        <v>1482.4</v>
       </c>
       <c r="C70" s="2">
-        <v>-26.05</v>
+        <v>38.85</v>
       </c>
       <c r="D70" s="2">
-        <v>-32.57</v>
+        <v>-10.28</v>
       </c>
       <c r="E70" s="2">
-        <v>-39.68</v>
+        <v>-19.81</v>
       </c>
       <c r="F70" s="2">
-        <v>1.45</v>
+        <v>20.93</v>
       </c>
       <c r="G70" s="2">
-        <v>80.40000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="H70" s="2">
-        <v>70.8</v>
+        <v>56.4</v>
       </c>
       <c r="I70" s="2">
-        <v>76.8</v>
+        <v>81.2</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>260</v>
@@ -3529,14 +3529,29 @@
       <c r="A71" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="B71" s="1">
+        <v>440.35</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3.24</v>
+      </c>
+      <c r="D71" s="2">
+        <v>-5.65</v>
+      </c>
+      <c r="E71" s="2">
+        <v>-4.34</v>
+      </c>
+      <c r="F71" s="2">
+        <v>19.77</v>
+      </c>
       <c r="G71" s="2">
-        <v>34.8</v>
+        <v>13.2</v>
       </c>
       <c r="H71" s="2">
-        <v>83.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="I71" s="2">
-        <v>90.40000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>260</v>
@@ -3546,14 +3561,29 @@
       <c r="A72" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="B72" s="1">
+        <v>99.16</v>
+      </c>
+      <c r="C72" s="2">
+        <v>-1.52</v>
+      </c>
+      <c r="D72" s="2">
+        <v>-7.84</v>
+      </c>
+      <c r="E72" s="2">
+        <v>-1.02</v>
+      </c>
+      <c r="F72" s="2">
+        <v>18.6</v>
+      </c>
       <c r="G72" s="2">
-        <v>82.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="H72" s="2">
-        <v>95.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="I72" s="2">
-        <v>99.2</v>
+        <v>5.2</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>260</v>
@@ -3563,14 +3593,29 @@
       <c r="A73" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="B73" s="1">
+        <v>121.85</v>
+      </c>
+      <c r="C73" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E73" s="2">
+        <v>-6.07</v>
+      </c>
+      <c r="F73" s="2">
+        <v>17.44</v>
+      </c>
       <c r="G73" s="2">
-        <v>32</v>
+        <v>14.4</v>
       </c>
       <c r="H73" s="2">
-        <v>29.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I73" s="2">
-        <v>25.6</v>
+        <v>32.4</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>260</v>
@@ -3580,14 +3625,29 @@
       <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="B74" s="1">
+        <v>755.5</v>
+      </c>
+      <c r="C74" s="2">
+        <v>56.69</v>
+      </c>
+      <c r="D74" s="2">
+        <v>-22.6</v>
+      </c>
+      <c r="E74" s="2">
+        <v>-23.78</v>
+      </c>
+      <c r="F74" s="2">
+        <v>16.28</v>
+      </c>
       <c r="G74" s="2">
-        <v>26</v>
+        <v>34.4</v>
       </c>
       <c r="H74" s="2">
-        <v>24.8</v>
+        <v>62.8</v>
       </c>
       <c r="I74" s="2">
-        <v>21.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>260</v>
@@ -3597,14 +3657,29 @@
       <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="B75" s="1">
+        <v>195.13</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2.92</v>
+      </c>
+      <c r="D75" s="2">
+        <v>-12.88</v>
+      </c>
+      <c r="E75" s="2">
+        <v>-2.06</v>
+      </c>
+      <c r="F75" s="2">
+        <v>15.12</v>
+      </c>
       <c r="G75" s="2">
-        <v>88.8</v>
+        <v>4.4</v>
       </c>
       <c r="H75" s="2">
-        <v>91.2</v>
+        <v>1.2</v>
       </c>
       <c r="I75" s="2">
-        <v>88.40000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>260</v>
@@ -3614,14 +3689,29 @@
       <c r="A76" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="B76" s="1">
+        <v>564.65</v>
+      </c>
+      <c r="C76" s="2">
+        <v>-4.49</v>
+      </c>
+      <c r="D76" s="2">
+        <v>-7.08</v>
+      </c>
+      <c r="E76" s="2">
+        <v>-1.42</v>
+      </c>
+      <c r="F76" s="2">
+        <v>13.95</v>
+      </c>
       <c r="G76" s="2">
-        <v>36</v>
+        <v>10.4</v>
       </c>
       <c r="H76" s="2">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I76" s="2">
-        <v>26</v>
+        <v>1.6</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>260</v>
@@ -3631,14 +3721,29 @@
       <c r="A77" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="B77" s="1">
+        <v>2753</v>
+      </c>
+      <c r="C77" s="2">
+        <v>7.18</v>
+      </c>
+      <c r="D77" s="2">
+        <v>-9.67</v>
+      </c>
+      <c r="E77" s="2">
+        <v>-8.41</v>
+      </c>
+      <c r="F77" s="2">
+        <v>12.79</v>
+      </c>
       <c r="G77" s="2">
-        <v>96</v>
+        <v>25.2</v>
       </c>
       <c r="H77" s="2">
-        <v>96.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I77" s="2">
-        <v>94.8</v>
+        <v>20</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>260</v>
@@ -3648,14 +3753,29 @@
       <c r="A78" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="B78" s="1">
+        <v>302.3</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1.41</v>
+      </c>
+      <c r="D78" s="2">
+        <v>-0.44</v>
+      </c>
+      <c r="E78" s="2">
+        <v>-10.8</v>
+      </c>
+      <c r="F78" s="2">
+        <v>11.63</v>
+      </c>
       <c r="G78" s="2">
-        <v>99.59999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="H78" s="2">
-        <v>98.8</v>
+        <v>17.2</v>
       </c>
       <c r="I78" s="2">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>260</v>
@@ -3665,14 +3785,29 @@
       <c r="A79" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="B79" s="1">
+        <v>263.7</v>
+      </c>
+      <c r="C79" s="2">
+        <v>-2.64</v>
+      </c>
+      <c r="D79" s="2">
+        <v>-15.09</v>
+      </c>
+      <c r="E79" s="2">
+        <v>-2.24</v>
+      </c>
+      <c r="F79" s="2">
+        <v>10.47</v>
+      </c>
       <c r="G79" s="2">
-        <v>62.8</v>
+        <v>7.2</v>
       </c>
       <c r="H79" s="2">
-        <v>84.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="I79" s="2">
-        <v>94.40000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>260</v>
@@ -3682,14 +3817,29 @@
       <c r="A80" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="B80" s="1">
+        <v>1479.6</v>
+      </c>
+      <c r="C80" s="2">
+        <v>2.3</v>
+      </c>
+      <c r="D80" s="2">
+        <v>-9.75</v>
+      </c>
+      <c r="E80" s="2">
+        <v>-7.88</v>
+      </c>
+      <c r="F80" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="G80" s="2">
-        <v>48</v>
+        <v>6.4</v>
       </c>
       <c r="H80" s="2">
-        <v>68.8</v>
+        <v>4.8</v>
       </c>
       <c r="I80" s="2">
-        <v>79.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>260</v>
@@ -3699,14 +3849,29 @@
       <c r="A81" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="B81" s="1">
+        <v>11.92</v>
+      </c>
+      <c r="C81" s="2">
+        <v>-5.62</v>
+      </c>
+      <c r="D81" s="2">
+        <v>-5.47</v>
+      </c>
+      <c r="E81" s="2">
+        <v>-7.81</v>
+      </c>
+      <c r="F81" s="2">
+        <v>8.140000000000001</v>
+      </c>
       <c r="G81" s="2">
-        <v>92.8</v>
+        <v>11.2</v>
       </c>
       <c r="H81" s="2">
-        <v>86.40000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I81" s="2">
-        <v>73.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>260</v>
@@ -3716,14 +3881,29 @@
       <c r="A82" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="B82" s="1">
+        <v>21.87</v>
+      </c>
+      <c r="C82" s="2">
+        <v>-10</v>
+      </c>
+      <c r="D82" s="2">
+        <v>-7.57</v>
+      </c>
+      <c r="E82" s="2">
+        <v>-5.24</v>
+      </c>
+      <c r="F82" s="2">
+        <v>6.98</v>
+      </c>
       <c r="G82" s="2">
-        <v>3.2</v>
+        <v>21.2</v>
       </c>
       <c r="H82" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I82" s="2">
-        <v>20.4</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>260</v>
@@ -3733,14 +3913,29 @@
       <c r="A83" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="B83" s="1">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="C83" s="2">
+        <v>-5.7</v>
+      </c>
+      <c r="D83" s="2">
+        <v>-14.23</v>
+      </c>
+      <c r="E83" s="2">
+        <v>-8.91</v>
+      </c>
+      <c r="F83" s="2">
+        <v>5.81</v>
+      </c>
       <c r="G83" s="2">
-        <v>67.2</v>
+        <v>19.2</v>
       </c>
       <c r="H83" s="2">
-        <v>67.2</v>
+        <v>20</v>
       </c>
       <c r="I83" s="2">
-        <v>77.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>260</v>
@@ -3750,14 +3945,29 @@
       <c r="A84" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="B84" s="1">
+        <v>311.9</v>
+      </c>
+      <c r="C84" s="2">
+        <v>-0.22</v>
+      </c>
+      <c r="D84" s="2">
+        <v>-20.77</v>
+      </c>
+      <c r="E84" s="2">
+        <v>-14.78</v>
+      </c>
+      <c r="F84" s="2">
+        <v>4.65</v>
+      </c>
       <c r="G84" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="H84" s="2">
         <v>34.4</v>
       </c>
-      <c r="H84" s="2">
-        <v>39.2</v>
-      </c>
       <c r="I84" s="2">
-        <v>26.4</v>
+        <v>38.8</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>260</v>
@@ -3767,14 +3977,29 @@
       <c r="A85" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="B85" s="1">
+        <v>57.71</v>
+      </c>
+      <c r="C85" s="2">
+        <v>-0.91</v>
+      </c>
+      <c r="D85" s="2">
+        <v>-20.83</v>
+      </c>
+      <c r="E85" s="2">
+        <v>-17.27</v>
+      </c>
+      <c r="F85" s="2">
+        <v>3.49</v>
+      </c>
       <c r="G85" s="2">
-        <v>40.8</v>
+        <v>1.2</v>
       </c>
       <c r="H85" s="2">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="I85" s="2">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>260</v>
@@ -3784,14 +4009,29 @@
       <c r="A86" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="B86" s="1">
+        <v>899.6</v>
+      </c>
+      <c r="C86" s="2">
+        <v>-23.67</v>
+      </c>
+      <c r="D86" s="2">
+        <v>-33.2</v>
+      </c>
+      <c r="E86" s="2">
+        <v>-5.05</v>
+      </c>
+      <c r="F86" s="2">
+        <v>2.33</v>
+      </c>
       <c r="G86" s="2">
-        <v>87.59999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="H86" s="2">
-        <v>89.59999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="I86" s="2">
-        <v>87.59999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>260</v>
@@ -3801,14 +4041,29 @@
       <c r="A87" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="B87" s="1">
+        <v>221.5</v>
+      </c>
+      <c r="C87" s="2">
+        <v>-40.18</v>
+      </c>
+      <c r="D87" s="2">
+        <v>-41.3</v>
+      </c>
+      <c r="E87" s="2">
+        <v>-52.2</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1.16</v>
+      </c>
       <c r="G87" s="2">
-        <v>73.59999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H87" s="2">
-        <v>82.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I87" s="2">
-        <v>86.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>260</v>
@@ -3819,13 +4074,13 @@
         <v>95</v>
       </c>
       <c r="G88" s="2">
-        <v>85.59999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H88" s="2">
-        <v>84.8</v>
+        <v>16</v>
       </c>
       <c r="I88" s="2">
-        <v>86.8</v>
+        <v>21.2</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>260</v>
@@ -3836,13 +4091,13 @@
         <v>96</v>
       </c>
       <c r="G89" s="2">
-        <v>25.6</v>
+        <v>34</v>
       </c>
       <c r="H89" s="2">
-        <v>44.4</v>
+        <v>36</v>
       </c>
       <c r="I89" s="2">
-        <v>56.4</v>
+        <v>45.6</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>260</v>
@@ -3853,13 +4108,13 @@
         <v>97</v>
       </c>
       <c r="G90" s="2">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="H90" s="2">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I90" s="2">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>260</v>
@@ -3870,13 +4125,13 @@
         <v>98</v>
       </c>
       <c r="G91" s="2">
-        <v>93.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="H91" s="2">
-        <v>90.40000000000001</v>
+        <v>34.8</v>
       </c>
       <c r="I91" s="2">
-        <v>92.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>260</v>
@@ -3887,13 +4142,13 @@
         <v>99</v>
       </c>
       <c r="G92" s="2">
-        <v>92</v>
+        <v>98.8</v>
       </c>
       <c r="H92" s="2">
-        <v>92.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I92" s="2">
-        <v>95.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>260</v>
@@ -3904,13 +4159,13 @@
         <v>100</v>
       </c>
       <c r="G93" s="2">
-        <v>6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H93" s="2">
-        <v>6</v>
+        <v>80.8</v>
       </c>
       <c r="I93" s="2">
-        <v>9.6</v>
+        <v>82</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>260</v>
@@ -3921,13 +4176,13 @@
         <v>101</v>
       </c>
       <c r="G94" s="2">
-        <v>51.6</v>
+        <v>25.6</v>
       </c>
       <c r="H94" s="2">
-        <v>76.8</v>
+        <v>37.6</v>
       </c>
       <c r="I94" s="2">
-        <v>76.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>260</v>
@@ -3938,13 +4193,13 @@
         <v>102</v>
       </c>
       <c r="G95" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H95" s="2">
-        <v>59.6</v>
+        <v>92</v>
       </c>
       <c r="I95" s="2">
-        <v>62</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>260</v>
@@ -3955,13 +4210,13 @@
         <v>103</v>
       </c>
       <c r="G96" s="2">
-        <v>72.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="H96" s="2">
-        <v>85.2</v>
+        <v>60.4</v>
       </c>
       <c r="I96" s="2">
-        <v>82.8</v>
+        <v>62</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>260</v>
@@ -3972,13 +4227,13 @@
         <v>104</v>
       </c>
       <c r="G97" s="2">
-        <v>18.4</v>
+        <v>64.8</v>
       </c>
       <c r="H97" s="2">
-        <v>20</v>
+        <v>55.2</v>
       </c>
       <c r="I97" s="2">
-        <v>37.2</v>
+        <v>54.4</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>260</v>
@@ -3989,13 +4244,13 @@
         <v>105</v>
       </c>
       <c r="G98" s="2">
-        <v>33.6</v>
+        <v>88.8</v>
       </c>
       <c r="H98" s="2">
-        <v>37.2</v>
+        <v>30</v>
       </c>
       <c r="I98" s="2">
-        <v>45.2</v>
+        <v>39.6</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>260</v>
@@ -4006,13 +4261,13 @@
         <v>106</v>
       </c>
       <c r="G99" s="2">
-        <v>81.2</v>
+        <v>85.2</v>
       </c>
       <c r="H99" s="2">
-        <v>72.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="I99" s="2">
-        <v>81.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>260</v>
@@ -4023,13 +4278,13 @@
         <v>107</v>
       </c>
       <c r="G100" s="2">
-        <v>70.40000000000001</v>
+        <v>26.4</v>
       </c>
       <c r="H100" s="2">
-        <v>59.2</v>
+        <v>44.8</v>
       </c>
       <c r="I100" s="2">
-        <v>67.2</v>
+        <v>48.4</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>260</v>
@@ -4040,13 +4295,13 @@
         <v>108</v>
       </c>
       <c r="G101" s="2">
-        <v>24.4</v>
+        <v>75.2</v>
       </c>
       <c r="H101" s="2">
-        <v>32.4</v>
+        <v>78</v>
       </c>
       <c r="I101" s="2">
-        <v>3.2</v>
+        <v>34</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>260</v>
@@ -4057,13 +4312,13 @@
         <v>109</v>
       </c>
       <c r="G102" s="2">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="H102" s="2">
-        <v>70.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I102" s="2">
-        <v>72</v>
+        <v>61.2</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>260</v>
@@ -4074,13 +4329,13 @@
         <v>110</v>
       </c>
       <c r="G103" s="2">
-        <v>41.6</v>
+        <v>50.4</v>
       </c>
       <c r="H103" s="2">
-        <v>53.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I103" s="2">
-        <v>48.4</v>
+        <v>60.8</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>260</v>
@@ -4091,13 +4346,13 @@
         <v>111</v>
       </c>
       <c r="G104" s="2">
-        <v>94.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H104" s="2">
-        <v>98</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I104" s="2">
-        <v>94</v>
+        <v>92.8</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>260</v>
@@ -4108,13 +4363,13 @@
         <v>112</v>
       </c>
       <c r="G105" s="2">
-        <v>35.6</v>
+        <v>86.8</v>
       </c>
       <c r="H105" s="2">
-        <v>38.4</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I105" s="2">
-        <v>38.8</v>
+        <v>56.8</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>260</v>
@@ -4125,13 +4380,13 @@
         <v>113</v>
       </c>
       <c r="G106" s="2">
-        <v>46.8</v>
+        <v>70.8</v>
       </c>
       <c r="H106" s="2">
-        <v>71.2</v>
+        <v>58</v>
       </c>
       <c r="I106" s="2">
-        <v>78</v>
+        <v>31.6</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>260</v>
@@ -4142,13 +4397,13 @@
         <v>114</v>
       </c>
       <c r="G107" s="2">
-        <v>36.4</v>
+        <v>50.8</v>
       </c>
       <c r="H107" s="2">
-        <v>28</v>
+        <v>48.4</v>
       </c>
       <c r="I107" s="2">
-        <v>24</v>
+        <v>57.2</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>260</v>
@@ -4159,13 +4414,13 @@
         <v>115</v>
       </c>
       <c r="G108" s="2">
-        <v>90.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="H108" s="2">
-        <v>88.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="I108" s="2">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>260</v>
@@ -4176,13 +4431,13 @@
         <v>116</v>
       </c>
       <c r="G109" s="2">
-        <v>12.4</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H109" s="2">
-        <v>0.4</v>
+        <v>79.2</v>
       </c>
       <c r="I109" s="2">
-        <v>0.4</v>
+        <v>62.8</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>260</v>
@@ -4193,10 +4448,10 @@
         <v>117</v>
       </c>
       <c r="G110" s="2">
-        <v>59.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H110" s="2">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I110" s="2">
         <v>59.2</v>
@@ -4210,13 +4465,13 @@
         <v>118</v>
       </c>
       <c r="G111" s="2">
-        <v>0.4</v>
+        <v>57.6</v>
       </c>
       <c r="H111" s="2">
-        <v>2.4</v>
+        <v>40</v>
       </c>
       <c r="I111" s="2">
-        <v>11.6</v>
+        <v>40.8</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>260</v>
@@ -4227,13 +4482,13 @@
         <v>119</v>
       </c>
       <c r="G112" s="2">
-        <v>60</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H112" s="2">
-        <v>66.8</v>
+        <v>68</v>
       </c>
       <c r="I112" s="2">
-        <v>57.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>260</v>
@@ -4244,13 +4499,13 @@
         <v>120</v>
       </c>
       <c r="G113" s="2">
-        <v>51.2</v>
+        <v>65.2</v>
       </c>
       <c r="H113" s="2">
-        <v>48.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I113" s="2">
-        <v>64.8</v>
+        <v>85.2</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>260</v>
@@ -4261,13 +4516,13 @@
         <v>121</v>
       </c>
       <c r="G114" s="2">
-        <v>86.8</v>
+        <v>59.6</v>
       </c>
       <c r="H114" s="2">
-        <v>82.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I114" s="2">
-        <v>91.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>260</v>
@@ -4278,13 +4533,13 @@
         <v>122</v>
       </c>
       <c r="G115" s="2">
-        <v>12</v>
+        <v>60.4</v>
       </c>
       <c r="H115" s="2">
-        <v>60.4</v>
+        <v>66</v>
       </c>
       <c r="I115" s="2">
-        <v>70</v>
+        <v>40.4</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>260</v>
@@ -4295,13 +4550,13 @@
         <v>123</v>
       </c>
       <c r="G116" s="2">
-        <v>52</v>
+        <v>61.6</v>
       </c>
       <c r="H116" s="2">
-        <v>52.8</v>
+        <v>32.8</v>
       </c>
       <c r="I116" s="2">
-        <v>47.6</v>
+        <v>46</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>260</v>
@@ -4312,13 +4567,13 @@
         <v>124</v>
       </c>
       <c r="G117" s="2">
-        <v>71.59999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="H117" s="2">
-        <v>78.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I117" s="2">
-        <v>64.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>260</v>
@@ -4329,13 +4584,13 @@
         <v>125</v>
       </c>
       <c r="G118" s="2">
-        <v>18.8</v>
+        <v>73.2</v>
       </c>
       <c r="H118" s="2">
-        <v>14</v>
+        <v>58.4</v>
       </c>
       <c r="I118" s="2">
-        <v>21.6</v>
+        <v>44.4</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>260</v>
@@ -4346,13 +4601,13 @@
         <v>126</v>
       </c>
       <c r="G119" s="2">
-        <v>42.4</v>
+        <v>68.8</v>
       </c>
       <c r="H119" s="2">
-        <v>56.4</v>
+        <v>50</v>
       </c>
       <c r="I119" s="2">
-        <v>69.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>260</v>
@@ -4363,13 +4618,13 @@
         <v>127</v>
       </c>
       <c r="G120" s="2">
-        <v>59.2</v>
+        <v>78</v>
       </c>
       <c r="H120" s="2">
-        <v>58.8</v>
+        <v>72.8</v>
       </c>
       <c r="I120" s="2">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>260</v>
@@ -4380,13 +4635,13 @@
         <v>128</v>
       </c>
       <c r="G121" s="2">
-        <v>39.6</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H121" s="2">
-        <v>49.2</v>
+        <v>98</v>
       </c>
       <c r="I121" s="2">
-        <v>58.4</v>
+        <v>43.6</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>260</v>
@@ -4397,13 +4652,13 @@
         <v>129</v>
       </c>
       <c r="G122" s="2">
-        <v>70.8</v>
+        <v>18.8</v>
       </c>
       <c r="H122" s="2">
-        <v>80</v>
+        <v>0.4</v>
       </c>
       <c r="I122" s="2">
-        <v>80.8</v>
+        <v>2.4</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>260</v>
@@ -4414,13 +4669,13 @@
         <v>130</v>
       </c>
       <c r="G123" s="2">
-        <v>91.2</v>
+        <v>4.8</v>
       </c>
       <c r="H123" s="2">
-        <v>94.8</v>
+        <v>4</v>
       </c>
       <c r="I123" s="2">
-        <v>96.40000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>260</v>
@@ -4431,13 +4686,13 @@
         <v>131</v>
       </c>
       <c r="G124" s="2">
-        <v>78</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="H124" s="2">
-        <v>34.4</v>
+        <v>91.2</v>
       </c>
       <c r="I124" s="2">
-        <v>32.4</v>
+        <v>94.8</v>
       </c>
       <c r="J124" s="4" t="s">
         <v>260</v>
@@ -4448,13 +4703,13 @@
         <v>132</v>
       </c>
       <c r="G125" s="2">
-        <v>77.59999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="H125" s="2">
-        <v>57.2</v>
+        <v>41.6</v>
       </c>
       <c r="I125" s="2">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>260</v>
@@ -4465,13 +4720,13 @@
         <v>133</v>
       </c>
       <c r="G126" s="2">
-        <v>61.2</v>
+        <v>12.8</v>
       </c>
       <c r="H126" s="2">
-        <v>54</v>
+        <v>25.2</v>
       </c>
       <c r="I126" s="2">
-        <v>54</v>
+        <v>7.6</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>260</v>
@@ -4482,13 +4737,13 @@
         <v>134</v>
       </c>
       <c r="G127" s="2">
-        <v>68.8</v>
+        <v>80.8</v>
       </c>
       <c r="H127" s="2">
-        <v>75.2</v>
+        <v>94.8</v>
       </c>
       <c r="I127" s="2">
-        <v>93.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>260</v>
@@ -4499,13 +4754,13 @@
         <v>135</v>
       </c>
       <c r="G128" s="2">
-        <v>8.4</v>
+        <v>17.6</v>
       </c>
       <c r="H128" s="2">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="I128" s="2">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>260</v>
@@ -4516,13 +4771,13 @@
         <v>136</v>
       </c>
       <c r="G129" s="2">
-        <v>54.4</v>
+        <v>32</v>
       </c>
       <c r="H129" s="2">
-        <v>62.8</v>
+        <v>43.6</v>
       </c>
       <c r="I129" s="2">
-        <v>49.2</v>
+        <v>12</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>260</v>
@@ -4533,13 +4788,13 @@
         <v>137</v>
       </c>
       <c r="G130" s="2">
-        <v>53.2</v>
+        <v>16.4</v>
       </c>
       <c r="H130" s="2">
-        <v>54.4</v>
+        <v>23.2</v>
       </c>
       <c r="I130" s="2">
-        <v>52.8</v>
+        <v>45.2</v>
       </c>
       <c r="J130" s="4" t="s">
         <v>260</v>
@@ -4550,13 +4805,13 @@
         <v>138</v>
       </c>
       <c r="G131" s="2">
-        <v>92.40000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="H131" s="2">
-        <v>92.8</v>
+        <v>21.2</v>
       </c>
       <c r="I131" s="2">
-        <v>83.2</v>
+        <v>16</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>260</v>
@@ -4567,13 +4822,13 @@
         <v>139</v>
       </c>
       <c r="G132" s="2">
-        <v>14.8</v>
+        <v>77.2</v>
       </c>
       <c r="H132" s="2">
-        <v>19.6</v>
+        <v>70</v>
       </c>
       <c r="I132" s="2">
-        <v>23.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>260</v>
@@ -4584,13 +4839,13 @@
         <v>140</v>
       </c>
       <c r="G133" s="2">
-        <v>35.2</v>
+        <v>54.8</v>
       </c>
       <c r="H133" s="2">
-        <v>30.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I133" s="2">
-        <v>61.6</v>
+        <v>86.8</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>260</v>
@@ -4601,13 +4856,13 @@
         <v>141</v>
       </c>
       <c r="G134" s="2">
-        <v>47.6</v>
+        <v>27.6</v>
       </c>
       <c r="H134" s="2">
-        <v>50.8</v>
+        <v>53.2</v>
       </c>
       <c r="I134" s="2">
-        <v>48.8</v>
+        <v>54</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>260</v>
@@ -4618,13 +4873,13 @@
         <v>142</v>
       </c>
       <c r="G135" s="2">
-        <v>78.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H135" s="2">
-        <v>61.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I135" s="2">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>260</v>
@@ -4635,13 +4890,13 @@
         <v>143</v>
       </c>
       <c r="G136" s="2">
-        <v>52.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H136" s="2">
-        <v>36.8</v>
+        <v>63.6</v>
       </c>
       <c r="I136" s="2">
-        <v>43.6</v>
+        <v>72.8</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>260</v>
@@ -4652,13 +4907,13 @@
         <v>144</v>
       </c>
       <c r="G137" s="2">
-        <v>57.6</v>
+        <v>36.8</v>
       </c>
       <c r="H137" s="2">
-        <v>79.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="I137" s="2">
-        <v>79.2</v>
+        <v>18.4</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>260</v>
@@ -4669,13 +4924,13 @@
         <v>145</v>
       </c>
       <c r="G138" s="2">
-        <v>1.6</v>
+        <v>95.2</v>
       </c>
       <c r="H138" s="2">
-        <v>3.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I138" s="2">
-        <v>5.6</v>
+        <v>93.2</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>260</v>
@@ -4686,13 +4941,13 @@
         <v>146</v>
       </c>
       <c r="G139" s="2">
-        <v>63.6</v>
+        <v>66</v>
       </c>
       <c r="H139" s="2">
-        <v>72.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I139" s="2">
-        <v>54.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>260</v>
@@ -4703,13 +4958,13 @@
         <v>147</v>
       </c>
       <c r="G140" s="2">
-        <v>86</v>
+        <v>16.8</v>
       </c>
       <c r="H140" s="2">
-        <v>69.2</v>
+        <v>47.6</v>
       </c>
       <c r="I140" s="2">
-        <v>85.2</v>
+        <v>50.4</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>260</v>
@@ -4720,13 +4975,13 @@
         <v>148</v>
       </c>
       <c r="G141" s="2">
-        <v>45.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H141" s="2">
-        <v>65.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I141" s="2">
-        <v>70.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>260</v>
@@ -4737,13 +4992,13 @@
         <v>149</v>
       </c>
       <c r="G142" s="2">
-        <v>40.4</v>
+        <v>47.6</v>
       </c>
       <c r="H142" s="2">
-        <v>35.2</v>
+        <v>44</v>
       </c>
       <c r="I142" s="2">
-        <v>57.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>260</v>
@@ -4754,13 +5009,13 @@
         <v>150</v>
       </c>
       <c r="G143" s="2">
-        <v>37.6</v>
+        <v>43.6</v>
       </c>
       <c r="H143" s="2">
-        <v>39.6</v>
+        <v>52.8</v>
       </c>
       <c r="I143" s="2">
-        <v>20.8</v>
+        <v>36.4</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>260</v>
@@ -4771,13 +5026,13 @@
         <v>151</v>
       </c>
       <c r="G144" s="2">
-        <v>66.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="H144" s="2">
-        <v>77.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I144" s="2">
-        <v>66.8</v>
+        <v>96</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>260</v>
@@ -4788,13 +5043,13 @@
         <v>152</v>
       </c>
       <c r="G145" s="2">
-        <v>79.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H145" s="2">
-        <v>83.2</v>
+        <v>48.8</v>
       </c>
       <c r="I145" s="2">
-        <v>80</v>
+        <v>34.4</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>260</v>
@@ -4805,13 +5060,13 @@
         <v>153</v>
       </c>
       <c r="G146" s="2">
-        <v>28</v>
+        <v>0.8</v>
       </c>
       <c r="H146" s="2">
-        <v>31.6</v>
+        <v>18</v>
       </c>
       <c r="I146" s="2">
-        <v>19.2</v>
+        <v>14.4</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>260</v>
@@ -4822,13 +5077,13 @@
         <v>154</v>
       </c>
       <c r="G147" s="2">
-        <v>14.4</v>
+        <v>26</v>
       </c>
       <c r="H147" s="2">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="I147" s="2">
-        <v>15.2</v>
+        <v>10.8</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>260</v>
@@ -4839,13 +5094,13 @@
         <v>155</v>
       </c>
       <c r="G148" s="2">
-        <v>5.6</v>
+        <v>37.6</v>
       </c>
       <c r="H148" s="2">
-        <v>6.4</v>
+        <v>40.8</v>
       </c>
       <c r="I148" s="2">
-        <v>5.2</v>
+        <v>23.6</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>260</v>
@@ -4856,13 +5111,13 @@
         <v>156</v>
       </c>
       <c r="G149" s="2">
-        <v>22.4</v>
+        <v>91.2</v>
       </c>
       <c r="H149" s="2">
-        <v>13.2</v>
+        <v>96</v>
       </c>
       <c r="I149" s="2">
-        <v>10.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>260</v>
@@ -4873,13 +5128,13 @@
         <v>157</v>
       </c>
       <c r="G150" s="2">
-        <v>60.4</v>
+        <v>21.6</v>
       </c>
       <c r="H150" s="2">
-        <v>62.4</v>
+        <v>42.4</v>
       </c>
       <c r="I150" s="2">
-        <v>73.2</v>
+        <v>56</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>260</v>
@@ -4890,13 +5145,13 @@
         <v>158</v>
       </c>
       <c r="G151" s="2">
-        <v>20.4</v>
+        <v>35.2</v>
       </c>
       <c r="H151" s="2">
-        <v>20.8</v>
+        <v>24</v>
       </c>
       <c r="I151" s="2">
-        <v>18.4</v>
+        <v>28.4</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>260</v>
@@ -4907,13 +5162,13 @@
         <v>159</v>
       </c>
       <c r="G152" s="2">
-        <v>55.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H152" s="2">
-        <v>54.8</v>
+        <v>85.2</v>
       </c>
       <c r="I152" s="2">
-        <v>50</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>260</v>
@@ -4924,13 +5179,13 @@
         <v>160</v>
       </c>
       <c r="G153" s="2">
-        <v>30.8</v>
+        <v>60.8</v>
       </c>
       <c r="H153" s="2">
-        <v>31.2</v>
+        <v>59.2</v>
       </c>
       <c r="I153" s="2">
-        <v>45.6</v>
+        <v>58.4</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>260</v>
@@ -4941,13 +5196,13 @@
         <v>161</v>
       </c>
       <c r="G154" s="2">
-        <v>12.8</v>
+        <v>8.4</v>
       </c>
       <c r="H154" s="2">
-        <v>5.2</v>
+        <v>20.8</v>
       </c>
       <c r="I154" s="2">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>260</v>
@@ -4958,13 +5213,13 @@
         <v>162</v>
       </c>
       <c r="G155" s="2">
-        <v>60.8</v>
+        <v>74</v>
       </c>
       <c r="H155" s="2">
-        <v>62</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I155" s="2">
-        <v>56.8</v>
+        <v>70</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>260</v>
@@ -4975,13 +5230,13 @@
         <v>163</v>
       </c>
       <c r="G156" s="2">
-        <v>28.4</v>
+        <v>82.8</v>
       </c>
       <c r="H156" s="2">
-        <v>42</v>
+        <v>84.8</v>
       </c>
       <c r="I156" s="2">
-        <v>62.8</v>
+        <v>60.4</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>260</v>
@@ -4992,13 +5247,13 @@
         <v>164</v>
       </c>
       <c r="G157" s="2">
-        <v>39.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H157" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I157" s="2">
-        <v>65.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="J157" s="4" t="s">
         <v>260</v>
@@ -5009,13 +5264,13 @@
         <v>165</v>
       </c>
       <c r="G158" s="2">
-        <v>85.2</v>
+        <v>48.8</v>
       </c>
       <c r="H158" s="2">
-        <v>91.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="I158" s="2">
-        <v>96.8</v>
+        <v>55.2</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>260</v>
@@ -5026,13 +5281,13 @@
         <v>166</v>
       </c>
       <c r="G159" s="2">
-        <v>96.8</v>
+        <v>79.2</v>
       </c>
       <c r="H159" s="2">
-        <v>96</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I159" s="2">
-        <v>98</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>260</v>
@@ -5043,13 +5298,13 @@
         <v>167</v>
       </c>
       <c r="G160" s="2">
-        <v>90.8</v>
+        <v>20.4</v>
       </c>
       <c r="H160" s="2">
-        <v>74</v>
+        <v>55.6</v>
       </c>
       <c r="I160" s="2">
-        <v>55.6</v>
+        <v>43.2</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>260</v>
@@ -5060,13 +5315,13 @@
         <v>168</v>
       </c>
       <c r="G161" s="2">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="H161" s="2">
-        <v>28.8</v>
+        <v>36.4</v>
       </c>
       <c r="I161" s="2">
-        <v>55.2</v>
+        <v>27.6</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>260</v>
@@ -5077,13 +5332,13 @@
         <v>169</v>
       </c>
       <c r="G162" s="2">
-        <v>10.8</v>
+        <v>5.6</v>
       </c>
       <c r="H162" s="2">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
       <c r="I162" s="2">
-        <v>16</v>
+        <v>11.2</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>260</v>
@@ -5094,13 +5349,13 @@
         <v>170</v>
       </c>
       <c r="G163" s="2">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H163" s="2">
-        <v>26.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I163" s="2">
-        <v>42</v>
+        <v>51.6</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>260</v>
@@ -5111,13 +5366,13 @@
         <v>171</v>
       </c>
       <c r="G164" s="2">
-        <v>40</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H164" s="2">
-        <v>41.2</v>
+        <v>61.2</v>
       </c>
       <c r="I164" s="2">
-        <v>71.2</v>
+        <v>53.6</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>260</v>
@@ -5128,13 +5383,13 @@
         <v>172</v>
       </c>
       <c r="G165" s="2">
-        <v>50.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H165" s="2">
-        <v>49.6</v>
+        <v>29.2</v>
       </c>
       <c r="I165" s="2">
-        <v>58</v>
+        <v>12.4</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>260</v>
@@ -5145,13 +5400,13 @@
         <v>173</v>
       </c>
       <c r="G166" s="2">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="H166" s="2">
-        <v>33.6</v>
+        <v>30.8</v>
       </c>
       <c r="I166" s="2">
-        <v>17.6</v>
+        <v>30.8</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>260</v>
@@ -5162,13 +5417,13 @@
         <v>174</v>
       </c>
       <c r="G167" s="2">
-        <v>67.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="H167" s="2">
-        <v>69.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I167" s="2">
-        <v>49.6</v>
+        <v>77.2</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>260</v>
@@ -5179,13 +5434,13 @@
         <v>175</v>
       </c>
       <c r="G168" s="2">
-        <v>84</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H168" s="2">
-        <v>74.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="I168" s="2">
-        <v>74.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>260</v>
@@ -5196,13 +5451,13 @@
         <v>176</v>
       </c>
       <c r="G169" s="2">
-        <v>83.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H169" s="2">
-        <v>79.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I169" s="2">
-        <v>68.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>260</v>
@@ -5213,13 +5468,13 @@
         <v>177</v>
       </c>
       <c r="G170" s="2">
-        <v>42.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H170" s="2">
-        <v>37.6</v>
+        <v>60.8</v>
       </c>
       <c r="I170" s="2">
-        <v>24.8</v>
+        <v>61.6</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>260</v>
@@ -5230,13 +5485,13 @@
         <v>178</v>
       </c>
       <c r="G171" s="2">
-        <v>64.8</v>
+        <v>34.8</v>
       </c>
       <c r="H171" s="2">
-        <v>68.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="I171" s="2">
-        <v>68.8</v>
+        <v>13.2</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>260</v>
@@ -5247,13 +5502,13 @@
         <v>179</v>
       </c>
       <c r="G172" s="2">
-        <v>79.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H172" s="2">
-        <v>63.2</v>
+        <v>70.8</v>
       </c>
       <c r="I172" s="2">
-        <v>39.2</v>
+        <v>80</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>260</v>
@@ -5264,13 +5519,13 @@
         <v>180</v>
       </c>
       <c r="G173" s="2">
-        <v>72.8</v>
+        <v>52.4</v>
       </c>
       <c r="H173" s="2">
-        <v>92</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I173" s="2">
-        <v>89.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>260</v>
@@ -5281,13 +5536,13 @@
         <v>181</v>
       </c>
       <c r="G174" s="2">
-        <v>98.8</v>
+        <v>58.4</v>
       </c>
       <c r="H174" s="2">
-        <v>88.8</v>
+        <v>52.4</v>
       </c>
       <c r="I174" s="2">
-        <v>84.8</v>
+        <v>30.4</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>260</v>
@@ -5298,13 +5553,13 @@
         <v>182</v>
       </c>
       <c r="G175" s="2">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="H175" s="2">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="I175" s="2">
-        <v>28.8</v>
+        <v>60</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>260</v>
@@ -5315,13 +5570,13 @@
         <v>183</v>
       </c>
       <c r="G176" s="2">
-        <v>10.4</v>
+        <v>44.8</v>
       </c>
       <c r="H176" s="2">
-        <v>2</v>
+        <v>33.2</v>
       </c>
       <c r="I176" s="2">
-        <v>0.8</v>
+        <v>35.6</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>260</v>
@@ -5332,13 +5587,13 @@
         <v>184</v>
       </c>
       <c r="G177" s="2">
-        <v>71.2</v>
+        <v>59.2</v>
       </c>
       <c r="H177" s="2">
-        <v>77.2</v>
+        <v>38</v>
       </c>
       <c r="I177" s="2">
-        <v>86</v>
+        <v>21.6</v>
       </c>
       <c r="J177" s="4" t="s">
         <v>260</v>
@@ -5349,13 +5604,13 @@
         <v>185</v>
       </c>
       <c r="G178" s="2">
-        <v>15.6</v>
+        <v>54</v>
       </c>
       <c r="H178" s="2">
-        <v>23.6</v>
+        <v>73.2</v>
       </c>
       <c r="I178" s="2">
-        <v>12.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>260</v>
@@ -5366,13 +5621,13 @@
         <v>186</v>
       </c>
       <c r="G179" s="2">
-        <v>11.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H179" s="2">
-        <v>9.199999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I179" s="2">
-        <v>10.4</v>
+        <v>96.8</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>260</v>
@@ -5383,13 +5638,13 @@
         <v>187</v>
       </c>
       <c r="G180" s="2">
-        <v>53.6</v>
+        <v>76</v>
       </c>
       <c r="H180" s="2">
-        <v>55.2</v>
+        <v>86</v>
       </c>
       <c r="I180" s="2">
-        <v>52.4</v>
+        <v>68.8</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>260</v>
@@ -5400,13 +5655,13 @@
         <v>188</v>
       </c>
       <c r="G181" s="2">
-        <v>45.2</v>
+        <v>39.2</v>
       </c>
       <c r="H181" s="2">
-        <v>38.8</v>
+        <v>33.6</v>
       </c>
       <c r="I181" s="2">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>260</v>
@@ -5417,13 +5672,13 @@
         <v>189</v>
       </c>
       <c r="G182" s="2">
-        <v>86.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="H182" s="2">
-        <v>84</v>
+        <v>82.8</v>
       </c>
       <c r="I182" s="2">
-        <v>85.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>260</v>
@@ -5434,13 +5689,13 @@
         <v>190</v>
       </c>
       <c r="G183" s="2">
-        <v>19.6</v>
+        <v>46.8</v>
       </c>
       <c r="H183" s="2">
-        <v>17.2</v>
+        <v>64</v>
       </c>
       <c r="I183" s="2">
-        <v>16.8</v>
+        <v>52</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>260</v>
@@ -5451,13 +5706,13 @@
         <v>191</v>
       </c>
       <c r="G184" s="2">
-        <v>10</v>
+        <v>76.8</v>
       </c>
       <c r="H184" s="2">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="I184" s="2">
-        <v>2</v>
+        <v>80.8</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>260</v>
@@ -5468,13 +5723,13 @@
         <v>192</v>
       </c>
       <c r="G185" s="2">
+        <v>56.4</v>
+      </c>
+      <c r="H185" s="2">
+        <v>39.6</v>
+      </c>
+      <c r="I185" s="2">
         <v>48.8</v>
-      </c>
-      <c r="H185" s="2">
-        <v>34.8</v>
-      </c>
-      <c r="I185" s="2">
-        <v>22.8</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>260</v>
@@ -5485,13 +5740,13 @@
         <v>193</v>
       </c>
       <c r="G186" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H186" s="2">
-        <v>34</v>
+        <v>53.6</v>
       </c>
       <c r="I186" s="2">
-        <v>30.4</v>
+        <v>54.8</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>260</v>
@@ -5502,13 +5757,13 @@
         <v>194</v>
       </c>
       <c r="G187" s="2">
-        <v>17.6</v>
+        <v>45.6</v>
       </c>
       <c r="H187" s="2">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="I187" s="2">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>260</v>
@@ -5519,13 +5774,13 @@
         <v>195</v>
       </c>
       <c r="G188" s="2">
-        <v>68.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="H188" s="2">
-        <v>63.6</v>
+        <v>34</v>
       </c>
       <c r="I188" s="2">
-        <v>72.8</v>
+        <v>50.8</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>260</v>
@@ -5536,13 +5791,13 @@
         <v>196</v>
       </c>
       <c r="G189" s="2">
-        <v>44.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H189" s="2">
-        <v>48.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I189" s="2">
-        <v>22.4</v>
+        <v>84</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>260</v>
@@ -5553,13 +5808,13 @@
         <v>197</v>
       </c>
       <c r="G190" s="2">
-        <v>21.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H190" s="2">
-        <v>17.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I190" s="2">
-        <v>33.2</v>
+        <v>84.8</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>260</v>
@@ -5570,13 +5825,13 @@
         <v>198</v>
       </c>
       <c r="G191" s="2">
-        <v>4</v>
+        <v>41.6</v>
       </c>
       <c r="H191" s="2">
-        <v>4.8</v>
+        <v>30.4</v>
       </c>
       <c r="I191" s="2">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>260</v>
@@ -5587,13 +5842,13 @@
         <v>199</v>
       </c>
       <c r="G192" s="2">
-        <v>30.4</v>
+        <v>41.2</v>
       </c>
       <c r="H192" s="2">
-        <v>9.6</v>
+        <v>36.8</v>
       </c>
       <c r="I192" s="2">
-        <v>23.2</v>
+        <v>42.4</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>260</v>
@@ -5604,13 +5859,13 @@
         <v>200</v>
       </c>
       <c r="G193" s="2">
-        <v>4.4</v>
+        <v>13.6</v>
       </c>
       <c r="H193" s="2">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="I193" s="2">
-        <v>4.4</v>
+        <v>17.2</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>260</v>
@@ -5621,13 +5876,13 @@
         <v>201</v>
       </c>
       <c r="G194" s="2">
-        <v>58.8</v>
+        <v>24.8</v>
       </c>
       <c r="H194" s="2">
-        <v>67.59999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="I194" s="2">
-        <v>75.2</v>
+        <v>2</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>260</v>
@@ -5638,13 +5893,13 @@
         <v>202</v>
       </c>
       <c r="G195" s="2">
-        <v>37.2</v>
+        <v>56</v>
       </c>
       <c r="H195" s="2">
-        <v>71.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="I195" s="2">
-        <v>71.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>260</v>
@@ -5655,13 +5910,13 @@
         <v>203</v>
       </c>
       <c r="G196" s="2">
-        <v>56.8</v>
+        <v>49.6</v>
       </c>
       <c r="H196" s="2">
-        <v>50.4</v>
+        <v>45.2</v>
       </c>
       <c r="I196" s="2">
-        <v>60.8</v>
+        <v>38.4</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>260</v>
@@ -5672,13 +5927,13 @@
         <v>204</v>
       </c>
       <c r="G197" s="2">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="H197" s="2">
-        <v>29.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I197" s="2">
-        <v>52</v>
+        <v>63.2</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>260</v>
@@ -5689,13 +5944,13 @@
         <v>205</v>
       </c>
       <c r="G198" s="2">
-        <v>23.6</v>
+        <v>67.2</v>
       </c>
       <c r="H198" s="2">
-        <v>18.4</v>
+        <v>66.8</v>
       </c>
       <c r="I198" s="2">
-        <v>14</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>260</v>
@@ -5706,13 +5961,13 @@
         <v>206</v>
       </c>
       <c r="G199" s="2">
-        <v>46</v>
+        <v>96.8</v>
       </c>
       <c r="H199" s="2">
-        <v>47.6</v>
+        <v>98.8</v>
       </c>
       <c r="I199" s="2">
-        <v>51.6</v>
+        <v>88.8</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>260</v>
@@ -5723,13 +5978,13 @@
         <v>207</v>
       </c>
       <c r="G200" s="2">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="H200" s="2">
-        <v>22.8</v>
+        <v>6</v>
       </c>
       <c r="I200" s="2">
-        <v>34.4</v>
+        <v>6</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>260</v>
@@ -5740,13 +5995,13 @@
         <v>208</v>
       </c>
       <c r="G201" s="2">
-        <v>76.40000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="H201" s="2">
-        <v>87.2</v>
+        <v>10.8</v>
       </c>
       <c r="I201" s="2">
-        <v>70.8</v>
+        <v>8.4</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>260</v>
@@ -5757,13 +6012,13 @@
         <v>209</v>
       </c>
       <c r="G202" s="2">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H202" s="2">
-        <v>36.4</v>
+        <v>44.4</v>
       </c>
       <c r="I202" s="2">
-        <v>18.8</v>
+        <v>49.6</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>260</v>
@@ -5774,13 +6029,13 @@
         <v>210</v>
       </c>
       <c r="G203" s="2">
-        <v>29.6</v>
+        <v>49.2</v>
       </c>
       <c r="H203" s="2">
-        <v>27.2</v>
+        <v>51.6</v>
       </c>
       <c r="I203" s="2">
-        <v>40</v>
+        <v>76.8</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>260</v>
@@ -5791,13 +6046,13 @@
         <v>211</v>
       </c>
       <c r="G204" s="2">
-        <v>34</v>
+        <v>93.2</v>
       </c>
       <c r="H204" s="2">
-        <v>51.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I204" s="2">
-        <v>54.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>260</v>
@@ -5808,13 +6063,13 @@
         <v>212</v>
       </c>
       <c r="G205" s="2">
-        <v>76</v>
+        <v>3.6</v>
       </c>
       <c r="H205" s="2">
-        <v>66</v>
+        <v>3.2</v>
       </c>
       <c r="I205" s="2">
-        <v>44.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>260</v>
@@ -5825,13 +6080,13 @@
         <v>213</v>
       </c>
       <c r="G206" s="2">
-        <v>26.8</v>
+        <v>23.2</v>
       </c>
       <c r="H206" s="2">
-        <v>16.8</v>
+        <v>20.4</v>
       </c>
       <c r="I206" s="2">
-        <v>8</v>
+        <v>20.8</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>260</v>
@@ -5842,13 +6097,13 @@
         <v>214</v>
       </c>
       <c r="G207" s="2">
-        <v>64.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="H207" s="2">
-        <v>52</v>
+        <v>90.8</v>
       </c>
       <c r="I207" s="2">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>260</v>
@@ -5859,13 +6114,13 @@
         <v>215</v>
       </c>
       <c r="G208" s="2">
-        <v>82</v>
+        <v>10.8</v>
       </c>
       <c r="H208" s="2">
-        <v>85.59999999999999</v>
+        <v>8</v>
       </c>
       <c r="I208" s="2">
-        <v>78.40000000000001</v>
+        <v>29.2</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>260</v>
@@ -5876,13 +6131,13 @@
         <v>216</v>
       </c>
       <c r="G209" s="2">
-        <v>65.2</v>
+        <v>43.2</v>
       </c>
       <c r="H209" s="2">
-        <v>76</v>
+        <v>46.4</v>
       </c>
       <c r="I209" s="2">
-        <v>47.2</v>
+        <v>42.8</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>260</v>
@@ -5893,13 +6148,13 @@
         <v>217</v>
       </c>
       <c r="G210" s="2">
-        <v>73.2</v>
+        <v>47.2</v>
       </c>
       <c r="H210" s="2">
-        <v>76.40000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="I210" s="2">
-        <v>82.40000000000001</v>
+        <v>38</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>260</v>
@@ -5910,13 +6165,13 @@
         <v>218</v>
       </c>
       <c r="G211" s="2">
-        <v>2.8</v>
+        <v>39.6</v>
       </c>
       <c r="H211" s="2">
-        <v>7.2</v>
+        <v>50.4</v>
       </c>
       <c r="I211" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>260</v>
@@ -5927,13 +6182,13 @@
         <v>219</v>
       </c>
       <c r="G212" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H212" s="2">
-        <v>66.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I212" s="2">
-        <v>62.4</v>
+        <v>76</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>260</v>
@@ -5944,13 +6199,13 @@
         <v>220</v>
       </c>
       <c r="G213" s="2">
-        <v>61.6</v>
+        <v>32.8</v>
       </c>
       <c r="H213" s="2">
-        <v>74.8</v>
+        <v>40.4</v>
       </c>
       <c r="I213" s="2">
-        <v>76</v>
+        <v>34.8</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>260</v>
@@ -5961,13 +6216,13 @@
         <v>221</v>
       </c>
       <c r="G214" s="2">
-        <v>23.2</v>
+        <v>62.8</v>
       </c>
       <c r="H214" s="2">
-        <v>45.6</v>
+        <v>61.6</v>
       </c>
       <c r="I214" s="2">
-        <v>15.6</v>
+        <v>74.8</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>260</v>
@@ -5978,13 +6233,13 @@
         <v>222</v>
       </c>
       <c r="G215" s="2">
-        <v>49.6</v>
+        <v>74.8</v>
       </c>
       <c r="H215" s="2">
-        <v>56.8</v>
+        <v>84</v>
       </c>
       <c r="I215" s="2">
-        <v>50.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>260</v>
@@ -5995,13 +6250,13 @@
         <v>223</v>
       </c>
       <c r="G216" s="2">
-        <v>25.2</v>
+        <v>2</v>
       </c>
       <c r="H216" s="2">
         <v>7.6</v>
       </c>
       <c r="I216" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>260</v>
@@ -6012,13 +6267,13 @@
         <v>224</v>
       </c>
       <c r="G217" s="2">
-        <v>82.8</v>
+        <v>52.8</v>
       </c>
       <c r="H217" s="2">
-        <v>65.2</v>
+        <v>63.2</v>
       </c>
       <c r="I217" s="2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>260</v>
@@ -6029,13 +6284,13 @@
         <v>225</v>
       </c>
       <c r="G218" s="2">
-        <v>66</v>
+        <v>45.2</v>
       </c>
       <c r="H218" s="2">
-        <v>40.8</v>
+        <v>68.8</v>
       </c>
       <c r="I218" s="2">
-        <v>20</v>
+        <v>75.2</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>260</v>
@@ -6046,13 +6301,13 @@
         <v>226</v>
       </c>
       <c r="G219" s="2">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="H219" s="2">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="I219" s="2">
-        <v>2.4</v>
+        <v>47.2</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>260</v>
@@ -6063,13 +6318,13 @@
         <v>227</v>
       </c>
       <c r="G220" s="2">
-        <v>38.4</v>
+        <v>22.4</v>
       </c>
       <c r="H220" s="2">
-        <v>24.4</v>
+        <v>28.8</v>
       </c>
       <c r="I220" s="2">
-        <v>38</v>
+        <v>25.2</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>260</v>
@@ -6080,13 +6335,13 @@
         <v>228</v>
       </c>
       <c r="G221" s="2">
-        <v>97.59999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="H221" s="2">
-        <v>93.59999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="I221" s="2">
-        <v>89.59999999999999</v>
+        <v>18</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>260</v>
@@ -6097,13 +6352,13 @@
         <v>229</v>
       </c>
       <c r="G222" s="2">
-        <v>33.2</v>
+        <v>8</v>
       </c>
       <c r="H222" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="I222" s="2">
-        <v>31.6</v>
+        <v>19.2</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>260</v>
@@ -6114,13 +6369,13 @@
         <v>230</v>
       </c>
       <c r="G223" s="2">
-        <v>43.6</v>
+        <v>48.4</v>
       </c>
       <c r="H223" s="2">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="I223" s="2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>260</v>
@@ -6131,13 +6386,13 @@
         <v>231</v>
       </c>
       <c r="G224" s="2">
-        <v>84.8</v>
+        <v>14</v>
       </c>
       <c r="H224" s="2">
-        <v>60.8</v>
+        <v>6.8</v>
       </c>
       <c r="I224" s="2">
-        <v>64</v>
+        <v>18.8</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>260</v>
@@ -6148,13 +6403,13 @@
         <v>232</v>
       </c>
       <c r="G225" s="2">
-        <v>91.59999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="H225" s="2">
-        <v>90.8</v>
+        <v>31.2</v>
       </c>
       <c r="I225" s="2">
-        <v>32.8</v>
+        <v>22</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>260</v>
@@ -6165,13 +6420,13 @@
         <v>233</v>
       </c>
       <c r="G226" s="2">
-        <v>16</v>
+        <v>31.2</v>
       </c>
       <c r="H226" s="2">
-        <v>21.6</v>
+        <v>4.4</v>
       </c>
       <c r="I226" s="2">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>260</v>
@@ -6182,13 +6437,13 @@
         <v>234</v>
       </c>
       <c r="G227" s="2">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="H227" s="2">
-        <v>4.4</v>
+        <v>15.6</v>
       </c>
       <c r="I227" s="2">
-        <v>4</v>
+        <v>23.2</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>260</v>
@@ -6199,13 +6454,13 @@
         <v>235</v>
       </c>
       <c r="G228" s="2">
-        <v>13.2</v>
+        <v>55.6</v>
       </c>
       <c r="H228" s="2">
-        <v>2.8</v>
+        <v>60</v>
       </c>
       <c r="I228" s="2">
-        <v>4.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J228" s="4" t="s">
         <v>260</v>
@@ -6216,13 +6471,13 @@
         <v>236</v>
       </c>
       <c r="G229" s="2">
-        <v>94.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H229" s="2">
-        <v>80.40000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="I229" s="2">
-        <v>82</v>
+        <v>12.8</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>260</v>
@@ -6233,13 +6488,13 @@
         <v>237</v>
       </c>
       <c r="G230" s="2">
-        <v>54</v>
+        <v>15.2</v>
       </c>
       <c r="H230" s="2">
-        <v>51.6</v>
+        <v>17.6</v>
       </c>
       <c r="I230" s="2">
-        <v>41.6</v>
+        <v>16.4</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>260</v>
@@ -6250,13 +6505,13 @@
         <v>238</v>
       </c>
       <c r="G231" s="2">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="H231" s="2">
-        <v>72</v>
+        <v>56.8</v>
       </c>
       <c r="I231" s="2">
-        <v>77.2</v>
+        <v>50</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>260</v>
@@ -6267,13 +6522,13 @@
         <v>239</v>
       </c>
       <c r="G232" s="2">
-        <v>74.40000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="H232" s="2">
-        <v>47.2</v>
+        <v>50.8</v>
       </c>
       <c r="I232" s="2">
-        <v>40.4</v>
+        <v>49.2</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>260</v>
@@ -6284,13 +6539,13 @@
         <v>240</v>
       </c>
       <c r="G233" s="2">
-        <v>46.4</v>
+        <v>15.6</v>
       </c>
       <c r="H233" s="2">
-        <v>43.2</v>
+        <v>21.6</v>
       </c>
       <c r="I233" s="2">
-        <v>40.8</v>
+        <v>17.6</v>
       </c>
       <c r="J233" s="4" t="s">
         <v>260</v>
@@ -6301,13 +6556,13 @@
         <v>241</v>
       </c>
       <c r="G234" s="2">
-        <v>2.4</v>
+        <v>32.4</v>
       </c>
       <c r="H234" s="2">
-        <v>3.2</v>
+        <v>35.2</v>
       </c>
       <c r="I234" s="2">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>260</v>
@@ -6318,13 +6573,13 @@
         <v>242</v>
       </c>
       <c r="G235" s="2">
-        <v>54.8</v>
+        <v>1.6</v>
       </c>
       <c r="H235" s="2">
-        <v>55.6</v>
+        <v>2.4</v>
       </c>
       <c r="I235" s="2">
-        <v>66.40000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>260</v>
@@ -6335,13 +6590,13 @@
         <v>243</v>
       </c>
       <c r="G236" s="2">
-        <v>41.2</v>
+        <v>44.4</v>
       </c>
       <c r="H236" s="2">
-        <v>41.6</v>
+        <v>54</v>
       </c>
       <c r="I236" s="2">
-        <v>53.6</v>
+        <v>51.2</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>260</v>
@@ -6352,13 +6607,13 @@
         <v>244</v>
       </c>
       <c r="G237" s="2">
-        <v>2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H237" s="2">
-        <v>19.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I237" s="2">
-        <v>29.2</v>
+        <v>78.8</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>260</v>
@@ -6369,13 +6624,13 @@
         <v>245</v>
       </c>
       <c r="G238" s="2">
-        <v>74.8</v>
+        <v>9.6</v>
       </c>
       <c r="H238" s="2">
-        <v>75.59999999999999</v>
+        <v>14</v>
       </c>
       <c r="I238" s="2">
-        <v>78.8</v>
+        <v>22.4</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>260</v>
@@ -6386,13 +6641,13 @@
         <v>246</v>
       </c>
       <c r="G239" s="2">
-        <v>80</v>
+        <v>53.6</v>
       </c>
       <c r="H239" s="2">
-        <v>80.8</v>
+        <v>48</v>
       </c>
       <c r="I239" s="2">
-        <v>80.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>260</v>
@@ -6403,13 +6658,13 @@
         <v>247</v>
       </c>
       <c r="G240" s="2">
-        <v>4.8</v>
+        <v>30.4</v>
       </c>
       <c r="H240" s="2">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="I240" s="2">
-        <v>24.4</v>
+        <v>13.6</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>260</v>
@@ -6420,13 +6675,13 @@
         <v>248</v>
       </c>
       <c r="G241" s="2">
+        <v>24</v>
+      </c>
+      <c r="H241" s="2">
         <v>24.8</v>
       </c>
-      <c r="H241" s="2">
+      <c r="I241" s="2">
         <v>10.4</v>
-      </c>
-      <c r="I241" s="2">
-        <v>13.2</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>260</v>
@@ -6437,13 +6692,13 @@
         <v>249</v>
       </c>
       <c r="G242" s="2">
-        <v>50.4</v>
+        <v>42.4</v>
       </c>
       <c r="H242" s="2">
-        <v>28.4</v>
+        <v>38.4</v>
       </c>
       <c r="I242" s="2">
-        <v>30.8</v>
+        <v>24</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>260</v>
@@ -6454,13 +6709,13 @@
         <v>250</v>
       </c>
       <c r="G243" s="2">
-        <v>31.2</v>
+        <v>16</v>
       </c>
       <c r="H243" s="2">
-        <v>22.4</v>
+        <v>11.2</v>
       </c>
       <c r="I243" s="2">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>260</v>
@@ -6471,13 +6726,13 @@
         <v>251</v>
       </c>
       <c r="G244" s="2">
-        <v>49.2</v>
+        <v>17.2</v>
       </c>
       <c r="H244" s="2">
-        <v>42.4</v>
+        <v>26</v>
       </c>
       <c r="I244" s="2">
-        <v>35.6</v>
+        <v>24.4</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>260</v>
@@ -6488,13 +6743,13 @@
         <v>252</v>
       </c>
       <c r="G245" s="2">
-        <v>27.2</v>
+        <v>36.4</v>
       </c>
       <c r="H245" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I245" s="2">
-        <v>19.6</v>
+        <v>33.6</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>260</v>
@@ -6505,13 +6760,13 @@
         <v>253</v>
       </c>
       <c r="G246" s="2">
-        <v>55.6</v>
+        <v>18</v>
       </c>
       <c r="H246" s="2">
-        <v>43.6</v>
+        <v>22.8</v>
       </c>
       <c r="I246" s="2">
-        <v>46.8</v>
+        <v>26.4</v>
       </c>
       <c r="J246" s="4" t="s">
         <v>260</v>
@@ -6522,13 +6777,13 @@
         <v>254</v>
       </c>
       <c r="G247" s="2">
-        <v>57.2</v>
+        <v>20</v>
       </c>
       <c r="H247" s="2">
-        <v>40.4</v>
+        <v>11.6</v>
       </c>
       <c r="I247" s="2">
-        <v>33.6</v>
+        <v>20.4</v>
       </c>
       <c r="J247" s="4" t="s">
         <v>260</v>
@@ -6539,13 +6794,13 @@
         <v>255</v>
       </c>
       <c r="G248" s="2">
-        <v>3.6</v>
+        <v>55.2</v>
       </c>
       <c r="H248" s="2">
-        <v>8</v>
+        <v>83.2</v>
       </c>
       <c r="I248" s="2">
-        <v>38.4</v>
+        <v>79.2</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>260</v>
@@ -6556,13 +6811,13 @@
         <v>256</v>
       </c>
       <c r="G249" s="2">
-        <v>38.8</v>
+        <v>40</v>
       </c>
       <c r="H249" s="2">
-        <v>58.4</v>
+        <v>49.2</v>
       </c>
       <c r="I249" s="2">
-        <v>69.2</v>
+        <v>42</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>260</v>
@@ -6573,13 +6828,13 @@
         <v>257</v>
       </c>
       <c r="G250" s="2">
-        <v>15.2</v>
+        <v>42.8</v>
       </c>
       <c r="H250" s="2">
-        <v>46.8</v>
+        <v>29.6</v>
       </c>
       <c r="I250" s="2">
-        <v>63.2</v>
+        <v>26.8</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>260</v>
@@ -6590,13 +6845,13 @@
         <v>258</v>
       </c>
       <c r="G251" s="2">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="H251" s="2">
-        <v>23.2</v>
+        <v>38.8</v>
       </c>
       <c r="I251" s="2">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>260</v>
@@ -6905,7 +7160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -6947,115 +7202,115 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>213.43</v>
+        <v>323.97</v>
       </c>
       <c r="C2" s="2">
-        <v>169.99</v>
+        <v>167.74</v>
       </c>
       <c r="D2" s="2">
-        <v>76.62</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>13.29</v>
+        <v>48.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I2" s="2">
-        <v>99.59999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>564.15</v>
+        <v>557.05</v>
       </c>
       <c r="C3" s="2">
-        <v>220.25</v>
+        <v>209.44</v>
       </c>
       <c r="D3" s="2">
-        <v>33.72</v>
+        <v>20.26</v>
       </c>
       <c r="E3" s="2">
-        <v>-9.67</v>
+        <v>-4.8</v>
       </c>
       <c r="F3" s="2">
-        <v>97.09999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="G3" s="2">
         <v>99.2</v>
       </c>
       <c r="H3" s="2">
+        <v>99.2</v>
+      </c>
+      <c r="I3" s="2">
         <v>99.59999999999999</v>
-      </c>
-      <c r="I3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>6906.5</v>
+        <v>332.55</v>
       </c>
       <c r="C4" s="2">
-        <v>98.16</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="D4" s="2">
-        <v>95.26000000000001</v>
+        <v>61.29</v>
       </c>
       <c r="E4" s="2">
-        <v>17.88</v>
+        <v>13.29</v>
       </c>
       <c r="F4" s="2">
-        <v>95.65000000000001</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>98.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2">
-        <v>95.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I4" s="2">
-        <v>93.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>383.8</v>
+        <v>222.95</v>
       </c>
       <c r="C5" s="2">
-        <v>106.07</v>
+        <v>112.52</v>
       </c>
       <c r="D5" s="2">
-        <v>45.63</v>
+        <v>24.57</v>
       </c>
       <c r="E5" s="2">
-        <v>24.71</v>
+        <v>13.24</v>
       </c>
       <c r="F5" s="2">
-        <v>94.2</v>
+        <v>94.19</v>
       </c>
       <c r="G5" s="2">
         <v>97.2</v>
       </c>
       <c r="H5" s="2">
-        <v>96.8</v>
+        <v>92.8</v>
       </c>
       <c r="I5" s="2">
-        <v>84.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7063,28 +7318,28 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>653.7</v>
+        <v>643.7</v>
       </c>
       <c r="C6" s="2">
-        <v>93.09</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>47.75</v>
+        <v>32.9</v>
       </c>
       <c r="E6" s="2">
-        <v>27.65</v>
+        <v>15.86</v>
       </c>
       <c r="F6" s="2">
-        <v>91.3</v>
+        <v>93.02</v>
       </c>
       <c r="G6" s="2">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H6" s="2">
         <v>96.40000000000001</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>94.40000000000001</v>
-      </c>
-      <c r="I6" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -7092,28 +7347,28 @@
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>246.32</v>
+        <v>1861.6</v>
       </c>
       <c r="C7" s="2">
-        <v>83.14</v>
+        <v>103.82</v>
       </c>
       <c r="D7" s="2">
-        <v>53.49</v>
+        <v>50.66</v>
       </c>
       <c r="E7" s="2">
-        <v>17.54</v>
+        <v>0.63</v>
       </c>
       <c r="F7" s="2">
-        <v>89.86</v>
+        <v>91.86</v>
       </c>
       <c r="G7" s="2">
-        <v>95.2</v>
+        <v>94.8</v>
       </c>
       <c r="H7" s="2">
-        <v>98.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I7" s="2">
-        <v>90</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7121,28 +7376,28 @@
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1520.2</v>
+        <v>88.66</v>
       </c>
       <c r="C8" s="2">
-        <v>102.1</v>
+        <v>127.1</v>
       </c>
       <c r="D8" s="2">
-        <v>52.42</v>
+        <v>18.8</v>
       </c>
       <c r="E8" s="2">
-        <v>7.09</v>
+        <v>-1.9</v>
       </c>
       <c r="F8" s="2">
-        <v>88.41</v>
+        <v>90.7</v>
       </c>
       <c r="G8" s="2">
-        <v>95.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="H8" s="2">
-        <v>93.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>90.8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -7150,61 +7405,148 @@
         <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>1813.4</v>
+        <v>238.05</v>
       </c>
       <c r="C9" s="2">
-        <v>88.02</v>
+        <v>82.37</v>
       </c>
       <c r="D9" s="2">
-        <v>66.8</v>
+        <v>39.83</v>
       </c>
       <c r="E9" s="2">
-        <v>4.98</v>
+        <v>7.07</v>
       </c>
       <c r="F9" s="2">
-        <v>86.95999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="G9" s="2">
-        <v>93.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H9" s="2">
-        <v>97.2</v>
+        <v>95.2</v>
       </c>
       <c r="I9" s="2">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>2041.2</v>
+        <v>1256.5</v>
       </c>
       <c r="C10" s="2">
-        <v>66.33</v>
+        <v>102.86</v>
       </c>
       <c r="D10" s="2">
-        <v>48.7</v>
+        <v>46.83</v>
       </c>
       <c r="E10" s="2">
-        <v>2.41</v>
+        <v>-7.5</v>
       </c>
       <c r="F10" s="2">
-        <v>82.61</v>
+        <v>88.37</v>
       </c>
       <c r="G10" s="2">
-        <v>89.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H10" s="2">
-        <v>97.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I10" s="2">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2133.3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>105</v>
+      </c>
+      <c r="D11" s="2">
+        <v>11.61</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-0.53</v>
+      </c>
+      <c r="F11" s="2">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="G11" s="2">
         <v>96</v>
       </c>
+      <c r="H11" s="2">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1">
+        <v>743.5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67.02</v>
+      </c>
+      <c r="D12" s="2">
+        <v>29.62</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.86</v>
+      </c>
+      <c r="F12" s="2">
+        <v>83.72</v>
+      </c>
+      <c r="G12" s="2">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H12" s="2">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="I12" s="2">
+        <v>88.40000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1908</v>
+      </c>
+      <c r="C13" s="2">
+        <v>58.85</v>
+      </c>
+      <c r="D13" s="2">
+        <v>32.66</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="F13" s="2">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G13" s="2">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H13" s="2">
+        <v>88.8</v>
+      </c>
+      <c r="I13" s="2">
+        <v>91.2</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7212,7 +7554,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7220,7 +7562,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7228,22 +7570,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -7254,7 +7596,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -7296,28 +7638,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>213.43</v>
+        <v>323.97</v>
       </c>
       <c r="C2" s="2">
-        <v>169.99</v>
+        <v>167.74</v>
       </c>
       <c r="D2" s="2">
-        <v>76.62</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E2" s="2">
-        <v>13.29</v>
+        <v>48.09</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I2" s="2">
-        <v>99.59999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7325,28 +7667,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>295.15</v>
+        <v>557.05</v>
       </c>
       <c r="C3" s="2">
-        <v>135.22</v>
+        <v>209.44</v>
       </c>
       <c r="D3" s="2">
-        <v>53.87</v>
+        <v>20.26</v>
       </c>
       <c r="E3" s="2">
-        <v>41.53</v>
+        <v>-4.8</v>
       </c>
       <c r="F3" s="2">
-        <v>98.55</v>
+        <v>98.84</v>
       </c>
       <c r="G3" s="2">
-        <v>90</v>
+        <v>99.2</v>
       </c>
       <c r="H3" s="2">
-        <v>89.2</v>
+        <v>99.2</v>
       </c>
       <c r="I3" s="2">
-        <v>74.8</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7354,322 +7696,438 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>564.15</v>
+        <v>816.2</v>
       </c>
       <c r="C4" s="2">
-        <v>220.25</v>
+        <v>57.57</v>
       </c>
       <c r="D4" s="2">
-        <v>33.72</v>
+        <v>68.48</v>
       </c>
       <c r="E4" s="2">
-        <v>-9.67</v>
+        <v>40.11</v>
       </c>
       <c r="F4" s="2">
-        <v>97.09999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="G4" s="2">
-        <v>99.2</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
-        <v>99.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I4" s="2">
-        <v>100</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>6906.5</v>
+        <v>332.55</v>
       </c>
       <c r="C5" s="2">
-        <v>98.16</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="D5" s="2">
-        <v>95.26000000000001</v>
+        <v>61.29</v>
       </c>
       <c r="E5" s="2">
-        <v>17.88</v>
+        <v>13.29</v>
       </c>
       <c r="F5" s="2">
-        <v>95.65000000000001</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>98.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2">
-        <v>95.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>93.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>383.8</v>
+        <v>222.95</v>
       </c>
       <c r="C6" s="2">
-        <v>106.07</v>
+        <v>112.52</v>
       </c>
       <c r="D6" s="2">
-        <v>45.63</v>
+        <v>24.57</v>
       </c>
       <c r="E6" s="2">
-        <v>24.71</v>
+        <v>13.24</v>
       </c>
       <c r="F6" s="2">
-        <v>94.2</v>
+        <v>94.19</v>
       </c>
       <c r="G6" s="2">
         <v>97.2</v>
       </c>
       <c r="H6" s="2">
-        <v>96.8</v>
+        <v>92.8</v>
       </c>
       <c r="I6" s="2">
-        <v>84.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>772.4</v>
+        <v>643.7</v>
       </c>
       <c r="C7" s="2">
-        <v>44.77</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D7" s="2">
-        <v>66.39</v>
+        <v>32.9</v>
       </c>
       <c r="E7" s="2">
-        <v>43.45</v>
+        <v>15.86</v>
       </c>
       <c r="F7" s="2">
-        <v>92.75</v>
+        <v>93.02</v>
       </c>
       <c r="G7" s="2">
-        <v>83.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H7" s="2">
-        <v>73.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>67.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
-        <v>653.7</v>
+        <v>1861.6</v>
       </c>
       <c r="C8" s="2">
-        <v>93.09</v>
+        <v>103.82</v>
       </c>
       <c r="D8" s="2">
-        <v>47.75</v>
+        <v>50.66</v>
       </c>
       <c r="E8" s="2">
-        <v>27.65</v>
+        <v>0.63</v>
       </c>
       <c r="F8" s="2">
-        <v>91.3</v>
+        <v>91.86</v>
       </c>
       <c r="G8" s="2">
-        <v>96.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="H8" s="2">
-        <v>94.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I8" s="2">
-        <v>88</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>246.32</v>
+        <v>88.66</v>
       </c>
       <c r="C9" s="2">
-        <v>83.14</v>
+        <v>127.1</v>
       </c>
       <c r="D9" s="2">
-        <v>53.49</v>
+        <v>18.8</v>
       </c>
       <c r="E9" s="2">
-        <v>17.54</v>
+        <v>-1.9</v>
       </c>
       <c r="F9" s="2">
-        <v>89.86</v>
+        <v>90.7</v>
       </c>
       <c r="G9" s="2">
-        <v>95.2</v>
+        <v>92.8</v>
       </c>
       <c r="H9" s="2">
-        <v>98.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1">
-        <v>1520.2</v>
+        <v>238.05</v>
       </c>
       <c r="C10" s="2">
-        <v>102.1</v>
+        <v>82.37</v>
       </c>
       <c r="D10" s="2">
-        <v>52.42</v>
+        <v>39.83</v>
       </c>
       <c r="E10" s="2">
-        <v>7.09</v>
+        <v>7.07</v>
       </c>
       <c r="F10" s="2">
-        <v>88.41</v>
+        <v>89.53</v>
       </c>
       <c r="G10" s="2">
         <v>95.59999999999999</v>
       </c>
       <c r="H10" s="2">
-        <v>93.2</v>
+        <v>95.2</v>
       </c>
       <c r="I10" s="2">
-        <v>90.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1">
-        <v>1813.4</v>
+        <v>1256.5</v>
       </c>
       <c r="C11" s="2">
-        <v>88.02</v>
+        <v>102.86</v>
       </c>
       <c r="D11" s="2">
-        <v>66.8</v>
+        <v>46.83</v>
       </c>
       <c r="E11" s="2">
-        <v>4.98</v>
+        <v>-7.5</v>
       </c>
       <c r="F11" s="2">
-        <v>86.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="G11" s="2">
-        <v>93.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H11" s="2">
-        <v>97.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I11" s="2">
-        <v>98.8</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1">
-        <v>728.95</v>
+        <v>2133.3</v>
       </c>
       <c r="C12" s="2">
-        <v>42.25</v>
+        <v>105</v>
       </c>
       <c r="D12" s="2">
-        <v>40.68</v>
+        <v>11.61</v>
       </c>
       <c r="E12" s="2">
-        <v>38.69</v>
+        <v>-0.53</v>
       </c>
       <c r="F12" s="2">
-        <v>85.51000000000001</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="G12" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2">
-        <v>44</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I12" s="2">
-        <v>32</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1">
-        <v>2439</v>
+        <v>71.75</v>
       </c>
       <c r="C13" s="2">
-        <v>62.46</v>
+        <v>39.75</v>
       </c>
       <c r="D13" s="2">
-        <v>27</v>
+        <v>30.76</v>
       </c>
       <c r="E13" s="2">
-        <v>22.93</v>
+        <v>20.02</v>
       </c>
       <c r="F13" s="2">
-        <v>84.06</v>
+        <v>86.05</v>
       </c>
       <c r="G13" s="2">
-        <v>80.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H13" s="2">
-        <v>82</v>
+        <v>75.2</v>
       </c>
       <c r="I13" s="2">
-        <v>42.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1">
-        <v>2041.2</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="C14" s="2">
-        <v>66.33</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="D14" s="2">
-        <v>48.7</v>
+        <v>12.19</v>
       </c>
       <c r="E14" s="2">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="F14" s="2">
-        <v>82.61</v>
+        <v>84.88</v>
       </c>
       <c r="G14" s="2">
-        <v>89.2</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2">
-        <v>97.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I14" s="2">
-        <v>96</v>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1">
+        <v>743.5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>67.02</v>
+      </c>
+      <c r="D15" s="2">
+        <v>29.62</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.86</v>
+      </c>
+      <c r="F15" s="2">
+        <v>83.72</v>
+      </c>
+      <c r="G15" s="2">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H15" s="2">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="I15" s="2">
+        <v>88.40000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1">
+        <v>403.2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>37.14</v>
+      </c>
+      <c r="D16" s="2">
+        <v>13.96</v>
+      </c>
+      <c r="E16" s="2">
+        <v>23.49</v>
+      </c>
+      <c r="F16" s="2">
+        <v>82.56</v>
+      </c>
+      <c r="G16" s="2">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H16" s="2">
+        <v>69.2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1908</v>
+      </c>
+      <c r="C17" s="2">
+        <v>58.85</v>
+      </c>
+      <c r="D17" s="2">
+        <v>32.66</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="F17" s="2">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G17" s="2">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H17" s="2">
+        <v>88.8</v>
+      </c>
+      <c r="I17" s="2">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1">
+        <v>178.48</v>
+      </c>
+      <c r="C18" s="2">
+        <v>51.51</v>
+      </c>
+      <c r="D18" s="2">
+        <v>15.79</v>
+      </c>
+      <c r="E18" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>80.23</v>
+      </c>
+      <c r="G18" s="2">
+        <v>88</v>
+      </c>
+      <c r="H18" s="2">
+        <v>76</v>
+      </c>
+      <c r="I18" s="2">
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7677,7 +8135,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D18">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7685,7 +8143,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7693,22 +8151,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F18">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G18">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H18">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -7744,13 +8202,13 @@
         <v>265</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="C2" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2">
-        <v>16.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7758,13 +8216,13 @@
         <v>266</v>
       </c>
       <c r="B3" s="2">
-        <v>46</v>
+        <v>34.4</v>
       </c>
       <c r="C3" s="2">
-        <v>60.8</v>
+        <v>51.6</v>
       </c>
       <c r="D3" s="2">
-        <v>61.6</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7772,13 +8230,13 @@
         <v>267</v>
       </c>
       <c r="B4" s="2">
-        <v>64.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2">
-        <v>69.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D4" s="2">
-        <v>63.6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7786,13 +8244,13 @@
         <v>268</v>
       </c>
       <c r="B5" s="2">
-        <v>71.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C5" s="2">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D5" s="2">
-        <v>62.4</v>
+        <v>63.6</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_250_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_250_Perception_Report.xlsx
@@ -17,21 +17,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="269">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Price_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_90d_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_50d_2026-07-31</t>
-  </si>
-  <si>
-    <t>Ret_20d_2026-07-31</t>
+    <t>Price_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_90d_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_50d_2026-08-07</t>
+  </si>
+  <si>
+    <t>Ret_20d_2026-08-07</t>
+  </si>
+  <si>
+    <t>RS_Score_2026-08-07</t>
   </si>
   <si>
     <t>RS_Score_2026-07-31</t>
@@ -43,759 +46,756 @@
     <t>RS_Score_2026-07-17</t>
   </si>
   <si>
-    <t>RS_Score_2026-07-10</t>
-  </si>
-  <si>
     <t>DIACABS</t>
   </si>
   <si>
+    <t>CUPID</t>
+  </si>
+  <si>
     <t>STLTECH</t>
   </si>
   <si>
     <t>BLUESTONE</t>
   </si>
   <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>LLOYDSENGG</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>EMIL</t>
+  </si>
+  <si>
+    <t>PARAS</t>
+  </si>
+  <si>
+    <t>ASKAUTOLTD</t>
+  </si>
+  <si>
+    <t>RBA</t>
+  </si>
+  <si>
     <t>SMLMAH</t>
   </si>
   <si>
+    <t>LOTUSDEV</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>VARROC</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>AEQUS</t>
+  </si>
+  <si>
+    <t>RAIN</t>
+  </si>
+  <si>
+    <t>THYROCARE</t>
+  </si>
+  <si>
+    <t>LLOYDSENT</t>
+  </si>
+  <si>
+    <t>UTLSOLAR</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>NAZARA</t>
+  </si>
+  <si>
+    <t>MTARTECH</t>
+  </si>
+  <si>
+    <t>APOLLO</t>
+  </si>
+  <si>
+    <t>SUDEEPPHRM</t>
+  </si>
+  <si>
+    <t>AZAD</t>
+  </si>
+  <si>
+    <t>SUDARSCHEM</t>
+  </si>
+  <si>
+    <t>ALIVUS</t>
+  </si>
+  <si>
+    <t>FIEMIND</t>
+  </si>
+  <si>
+    <t>SHAILY</t>
+  </si>
+  <si>
+    <t>LXCHEM</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>BALAMINES</t>
+  </si>
+  <si>
+    <t>MARKSANS</t>
+  </si>
+  <si>
+    <t>TANLA</t>
+  </si>
+  <si>
+    <t>AKUMS</t>
+  </si>
+  <si>
+    <t>ARVIND</t>
+  </si>
+  <si>
+    <t>KTKBANK</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>TDPOWERSYS</t>
+  </si>
+  <si>
+    <t>UJJIVANSFB</t>
+  </si>
+  <si>
+    <t>ELLEN</t>
+  </si>
+  <si>
+    <t>AGARWALEYE</t>
+  </si>
+  <si>
+    <t>ASHAPURMIN</t>
+  </si>
+  <si>
+    <t>WABAG</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>SUPRIYA</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>JAMNAAUTO</t>
+  </si>
+  <si>
+    <t>SENCO</t>
+  </si>
+  <si>
+    <t>VIYASH</t>
+  </si>
+  <si>
+    <t>DYNAMATECH</t>
+  </si>
+  <si>
+    <t>MANORAMA</t>
+  </si>
+  <si>
+    <t>SOUTHBANK</t>
+  </si>
+  <si>
+    <t>APLLTD</t>
+  </si>
+  <si>
+    <t>CAPILLARY</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>SPARC</t>
+  </si>
+  <si>
+    <t>PNGJL</t>
+  </si>
+  <si>
+    <t>SHAREINDIA</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>THANGAMAYL</t>
+  </si>
+  <si>
+    <t>KNRCON</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>SUBROS</t>
+  </si>
+  <si>
+    <t>CERA</t>
+  </si>
+  <si>
+    <t>REDTAPE</t>
+  </si>
+  <si>
+    <t>JKPAPER</t>
+  </si>
+  <si>
+    <t>IMFA</t>
+  </si>
+  <si>
+    <t>VOLTAMP</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>EQUITASBNK</t>
+  </si>
+  <si>
+    <t>CCAVENUE</t>
+  </si>
+  <si>
+    <t>JSLL</t>
+  </si>
+  <si>
+    <t>DATAMATICS</t>
+  </si>
+  <si>
+    <t>PCJEWELLER</t>
+  </si>
+  <si>
+    <t>QPOWER</t>
+  </si>
+  <si>
+    <t>TARC</t>
+  </si>
+  <si>
+    <t>CRAMC</t>
+  </si>
+  <si>
+    <t>THOMASCOOK</t>
+  </si>
+  <si>
+    <t>STYRENIX</t>
+  </si>
+  <si>
+    <t>PNCINFRA</t>
+  </si>
+  <si>
+    <t>INOXGREEN</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>SFL</t>
+  </si>
+  <si>
+    <t>HAPPSTMNDS</t>
+  </si>
+  <si>
+    <t>HEMIPROP</t>
+  </si>
+  <si>
+    <t>BORORENEW</t>
+  </si>
+  <si>
+    <t>REFEX</t>
+  </si>
+  <si>
+    <t>WEBELSOLAR</t>
+  </si>
+  <si>
+    <t>JAYNECOIND</t>
+  </si>
+  <si>
+    <t>SANDUMA</t>
+  </si>
+  <si>
+    <t>AARTIPHARM</t>
+  </si>
+  <si>
+    <t>GSFC</t>
+  </si>
+  <si>
+    <t>TIPSMUSIC</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>GPPL</t>
+  </si>
+  <si>
+    <t>FEDFINA</t>
+  </si>
+  <si>
+    <t>CELLO</t>
+  </si>
+  <si>
+    <t>EUREKAFORB</t>
+  </si>
+  <si>
+    <t>GHCL</t>
+  </si>
+  <si>
+    <t>FINPIPE</t>
+  </si>
+  <si>
+    <t>MOIL</t>
+  </si>
+  <si>
+    <t>RTNPOWER</t>
+  </si>
+  <si>
+    <t>GODREJAGRO</t>
+  </si>
+  <si>
+    <t>TIINDIA</t>
+  </si>
+  <si>
+    <t>RAYMONDLSL</t>
+  </si>
+  <si>
+    <t>SHAKTIPUMP</t>
+  </si>
+  <si>
+    <t>ANUP</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>WAKEFIT</t>
+  </si>
+  <si>
+    <t>STAR</t>
+  </si>
+  <si>
+    <t>NETWORK18</t>
+  </si>
+  <si>
+    <t>GMRP&amp;UI</t>
+  </si>
+  <si>
+    <t>ASHOKA</t>
+  </si>
+  <si>
+    <t>IXIGO</t>
+  </si>
+  <si>
+    <t>PRSMJOHNSN</t>
+  </si>
+  <si>
+    <t>IONEXCHANG</t>
+  </si>
+  <si>
+    <t>RELIGARE</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>CRIZAC</t>
+  </si>
+  <si>
+    <t>AWFIS</t>
+  </si>
+  <si>
+    <t>SHARDACROP</t>
+  </si>
+  <si>
+    <t>OSWALPUMPS</t>
+  </si>
+  <si>
+    <t>RATNAMANI</t>
+  </si>
+  <si>
+    <t>CSBBANK</t>
+  </si>
+  <si>
+    <t>AVANTIFEED</t>
+  </si>
+  <si>
+    <t>VIKRAMSOLR</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>VGUARD</t>
+  </si>
+  <si>
+    <t>BLACKBUCK</t>
+  </si>
+  <si>
+    <t>PRIVISCL</t>
+  </si>
+  <si>
+    <t>PRICOLLTD</t>
+  </si>
+  <si>
+    <t>GOKULAGRO</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>TIMETECHNO</t>
+  </si>
+  <si>
     <t>QUESS</t>
   </si>
   <si>
-    <t>RAIN</t>
+    <t>AETHER</t>
   </si>
   <si>
     <t>SKYGOLD</t>
   </si>
   <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>LLOYDSENGG</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>PARAS</t>
-  </si>
-  <si>
-    <t>BALAMINES</t>
-  </si>
-  <si>
-    <t>UJJIVANSFB</t>
-  </si>
-  <si>
-    <t>LLOYDSENT</t>
+    <t>JSFB</t>
+  </si>
+  <si>
+    <t>BECTORFOOD</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>WESTLIFE</t>
+  </si>
+  <si>
+    <t>SKIPPER</t>
+  </si>
+  <si>
+    <t>MASTEK</t>
+  </si>
+  <si>
+    <t>SAMHI</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>METROPOLIS</t>
+  </si>
+  <si>
+    <t>EIEL</t>
+  </si>
+  <si>
+    <t>JUSTDIAL</t>
+  </si>
+  <si>
+    <t>AXISCADES</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>GRWRHITECH</t>
+  </si>
+  <si>
+    <t>RELAXO</t>
+  </si>
+  <si>
+    <t>SWSOLAR</t>
+  </si>
+  <si>
+    <t>GNFC</t>
+  </si>
+  <si>
+    <t>WAAREERTL</t>
+  </si>
+  <si>
+    <t>NEOGEN</t>
+  </si>
+  <si>
+    <t>EDELWEISS</t>
+  </si>
+  <si>
+    <t>MANYAVAR</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>BBOX</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>KIRLOSBROS</t>
+  </si>
+  <si>
+    <t>MEDPLUS</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>LUMAXTECH</t>
+  </si>
+  <si>
+    <t>AURIONPRO</t>
+  </si>
+  <si>
+    <t>ICIL</t>
+  </si>
+  <si>
+    <t>RALLIS</t>
+  </si>
+  <si>
+    <t>INDIAGLYCO</t>
+  </si>
+  <si>
+    <t>PRUDENT</t>
+  </si>
+  <si>
+    <t>SHRIPISTON</t>
+  </si>
+  <si>
+    <t>INDIASHLTR</t>
+  </si>
+  <si>
+    <t>KPIGREEN</t>
+  </si>
+  <si>
+    <t>KRN</t>
+  </si>
+  <si>
+    <t>CAMPUS</t>
+  </si>
+  <si>
+    <t>VMART</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>GOKEX</t>
+  </si>
+  <si>
+    <t>ATLANTAELE</t>
+  </si>
+  <si>
+    <t>HERITGFOOD</t>
+  </si>
+  <si>
+    <t>AVL</t>
+  </si>
+  <si>
+    <t>PRAJIND</t>
+  </si>
+  <si>
+    <t>V2RETAIL</t>
+  </si>
+  <si>
+    <t>JLHL</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>TRANSRAILL</t>
+  </si>
+  <si>
+    <t>POWERMECH</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>PGIL</t>
+  </si>
+  <si>
+    <t>TEXRAIL</t>
+  </si>
+  <si>
+    <t>MIDHANI</t>
+  </si>
+  <si>
+    <t>JKLAKSHMI</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
+  </si>
+  <si>
+    <t>JYOTHYLAB</t>
+  </si>
+  <si>
+    <t>VAIBHAVGBL</t>
+  </si>
+  <si>
+    <t>SMARTWORKS</t>
+  </si>
+  <si>
+    <t>AARTIDRUGS</t>
+  </si>
+  <si>
+    <t>ARVINDFASN</t>
+  </si>
+  <si>
+    <t>INDIGOPNTS</t>
+  </si>
+  <si>
+    <t>BALUFORGE</t>
+  </si>
+  <si>
+    <t>OPTIEMUS</t>
+  </si>
+  <si>
+    <t>ZAGGLE</t>
+  </si>
+  <si>
+    <t>STYL</t>
+  </si>
+  <si>
+    <t>PICCADIL</t>
+  </si>
+  <si>
+    <t>KSCL</t>
+  </si>
+  <si>
+    <t>MAHSCOOTER</t>
+  </si>
+  <si>
+    <t>IIFLCAPS</t>
+  </si>
+  <si>
+    <t>BIRLACORPN</t>
+  </si>
+  <si>
+    <t>SUNTECK</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>ETHOSLTD</t>
+  </si>
+  <si>
+    <t>WELENT</t>
   </si>
   <si>
     <t>WEWORK</t>
   </si>
   <si>
-    <t>SENCO</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>LXCHEM</t>
-  </si>
-  <si>
-    <t>WABAG</t>
-  </si>
-  <si>
-    <t>THYROCARE</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>VAIBHAVGBL</t>
-  </si>
-  <si>
-    <t>PNGJL</t>
-  </si>
-  <si>
-    <t>APOLLO</t>
-  </si>
-  <si>
-    <t>MSTCLTD</t>
+    <t>KANSAINER</t>
+  </si>
+  <si>
+    <t>KSB</t>
+  </si>
+  <si>
+    <t>ORKLAINDIA</t>
+  </si>
+  <si>
+    <t>DBL</t>
   </si>
   <si>
     <t>IFBIND</t>
   </si>
   <si>
-    <t>BECTORFOOD</t>
-  </si>
-  <si>
-    <t>VARROC</t>
-  </si>
-  <si>
-    <t>AARTIDRUGS</t>
-  </si>
-  <si>
-    <t>KTKBANK</t>
-  </si>
-  <si>
-    <t>SKIPPER</t>
-  </si>
-  <si>
-    <t>EMIL</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>SOUTHBANK</t>
+    <t>ORIENTCEM</t>
+  </si>
+  <si>
+    <t>ADVENZYMES</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
+  </si>
+  <si>
+    <t>ELECTCAST</t>
+  </si>
+  <si>
+    <t>KITEX</t>
+  </si>
+  <si>
+    <t>EPL</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>BANCOINDIA</t>
+  </si>
+  <si>
+    <t>RENUKA</t>
+  </si>
+  <si>
+    <t>SURYAROSNI</t>
+  </si>
+  <si>
+    <t>PURVA</t>
+  </si>
+  <si>
+    <t>ALKYLAMINE</t>
+  </si>
+  <si>
+    <t>MAHSEAMLES</t>
+  </si>
+  <si>
+    <t>BAJAJELEC</t>
+  </si>
+  <si>
+    <t>RTNINDIA</t>
+  </si>
+  <si>
+    <t>STARCEMENT</t>
   </si>
   <si>
     <t>TVSSCS</t>
   </si>
   <si>
-    <t>MANORAMA</t>
-  </si>
-  <si>
-    <t>GMMPFAUDLR</t>
-  </si>
-  <si>
-    <t>IONEXCHANG</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>IMFA</t>
-  </si>
-  <si>
-    <t>ALIVUS</t>
-  </si>
-  <si>
-    <t>SPARC</t>
-  </si>
-  <si>
-    <t>WESTLIFE</t>
+    <t>ALOKINDS</t>
+  </si>
+  <si>
+    <t>DBREALTY</t>
+  </si>
+  <si>
+    <t>VIPIND</t>
+  </si>
+  <si>
+    <t>HGINFRA</t>
+  </si>
+  <si>
+    <t>JAIBALAJI</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>NFL</t>
   </si>
   <si>
     <t>CENTURYPLY</t>
   </si>
   <si>
-    <t>ETHOSLTD</t>
-  </si>
-  <si>
-    <t>GNFC</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
-    <t>THOMASCOOK</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>PCJEWELLER</t>
+    <t>TSFINV</t>
+  </si>
+  <si>
+    <t>AHLUCONT</t>
+  </si>
+  <si>
+    <t>SANOFICONR</t>
   </si>
   <si>
     <t>SAATVIKGL</t>
   </si>
   <si>
-    <t>SANDUMA</t>
-  </si>
-  <si>
-    <t>JAMNAAUTO</t>
-  </si>
-  <si>
-    <t>AGARWALEYE</t>
-  </si>
-  <si>
-    <t>TEXRAIL</t>
-  </si>
-  <si>
-    <t>LUMAXTECH</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
-    <t>GODREJAGRO</t>
-  </si>
-  <si>
-    <t>EDELWEISS</t>
-  </si>
-  <si>
-    <t>KSB</t>
-  </si>
-  <si>
-    <t>SWSOLAR</t>
-  </si>
-  <si>
-    <t>TRANSRAILL</t>
-  </si>
-  <si>
-    <t>ASHOKA</t>
-  </si>
-  <si>
-    <t>CAPILLARY</t>
-  </si>
-  <si>
-    <t>RTNINDIA</t>
-  </si>
-  <si>
-    <t>MOIL</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>BALUFORGE</t>
-  </si>
-  <si>
-    <t>GMRP&amp;UI</t>
-  </si>
-  <si>
-    <t>KNRCON</t>
-  </si>
-  <si>
-    <t>BBOX</t>
-  </si>
-  <si>
-    <t>CRIZAC</t>
-  </si>
-  <si>
-    <t>JKLAKSHMI</t>
-  </si>
-  <si>
-    <t>TIINDIA</t>
-  </si>
-  <si>
-    <t>SUNTECK</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>ALOKINDS</t>
-  </si>
-  <si>
-    <t>RENUKA</t>
-  </si>
-  <si>
-    <t>ELECTCAST</t>
-  </si>
-  <si>
-    <t>PRAJIND</t>
-  </si>
-  <si>
-    <t>JAIBALAJI</t>
-  </si>
-  <si>
-    <t>AVANTIFEED</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>VGUARD</t>
-  </si>
-  <si>
-    <t>TDPOWERSYS</t>
-  </si>
-  <si>
-    <t>CUPID</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>THANGAMAYL</t>
-  </si>
-  <si>
-    <t>AZAD</t>
-  </si>
-  <si>
-    <t>BLACKBUCK</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>PRIVISCL</t>
-  </si>
-  <si>
-    <t>PRICOLLTD</t>
-  </si>
-  <si>
-    <t>LOTUSDEV</t>
-  </si>
-  <si>
-    <t>AEQUS</t>
-  </si>
-  <si>
-    <t>GOKULAGRO</t>
-  </si>
-  <si>
-    <t>TIMETECHNO</t>
-  </si>
-  <si>
-    <t>TANLA</t>
-  </si>
-  <si>
-    <t>NAZARA</t>
-  </si>
-  <si>
-    <t>AETHER</t>
-  </si>
-  <si>
-    <t>JSFB</t>
-  </si>
-  <si>
-    <t>ASHAPURMIN</t>
-  </si>
-  <si>
-    <t>HAPPSTMNDS</t>
-  </si>
-  <si>
-    <t>VIKRAMSOLR</t>
-  </si>
-  <si>
-    <t>SUDARSCHEM</t>
-  </si>
-  <si>
-    <t>TMB</t>
-  </si>
-  <si>
-    <t>INOXGREEN</t>
-  </si>
-  <si>
-    <t>REFEX</t>
-  </si>
-  <si>
-    <t>BORORENEW</t>
-  </si>
-  <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
-    <t>MASTEK</t>
-  </si>
-  <si>
-    <t>SAMHI</t>
-  </si>
-  <si>
-    <t>SHAILY</t>
-  </si>
-  <si>
-    <t>ROUTE</t>
-  </si>
-  <si>
-    <t>METROPOLIS</t>
-  </si>
-  <si>
-    <t>EIEL</t>
-  </si>
-  <si>
-    <t>JUSTDIAL</t>
-  </si>
-  <si>
-    <t>AXISCADES</t>
-  </si>
-  <si>
-    <t>RAYMONDLSL</t>
-  </si>
-  <si>
-    <t>GRWRHITECH</t>
-  </si>
-  <si>
-    <t>SHAKTIPUMP</t>
-  </si>
-  <si>
-    <t>WAKEFIT</t>
-  </si>
-  <si>
-    <t>RELAXO</t>
-  </si>
-  <si>
-    <t>SHARDACROP</t>
-  </si>
-  <si>
-    <t>CSBBANK</t>
-  </si>
-  <si>
-    <t>RATNAMANI</t>
-  </si>
-  <si>
-    <t>GPPL</t>
-  </si>
-  <si>
-    <t>EQUITASBNK</t>
-  </si>
-  <si>
-    <t>CCAVENUE</t>
-  </si>
-  <si>
-    <t>WAAREERTL</t>
-  </si>
-  <si>
-    <t>NEOGEN</t>
-  </si>
-  <si>
-    <t>TIPSMUSIC</t>
-  </si>
-  <si>
-    <t>MANYAVAR</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
-  </si>
-  <si>
-    <t>MARKSANS</t>
-  </si>
-  <si>
-    <t>OSWALPUMPS</t>
-  </si>
-  <si>
-    <t>ARVIND</t>
-  </si>
-  <si>
-    <t>KIRLOSBROS</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>JKPAPER</t>
-  </si>
-  <si>
-    <t>MEDPLUS</t>
-  </si>
-  <si>
-    <t>VOLTAMP</t>
-  </si>
-  <si>
-    <t>JAYNECOIND</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>STAR</t>
-  </si>
-  <si>
-    <t>AURIONPRO</t>
-  </si>
-  <si>
-    <t>ICIL</t>
-  </si>
-  <si>
-    <t>SUPRIYA</t>
-  </si>
-  <si>
-    <t>RALLIS</t>
-  </si>
-  <si>
-    <t>WEBELSOLAR</t>
-  </si>
-  <si>
-    <t>INDIAGLYCO</t>
-  </si>
-  <si>
-    <t>ELLEN</t>
-  </si>
-  <si>
-    <t>PRUDENT</t>
-  </si>
-  <si>
-    <t>SHRIPISTON</t>
-  </si>
-  <si>
-    <t>INDIASHLTR</t>
-  </si>
-  <si>
-    <t>KPIGREEN</t>
-  </si>
-  <si>
-    <t>JSLL</t>
-  </si>
-  <si>
-    <t>ASKAUTOLTD</t>
-  </si>
-  <si>
-    <t>KRN</t>
-  </si>
-  <si>
-    <t>CAMPUS</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>VMART</t>
-  </si>
-  <si>
-    <t>AKUMS</t>
-  </si>
-  <si>
-    <t>SHAREINDIA</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>GHCL</t>
-  </si>
-  <si>
-    <t>GOKEX</t>
-  </si>
-  <si>
-    <t>ATLANTAELE</t>
-  </si>
-  <si>
-    <t>CRAMC</t>
-  </si>
-  <si>
-    <t>RBA</t>
-  </si>
-  <si>
-    <t>HERITGFOOD</t>
-  </si>
-  <si>
-    <t>FIEMIND</t>
-  </si>
-  <si>
-    <t>AVL</t>
-  </si>
-  <si>
-    <t>UTLSOLAR</t>
-  </si>
-  <si>
-    <t>SUDEEPPHRM</t>
-  </si>
-  <si>
-    <t>V2RETAIL</t>
-  </si>
-  <si>
-    <t>JLHL</t>
-  </si>
-  <si>
-    <t>FEDFINA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>POWERMECH</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>DYNAMATECH</t>
-  </si>
-  <si>
-    <t>STYRENIX</t>
-  </si>
-  <si>
-    <t>PGIL</t>
-  </si>
-  <si>
-    <t>SFL</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>MIDHANI</t>
-  </si>
-  <si>
-    <t>GSFC</t>
-  </si>
-  <si>
-    <t>JYOTHYLAB</t>
-  </si>
-  <si>
-    <t>SMARTWORKS</t>
-  </si>
-  <si>
-    <t>ARVINDFASN</t>
-  </si>
-  <si>
-    <t>INDIGOPNTS</t>
-  </si>
-  <si>
-    <t>PNCINFRA</t>
-  </si>
-  <si>
-    <t>OPTIEMUS</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>ZAGGLE</t>
-  </si>
-  <si>
-    <t>QPOWER</t>
-  </si>
-  <si>
-    <t>RELIGARE</t>
-  </si>
-  <si>
-    <t>STYL</t>
-  </si>
-  <si>
-    <t>NETWORK18</t>
-  </si>
-  <si>
-    <t>RTNPOWER</t>
-  </si>
-  <si>
-    <t>PICCADIL</t>
-  </si>
-  <si>
-    <t>KSCL</t>
-  </si>
-  <si>
-    <t>MAHSCOOTER</t>
-  </si>
-  <si>
-    <t>IIFLCAPS</t>
-  </si>
-  <si>
-    <t>BIRLACORPN</t>
-  </si>
-  <si>
-    <t>DATAMATICS</t>
-  </si>
-  <si>
-    <t>AARTIPHARM</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>WELENT</t>
-  </si>
-  <si>
-    <t>CELLO</t>
-  </si>
-  <si>
-    <t>ANUP</t>
-  </si>
-  <si>
-    <t>IXIGO</t>
-  </si>
-  <si>
-    <t>REDTAPE</t>
-  </si>
-  <si>
-    <t>KANSAINER</t>
-  </si>
-  <si>
-    <t>ORKLAINDIA</t>
-  </si>
-  <si>
-    <t>DBL</t>
-  </si>
-  <si>
-    <t>TARC</t>
-  </si>
-  <si>
-    <t>FINPIPE</t>
-  </si>
-  <si>
-    <t>ORIENTCEM</t>
-  </si>
-  <si>
-    <t>ADVENZYMES</t>
-  </si>
-  <si>
-    <t>AWFIS</t>
-  </si>
-  <si>
-    <t>APLLTD</t>
-  </si>
-  <si>
-    <t>KITEX</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>EPL</t>
-  </si>
-  <si>
-    <t>BANCOINDIA</t>
-  </si>
-  <si>
-    <t>EUREKAFORB</t>
-  </si>
-  <si>
-    <t>SURYAROSNI</t>
-  </si>
-  <si>
-    <t>PRSMJOHNSN</t>
-  </si>
-  <si>
-    <t>PURVA</t>
-  </si>
-  <si>
-    <t>ALKYLAMINE</t>
-  </si>
-  <si>
-    <t>MAHSEAMLES</t>
-  </si>
-  <si>
-    <t>CERA</t>
-  </si>
-  <si>
-    <t>BAJAJELEC</t>
-  </si>
-  <si>
-    <t>STARCEMENT</t>
-  </si>
-  <si>
-    <t>DBREALTY</t>
-  </si>
-  <si>
-    <t>VIPIND</t>
-  </si>
-  <si>
-    <t>HGINFRA</t>
-  </si>
-  <si>
-    <t>SAFARI</t>
-  </si>
-  <si>
-    <t>HEMIPROP</t>
-  </si>
-  <si>
-    <t>NFL</t>
-  </si>
-  <si>
-    <t>TSFINV</t>
-  </si>
-  <si>
-    <t>AHLUCONT</t>
-  </si>
-  <si>
-    <t>SANOFICONR</t>
-  </si>
-  <si>
-    <t>SUBROS</t>
-  </si>
-  <si>
     <t>TradingView Chart</t>
   </si>
   <si>
@@ -814,6 +814,9 @@
     <t>Stocks_Above_200EMA_%</t>
   </si>
   <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
     <t>2026-07-31</t>
   </si>
   <si>
@@ -821,9 +824,6 @@
   </si>
   <si>
     <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
   </si>
 </sst>
 </file>
@@ -1322,28 +1322,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.97</v>
+        <v>364.05</v>
       </c>
       <c r="C2" s="2">
-        <v>167.74</v>
+        <v>190.29</v>
       </c>
       <c r="D2" s="2">
-        <v>64.79000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="E2" s="2">
-        <v>48.09</v>
+        <v>60.05</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>90</v>
-      </c>
-      <c r="I2" s="2">
-        <v>89.2</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>260</v>
@@ -1354,28 +1354,25 @@
         <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>557.05</v>
+        <v>262.13</v>
       </c>
       <c r="C3" s="2">
-        <v>209.44</v>
+        <v>199.44</v>
       </c>
       <c r="D3" s="2">
-        <v>20.26</v>
+        <v>103.06</v>
       </c>
       <c r="E3" s="2">
-        <v>-4.8</v>
+        <v>26.74</v>
       </c>
       <c r="F3" s="2">
-        <v>98.84</v>
-      </c>
-      <c r="G3" s="2">
-        <v>99.2</v>
+        <v>99.23</v>
       </c>
       <c r="H3" s="2">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>260</v>
@@ -1386,28 +1383,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>816.2</v>
+        <v>638.9</v>
       </c>
       <c r="C4" s="2">
-        <v>57.57</v>
+        <v>259.28</v>
       </c>
       <c r="D4" s="2">
-        <v>68.48</v>
+        <v>13.49</v>
       </c>
       <c r="E4" s="2">
-        <v>40.11</v>
+        <v>23.3</v>
       </c>
       <c r="F4" s="2">
-        <v>97.67</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>98</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>83.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I4" s="2">
-        <v>73.2</v>
+        <v>99.2</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>260</v>
@@ -1418,28 +1415,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>5685.6</v>
+        <v>814.5</v>
       </c>
       <c r="C5" s="2">
-        <v>43.72</v>
+        <v>90.5</v>
       </c>
       <c r="D5" s="2">
-        <v>48.03</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>46.07</v>
+        <v>38.33</v>
       </c>
       <c r="F5" s="2">
-        <v>96.51000000000001</v>
+        <v>97.69</v>
       </c>
       <c r="G5" s="2">
-        <v>33.2</v>
+        <v>97.7</v>
       </c>
       <c r="H5" s="2">
-        <v>42.8</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>37.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>260</v>
@@ -1450,28 +1447,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>332.55</v>
+        <v>759.75</v>
       </c>
       <c r="C6" s="2">
-        <v>92.06999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="D6" s="2">
-        <v>61.29</v>
+        <v>52.18</v>
       </c>
       <c r="E6" s="2">
-        <v>13.29</v>
+        <v>20.56</v>
       </c>
       <c r="F6" s="2">
-        <v>95.34999999999999</v>
-      </c>
-      <c r="G6" s="2">
-        <v>94</v>
+        <v>96.92</v>
       </c>
       <c r="H6" s="2">
-        <v>93.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I6" s="2">
-        <v>90.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>260</v>
@@ -1482,28 +1476,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>222.95</v>
+        <v>96.88</v>
       </c>
       <c r="C7" s="2">
-        <v>112.52</v>
+        <v>130.17</v>
       </c>
       <c r="D7" s="2">
-        <v>24.57</v>
+        <v>35.9</v>
       </c>
       <c r="E7" s="2">
-        <v>13.24</v>
+        <v>6.67</v>
       </c>
       <c r="F7" s="2">
-        <v>94.19</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>97.2</v>
+        <v>90.8</v>
       </c>
       <c r="H7" s="2">
         <v>92.8</v>
       </c>
       <c r="I7" s="2">
-        <v>86.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>260</v>
@@ -1514,28 +1508,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>643.7</v>
+        <v>1965.3</v>
       </c>
       <c r="C8" s="2">
-        <v>98.45999999999999</v>
+        <v>109.6</v>
       </c>
       <c r="D8" s="2">
-        <v>32.9</v>
+        <v>35.37</v>
       </c>
       <c r="E8" s="2">
-        <v>15.86</v>
+        <v>14.2</v>
       </c>
       <c r="F8" s="2">
-        <v>93.02</v>
-      </c>
-      <c r="G8" s="2">
-        <v>97.59999999999999</v>
+        <v>95.38</v>
       </c>
       <c r="H8" s="2">
-        <v>96.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2">
-        <v>94.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>260</v>
@@ -1546,28 +1537,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1861.6</v>
+        <v>165.83</v>
       </c>
       <c r="C9" s="2">
-        <v>103.82</v>
+        <v>75.11</v>
       </c>
       <c r="D9" s="2">
-        <v>50.66</v>
+        <v>45.67</v>
       </c>
       <c r="E9" s="2">
-        <v>0.63</v>
+        <v>25.8</v>
       </c>
       <c r="F9" s="2">
-        <v>91.86</v>
+        <v>94.62</v>
       </c>
       <c r="G9" s="2">
-        <v>94.8</v>
+        <v>63.22</v>
       </c>
       <c r="H9" s="2">
-        <v>93.2</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2">
-        <v>97.2</v>
+        <v>77.2</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>260</v>
@@ -1578,28 +1569,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>88.66</v>
+        <v>1277.1</v>
       </c>
       <c r="C10" s="2">
-        <v>127.1</v>
+        <v>100.94</v>
       </c>
       <c r="D10" s="2">
-        <v>18.8</v>
+        <v>56.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-1.9</v>
+        <v>4.3</v>
       </c>
       <c r="F10" s="2">
-        <v>90.7</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>92.8</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>94.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>98</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>260</v>
@@ -1610,28 +1601,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>238.05</v>
+        <v>634.95</v>
       </c>
       <c r="C11" s="2">
-        <v>82.37</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2">
-        <v>39.83</v>
+        <v>44.49</v>
       </c>
       <c r="E11" s="2">
-        <v>7.07</v>
+        <v>35.49</v>
       </c>
       <c r="F11" s="2">
-        <v>89.53</v>
-      </c>
-      <c r="G11" s="2">
-        <v>95.59999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="H11" s="2">
-        <v>95.2</v>
+        <v>72</v>
       </c>
       <c r="I11" s="2">
-        <v>98.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>260</v>
@@ -1642,28 +1630,25 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1256.5</v>
+        <v>94.92</v>
       </c>
       <c r="C12" s="2">
-        <v>102.86</v>
+        <v>55.48</v>
       </c>
       <c r="D12" s="2">
-        <v>46.83</v>
+        <v>39.69</v>
       </c>
       <c r="E12" s="2">
-        <v>-7.5</v>
+        <v>30.8</v>
       </c>
       <c r="F12" s="2">
-        <v>88.37</v>
-      </c>
-      <c r="G12" s="2">
-        <v>93.59999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H12" s="2">
-        <v>82.40000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="I12" s="2">
-        <v>95.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>260</v>
@@ -1674,28 +1659,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>2133.3</v>
+        <v>5554</v>
       </c>
       <c r="C13" s="2">
-        <v>105</v>
+        <v>37.57</v>
       </c>
       <c r="D13" s="2">
-        <v>11.61</v>
+        <v>52.76</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.53</v>
+        <v>32.22</v>
       </c>
       <c r="F13" s="2">
-        <v>87.20999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="G13" s="2">
-        <v>96</v>
+        <v>96.55</v>
       </c>
       <c r="H13" s="2">
-        <v>99.59999999999999</v>
+        <v>33.2</v>
       </c>
       <c r="I13" s="2">
-        <v>98.8</v>
+        <v>42.8</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>260</v>
@@ -1706,28 +1691,25 @@
         <v>21</v>
       </c>
       <c r="B14" s="1">
-        <v>71.75</v>
+        <v>185.83</v>
       </c>
       <c r="C14" s="2">
-        <v>39.75</v>
+        <v>63.32</v>
       </c>
       <c r="D14" s="2">
-        <v>30.76</v>
+        <v>33.54</v>
       </c>
       <c r="E14" s="2">
-        <v>20.02</v>
+        <v>28.64</v>
       </c>
       <c r="F14" s="2">
-        <v>86.05</v>
-      </c>
-      <c r="G14" s="2">
-        <v>88.40000000000001</v>
+        <v>90.77</v>
       </c>
       <c r="H14" s="2">
-        <v>75.2</v>
+        <v>88.8</v>
       </c>
       <c r="I14" s="2">
-        <v>63.6</v>
+        <v>30</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>260</v>
@@ -1738,28 +1720,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>79.95999999999999</v>
+        <v>3863.8</v>
       </c>
       <c r="C15" s="2">
-        <v>86.81999999999999</v>
+        <v>80.84</v>
       </c>
       <c r="D15" s="2">
-        <v>12.19</v>
+        <v>37.68</v>
       </c>
       <c r="E15" s="2">
-        <v>2.88</v>
+        <v>17.76</v>
       </c>
       <c r="F15" s="2">
-        <v>84.88</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2">
-        <v>84</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="H15" s="2">
-        <v>79.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I15" s="2">
-        <v>83.2</v>
+        <v>87.2</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>260</v>
@@ -1770,28 +1752,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>743.5</v>
+        <v>811.2</v>
       </c>
       <c r="C16" s="2">
-        <v>67.02</v>
+        <v>65.89</v>
       </c>
       <c r="D16" s="2">
-        <v>29.62</v>
+        <v>41.21</v>
       </c>
       <c r="E16" s="2">
-        <v>0.86</v>
+        <v>23.19</v>
       </c>
       <c r="F16" s="2">
-        <v>83.72</v>
+        <v>89.23</v>
       </c>
       <c r="G16" s="2">
-        <v>90.40000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="H16" s="2">
-        <v>90.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="I16" s="2">
-        <v>88.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>260</v>
@@ -1802,28 +1784,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>403.2</v>
+        <v>1840</v>
       </c>
       <c r="C17" s="2">
-        <v>37.14</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D17" s="2">
-        <v>13.96</v>
+        <v>39.8</v>
       </c>
       <c r="E17" s="2">
-        <v>23.49</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2">
-        <v>82.56</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="G17" s="2">
-        <v>80.40000000000001</v>
+        <v>91.95</v>
       </c>
       <c r="H17" s="2">
-        <v>69.2</v>
+        <v>94.8</v>
       </c>
       <c r="I17" s="2">
-        <v>55.6</v>
+        <v>93.2</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>260</v>
@@ -1834,28 +1816,25 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1908</v>
+        <v>248.31</v>
       </c>
       <c r="C18" s="2">
-        <v>58.85</v>
+        <v>100.96</v>
       </c>
       <c r="D18" s="2">
-        <v>32.66</v>
+        <v>34.32</v>
       </c>
       <c r="E18" s="2">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="F18" s="2">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="G18" s="2">
-        <v>91.59999999999999</v>
+        <v>87.69</v>
       </c>
       <c r="H18" s="2">
-        <v>88.8</v>
+        <v>85.2</v>
       </c>
       <c r="I18" s="2">
-        <v>91.2</v>
+        <v>88</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>260</v>
@@ -1866,28 +1845,28 @@
         <v>26</v>
       </c>
       <c r="B19" s="1">
-        <v>178.48</v>
+        <v>222.88</v>
       </c>
       <c r="C19" s="2">
-        <v>51.51</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D19" s="2">
-        <v>15.79</v>
+        <v>16.87</v>
       </c>
       <c r="E19" s="2">
-        <v>13.3</v>
+        <v>4.44</v>
       </c>
       <c r="F19" s="2">
-        <v>80.23</v>
+        <v>86.92</v>
       </c>
       <c r="G19" s="2">
-        <v>88</v>
+        <v>94.25</v>
       </c>
       <c r="H19" s="2">
-        <v>76</v>
+        <v>97.2</v>
       </c>
       <c r="I19" s="2">
-        <v>57.6</v>
+        <v>92.8</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>260</v>
@@ -1898,28 +1877,28 @@
         <v>27</v>
       </c>
       <c r="B20" s="1">
-        <v>1977.2</v>
+        <v>603.25</v>
       </c>
       <c r="C20" s="2">
-        <v>63.98</v>
+        <v>66.97</v>
       </c>
       <c r="D20" s="2">
-        <v>36.43</v>
+        <v>16.99</v>
       </c>
       <c r="E20" s="2">
-        <v>-3.57</v>
+        <v>18.25</v>
       </c>
       <c r="F20" s="2">
-        <v>79.06999999999999</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="G20" s="2">
-        <v>89.2</v>
+        <v>78.16</v>
       </c>
       <c r="H20" s="2">
-        <v>89.2</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2">
-        <v>97.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>260</v>
@@ -1930,28 +1909,28 @@
         <v>28</v>
       </c>
       <c r="B21" s="1">
-        <v>579</v>
+        <v>83.5</v>
       </c>
       <c r="C21" s="2">
-        <v>60.06</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D21" s="2">
-        <v>18.94</v>
+        <v>23.33</v>
       </c>
       <c r="E21" s="2">
-        <v>6.2</v>
+        <v>5.87</v>
       </c>
       <c r="F21" s="2">
-        <v>77.91</v>
+        <v>85.38</v>
       </c>
       <c r="G21" s="2">
-        <v>86</v>
+        <v>85.06</v>
       </c>
       <c r="H21" s="2">
-        <v>67.2</v>
+        <v>84</v>
       </c>
       <c r="I21" s="2">
-        <v>66.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>260</v>
@@ -1962,28 +1941,25 @@
         <v>29</v>
       </c>
       <c r="B22" s="1">
-        <v>3346.9</v>
+        <v>389.95</v>
       </c>
       <c r="C22" s="2">
-        <v>58.18</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="D22" s="2">
-        <v>15.2</v>
+        <v>28.02</v>
       </c>
       <c r="E22" s="2">
-        <v>4.9</v>
+        <v>-2.78</v>
       </c>
       <c r="F22" s="2">
-        <v>76.73999999999999</v>
-      </c>
-      <c r="G22" s="2">
-        <v>83.2</v>
+        <v>84.62</v>
       </c>
       <c r="H22" s="2">
-        <v>87.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>86</v>
+        <v>97.2</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>260</v>
@@ -1994,28 +1970,25 @@
         <v>30</v>
       </c>
       <c r="B23" s="1">
-        <v>266.36</v>
+        <v>949.15</v>
       </c>
       <c r="C23" s="2">
-        <v>36.47</v>
+        <v>92.33</v>
       </c>
       <c r="D23" s="2">
-        <v>16.93</v>
+        <v>22.13</v>
       </c>
       <c r="E23" s="2">
-        <v>13.6</v>
+        <v>0.26</v>
       </c>
       <c r="F23" s="2">
-        <v>75.58</v>
-      </c>
-      <c r="G23" s="2">
-        <v>74.40000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H23" s="2">
-        <v>76.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2">
-        <v>65.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>260</v>
@@ -2026,28 +1999,25 @@
         <v>31</v>
       </c>
       <c r="B24" s="1">
-        <v>670.3</v>
+        <v>352.35</v>
       </c>
       <c r="C24" s="2">
-        <v>19.58</v>
+        <v>49.99</v>
       </c>
       <c r="D24" s="2">
-        <v>26.94</v>
+        <v>29.28</v>
       </c>
       <c r="E24" s="2">
-        <v>15.62</v>
+        <v>14.66</v>
       </c>
       <c r="F24" s="2">
-        <v>74.42</v>
-      </c>
-      <c r="G24" s="2">
-        <v>81.2</v>
+        <v>83.08</v>
       </c>
       <c r="H24" s="2">
-        <v>43.2</v>
+        <v>50.4</v>
       </c>
       <c r="I24" s="2">
-        <v>33.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>260</v>
@@ -2058,28 +2028,25 @@
         <v>32</v>
       </c>
       <c r="B25" s="1">
-        <v>389.9</v>
+        <v>7085.5</v>
       </c>
       <c r="C25" s="2">
-        <v>95.20999999999999</v>
+        <v>98.12</v>
       </c>
       <c r="D25" s="2">
-        <v>-4.48</v>
+        <v>0.23</v>
       </c>
       <c r="E25" s="2">
-        <v>-8.01</v>
+        <v>5.03</v>
       </c>
       <c r="F25" s="2">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="G25" s="2">
-        <v>87.59999999999999</v>
+        <v>82.31</v>
       </c>
       <c r="H25" s="2">
-        <v>88.40000000000001</v>
+        <v>26.8</v>
       </c>
       <c r="I25" s="2">
-        <v>90</v>
+        <v>34.8</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>260</v>
@@ -2090,28 +2057,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="1">
-        <v>618.2</v>
+        <v>403.85</v>
       </c>
       <c r="C26" s="2">
-        <v>55.5</v>
+        <v>104.86</v>
       </c>
       <c r="D26" s="2">
-        <v>43.75</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E26" s="2">
-        <v>-14.95</v>
+        <v>0.25</v>
       </c>
       <c r="F26" s="2">
-        <v>72.09</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="G26" s="2">
-        <v>77.59999999999999</v>
+        <v>72.41</v>
       </c>
       <c r="H26" s="2">
-        <v>69.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I26" s="2">
-        <v>88</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>260</v>
@@ -2122,28 +2089,25 @@
         <v>34</v>
       </c>
       <c r="B27" s="1">
-        <v>1315.7</v>
+        <v>957.55</v>
       </c>
       <c r="C27" s="2">
-        <v>34.17</v>
+        <v>55.95</v>
       </c>
       <c r="D27" s="2">
-        <v>25.04</v>
+        <v>22.9</v>
       </c>
       <c r="E27" s="2">
-        <v>3.22</v>
+        <v>13.18</v>
       </c>
       <c r="F27" s="2">
-        <v>70.93000000000001</v>
-      </c>
-      <c r="G27" s="2">
-        <v>72.8</v>
+        <v>80.77</v>
       </c>
       <c r="H27" s="2">
-        <v>67.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="I27" s="2">
-        <v>69.2</v>
+        <v>86</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>260</v>
@@ -2154,28 +2118,25 @@
         <v>35</v>
       </c>
       <c r="B28" s="1">
-        <v>206.46</v>
+        <v>2489</v>
       </c>
       <c r="C28" s="2">
-        <v>13.96</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2">
-        <v>15.42</v>
+        <v>25.69</v>
       </c>
       <c r="E28" s="2">
-        <v>16.47</v>
+        <v>4.65</v>
       </c>
       <c r="F28" s="2">
-        <v>69.77</v>
-      </c>
-      <c r="G28" s="2">
-        <v>71.2</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2">
-        <v>31.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I28" s="2">
-        <v>1.2</v>
+        <v>80.8</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>260</v>
@@ -2186,28 +2147,25 @@
         <v>36</v>
       </c>
       <c r="B29" s="1">
-        <v>679.2</v>
+        <v>1139.6</v>
       </c>
       <c r="C29" s="2">
-        <v>38.84</v>
+        <v>49.51</v>
       </c>
       <c r="D29" s="2">
-        <v>16.73</v>
+        <v>25.7</v>
       </c>
       <c r="E29" s="2">
-        <v>2.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F29" s="2">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="G29" s="2">
-        <v>70</v>
+        <v>79.23</v>
       </c>
       <c r="H29" s="2">
-        <v>74.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I29" s="2">
-        <v>75.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>260</v>
@@ -2218,28 +2176,28 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>422.75</v>
+        <v>1329.8</v>
       </c>
       <c r="C30" s="2">
-        <v>26.02</v>
+        <v>34.38</v>
       </c>
       <c r="D30" s="2">
-        <v>7.17</v>
+        <v>26.89</v>
       </c>
       <c r="E30" s="2">
-        <v>11.34</v>
+        <v>14.64</v>
       </c>
       <c r="F30" s="2">
-        <v>67.44</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="G30" s="2">
-        <v>64</v>
+        <v>51.72</v>
       </c>
       <c r="H30" s="2">
-        <v>74.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="I30" s="2">
-        <v>46.8</v>
+        <v>58.8</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>260</v>
@@ -2250,28 +2208,25 @@
         <v>38</v>
       </c>
       <c r="B31" s="1">
-        <v>284.75</v>
+        <v>2580.3</v>
       </c>
       <c r="C31" s="2">
-        <v>30.55</v>
+        <v>32.22</v>
       </c>
       <c r="D31" s="2">
-        <v>7.76</v>
+        <v>17.42</v>
       </c>
       <c r="E31" s="2">
-        <v>8.19</v>
+        <v>17.35</v>
       </c>
       <c r="F31" s="2">
-        <v>66.28</v>
-      </c>
-      <c r="G31" s="2">
-        <v>63.2</v>
+        <v>77.69</v>
       </c>
       <c r="H31" s="2">
-        <v>59.6</v>
+        <v>59.2</v>
       </c>
       <c r="I31" s="2">
-        <v>59.6</v>
+        <v>38</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>260</v>
@@ -2282,28 +2237,25 @@
         <v>39</v>
       </c>
       <c r="B32" s="1">
-        <v>527.75</v>
+        <v>3162.3</v>
       </c>
       <c r="C32" s="2">
-        <v>55.82</v>
+        <v>51.79</v>
       </c>
       <c r="D32" s="2">
-        <v>9.869999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E32" s="2">
-        <v>-6.02</v>
+        <v>14.82</v>
       </c>
       <c r="F32" s="2">
-        <v>65.12</v>
-      </c>
-      <c r="G32" s="2">
-        <v>78.8</v>
+        <v>76.92</v>
       </c>
       <c r="H32" s="2">
-        <v>81.2</v>
+        <v>62.4</v>
       </c>
       <c r="I32" s="2">
-        <v>72.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>260</v>
@@ -2314,28 +2266,28 @@
         <v>40</v>
       </c>
       <c r="B33" s="1">
-        <v>130.16</v>
+        <v>175.64</v>
       </c>
       <c r="C33" s="2">
-        <v>45.9</v>
+        <v>49.1</v>
       </c>
       <c r="D33" s="2">
-        <v>11.47</v>
+        <v>18.32</v>
       </c>
       <c r="E33" s="2">
-        <v>-2.84</v>
+        <v>7.15</v>
       </c>
       <c r="F33" s="2">
-        <v>63.95</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="G33" s="2">
-        <v>80</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="H33" s="2">
-        <v>77.2</v>
+        <v>88</v>
       </c>
       <c r="I33" s="2">
-        <v>81.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>260</v>
@@ -2346,28 +2298,25 @@
         <v>41</v>
       </c>
       <c r="B34" s="1">
-        <v>292.65</v>
+        <v>2133.8</v>
       </c>
       <c r="C34" s="2">
-        <v>42.51</v>
+        <v>55.2</v>
       </c>
       <c r="D34" s="2">
-        <v>4.86</v>
+        <v>16.56</v>
       </c>
       <c r="E34" s="2">
-        <v>1.69</v>
+        <v>4.89</v>
       </c>
       <c r="F34" s="2">
-        <v>62.79</v>
-      </c>
-      <c r="G34" s="2">
-        <v>69.59999999999999</v>
+        <v>75.38</v>
       </c>
       <c r="H34" s="2">
-        <v>57.6</v>
+        <v>59.6</v>
       </c>
       <c r="I34" s="2">
-        <v>79.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>260</v>
@@ -2378,28 +2327,28 @@
         <v>42</v>
       </c>
       <c r="B35" s="1">
-        <v>172.11</v>
+        <v>2029.6</v>
       </c>
       <c r="C35" s="2">
-        <v>33.72</v>
+        <v>91.44</v>
       </c>
       <c r="D35" s="2">
-        <v>5.61</v>
+        <v>16.43</v>
       </c>
       <c r="E35" s="2">
-        <v>5.65</v>
+        <v>-13.3</v>
       </c>
       <c r="F35" s="2">
-        <v>61.63</v>
+        <v>74.62</v>
       </c>
       <c r="G35" s="2">
-        <v>28.4</v>
+        <v>87.36</v>
       </c>
       <c r="H35" s="2">
-        <v>16.4</v>
+        <v>96</v>
       </c>
       <c r="I35" s="2">
-        <v>32.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>260</v>
@@ -2410,28 +2359,25 @@
         <v>43</v>
       </c>
       <c r="B36" s="1">
-        <v>46.7</v>
+        <v>273.85</v>
       </c>
       <c r="C36" s="2">
-        <v>34.43</v>
+        <v>62.86</v>
       </c>
       <c r="D36" s="2">
-        <v>13.9</v>
+        <v>14.74</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.34</v>
+        <v>1.69</v>
       </c>
       <c r="F36" s="2">
-        <v>60.47</v>
-      </c>
-      <c r="G36" s="2">
-        <v>66.40000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H36" s="2">
-        <v>47.2</v>
+        <v>66</v>
       </c>
       <c r="I36" s="2">
-        <v>44.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>260</v>
@@ -2442,28 +2388,25 @@
         <v>44</v>
       </c>
       <c r="B37" s="1">
-        <v>135.11</v>
+        <v>613.55</v>
       </c>
       <c r="C37" s="2">
-        <v>38.59</v>
+        <v>46.76</v>
       </c>
       <c r="D37" s="2">
-        <v>11.84</v>
+        <v>18.57</v>
       </c>
       <c r="E37" s="2">
-        <v>-2.18</v>
+        <v>7.73</v>
       </c>
       <c r="F37" s="2">
-        <v>59.3</v>
-      </c>
-      <c r="G37" s="2">
-        <v>69.2</v>
+        <v>73.08</v>
       </c>
       <c r="H37" s="2">
-        <v>64.8</v>
+        <v>84.8</v>
       </c>
       <c r="I37" s="2">
-        <v>68</v>
+        <v>78.8</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>260</v>
@@ -2474,28 +2417,25 @@
         <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>1604.5</v>
+        <v>697.45</v>
       </c>
       <c r="C38" s="2">
-        <v>26.85</v>
+        <v>40.42</v>
       </c>
       <c r="D38" s="2">
-        <v>13.99</v>
+        <v>33.56</v>
       </c>
       <c r="E38" s="2">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="F38" s="2">
-        <v>58.14</v>
-      </c>
-      <c r="G38" s="2">
-        <v>57.2</v>
+        <v>72.31</v>
       </c>
       <c r="H38" s="2">
-        <v>52</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I38" s="2">
-        <v>52.4</v>
+        <v>82</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>260</v>
@@ -2506,28 +2446,25 @@
         <v>46</v>
       </c>
       <c r="B39" s="1">
-        <v>864.4</v>
+        <v>560.55</v>
       </c>
       <c r="C39" s="2">
-        <v>4.09</v>
+        <v>53.47</v>
       </c>
       <c r="D39" s="2">
-        <v>7.37</v>
+        <v>16.99</v>
       </c>
       <c r="E39" s="2">
-        <v>12.44</v>
+        <v>2.98</v>
       </c>
       <c r="F39" s="2">
-        <v>56.98</v>
-      </c>
-      <c r="G39" s="2">
-        <v>22</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="H39" s="2">
-        <v>13.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I39" s="2">
-        <v>2.8</v>
+        <v>86.8</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>260</v>
@@ -2538,28 +2475,28 @@
         <v>47</v>
       </c>
       <c r="B40" s="1">
-        <v>420.7</v>
+        <v>310</v>
       </c>
       <c r="C40" s="2">
-        <v>27.04</v>
+        <v>36.28</v>
       </c>
       <c r="D40" s="2">
-        <v>3.04</v>
+        <v>16.67</v>
       </c>
       <c r="E40" s="2">
-        <v>3.06</v>
+        <v>11.13</v>
       </c>
       <c r="F40" s="2">
-        <v>55.81</v>
+        <v>70.77</v>
       </c>
       <c r="G40" s="2">
-        <v>62</v>
+        <v>65.52</v>
       </c>
       <c r="H40" s="2">
-        <v>76.8</v>
+        <v>63.2</v>
       </c>
       <c r="I40" s="2">
-        <v>87.2</v>
+        <v>59.6</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>260</v>
@@ -2570,28 +2507,25 @@
         <v>48</v>
       </c>
       <c r="B41" s="1">
-        <v>61.14</v>
+        <v>203.3</v>
       </c>
       <c r="C41" s="2">
-        <v>41.72</v>
+        <v>23.06</v>
       </c>
       <c r="D41" s="2">
-        <v>-2.75</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E41" s="2">
-        <v>-2.46</v>
+        <v>19.06</v>
       </c>
       <c r="F41" s="2">
-        <v>54.65</v>
-      </c>
-      <c r="G41" s="2">
-        <v>38.8</v>
+        <v>70</v>
       </c>
       <c r="H41" s="2">
-        <v>37.2</v>
+        <v>2.4</v>
       </c>
       <c r="I41" s="2">
-        <v>71.59999999999999</v>
+        <v>6</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>260</v>
@@ -2602,28 +2536,25 @@
         <v>49</v>
       </c>
       <c r="B42" s="1">
-        <v>1448.6</v>
+        <v>1260.9</v>
       </c>
       <c r="C42" s="2">
-        <v>21.48</v>
+        <v>46.18</v>
       </c>
       <c r="D42" s="2">
-        <v>-2.65</v>
+        <v>2.55</v>
       </c>
       <c r="E42" s="2">
-        <v>7.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F42" s="2">
-        <v>53.49</v>
-      </c>
-      <c r="G42" s="2">
-        <v>35.6</v>
+        <v>69.23</v>
       </c>
       <c r="H42" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I42" s="2">
-        <v>31.2</v>
+        <v>36</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>260</v>
@@ -2634,28 +2565,28 @@
         <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1160</v>
+        <v>70.11</v>
       </c>
       <c r="C43" s="2">
-        <v>19.61</v>
+        <v>26.51</v>
       </c>
       <c r="D43" s="2">
-        <v>10.51</v>
+        <v>30.15</v>
       </c>
       <c r="E43" s="2">
-        <v>0.83</v>
+        <v>4.85</v>
       </c>
       <c r="F43" s="2">
-        <v>52.33</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="G43" s="2">
-        <v>46</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H43" s="2">
-        <v>58.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I43" s="2">
-        <v>67.2</v>
+        <v>75.2</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>260</v>
@@ -2666,28 +2597,25 @@
         <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>206.21</v>
+        <v>292.35</v>
       </c>
       <c r="C44" s="2">
-        <v>84.3</v>
+        <v>47.74</v>
       </c>
       <c r="D44" s="2">
-        <v>-11.49</v>
+        <v>18.91</v>
       </c>
       <c r="E44" s="2">
-        <v>-21.21</v>
+        <v>-1.25</v>
       </c>
       <c r="F44" s="2">
-        <v>51.16</v>
-      </c>
-      <c r="G44" s="2">
-        <v>87.2</v>
+        <v>67.69</v>
       </c>
       <c r="H44" s="2">
-        <v>94</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I44" s="2">
-        <v>99.2</v>
+        <v>56</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>260</v>
@@ -2698,28 +2626,28 @@
         <v>52</v>
       </c>
       <c r="B45" s="1">
-        <v>507.1</v>
+        <v>546.25</v>
       </c>
       <c r="C45" s="2">
-        <v>19.37</v>
+        <v>31</v>
       </c>
       <c r="D45" s="2">
-        <v>8.59</v>
+        <v>13.48</v>
       </c>
       <c r="E45" s="2">
-        <v>0.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F45" s="2">
-        <v>50</v>
+        <v>66.92</v>
       </c>
       <c r="G45" s="2">
-        <v>29.6</v>
+        <v>36.78</v>
       </c>
       <c r="H45" s="2">
-        <v>15.2</v>
+        <v>48</v>
       </c>
       <c r="I45" s="2">
-        <v>46.4</v>
+        <v>49.6</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>260</v>
@@ -2730,28 +2658,25 @@
         <v>53</v>
       </c>
       <c r="B46" s="1">
-        <v>799.5</v>
+        <v>738.35</v>
       </c>
       <c r="C46" s="2">
-        <v>17.78</v>
+        <v>50.79</v>
       </c>
       <c r="D46" s="2">
-        <v>2.76</v>
+        <v>3.07</v>
       </c>
       <c r="E46" s="2">
-        <v>2.8</v>
+        <v>4.95</v>
       </c>
       <c r="F46" s="2">
-        <v>48.84</v>
-      </c>
-      <c r="G46" s="2">
-        <v>56.8</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="H46" s="2">
-        <v>57.2</v>
+        <v>70.8</v>
       </c>
       <c r="I46" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>260</v>
@@ -2762,28 +2687,28 @@
         <v>54</v>
       </c>
       <c r="B47" s="1">
-        <v>2575.4</v>
+        <v>1957.7</v>
       </c>
       <c r="C47" s="2">
-        <v>16.76</v>
+        <v>58.32</v>
       </c>
       <c r="D47" s="2">
-        <v>6.06</v>
+        <v>26.12</v>
       </c>
       <c r="E47" s="2">
-        <v>1.51</v>
+        <v>-11.03</v>
       </c>
       <c r="F47" s="2">
-        <v>47.67</v>
+        <v>65.38</v>
       </c>
       <c r="G47" s="2">
-        <v>64.40000000000001</v>
+        <v>79.31</v>
       </c>
       <c r="H47" s="2">
-        <v>72</v>
+        <v>89.2</v>
       </c>
       <c r="I47" s="2">
-        <v>35.2</v>
+        <v>89.2</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>260</v>
@@ -2794,28 +2719,25 @@
         <v>55</v>
       </c>
       <c r="B48" s="1">
-        <v>510.3</v>
+        <v>2058.8</v>
       </c>
       <c r="C48" s="2">
-        <v>30.48</v>
+        <v>38.08</v>
       </c>
       <c r="D48" s="2">
-        <v>-0.92</v>
+        <v>23.34</v>
       </c>
       <c r="E48" s="2">
-        <v>-2.05</v>
+        <v>0.23</v>
       </c>
       <c r="F48" s="2">
-        <v>46.51</v>
-      </c>
-      <c r="G48" s="2">
-        <v>36</v>
+        <v>64.62</v>
       </c>
       <c r="H48" s="2">
-        <v>28.4</v>
+        <v>76.8</v>
       </c>
       <c r="I48" s="2">
-        <v>41.6</v>
+        <v>80</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>260</v>
@@ -2826,28 +2748,25 @@
         <v>56</v>
       </c>
       <c r="B49" s="1">
-        <v>818.45</v>
+        <v>923.45</v>
       </c>
       <c r="C49" s="2">
-        <v>26.43</v>
+        <v>50.84</v>
       </c>
       <c r="D49" s="2">
-        <v>-0.26</v>
+        <v>-12.26</v>
       </c>
       <c r="E49" s="2">
-        <v>-2.86</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F49" s="2">
-        <v>45.35</v>
-      </c>
-      <c r="G49" s="2">
-        <v>53.2</v>
+        <v>63.85</v>
       </c>
       <c r="H49" s="2">
-        <v>51.2</v>
+        <v>60.8</v>
       </c>
       <c r="I49" s="2">
-        <v>48</v>
+        <v>59.2</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>260</v>
@@ -2858,28 +2777,28 @@
         <v>57</v>
       </c>
       <c r="B50" s="1">
-        <v>104.27</v>
+        <v>292.25</v>
       </c>
       <c r="C50" s="2">
-        <v>10.02</v>
+        <v>48.21</v>
       </c>
       <c r="D50" s="2">
-        <v>11.91</v>
+        <v>6.64</v>
       </c>
       <c r="E50" s="2">
-        <v>-2.41</v>
+        <v>0.62</v>
       </c>
       <c r="F50" s="2">
-        <v>44.19</v>
+        <v>63.08</v>
       </c>
       <c r="G50" s="2">
-        <v>27.2</v>
+        <v>62.07</v>
       </c>
       <c r="H50" s="2">
-        <v>32</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I50" s="2">
-        <v>28.8</v>
+        <v>57.6</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>260</v>
@@ -2890,28 +2809,28 @@
         <v>58</v>
       </c>
       <c r="B51" s="1">
-        <v>21.44</v>
+        <v>144.7</v>
       </c>
       <c r="C51" s="2">
-        <v>45.95</v>
+        <v>24.7</v>
       </c>
       <c r="D51" s="2">
-        <v>-4.2</v>
+        <v>14.86</v>
       </c>
       <c r="E51" s="2">
-        <v>-12.85</v>
+        <v>6.9</v>
       </c>
       <c r="F51" s="2">
-        <v>43.02</v>
+        <v>62.31</v>
       </c>
       <c r="G51" s="2">
-        <v>40.4</v>
+        <v>37.93</v>
       </c>
       <c r="H51" s="2">
-        <v>32.4</v>
+        <v>54.4</v>
       </c>
       <c r="I51" s="2">
-        <v>64.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>260</v>
@@ -2922,28 +2841,28 @@
         <v>59</v>
       </c>
       <c r="B52" s="1">
-        <v>9.26</v>
+        <v>388.8</v>
       </c>
       <c r="C52" s="2">
-        <v>15.75</v>
+        <v>34.63</v>
       </c>
       <c r="D52" s="2">
-        <v>3.81</v>
+        <v>14.52</v>
       </c>
       <c r="E52" s="2">
-        <v>-2.11</v>
+        <v>2.05</v>
       </c>
       <c r="F52" s="2">
-        <v>41.86</v>
+        <v>61.54</v>
       </c>
       <c r="G52" s="2">
-        <v>61.2</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H52" s="2">
-        <v>62.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I52" s="2">
-        <v>53.2</v>
+        <v>69.2</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>260</v>
@@ -2954,28 +2873,28 @@
         <v>60</v>
       </c>
       <c r="B53" s="1">
-        <v>433.55</v>
+        <v>277</v>
       </c>
       <c r="C53" s="2">
-        <v>17.8</v>
+        <v>44.45</v>
       </c>
       <c r="D53" s="2">
-        <v>-2.46</v>
+        <v>10.62</v>
       </c>
       <c r="E53" s="2">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="F53" s="2">
-        <v>40.7</v>
+        <v>60.77</v>
       </c>
       <c r="G53" s="2">
-        <v>46.4</v>
+        <v>32.18</v>
       </c>
       <c r="H53" s="2">
-        <v>62</v>
+        <v>51.6</v>
       </c>
       <c r="I53" s="2">
-        <v>36</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>260</v>
@@ -2986,28 +2905,25 @@
         <v>61</v>
       </c>
       <c r="B54" s="1">
-        <v>212.84</v>
+        <v>11401</v>
       </c>
       <c r="C54" s="2">
-        <v>20.36</v>
+        <v>21.49</v>
       </c>
       <c r="D54" s="2">
-        <v>-8.42</v>
+        <v>9.06</v>
       </c>
       <c r="E54" s="2">
-        <v>0.89</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F54" s="2">
-        <v>39.53</v>
-      </c>
-      <c r="G54" s="2">
-        <v>12.4</v>
+        <v>60</v>
       </c>
       <c r="H54" s="2">
-        <v>6.4</v>
+        <v>45.6</v>
       </c>
       <c r="I54" s="2">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>260</v>
@@ -3018,28 +2934,28 @@
         <v>62</v>
       </c>
       <c r="B55" s="1">
-        <v>131.18</v>
+        <v>1636.2</v>
       </c>
       <c r="C55" s="2">
-        <v>11.36</v>
+        <v>34.15</v>
       </c>
       <c r="D55" s="2">
-        <v>11.51</v>
+        <v>13.79</v>
       </c>
       <c r="E55" s="2">
-        <v>-4.73</v>
+        <v>0.55</v>
       </c>
       <c r="F55" s="2">
-        <v>38.37</v>
+        <v>59.23</v>
       </c>
       <c r="G55" s="2">
-        <v>54.4</v>
+        <v>57.47</v>
       </c>
       <c r="H55" s="2">
-        <v>39.2</v>
+        <v>57.2</v>
       </c>
       <c r="I55" s="2">
-        <v>47.6</v>
+        <v>52</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>260</v>
@@ -3050,28 +2966,28 @@
         <v>63</v>
       </c>
       <c r="B56" s="1">
-        <v>478</v>
+        <v>47.17</v>
       </c>
       <c r="C56" s="2">
-        <v>14.29</v>
+        <v>28.39</v>
       </c>
       <c r="D56" s="2">
-        <v>-0.35</v>
+        <v>14.88</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.67</v>
+        <v>2.81</v>
       </c>
       <c r="F56" s="2">
-        <v>37.21</v>
+        <v>58.46</v>
       </c>
       <c r="G56" s="2">
-        <v>48</v>
+        <v>59.77</v>
       </c>
       <c r="H56" s="2">
-        <v>49.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I56" s="2">
-        <v>56.4</v>
+        <v>47.2</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>260</v>
@@ -3082,28 +2998,25 @@
         <v>64</v>
       </c>
       <c r="B57" s="1">
-        <v>111.39</v>
+        <v>830.1</v>
       </c>
       <c r="C57" s="2">
-        <v>25.81</v>
+        <v>28.38</v>
       </c>
       <c r="D57" s="2">
-        <v>-1.67</v>
+        <v>17.01</v>
       </c>
       <c r="E57" s="2">
-        <v>-7.97</v>
+        <v>1.37</v>
       </c>
       <c r="F57" s="2">
-        <v>36.05</v>
-      </c>
-      <c r="G57" s="2">
-        <v>51.2</v>
+        <v>57.69</v>
       </c>
       <c r="H57" s="2">
-        <v>54.4</v>
+        <v>55.6</v>
       </c>
       <c r="I57" s="2">
-        <v>62.4</v>
+        <v>60</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>260</v>
@@ -3114,28 +3027,28 @@
         <v>65</v>
       </c>
       <c r="B58" s="1">
-        <v>1568.3</v>
+        <v>560.55</v>
       </c>
       <c r="C58" s="2">
-        <v>-0.22</v>
+        <v>13.68</v>
       </c>
       <c r="D58" s="2">
-        <v>-1.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E58" s="2">
-        <v>3.43</v>
+        <v>11.21</v>
       </c>
       <c r="F58" s="2">
-        <v>34.88</v>
+        <v>56.92</v>
       </c>
       <c r="G58" s="2">
-        <v>11.6</v>
+        <v>24.14</v>
       </c>
       <c r="H58" s="2">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="I58" s="2">
-        <v>3.6</v>
+        <v>19.2</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>260</v>
@@ -3146,28 +3059,28 @@
         <v>66</v>
       </c>
       <c r="B59" s="1">
-        <v>127.4</v>
+        <v>870.5</v>
       </c>
       <c r="C59" s="2">
-        <v>11.77</v>
+        <v>29.63</v>
       </c>
       <c r="D59" s="2">
-        <v>-2.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="E59" s="2">
-        <v>-2.41</v>
+        <v>2.96</v>
       </c>
       <c r="F59" s="2">
-        <v>33.72</v>
+        <v>56.15</v>
       </c>
       <c r="G59" s="2">
-        <v>30</v>
+        <v>44.83</v>
       </c>
       <c r="H59" s="2">
-        <v>26.4</v>
+        <v>53.2</v>
       </c>
       <c r="I59" s="2">
-        <v>37.6</v>
+        <v>51.2</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>260</v>
@@ -3178,28 +3091,28 @@
         <v>67</v>
       </c>
       <c r="B60" s="1">
-        <v>252</v>
+        <v>213.21</v>
       </c>
       <c r="C60" s="2">
-        <v>33.49</v>
+        <v>71.86</v>
       </c>
       <c r="D60" s="2">
-        <v>-3.43</v>
+        <v>8.58</v>
       </c>
       <c r="E60" s="2">
-        <v>-13.06</v>
+        <v>-17.81</v>
       </c>
       <c r="F60" s="2">
-        <v>32.56</v>
+        <v>55.38</v>
       </c>
       <c r="G60" s="2">
-        <v>51.6</v>
+        <v>50.57</v>
       </c>
       <c r="H60" s="2">
-        <v>73.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I60" s="2">
-        <v>82.8</v>
+        <v>94</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>260</v>
@@ -3210,28 +3123,28 @@
         <v>68</v>
       </c>
       <c r="B61" s="1">
-        <v>556.8</v>
+        <v>642.85</v>
       </c>
       <c r="C61" s="2">
-        <v>1.87</v>
+        <v>12.98</v>
       </c>
       <c r="D61" s="2">
-        <v>-0.79</v>
+        <v>16.52</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.08</v>
+        <v>7.44</v>
       </c>
       <c r="F61" s="2">
-        <v>31.4</v>
+        <v>54.62</v>
       </c>
       <c r="G61" s="2">
-        <v>37.2</v>
+        <v>73.56</v>
       </c>
       <c r="H61" s="2">
-        <v>26.8</v>
+        <v>81.2</v>
       </c>
       <c r="I61" s="2">
-        <v>16.8</v>
+        <v>43.2</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>260</v>
@@ -3242,28 +3155,25 @@
         <v>69</v>
       </c>
       <c r="B62" s="1">
-        <v>115.47</v>
+        <v>168.44</v>
       </c>
       <c r="C62" s="2">
-        <v>11.29</v>
+        <v>30.65</v>
       </c>
       <c r="D62" s="2">
-        <v>3.14</v>
+        <v>24.35</v>
       </c>
       <c r="E62" s="2">
-        <v>-8.44</v>
+        <v>-5.65</v>
       </c>
       <c r="F62" s="2">
-        <v>30.23</v>
-      </c>
-      <c r="G62" s="2">
-        <v>38.4</v>
+        <v>53.85</v>
       </c>
       <c r="H62" s="2">
-        <v>25.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I62" s="2">
-        <v>44</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>260</v>
@@ -3274,28 +3184,28 @@
         <v>70</v>
       </c>
       <c r="B63" s="1">
-        <v>855.9</v>
+        <v>63.04</v>
       </c>
       <c r="C63" s="2">
-        <v>7.62</v>
+        <v>44.92</v>
       </c>
       <c r="D63" s="2">
-        <v>4.74</v>
+        <v>9.44</v>
       </c>
       <c r="E63" s="2">
-        <v>-8.43</v>
+        <v>-5.81</v>
       </c>
       <c r="F63" s="2">
-        <v>29.07</v>
+        <v>53.08</v>
       </c>
       <c r="G63" s="2">
-        <v>33.6</v>
+        <v>54.02</v>
       </c>
       <c r="H63" s="2">
-        <v>45.6</v>
+        <v>38.8</v>
       </c>
       <c r="I63" s="2">
-        <v>65.2</v>
+        <v>37.2</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>260</v>
@@ -3306,28 +3216,25 @@
         <v>71</v>
       </c>
       <c r="B64" s="1">
-        <v>203.96</v>
+        <v>5275</v>
       </c>
       <c r="C64" s="2">
-        <v>25.34</v>
+        <v>49.27</v>
       </c>
       <c r="D64" s="2">
-        <v>3.51</v>
+        <v>23.47</v>
       </c>
       <c r="E64" s="2">
-        <v>-16.79</v>
+        <v>-15.13</v>
       </c>
       <c r="F64" s="2">
-        <v>27.91</v>
-      </c>
-      <c r="G64" s="2">
-        <v>31.6</v>
+        <v>52.31</v>
       </c>
       <c r="H64" s="2">
-        <v>46.8</v>
+        <v>98.8</v>
       </c>
       <c r="I64" s="2">
-        <v>70.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>260</v>
@@ -3338,28 +3245,28 @@
         <v>72</v>
       </c>
       <c r="B65" s="1">
-        <v>502.95</v>
+        <v>139.99</v>
       </c>
       <c r="C65" s="2">
-        <v>0.98</v>
+        <v>15.62</v>
       </c>
       <c r="D65" s="2">
-        <v>-1.47</v>
+        <v>8.6</v>
       </c>
       <c r="E65" s="2">
-        <v>-3.32</v>
+        <v>8.5</v>
       </c>
       <c r="F65" s="2">
-        <v>26.74</v>
+        <v>51.54</v>
       </c>
       <c r="G65" s="2">
-        <v>12</v>
+        <v>17.24</v>
       </c>
       <c r="H65" s="2">
-        <v>18.8</v>
+        <v>14.4</v>
       </c>
       <c r="I65" s="2">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>260</v>
@@ -3370,28 +3277,25 @@
         <v>73</v>
       </c>
       <c r="B66" s="1">
-        <v>121.09</v>
+        <v>378.65</v>
       </c>
       <c r="C66" s="2">
-        <v>9.52</v>
+        <v>23.14</v>
       </c>
       <c r="D66" s="2">
-        <v>-1.77</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E66" s="2">
-        <v>-7.53</v>
+        <v>3.94</v>
       </c>
       <c r="F66" s="2">
-        <v>25.58</v>
-      </c>
-      <c r="G66" s="2">
-        <v>20.8</v>
+        <v>50.77</v>
       </c>
       <c r="H66" s="2">
-        <v>16.8</v>
+        <v>44</v>
       </c>
       <c r="I66" s="2">
-        <v>24.8</v>
+        <v>30.8</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>260</v>
@@ -3402,28 +3306,25 @@
         <v>74</v>
       </c>
       <c r="B67" s="1">
-        <v>497.35</v>
+        <v>828.7</v>
       </c>
       <c r="C67" s="2">
-        <v>4.23</v>
+        <v>21.58</v>
       </c>
       <c r="D67" s="2">
-        <v>-4.74</v>
+        <v>16.69</v>
       </c>
       <c r="E67" s="2">
-        <v>-3.59</v>
+        <v>0.85</v>
       </c>
       <c r="F67" s="2">
-        <v>24.42</v>
-      </c>
-      <c r="G67" s="2">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="I67" s="2">
-        <v>22.8</v>
+        <v>38.8</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>260</v>
@@ -3434,28 +3335,25 @@
         <v>75</v>
       </c>
       <c r="B68" s="1">
-        <v>31.34</v>
+        <v>6062</v>
       </c>
       <c r="C68" s="2">
-        <v>14.09</v>
+        <v>31.1</v>
       </c>
       <c r="D68" s="2">
-        <v>-10.35</v>
+        <v>9.85</v>
       </c>
       <c r="E68" s="2">
-        <v>-5.94</v>
+        <v>-1.39</v>
       </c>
       <c r="F68" s="2">
-        <v>23.26</v>
-      </c>
-      <c r="G68" s="2">
-        <v>38</v>
+        <v>49.23</v>
       </c>
       <c r="H68" s="2">
-        <v>22</v>
+        <v>53.6</v>
       </c>
       <c r="I68" s="2">
-        <v>29.6</v>
+        <v>48</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>260</v>
@@ -3466,28 +3364,25 @@
         <v>76</v>
       </c>
       <c r="B69" s="1">
-        <v>281.05</v>
+        <v>139.97</v>
       </c>
       <c r="C69" s="2">
-        <v>-2.97</v>
+        <v>24.37</v>
       </c>
       <c r="D69" s="2">
-        <v>-7.17</v>
+        <v>2.29</v>
       </c>
       <c r="E69" s="2">
-        <v>0.48</v>
+        <v>4.13</v>
       </c>
       <c r="F69" s="2">
-        <v>22.09</v>
-      </c>
-      <c r="G69" s="2">
-        <v>6</v>
+        <v>48.46</v>
       </c>
       <c r="H69" s="2">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="I69" s="2">
-        <v>5.6</v>
+        <v>46</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>260</v>
@@ -3498,28 +3393,25 @@
         <v>77</v>
       </c>
       <c r="B70" s="1">
-        <v>1482.4</v>
+        <v>387.05</v>
       </c>
       <c r="C70" s="2">
-        <v>38.85</v>
+        <v>17.38</v>
       </c>
       <c r="D70" s="2">
-        <v>-10.28</v>
+        <v>7.01</v>
       </c>
       <c r="E70" s="2">
-        <v>-19.81</v>
+        <v>4.88</v>
       </c>
       <c r="F70" s="2">
-        <v>20.93</v>
-      </c>
-      <c r="G70" s="2">
-        <v>30.8</v>
+        <v>47.69</v>
       </c>
       <c r="H70" s="2">
-        <v>56.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I70" s="2">
-        <v>81.2</v>
+        <v>48.8</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>260</v>
@@ -3530,28 +3422,28 @@
         <v>78</v>
       </c>
       <c r="B71" s="1">
-        <v>440.35</v>
+        <v>1472.2</v>
       </c>
       <c r="C71" s="2">
-        <v>3.24</v>
+        <v>17.71</v>
       </c>
       <c r="D71" s="2">
-        <v>-5.65</v>
+        <v>4.85</v>
       </c>
       <c r="E71" s="2">
-        <v>-4.34</v>
+        <v>5.74</v>
       </c>
       <c r="F71" s="2">
-        <v>19.77</v>
+        <v>46.92</v>
       </c>
       <c r="G71" s="2">
-        <v>13.2</v>
+        <v>52.87</v>
       </c>
       <c r="H71" s="2">
-        <v>14.8</v>
+        <v>35.6</v>
       </c>
       <c r="I71" s="2">
-        <v>19.6</v>
+        <v>28</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>260</v>
@@ -3562,28 +3454,25 @@
         <v>79</v>
       </c>
       <c r="B72" s="1">
-        <v>99.16</v>
+        <v>9965</v>
       </c>
       <c r="C72" s="2">
-        <v>-1.52</v>
+        <v>9.84</v>
       </c>
       <c r="D72" s="2">
-        <v>-7.84</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E72" s="2">
-        <v>-1.02</v>
+        <v>6.36</v>
       </c>
       <c r="F72" s="2">
-        <v>18.6</v>
-      </c>
-      <c r="G72" s="2">
-        <v>10</v>
+        <v>46.15</v>
       </c>
       <c r="H72" s="2">
-        <v>12.8</v>
+        <v>26</v>
       </c>
       <c r="I72" s="2">
-        <v>5.2</v>
+        <v>27.6</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>260</v>
@@ -3594,28 +3483,25 @@
         <v>80</v>
       </c>
       <c r="B73" s="1">
-        <v>121.85</v>
+        <v>192.62</v>
       </c>
       <c r="C73" s="2">
-        <v>8.1</v>
+        <v>17.38</v>
       </c>
       <c r="D73" s="2">
-        <v>-8.619999999999999</v>
+        <v>11.09</v>
       </c>
       <c r="E73" s="2">
-        <v>-6.07</v>
+        <v>0.2</v>
       </c>
       <c r="F73" s="2">
-        <v>17.44</v>
-      </c>
-      <c r="G73" s="2">
-        <v>14.4</v>
+        <v>45.38</v>
       </c>
       <c r="H73" s="2">
-        <v>8.800000000000001</v>
+        <v>43.6</v>
       </c>
       <c r="I73" s="2">
-        <v>32.4</v>
+        <v>52.8</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>260</v>
@@ -3626,28 +3512,25 @@
         <v>81</v>
       </c>
       <c r="B74" s="1">
-        <v>755.5</v>
+        <v>75.22</v>
       </c>
       <c r="C74" s="2">
-        <v>56.69</v>
+        <v>38.65</v>
       </c>
       <c r="D74" s="2">
-        <v>-22.6</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E74" s="2">
-        <v>-23.78</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="F74" s="2">
-        <v>16.28</v>
-      </c>
-      <c r="G74" s="2">
-        <v>34.4</v>
+        <v>44.62</v>
       </c>
       <c r="H74" s="2">
-        <v>62.8</v>
+        <v>77.2</v>
       </c>
       <c r="I74" s="2">
-        <v>84.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>260</v>
@@ -3658,28 +3541,25 @@
         <v>82</v>
       </c>
       <c r="B75" s="1">
-        <v>195.13</v>
+        <v>17.17</v>
       </c>
       <c r="C75" s="2">
-        <v>2.92</v>
+        <v>16.33</v>
       </c>
       <c r="D75" s="2">
-        <v>-12.88</v>
+        <v>22.99</v>
       </c>
       <c r="E75" s="2">
-        <v>-2.06</v>
+        <v>-5.71</v>
       </c>
       <c r="F75" s="2">
-        <v>15.12</v>
-      </c>
-      <c r="G75" s="2">
-        <v>4.4</v>
+        <v>43.85</v>
       </c>
       <c r="H75" s="2">
-        <v>1.2</v>
+        <v>54.8</v>
       </c>
       <c r="I75" s="2">
-        <v>4.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>260</v>
@@ -3690,28 +3570,25 @@
         <v>83</v>
       </c>
       <c r="B76" s="1">
-        <v>564.65</v>
+        <v>598.1</v>
       </c>
       <c r="C76" s="2">
-        <v>-4.49</v>
+        <v>-1.4</v>
       </c>
       <c r="D76" s="2">
-        <v>-7.08</v>
+        <v>21.52</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.42</v>
+        <v>3.04</v>
       </c>
       <c r="F76" s="2">
-        <v>13.95</v>
-      </c>
-      <c r="G76" s="2">
-        <v>10.4</v>
+        <v>43.08</v>
       </c>
       <c r="H76" s="2">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="I76" s="2">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>260</v>
@@ -3722,28 +3599,25 @@
         <v>84</v>
       </c>
       <c r="B77" s="1">
-        <v>2753</v>
+        <v>865.15</v>
       </c>
       <c r="C77" s="2">
-        <v>7.18</v>
+        <v>22.65</v>
       </c>
       <c r="D77" s="2">
-        <v>-9.67</v>
+        <v>8.06</v>
       </c>
       <c r="E77" s="2">
-        <v>-8.41</v>
+        <v>-3.48</v>
       </c>
       <c r="F77" s="2">
-        <v>12.79</v>
-      </c>
-      <c r="G77" s="2">
-        <v>25.2</v>
+        <v>42.31</v>
       </c>
       <c r="H77" s="2">
-        <v>18.4</v>
+        <v>58</v>
       </c>
       <c r="I77" s="2">
-        <v>20</v>
+        <v>65.2</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>260</v>
@@ -3754,28 +3628,28 @@
         <v>85</v>
       </c>
       <c r="B78" s="1">
-        <v>302.3</v>
+        <v>9.77</v>
       </c>
       <c r="C78" s="2">
-        <v>1.41</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2">
-        <v>-0.44</v>
+        <v>5.74</v>
       </c>
       <c r="E78" s="2">
-        <v>-10.8</v>
+        <v>-1.51</v>
       </c>
       <c r="F78" s="2">
-        <v>11.63</v>
+        <v>41.54</v>
       </c>
       <c r="G78" s="2">
-        <v>24.4</v>
+        <v>41.38</v>
       </c>
       <c r="H78" s="2">
-        <v>17.2</v>
+        <v>61.2</v>
       </c>
       <c r="I78" s="2">
-        <v>27.2</v>
+        <v>62.4</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>260</v>
@@ -3786,28 +3660,25 @@
         <v>86</v>
       </c>
       <c r="B79" s="1">
-        <v>263.7</v>
+        <v>1124.1</v>
       </c>
       <c r="C79" s="2">
-        <v>-2.64</v>
+        <v>28.96</v>
       </c>
       <c r="D79" s="2">
-        <v>-15.09</v>
+        <v>7.31</v>
       </c>
       <c r="E79" s="2">
-        <v>-2.24</v>
+        <v>-7.66</v>
       </c>
       <c r="F79" s="2">
-        <v>10.47</v>
-      </c>
-      <c r="G79" s="2">
-        <v>7.2</v>
+        <v>40.77</v>
       </c>
       <c r="H79" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I79" s="2">
-        <v>0.8</v>
+        <v>44.4</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>260</v>
@@ -3818,28 +3689,25 @@
         <v>87</v>
       </c>
       <c r="B80" s="1">
-        <v>1479.6</v>
+        <v>130.78</v>
       </c>
       <c r="C80" s="2">
-        <v>2.3</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D80" s="2">
-        <v>-9.75</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E80" s="2">
-        <v>-7.88</v>
+        <v>5.71</v>
       </c>
       <c r="F80" s="2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G80" s="2">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="H80" s="2">
-        <v>4.8</v>
+        <v>48.4</v>
       </c>
       <c r="I80" s="2">
-        <v>14.8</v>
+        <v>2.8</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>260</v>
@@ -3850,28 +3718,25 @@
         <v>88</v>
       </c>
       <c r="B81" s="1">
-        <v>11.92</v>
+        <v>262.1</v>
       </c>
       <c r="C81" s="2">
-        <v>-5.62</v>
+        <v>14.3</v>
       </c>
       <c r="D81" s="2">
-        <v>-5.47</v>
+        <v>6.13</v>
       </c>
       <c r="E81" s="2">
-        <v>-7.81</v>
+        <v>-0.21</v>
       </c>
       <c r="F81" s="2">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G81" s="2">
-        <v>11.2</v>
+        <v>39.23</v>
       </c>
       <c r="H81" s="2">
-        <v>7.2</v>
+        <v>58.4</v>
       </c>
       <c r="I81" s="2">
-        <v>11.6</v>
+        <v>52.4</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>260</v>
@@ -3882,28 +3747,28 @@
         <v>89</v>
       </c>
       <c r="B82" s="1">
-        <v>21.87</v>
+        <v>104.13</v>
       </c>
       <c r="C82" s="2">
-        <v>-10</v>
+        <v>8.81</v>
       </c>
       <c r="D82" s="2">
-        <v>-7.57</v>
+        <v>10.86</v>
       </c>
       <c r="E82" s="2">
-        <v>-5.24</v>
+        <v>-0.29</v>
       </c>
       <c r="F82" s="2">
-        <v>6.98</v>
+        <v>38.46</v>
       </c>
       <c r="G82" s="2">
-        <v>21.2</v>
+        <v>43.68</v>
       </c>
       <c r="H82" s="2">
-        <v>8.4</v>
+        <v>27.2</v>
       </c>
       <c r="I82" s="2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>260</v>
@@ -3914,28 +3779,25 @@
         <v>90</v>
       </c>
       <c r="B83" s="1">
-        <v>70.65000000000001</v>
+        <v>2257.2</v>
       </c>
       <c r="C83" s="2">
-        <v>-5.7</v>
+        <v>23.38</v>
       </c>
       <c r="D83" s="2">
-        <v>-14.23</v>
+        <v>0.92</v>
       </c>
       <c r="E83" s="2">
-        <v>-8.91</v>
+        <v>-2.61</v>
       </c>
       <c r="F83" s="2">
-        <v>5.81</v>
-      </c>
-      <c r="G83" s="2">
-        <v>19.2</v>
+        <v>37.69</v>
       </c>
       <c r="H83" s="2">
-        <v>20</v>
+        <v>66.8</v>
       </c>
       <c r="I83" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>260</v>
@@ -3946,28 +3808,25 @@
         <v>91</v>
       </c>
       <c r="B84" s="1">
-        <v>311.9</v>
+        <v>224.38</v>
       </c>
       <c r="C84" s="2">
-        <v>-0.22</v>
+        <v>28.96</v>
       </c>
       <c r="D84" s="2">
-        <v>-20.77</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E84" s="2">
-        <v>-14.78</v>
+        <v>-9.33</v>
       </c>
       <c r="F84" s="2">
-        <v>4.65</v>
-      </c>
-      <c r="G84" s="2">
-        <v>14.8</v>
+        <v>36.92</v>
       </c>
       <c r="H84" s="2">
-        <v>34.4</v>
+        <v>67.2</v>
       </c>
       <c r="I84" s="2">
-        <v>38.8</v>
+        <v>66.8</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>260</v>
@@ -3978,28 +3837,25 @@
         <v>92</v>
       </c>
       <c r="B85" s="1">
-        <v>57.71</v>
+        <v>179.43</v>
       </c>
       <c r="C85" s="2">
-        <v>-0.91</v>
+        <v>24.1</v>
       </c>
       <c r="D85" s="2">
-        <v>-20.83</v>
+        <v>5.95</v>
       </c>
       <c r="E85" s="2">
-        <v>-17.27</v>
+        <v>-5.85</v>
       </c>
       <c r="F85" s="2">
-        <v>3.49</v>
-      </c>
-      <c r="G85" s="2">
-        <v>1.2</v>
+        <v>36.15</v>
       </c>
       <c r="H85" s="2">
-        <v>3.6</v>
+        <v>57.6</v>
       </c>
       <c r="I85" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>260</v>
@@ -4010,28 +3866,28 @@
         <v>93</v>
       </c>
       <c r="B86" s="1">
-        <v>899.6</v>
+        <v>198.85</v>
       </c>
       <c r="C86" s="2">
-        <v>-23.67</v>
+        <v>51.82</v>
       </c>
       <c r="D86" s="2">
-        <v>-33.2</v>
+        <v>11.07</v>
       </c>
       <c r="E86" s="2">
-        <v>-5.05</v>
+        <v>-23.53</v>
       </c>
       <c r="F86" s="2">
-        <v>2.33</v>
+        <v>35.38</v>
       </c>
       <c r="G86" s="2">
-        <v>2.8</v>
+        <v>89.66</v>
       </c>
       <c r="H86" s="2">
-        <v>12.4</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I86" s="2">
-        <v>0.4</v>
+        <v>95.2</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>260</v>
@@ -4042,28 +3898,25 @@
         <v>94</v>
       </c>
       <c r="B87" s="1">
-        <v>221.5</v>
+        <v>677.4</v>
       </c>
       <c r="C87" s="2">
-        <v>-40.18</v>
+        <v>36</v>
       </c>
       <c r="D87" s="2">
-        <v>-41.3</v>
+        <v>11.84</v>
       </c>
       <c r="E87" s="2">
-        <v>-52.2</v>
+        <v>-16.05</v>
       </c>
       <c r="F87" s="2">
-        <v>1.16</v>
-      </c>
-      <c r="G87" s="2">
-        <v>0.4</v>
+        <v>34.62</v>
       </c>
       <c r="H87" s="2">
-        <v>80.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I87" s="2">
-        <v>70.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>260</v>
@@ -4073,14 +3926,26 @@
       <c r="A88" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G88" s="2">
-        <v>7.6</v>
+      <c r="B88" s="1">
+        <v>407.7</v>
+      </c>
+      <c r="C88" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="D88" s="2">
+        <v>8.65</v>
+      </c>
+      <c r="E88" s="2">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>33.85</v>
       </c>
       <c r="H88" s="2">
-        <v>16</v>
+        <v>50.8</v>
       </c>
       <c r="I88" s="2">
-        <v>21.2</v>
+        <v>48.4</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>260</v>
@@ -4090,14 +3955,26 @@
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G89" s="2">
-        <v>34</v>
+      <c r="B89" s="1">
+        <v>138.04</v>
+      </c>
+      <c r="C89" s="2">
+        <v>17.04</v>
+      </c>
+      <c r="D89" s="2">
+        <v>-1.08</v>
+      </c>
+      <c r="E89" s="2">
+        <v>-1.26</v>
+      </c>
+      <c r="F89" s="2">
+        <v>33.08</v>
       </c>
       <c r="H89" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I89" s="2">
-        <v>45.6</v>
+        <v>22.8</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>260</v>
@@ -4107,14 +3984,26 @@
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G90" s="2">
-        <v>100</v>
+      <c r="B90" s="1">
+        <v>548.65</v>
+      </c>
+      <c r="C90" s="2">
+        <v>32.3</v>
+      </c>
+      <c r="D90" s="2">
+        <v>11.53</v>
+      </c>
+      <c r="E90" s="2">
+        <v>-15.24</v>
+      </c>
+      <c r="F90" s="2">
+        <v>32.31</v>
       </c>
       <c r="H90" s="2">
-        <v>100</v>
+        <v>65.2</v>
       </c>
       <c r="I90" s="2">
-        <v>100</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>260</v>
@@ -4124,14 +4013,26 @@
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G91" s="2">
-        <v>26.8</v>
+      <c r="B91" s="1">
+        <v>292.9</v>
+      </c>
+      <c r="C91" s="2">
+        <v>44</v>
+      </c>
+      <c r="D91" s="2">
+        <v>-4.51</v>
+      </c>
+      <c r="E91" s="2">
+        <v>-13.18</v>
+      </c>
+      <c r="F91" s="2">
+        <v>31.54</v>
       </c>
       <c r="H91" s="2">
-        <v>34.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I91" s="2">
-        <v>83.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>260</v>
@@ -4141,14 +4042,26 @@
       <c r="A92" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G92" s="2">
-        <v>98.8</v>
+      <c r="B92" s="1">
+        <v>96.38</v>
+      </c>
+      <c r="C92" s="2">
+        <v>26.22</v>
+      </c>
+      <c r="D92" s="2">
+        <v>-10.01</v>
+      </c>
+      <c r="E92" s="2">
+        <v>-3.3</v>
+      </c>
+      <c r="F92" s="2">
+        <v>30.77</v>
       </c>
       <c r="H92" s="2">
-        <v>98.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="I92" s="2">
-        <v>95.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>260</v>
@@ -4158,14 +4071,26 @@
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G93" s="2">
-        <v>92.40000000000001</v>
+      <c r="B93" s="1">
+        <v>92.37</v>
+      </c>
+      <c r="C93" s="2">
+        <v>16.94</v>
+      </c>
+      <c r="D93" s="2">
+        <v>-6.56</v>
+      </c>
+      <c r="E93" s="2">
+        <v>-1.66</v>
+      </c>
+      <c r="F93" s="2">
+        <v>30</v>
       </c>
       <c r="H93" s="2">
-        <v>80.8</v>
+        <v>37.6</v>
       </c>
       <c r="I93" s="2">
-        <v>82</v>
+        <v>40.8</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>260</v>
@@ -4175,14 +4100,29 @@
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="B94" s="1">
+        <v>205.37</v>
+      </c>
+      <c r="C94" s="2">
+        <v>12.21</v>
+      </c>
+      <c r="D94" s="2">
+        <v>-9.23</v>
+      </c>
+      <c r="E94" s="2">
+        <v>1.04</v>
+      </c>
+      <c r="F94" s="2">
+        <v>29.23</v>
+      </c>
       <c r="G94" s="2">
-        <v>25.6</v>
+        <v>39.08</v>
       </c>
       <c r="H94" s="2">
-        <v>37.6</v>
+        <v>12.4</v>
       </c>
       <c r="I94" s="2">
-        <v>39.2</v>
+        <v>6.4</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>260</v>
@@ -4192,14 +4132,26 @@
       <c r="A95" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G95" s="2">
-        <v>90</v>
+      <c r="B95" s="1">
+        <v>685.85</v>
+      </c>
+      <c r="C95" s="2">
+        <v>6.23</v>
+      </c>
+      <c r="D95" s="2">
+        <v>6.77</v>
+      </c>
+      <c r="E95" s="2">
+        <v>-4.45</v>
+      </c>
+      <c r="F95" s="2">
+        <v>28.46</v>
       </c>
       <c r="H95" s="2">
-        <v>92</v>
+        <v>32.8</v>
       </c>
       <c r="I95" s="2">
-        <v>92.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>260</v>
@@ -4209,14 +4161,26 @@
       <c r="A96" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G96" s="2">
-        <v>58.8</v>
+      <c r="B96" s="1">
+        <v>161.22</v>
+      </c>
+      <c r="C96" s="2">
+        <v>6.14</v>
+      </c>
+      <c r="D96" s="2">
+        <v>-1.63</v>
+      </c>
+      <c r="E96" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="F96" s="2">
+        <v>27.69</v>
       </c>
       <c r="H96" s="2">
-        <v>60.4</v>
+        <v>13.6</v>
       </c>
       <c r="I96" s="2">
-        <v>62</v>
+        <v>19.6</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>260</v>
@@ -4226,14 +4190,26 @@
       <c r="A97" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G97" s="2">
-        <v>64.8</v>
+      <c r="B97" s="1">
+        <v>645.35</v>
+      </c>
+      <c r="C97" s="2">
+        <v>22.11</v>
+      </c>
+      <c r="D97" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="E97" s="2">
+        <v>-9.58</v>
+      </c>
+      <c r="F97" s="2">
+        <v>26.92</v>
       </c>
       <c r="H97" s="2">
-        <v>55.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I97" s="2">
-        <v>54.4</v>
+        <v>63.6</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>260</v>
@@ -4243,14 +4219,29 @@
       <c r="A98" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="B98" s="1">
+        <v>20.52</v>
+      </c>
+      <c r="C98" s="2">
+        <v>33.25</v>
+      </c>
+      <c r="D98" s="2">
+        <v>-7.94</v>
+      </c>
+      <c r="E98" s="2">
+        <v>-13.67</v>
+      </c>
+      <c r="F98" s="2">
+        <v>26.15</v>
+      </c>
       <c r="G98" s="2">
-        <v>88.8</v>
+        <v>42.53</v>
       </c>
       <c r="H98" s="2">
-        <v>30</v>
+        <v>40.4</v>
       </c>
       <c r="I98" s="2">
-        <v>39.6</v>
+        <v>32.4</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>260</v>
@@ -4260,14 +4251,26 @@
       <c r="A99" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G99" s="2">
-        <v>85.2</v>
+      <c r="B99" s="1">
+        <v>151.63</v>
+      </c>
+      <c r="C99" s="2">
+        <v>4.16</v>
+      </c>
+      <c r="D99" s="2">
+        <v>-3.04</v>
+      </c>
+      <c r="E99" s="2">
+        <v>-2.53</v>
+      </c>
+      <c r="F99" s="2">
+        <v>25.38</v>
       </c>
       <c r="H99" s="2">
-        <v>88</v>
+        <v>22.8</v>
       </c>
       <c r="I99" s="2">
-        <v>94</v>
+        <v>21.2</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>260</v>
@@ -4277,14 +4280,26 @@
       <c r="A100" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="2">
-        <v>26.4</v>
+      <c r="B100" s="1">
+        <v>149.59</v>
+      </c>
+      <c r="C100" s="2">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D100" s="2">
+        <v>-4.51</v>
+      </c>
+      <c r="E100" s="2">
+        <v>-4.87</v>
+      </c>
+      <c r="F100" s="2">
+        <v>24.62</v>
       </c>
       <c r="H100" s="2">
-        <v>44.8</v>
+        <v>46.8</v>
       </c>
       <c r="I100" s="2">
-        <v>48.4</v>
+        <v>64</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>260</v>
@@ -4294,14 +4309,26 @@
       <c r="A101" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G101" s="2">
-        <v>75.2</v>
+      <c r="B101" s="1">
+        <v>373.15</v>
+      </c>
+      <c r="C101" s="2">
+        <v>-7.35</v>
+      </c>
+      <c r="D101" s="2">
+        <v>-2.67</v>
+      </c>
+      <c r="E101" s="2">
+        <v>2.42</v>
+      </c>
+      <c r="F101" s="2">
+        <v>23.85</v>
       </c>
       <c r="H101" s="2">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="I101" s="2">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>260</v>
@@ -4311,14 +4338,26 @@
       <c r="A102" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G102" s="2">
-        <v>84.8</v>
+      <c r="B102" s="1">
+        <v>450.55</v>
+      </c>
+      <c r="C102" s="2">
+        <v>-2.76</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="E102" s="2">
+        <v>-2.01</v>
+      </c>
+      <c r="F102" s="2">
+        <v>23.08</v>
       </c>
       <c r="H102" s="2">
-        <v>78.8</v>
+        <v>15.6</v>
       </c>
       <c r="I102" s="2">
-        <v>61.2</v>
+        <v>21.6</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>260</v>
@@ -4328,14 +4367,26 @@
       <c r="A103" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G103" s="2">
-        <v>50.4</v>
+      <c r="B103" s="1">
+        <v>436.05</v>
+      </c>
+      <c r="C103" s="2">
+        <v>-1.41</v>
+      </c>
+      <c r="D103" s="2">
+        <v>-2.59</v>
+      </c>
+      <c r="E103" s="2">
+        <v>-2.17</v>
+      </c>
+      <c r="F103" s="2">
+        <v>22.31</v>
       </c>
       <c r="H103" s="2">
-        <v>65.59999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="I103" s="2">
-        <v>60.8</v>
+        <v>22.4</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>260</v>
@@ -4345,14 +4396,26 @@
       <c r="A104" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G104" s="2">
-        <v>82.40000000000001</v>
+      <c r="B104" s="1">
+        <v>164.43</v>
+      </c>
+      <c r="C104" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="D104" s="2">
+        <v>-7.61</v>
+      </c>
+      <c r="E104" s="2">
+        <v>-2.45</v>
+      </c>
+      <c r="F104" s="2">
+        <v>21.54</v>
       </c>
       <c r="H104" s="2">
-        <v>92.40000000000001</v>
+        <v>14</v>
       </c>
       <c r="I104" s="2">
-        <v>92.8</v>
+        <v>6.8</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>260</v>
@@ -4362,14 +4425,29 @@
       <c r="A105" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="B105" s="1">
+        <v>278.15</v>
+      </c>
+      <c r="C105" s="2">
+        <v>-5.13</v>
+      </c>
+      <c r="D105" s="2">
+        <v>-6.19</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="F105" s="2">
+        <v>20.77</v>
+      </c>
       <c r="G105" s="2">
-        <v>86.8</v>
+        <v>21.84</v>
       </c>
       <c r="H105" s="2">
-        <v>77.59999999999999</v>
+        <v>6</v>
       </c>
       <c r="I105" s="2">
-        <v>56.8</v>
+        <v>9.6</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>260</v>
@@ -4379,14 +4457,26 @@
       <c r="A106" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G106" s="2">
-        <v>70.8</v>
+      <c r="B106" s="1">
+        <v>8.68</v>
+      </c>
+      <c r="C106" s="2">
+        <v>5.08</v>
+      </c>
+      <c r="D106" s="2">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E106" s="2">
+        <v>-3.77</v>
+      </c>
+      <c r="F106" s="2">
+        <v>20</v>
       </c>
       <c r="H106" s="2">
-        <v>58</v>
+        <v>23.2</v>
       </c>
       <c r="I106" s="2">
-        <v>31.6</v>
+        <v>20.4</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>260</v>
@@ -4396,14 +4486,29 @@
       <c r="A107" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="B107" s="1">
+        <v>542.85</v>
+      </c>
+      <c r="C107" s="2">
+        <v>-2.86</v>
+      </c>
+      <c r="D107" s="2">
+        <v>-4.13</v>
+      </c>
+      <c r="E107" s="2">
+        <v>-2.12</v>
+      </c>
+      <c r="F107" s="2">
+        <v>19.23</v>
+      </c>
       <c r="G107" s="2">
-        <v>50.8</v>
+        <v>31.03</v>
       </c>
       <c r="H107" s="2">
-        <v>48.4</v>
+        <v>37.2</v>
       </c>
       <c r="I107" s="2">
-        <v>57.2</v>
+        <v>26.8</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>260</v>
@@ -4413,14 +4518,29 @@
       <c r="A108" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="B108" s="1">
+        <v>2772</v>
+      </c>
+      <c r="C108" s="2">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="D108" s="2">
+        <v>-9.26</v>
+      </c>
+      <c r="E108" s="2">
+        <v>-5.05</v>
+      </c>
+      <c r="F108" s="2">
+        <v>18.46</v>
+      </c>
       <c r="G108" s="2">
+        <v>12.64</v>
+      </c>
+      <c r="H108" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="I108" s="2">
         <v>18.4</v>
-      </c>
-      <c r="H108" s="2">
-        <v>24.4</v>
-      </c>
-      <c r="I108" s="2">
-        <v>32</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>260</v>
@@ -4430,14 +4550,26 @@
       <c r="A109" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G109" s="2">
-        <v>83.59999999999999</v>
+      <c r="B109" s="1">
+        <v>731.8</v>
+      </c>
+      <c r="C109" s="2">
+        <v>-5.88</v>
+      </c>
+      <c r="D109" s="2">
+        <v>-2.94</v>
+      </c>
+      <c r="E109" s="2">
+        <v>-1.42</v>
+      </c>
+      <c r="F109" s="2">
+        <v>17.69</v>
       </c>
       <c r="H109" s="2">
-        <v>79.2</v>
+        <v>4.8</v>
       </c>
       <c r="I109" s="2">
-        <v>62.8</v>
+        <v>4</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>260</v>
@@ -4447,14 +4579,26 @@
       <c r="A110" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G110" s="2">
-        <v>79.59999999999999</v>
+      <c r="B110" s="1">
+        <v>516.3</v>
+      </c>
+      <c r="C110" s="2">
+        <v>4.33</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E110" s="2">
+        <v>-9.74</v>
+      </c>
+      <c r="F110" s="2">
+        <v>16.92</v>
       </c>
       <c r="H110" s="2">
-        <v>74</v>
+        <v>40.8</v>
       </c>
       <c r="I110" s="2">
-        <v>59.2</v>
+        <v>41.6</v>
       </c>
       <c r="J110" s="4" t="s">
         <v>260</v>
@@ -4464,14 +4608,26 @@
       <c r="A111" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G111" s="2">
-        <v>57.6</v>
+      <c r="B111" s="1">
+        <v>1896</v>
+      </c>
+      <c r="C111" s="2">
+        <v>8.42</v>
+      </c>
+      <c r="D111" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="E111" s="2">
+        <v>-12.98</v>
+      </c>
+      <c r="F111" s="2">
+        <v>16.15</v>
       </c>
       <c r="H111" s="2">
-        <v>40</v>
+        <v>52.8</v>
       </c>
       <c r="I111" s="2">
-        <v>40.8</v>
+        <v>63.2</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>260</v>
@@ -4481,14 +4637,26 @@
       <c r="A112" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G112" s="2">
-        <v>71.59999999999999</v>
+      <c r="B112" s="1">
+        <v>1047.1</v>
+      </c>
+      <c r="C112" s="2">
+        <v>-1.33</v>
+      </c>
+      <c r="D112" s="2">
+        <v>-7.83</v>
+      </c>
+      <c r="E112" s="2">
+        <v>-2.93</v>
+      </c>
+      <c r="F112" s="2">
+        <v>15.38</v>
       </c>
       <c r="H112" s="2">
-        <v>68</v>
+        <v>15.2</v>
       </c>
       <c r="I112" s="2">
-        <v>87.59999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="J112" s="4" t="s">
         <v>260</v>
@@ -4498,14 +4666,26 @@
       <c r="A113" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G113" s="2">
-        <v>65.2</v>
+      <c r="B113" s="1">
+        <v>127.76</v>
+      </c>
+      <c r="C113" s="2">
+        <v>-13.24</v>
+      </c>
+      <c r="D113" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="E113" s="2">
+        <v>-3.97</v>
+      </c>
+      <c r="F113" s="2">
+        <v>14.62</v>
       </c>
       <c r="H113" s="2">
-        <v>72.40000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="I113" s="2">
-        <v>85.2</v>
+        <v>25.2</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>260</v>
@@ -4515,14 +4695,26 @@
       <c r="A114" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G114" s="2">
-        <v>59.6</v>
+      <c r="B114" s="1">
+        <v>1003.8</v>
+      </c>
+      <c r="C114" s="2">
+        <v>3.85</v>
+      </c>
+      <c r="D114" s="2">
+        <v>-7.82</v>
+      </c>
+      <c r="E114" s="2">
+        <v>-6.1</v>
+      </c>
+      <c r="F114" s="2">
+        <v>13.85</v>
       </c>
       <c r="H114" s="2">
-        <v>75.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="I114" s="2">
-        <v>71.2</v>
+        <v>42.4</v>
       </c>
       <c r="J114" s="4" t="s">
         <v>260</v>
@@ -4532,14 +4724,26 @@
       <c r="A115" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G115" s="2">
-        <v>60.4</v>
+      <c r="B115" s="1">
+        <v>29.56</v>
+      </c>
+      <c r="C115" s="2">
+        <v>-1.24</v>
+      </c>
+      <c r="D115" s="2">
+        <v>-1.99</v>
+      </c>
+      <c r="E115" s="2">
+        <v>-7.01</v>
+      </c>
+      <c r="F115" s="2">
+        <v>13.08</v>
       </c>
       <c r="H115" s="2">
-        <v>66</v>
+        <v>3.6</v>
       </c>
       <c r="I115" s="2">
-        <v>40.4</v>
+        <v>3.2</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>260</v>
@@ -4549,14 +4753,29 @@
       <c r="A116" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="B116" s="1">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="C116" s="2">
+        <v>-1.33</v>
+      </c>
+      <c r="D116" s="2">
+        <v>-11.32</v>
+      </c>
+      <c r="E116" s="2">
+        <v>-2.38</v>
+      </c>
+      <c r="F116" s="2">
+        <v>12.31</v>
+      </c>
       <c r="G116" s="2">
-        <v>61.6</v>
+        <v>18.39</v>
       </c>
       <c r="H116" s="2">
-        <v>32.8</v>
+        <v>10</v>
       </c>
       <c r="I116" s="2">
-        <v>46</v>
+        <v>12.8</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>260</v>
@@ -4566,14 +4785,29 @@
       <c r="A117" s="1" t="s">
         <v>124</v>
       </c>
+      <c r="B117" s="1">
+        <v>118.33</v>
+      </c>
+      <c r="C117" s="2">
+        <v>5.73</v>
+      </c>
+      <c r="D117" s="2">
+        <v>-2.87</v>
+      </c>
+      <c r="E117" s="2">
+        <v>-10.46</v>
+      </c>
+      <c r="F117" s="2">
+        <v>11.54</v>
+      </c>
       <c r="G117" s="2">
-        <v>62.4</v>
+        <v>25.29</v>
       </c>
       <c r="H117" s="2">
-        <v>70.40000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="I117" s="2">
-        <v>58.8</v>
+        <v>16.8</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>260</v>
@@ -4583,14 +4817,26 @@
       <c r="A118" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G118" s="2">
-        <v>73.2</v>
+      <c r="B118" s="1">
+        <v>176.25</v>
+      </c>
+      <c r="C118" s="2">
+        <v>5.79</v>
+      </c>
+      <c r="D118" s="2">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="E118" s="2">
+        <v>-16.24</v>
+      </c>
+      <c r="F118" s="2">
+        <v>10.77</v>
       </c>
       <c r="H118" s="2">
-        <v>58.4</v>
+        <v>45.2</v>
       </c>
       <c r="I118" s="2">
-        <v>44.4</v>
+        <v>68.8</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>260</v>
@@ -4600,14 +4846,26 @@
       <c r="A119" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G119" s="2">
-        <v>68.8</v>
+      <c r="B119" s="1">
+        <v>111.56</v>
+      </c>
+      <c r="C119" s="2">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="D119" s="2">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="E119" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="F119" s="2">
+        <v>10</v>
       </c>
       <c r="H119" s="2">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I119" s="2">
-        <v>66</v>
+        <v>2.4</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>260</v>
@@ -4617,14 +4875,29 @@
       <c r="A120" s="1" t="s">
         <v>127</v>
       </c>
+      <c r="B120" s="1">
+        <v>371.6</v>
+      </c>
+      <c r="C120" s="2">
+        <v>6.94</v>
+      </c>
+      <c r="D120" s="2">
+        <v>5.34</v>
+      </c>
+      <c r="E120" s="2">
+        <v>-17.73</v>
+      </c>
+      <c r="F120" s="2">
+        <v>9.23</v>
+      </c>
       <c r="G120" s="2">
-        <v>78</v>
+        <v>55.17</v>
       </c>
       <c r="H120" s="2">
-        <v>72.8</v>
+        <v>62</v>
       </c>
       <c r="I120" s="2">
-        <v>92</v>
+        <v>76.8</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>260</v>
@@ -4634,14 +4907,26 @@
       <c r="A121" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G121" s="2">
-        <v>94.40000000000001</v>
+      <c r="B121" s="1">
+        <v>232.35</v>
+      </c>
+      <c r="C121" s="2">
+        <v>3.78</v>
+      </c>
+      <c r="D121" s="2">
+        <v>-1.38</v>
+      </c>
+      <c r="E121" s="2">
+        <v>-13.35</v>
+      </c>
+      <c r="F121" s="2">
+        <v>8.460000000000001</v>
       </c>
       <c r="H121" s="2">
-        <v>98</v>
+        <v>49.2</v>
       </c>
       <c r="I121" s="2">
-        <v>43.6</v>
+        <v>51.6</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>260</v>
@@ -4651,14 +4936,26 @@
       <c r="A122" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G122" s="2">
-        <v>18.8</v>
+      <c r="B122" s="1">
+        <v>506.65</v>
+      </c>
+      <c r="C122" s="2">
+        <v>-12.82</v>
+      </c>
+      <c r="D122" s="2">
+        <v>-4.9</v>
+      </c>
+      <c r="E122" s="2">
+        <v>-4.27</v>
+      </c>
+      <c r="F122" s="2">
+        <v>7.69</v>
       </c>
       <c r="H122" s="2">
-        <v>0.4</v>
+        <v>41.6</v>
       </c>
       <c r="I122" s="2">
-        <v>2.4</v>
+        <v>30.4</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>260</v>
@@ -4668,14 +4965,29 @@
       <c r="A123" s="1" t="s">
         <v>130</v>
       </c>
+      <c r="B123" s="1">
+        <v>187.98</v>
+      </c>
+      <c r="C123" s="2">
+        <v>-2.85</v>
+      </c>
+      <c r="D123" s="2">
+        <v>-12.96</v>
+      </c>
+      <c r="E123" s="2">
+        <v>-5.5</v>
+      </c>
+      <c r="F123" s="2">
+        <v>6.92</v>
+      </c>
       <c r="G123" s="2">
-        <v>4.8</v>
+        <v>14.94</v>
       </c>
       <c r="H123" s="2">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I123" s="2">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>260</v>
@@ -4685,14 +4997,26 @@
       <c r="A124" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G124" s="2">
-        <v>89.59999999999999</v>
+      <c r="B124" s="1">
+        <v>271.65</v>
+      </c>
+      <c r="C124" s="2">
+        <v>5.16</v>
+      </c>
+      <c r="D124" s="2">
+        <v>-14.64</v>
+      </c>
+      <c r="E124" s="2">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="F124" s="2">
+        <v>6.15</v>
       </c>
       <c r="H124" s="2">
-        <v>91.2</v>
+        <v>4</v>
       </c>
       <c r="I124" s="2">
-        <v>94.8</v>
+        <v>15.6</v>
       </c>
       <c r="J124" s="4" t="s">
         <v>260</v>
@@ -4702,14 +5026,26 @@
       <c r="A125" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G125" s="2">
-        <v>40.8</v>
+      <c r="B125" s="1">
+        <v>814.05</v>
+      </c>
+      <c r="C125" s="2">
+        <v>-7.24</v>
+      </c>
+      <c r="D125" s="2">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E125" s="2">
+        <v>-9.67</v>
+      </c>
+      <c r="F125" s="2">
+        <v>5.38</v>
       </c>
       <c r="H125" s="2">
-        <v>41.6</v>
+        <v>17.6</v>
       </c>
       <c r="I125" s="2">
-        <v>52.8</v>
+        <v>5.6</v>
       </c>
       <c r="J125" s="4" t="s">
         <v>260</v>
@@ -4719,14 +5055,26 @@
       <c r="A126" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G126" s="2">
-        <v>12.8</v>
+      <c r="B126" s="1">
+        <v>326.1</v>
+      </c>
+      <c r="C126" s="2">
+        <v>4.79</v>
+      </c>
+      <c r="D126" s="2">
+        <v>-8.5</v>
+      </c>
+      <c r="E126" s="2">
+        <v>-20.07</v>
+      </c>
+      <c r="F126" s="2">
+        <v>4.62</v>
       </c>
       <c r="H126" s="2">
-        <v>25.2</v>
+        <v>16.8</v>
       </c>
       <c r="I126" s="2">
-        <v>7.6</v>
+        <v>47.6</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>260</v>
@@ -4736,14 +5084,26 @@
       <c r="A127" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G127" s="2">
-        <v>80.8</v>
+      <c r="B127" s="1">
+        <v>2197.6</v>
+      </c>
+      <c r="C127" s="2">
+        <v>-2.55</v>
+      </c>
+      <c r="D127" s="2">
+        <v>-12.5</v>
+      </c>
+      <c r="E127" s="2">
+        <v>-17.28</v>
+      </c>
+      <c r="F127" s="2">
+        <v>3.85</v>
       </c>
       <c r="H127" s="2">
-        <v>94.8</v>
+        <v>16.4</v>
       </c>
       <c r="I127" s="2">
-        <v>80.40000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>260</v>
@@ -4753,14 +5113,26 @@
       <c r="A128" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G128" s="2">
-        <v>17.6</v>
+      <c r="B128" s="1">
+        <v>316.95</v>
+      </c>
+      <c r="C128" s="2">
+        <v>-14.12</v>
+      </c>
+      <c r="D128" s="2">
+        <v>-11.73</v>
+      </c>
+      <c r="E128" s="2">
+        <v>-12.67</v>
+      </c>
+      <c r="F128" s="2">
+        <v>3.08</v>
       </c>
       <c r="H128" s="2">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="I128" s="2">
-        <v>6.4</v>
+        <v>43.6</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>260</v>
@@ -4770,14 +5142,29 @@
       <c r="A129" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="B129" s="1">
+        <v>906.55</v>
+      </c>
+      <c r="C129" s="2">
+        <v>-24.47</v>
+      </c>
+      <c r="D129" s="2">
+        <v>-20.86</v>
+      </c>
+      <c r="E129" s="2">
+        <v>-3.35</v>
+      </c>
+      <c r="F129" s="2">
+        <v>2.31</v>
+      </c>
       <c r="G129" s="2">
-        <v>32</v>
+        <v>2.3</v>
       </c>
       <c r="H129" s="2">
-        <v>43.6</v>
+        <v>2.8</v>
       </c>
       <c r="I129" s="2">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="J129" s="4" t="s">
         <v>260</v>
@@ -4787,14 +5174,26 @@
       <c r="A130" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G130" s="2">
-        <v>16.4</v>
+      <c r="B130" s="1">
+        <v>164.34</v>
+      </c>
+      <c r="C130" s="2">
+        <v>-11.41</v>
+      </c>
+      <c r="D130" s="2">
+        <v>-16.49</v>
+      </c>
+      <c r="E130" s="2">
+        <v>-15.83</v>
+      </c>
+      <c r="F130" s="2">
+        <v>1.54</v>
       </c>
       <c r="H130" s="2">
-        <v>23.2</v>
+        <v>18.4</v>
       </c>
       <c r="I130" s="2">
-        <v>45.2</v>
+        <v>24.4</v>
       </c>
       <c r="J130" s="4" t="s">
         <v>260</v>
@@ -4804,14 +5203,29 @@
       <c r="A131" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="B131" s="1">
+        <v>233.22</v>
+      </c>
+      <c r="C131" s="2">
+        <v>-39.9</v>
+      </c>
+      <c r="D131" s="2">
+        <v>-36.23</v>
+      </c>
+      <c r="E131" s="2">
+        <v>-51.12</v>
+      </c>
+      <c r="F131" s="2">
+        <v>0.77</v>
+      </c>
       <c r="G131" s="2">
-        <v>22.8</v>
+        <v>1.15</v>
       </c>
       <c r="H131" s="2">
-        <v>21.2</v>
+        <v>0.4</v>
       </c>
       <c r="I131" s="2">
-        <v>16</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>260</v>
@@ -4821,14 +5235,11 @@
       <c r="A132" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G132" s="2">
-        <v>77.2</v>
-      </c>
       <c r="H132" s="2">
-        <v>70</v>
+        <v>7.6</v>
       </c>
       <c r="I132" s="2">
-        <v>69.59999999999999</v>
+        <v>16</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>260</v>
@@ -4838,14 +5249,11 @@
       <c r="A133" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G133" s="2">
-        <v>54.8</v>
-      </c>
       <c r="H133" s="2">
-        <v>78.40000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="I133" s="2">
-        <v>86.8</v>
+        <v>37.6</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>260</v>
@@ -4855,14 +5263,11 @@
       <c r="A134" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G134" s="2">
-        <v>27.6</v>
-      </c>
       <c r="H134" s="2">
-        <v>53.2</v>
+        <v>58.8</v>
       </c>
       <c r="I134" s="2">
-        <v>54</v>
+        <v>60.4</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>260</v>
@@ -4872,14 +5277,11 @@
       <c r="A135" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G135" s="2">
-        <v>84.40000000000001</v>
-      </c>
       <c r="H135" s="2">
-        <v>89.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="I135" s="2">
-        <v>78</v>
+        <v>55.2</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>260</v>
@@ -4889,14 +5291,11 @@
       <c r="A136" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G136" s="2">
-        <v>78.40000000000001</v>
-      </c>
       <c r="H136" s="2">
-        <v>63.6</v>
+        <v>26.4</v>
       </c>
       <c r="I136" s="2">
-        <v>72.8</v>
+        <v>44.8</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>260</v>
@@ -4907,13 +5306,13 @@
         <v>144</v>
       </c>
       <c r="G137" s="2">
-        <v>36.8</v>
+        <v>60.92</v>
       </c>
       <c r="H137" s="2">
-        <v>23.6</v>
+        <v>28.4</v>
       </c>
       <c r="I137" s="2">
-        <v>18.4</v>
+        <v>16.4</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>260</v>
@@ -4923,14 +5322,11 @@
       <c r="A138" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G138" s="2">
-        <v>95.2</v>
-      </c>
       <c r="H138" s="2">
-        <v>95.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="I138" s="2">
-        <v>93.2</v>
+        <v>78</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>260</v>
@@ -4941,13 +5337,13 @@
         <v>146</v>
       </c>
       <c r="G139" s="2">
-        <v>66</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H139" s="2">
-        <v>87.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="I139" s="2">
-        <v>89.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>260</v>
@@ -4957,14 +5353,11 @@
       <c r="A140" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G140" s="2">
-        <v>16.8</v>
-      </c>
       <c r="H140" s="2">
-        <v>47.6</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I140" s="2">
-        <v>50.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>260</v>
@@ -4975,13 +5368,13 @@
         <v>148</v>
       </c>
       <c r="G141" s="2">
-        <v>67.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H141" s="2">
-        <v>86.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I141" s="2">
-        <v>82.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>260</v>
@@ -4991,14 +5384,11 @@
       <c r="A142" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G142" s="2">
-        <v>47.6</v>
-      </c>
       <c r="H142" s="2">
-        <v>44</v>
+        <v>86.8</v>
       </c>
       <c r="I142" s="2">
-        <v>67.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J142" s="4" t="s">
         <v>260</v>
@@ -5009,13 +5399,13 @@
         <v>150</v>
       </c>
       <c r="G143" s="2">
-        <v>43.6</v>
+        <v>68.97</v>
       </c>
       <c r="H143" s="2">
-        <v>52.8</v>
+        <v>71.2</v>
       </c>
       <c r="I143" s="2">
-        <v>36.4</v>
+        <v>31.6</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>260</v>
@@ -5025,14 +5415,11 @@
       <c r="A144" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G144" s="2">
-        <v>92</v>
-      </c>
       <c r="H144" s="2">
-        <v>96.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I144" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>260</v>
@@ -5043,13 +5430,13 @@
         <v>152</v>
       </c>
       <c r="G145" s="2">
-        <v>76.40000000000001</v>
+        <v>49.43</v>
       </c>
       <c r="H145" s="2">
-        <v>48.8</v>
+        <v>29.6</v>
       </c>
       <c r="I145" s="2">
-        <v>34.4</v>
+        <v>15.2</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>260</v>
@@ -5060,13 +5447,13 @@
         <v>153</v>
       </c>
       <c r="G146" s="2">
-        <v>0.8</v>
+        <v>64.37</v>
       </c>
       <c r="H146" s="2">
-        <v>18</v>
+        <v>78.8</v>
       </c>
       <c r="I146" s="2">
-        <v>14.4</v>
+        <v>81.2</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>260</v>
@@ -5076,14 +5463,11 @@
       <c r="A147" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G147" s="2">
-        <v>26</v>
-      </c>
       <c r="H147" s="2">
-        <v>27.6</v>
+        <v>60.4</v>
       </c>
       <c r="I147" s="2">
-        <v>10.8</v>
+        <v>66</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>260</v>
@@ -5093,14 +5477,11 @@
       <c r="A148" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G148" s="2">
-        <v>37.6</v>
-      </c>
       <c r="H148" s="2">
-        <v>40.8</v>
+        <v>61.6</v>
       </c>
       <c r="I148" s="2">
-        <v>23.6</v>
+        <v>32.8</v>
       </c>
       <c r="J148" s="4" t="s">
         <v>260</v>
@@ -5110,14 +5491,11 @@
       <c r="A149" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G149" s="2">
-        <v>91.2</v>
-      </c>
       <c r="H149" s="2">
-        <v>96</v>
+        <v>73.2</v>
       </c>
       <c r="I149" s="2">
-        <v>96.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="J149" s="4" t="s">
         <v>260</v>
@@ -5127,14 +5505,11 @@
       <c r="A150" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G150" s="2">
-        <v>21.6</v>
-      </c>
       <c r="H150" s="2">
-        <v>42.4</v>
+        <v>68.8</v>
       </c>
       <c r="I150" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>260</v>
@@ -5144,14 +5519,11 @@
       <c r="A151" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G151" s="2">
-        <v>35.2</v>
-      </c>
       <c r="H151" s="2">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="I151" s="2">
-        <v>28.4</v>
+        <v>72.8</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>260</v>
@@ -5161,14 +5533,11 @@
       <c r="A152" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G152" s="2">
-        <v>85.59999999999999</v>
-      </c>
       <c r="H152" s="2">
-        <v>85.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I152" s="2">
-        <v>91.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>260</v>
@@ -5178,14 +5547,11 @@
       <c r="A153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G153" s="2">
-        <v>60.8</v>
-      </c>
       <c r="H153" s="2">
-        <v>59.2</v>
+        <v>18.8</v>
       </c>
       <c r="I153" s="2">
-        <v>58.4</v>
+        <v>0.4</v>
       </c>
       <c r="J153" s="4" t="s">
         <v>260</v>
@@ -5196,13 +5562,13 @@
         <v>161</v>
       </c>
       <c r="G154" s="2">
-        <v>8.4</v>
+        <v>81.61</v>
       </c>
       <c r="H154" s="2">
-        <v>20.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I154" s="2">
-        <v>10</v>
+        <v>88.8</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>260</v>
@@ -5212,14 +5578,11 @@
       <c r="A155" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G155" s="2">
-        <v>74</v>
-      </c>
       <c r="H155" s="2">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I155" s="2">
-        <v>70</v>
+        <v>91.2</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>260</v>
@@ -5229,14 +5592,11 @@
       <c r="A156" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G156" s="2">
-        <v>82.8</v>
-      </c>
       <c r="H156" s="2">
-        <v>84.8</v>
+        <v>80.8</v>
       </c>
       <c r="I156" s="2">
-        <v>60.4</v>
+        <v>94.8</v>
       </c>
       <c r="J156" s="4" t="s">
         <v>260</v>
@@ -5247,13 +5607,13 @@
         <v>164</v>
       </c>
       <c r="G157" s="2">
-        <v>73.59999999999999</v>
+        <v>27.59</v>
       </c>
       <c r="H157" s="2">
-        <v>56</v>
+        <v>31.6</v>
       </c>
       <c r="I157" s="2">
-        <v>64</v>
+        <v>46.8</v>
       </c>
       <c r="J157" s="4" t="s">
         <v>260</v>
@@ -5264,13 +5624,13 @@
         <v>165</v>
       </c>
       <c r="G158" s="2">
-        <v>48.8</v>
+        <v>45.98</v>
       </c>
       <c r="H158" s="2">
-        <v>54.8</v>
+        <v>36</v>
       </c>
       <c r="I158" s="2">
-        <v>55.2</v>
+        <v>28.4</v>
       </c>
       <c r="J158" s="4" t="s">
         <v>260</v>
@@ -5280,14 +5640,11 @@
       <c r="A159" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G159" s="2">
-        <v>79.2</v>
-      </c>
       <c r="H159" s="2">
-        <v>81.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="I159" s="2">
-        <v>78.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>260</v>
@@ -5297,14 +5654,11 @@
       <c r="A160" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G160" s="2">
-        <v>20.4</v>
-      </c>
       <c r="H160" s="2">
-        <v>55.6</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I160" s="2">
-        <v>43.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>260</v>
@@ -5315,13 +5669,13 @@
         <v>168</v>
       </c>
       <c r="G161" s="2">
-        <v>23.6</v>
+        <v>29.89</v>
       </c>
       <c r="H161" s="2">
-        <v>36.4</v>
+        <v>38.4</v>
       </c>
       <c r="I161" s="2">
-        <v>27.6</v>
+        <v>25.6</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>260</v>
@@ -5331,14 +5685,11 @@
       <c r="A162" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G162" s="2">
-        <v>5.6</v>
-      </c>
       <c r="H162" s="2">
-        <v>0.8</v>
+        <v>36.8</v>
       </c>
       <c r="I162" s="2">
-        <v>11.2</v>
+        <v>23.6</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>260</v>
@@ -5348,14 +5699,11 @@
       <c r="A163" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G163" s="2">
-        <v>72</v>
-      </c>
       <c r="H163" s="2">
-        <v>64.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I163" s="2">
-        <v>51.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>260</v>
@@ -5366,13 +5714,13 @@
         <v>171</v>
       </c>
       <c r="G164" s="2">
-        <v>68.40000000000001</v>
+        <v>16.09</v>
       </c>
       <c r="H164" s="2">
-        <v>61.2</v>
+        <v>34.4</v>
       </c>
       <c r="I164" s="2">
-        <v>53.6</v>
+        <v>62.8</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>260</v>
@@ -5383,13 +5731,13 @@
         <v>172</v>
       </c>
       <c r="G165" s="2">
-        <v>8.800000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="H165" s="2">
-        <v>29.2</v>
+        <v>7.2</v>
       </c>
       <c r="I165" s="2">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="J165" s="4" t="s">
         <v>260</v>
@@ -5399,14 +5747,11 @@
       <c r="A166" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G166" s="2">
+      <c r="H166" s="2">
+        <v>47.6</v>
+      </c>
+      <c r="I166" s="2">
         <v>44</v>
-      </c>
-      <c r="H166" s="2">
-        <v>30.8</v>
-      </c>
-      <c r="I166" s="2">
-        <v>30.8</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>260</v>
@@ -5416,14 +5761,11 @@
       <c r="A167" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G167" s="2">
-        <v>63.6</v>
-      </c>
       <c r="H167" s="2">
-        <v>71.2</v>
+        <v>0.8</v>
       </c>
       <c r="I167" s="2">
-        <v>77.2</v>
+        <v>18</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>260</v>
@@ -5434,13 +5776,13 @@
         <v>175</v>
       </c>
       <c r="G168" s="2">
-        <v>86.40000000000001</v>
+        <v>20.69</v>
       </c>
       <c r="H168" s="2">
-        <v>82</v>
+        <v>30.8</v>
       </c>
       <c r="I168" s="2">
-        <v>85.59999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>260</v>
@@ -5451,13 +5793,13 @@
         <v>176</v>
       </c>
       <c r="G169" s="2">
-        <v>96.40000000000001</v>
+        <v>34.48</v>
       </c>
       <c r="H169" s="2">
-        <v>91.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="I169" s="2">
-        <v>90.8</v>
+        <v>1.6</v>
       </c>
       <c r="J169" s="4" t="s">
         <v>260</v>
@@ -5467,14 +5809,11 @@
       <c r="A170" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G170" s="2">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H170" s="2">
-        <v>60.8</v>
+        <v>35.2</v>
       </c>
       <c r="I170" s="2">
-        <v>61.6</v>
+        <v>24</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>260</v>
@@ -5484,14 +5823,11 @@
       <c r="A171" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G171" s="2">
-        <v>34.8</v>
-      </c>
       <c r="H171" s="2">
-        <v>22.4</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I171" s="2">
-        <v>13.2</v>
+        <v>85.2</v>
       </c>
       <c r="J171" s="4" t="s">
         <v>260</v>
@@ -5501,14 +5837,11 @@
       <c r="A172" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G172" s="2">
-        <v>75.59999999999999</v>
-      </c>
       <c r="H172" s="2">
-        <v>70.8</v>
+        <v>8.4</v>
       </c>
       <c r="I172" s="2">
-        <v>80</v>
+        <v>20.8</v>
       </c>
       <c r="J172" s="4" t="s">
         <v>260</v>
@@ -5518,14 +5851,11 @@
       <c r="A173" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G173" s="2">
-        <v>52.4</v>
-      </c>
       <c r="H173" s="2">
-        <v>66.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I173" s="2">
-        <v>77.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="J173" s="4" t="s">
         <v>260</v>
@@ -5535,14 +5865,11 @@
       <c r="A174" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G174" s="2">
-        <v>58.4</v>
-      </c>
       <c r="H174" s="2">
-        <v>52.4</v>
+        <v>48.8</v>
       </c>
       <c r="I174" s="2">
-        <v>30.4</v>
+        <v>54.8</v>
       </c>
       <c r="J174" s="4" t="s">
         <v>260</v>
@@ -5552,14 +5879,11 @@
       <c r="A175" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G175" s="2">
-        <v>3.2</v>
-      </c>
       <c r="H175" s="2">
-        <v>12</v>
+        <v>79.2</v>
       </c>
       <c r="I175" s="2">
-        <v>60</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J175" s="4" t="s">
         <v>260</v>
@@ -5569,14 +5893,11 @@
       <c r="A176" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G176" s="2">
-        <v>44.8</v>
-      </c>
       <c r="H176" s="2">
-        <v>33.2</v>
+        <v>20.4</v>
       </c>
       <c r="I176" s="2">
-        <v>35.6</v>
+        <v>55.6</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>260</v>
@@ -5586,14 +5907,11 @@
       <c r="A177" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G177" s="2">
-        <v>59.2</v>
-      </c>
       <c r="H177" s="2">
-        <v>38</v>
+        <v>23.6</v>
       </c>
       <c r="I177" s="2">
-        <v>21.6</v>
+        <v>36.4</v>
       </c>
       <c r="J177" s="4" t="s">
         <v>260</v>
@@ -5603,14 +5921,11 @@
       <c r="A178" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G178" s="2">
-        <v>54</v>
-      </c>
       <c r="H178" s="2">
-        <v>73.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I178" s="2">
-        <v>76.40000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="J178" s="4" t="s">
         <v>260</v>
@@ -5620,14 +5935,11 @@
       <c r="A179" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G179" s="2">
-        <v>98.40000000000001</v>
-      </c>
       <c r="H179" s="2">
-        <v>97.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I179" s="2">
-        <v>96.8</v>
+        <v>29.2</v>
       </c>
       <c r="J179" s="4" t="s">
         <v>260</v>
@@ -5637,14 +5949,11 @@
       <c r="A180" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G180" s="2">
-        <v>76</v>
-      </c>
       <c r="H180" s="2">
-        <v>86</v>
+        <v>63.6</v>
       </c>
       <c r="I180" s="2">
-        <v>68.8</v>
+        <v>71.2</v>
       </c>
       <c r="J180" s="4" t="s">
         <v>260</v>
@@ -5654,14 +5963,11 @@
       <c r="A181" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G181" s="2">
-        <v>39.2</v>
-      </c>
       <c r="H181" s="2">
-        <v>33.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I181" s="2">
-        <v>36.8</v>
+        <v>60.8</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>260</v>
@@ -5671,14 +5977,11 @@
       <c r="A182" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G182" s="2">
-        <v>82</v>
-      </c>
       <c r="H182" s="2">
-        <v>82.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I182" s="2">
-        <v>64.8</v>
+        <v>70.8</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>260</v>
@@ -5688,14 +5991,11 @@
       <c r="A183" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G183" s="2">
-        <v>46.8</v>
-      </c>
       <c r="H183" s="2">
-        <v>64</v>
+        <v>52.4</v>
       </c>
       <c r="I183" s="2">
-        <v>52</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>260</v>
@@ -5705,14 +6005,11 @@
       <c r="A184" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G184" s="2">
-        <v>76.8</v>
-      </c>
       <c r="H184" s="2">
-        <v>80</v>
+        <v>44.8</v>
       </c>
       <c r="I184" s="2">
-        <v>80.8</v>
+        <v>33.2</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>260</v>
@@ -5722,14 +6019,11 @@
       <c r="A185" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G185" s="2">
-        <v>56.4</v>
-      </c>
       <c r="H185" s="2">
-        <v>39.6</v>
+        <v>54</v>
       </c>
       <c r="I185" s="2">
-        <v>48.8</v>
+        <v>73.2</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>260</v>
@@ -5740,13 +6034,13 @@
         <v>193</v>
       </c>
       <c r="G186" s="2">
-        <v>52</v>
+        <v>4.6</v>
       </c>
       <c r="H186" s="2">
-        <v>53.6</v>
+        <v>14.8</v>
       </c>
       <c r="I186" s="2">
-        <v>54.8</v>
+        <v>34.4</v>
       </c>
       <c r="J186" s="4" t="s">
         <v>260</v>
@@ -5756,14 +6050,11 @@
       <c r="A187" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G187" s="2">
-        <v>45.6</v>
-      </c>
       <c r="H187" s="2">
-        <v>14.4</v>
+        <v>39.2</v>
       </c>
       <c r="I187" s="2">
-        <v>25.6</v>
+        <v>33.6</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>260</v>
@@ -5774,13 +6065,13 @@
         <v>195</v>
       </c>
       <c r="G188" s="2">
-        <v>66.8</v>
+        <v>75.86</v>
       </c>
       <c r="H188" s="2">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="I188" s="2">
-        <v>50.8</v>
+        <v>82.8</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>260</v>
@@ -5791,13 +6082,13 @@
         <v>196</v>
       </c>
       <c r="G189" s="2">
-        <v>70.40000000000001</v>
+        <v>33.33</v>
       </c>
       <c r="H189" s="2">
-        <v>86.40000000000001</v>
+        <v>30</v>
       </c>
       <c r="I189" s="2">
-        <v>84</v>
+        <v>26.4</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>260</v>
@@ -5808,13 +6099,13 @@
         <v>197</v>
       </c>
       <c r="G190" s="2">
-        <v>81.59999999999999</v>
+        <v>26.44</v>
       </c>
       <c r="H190" s="2">
-        <v>85.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="I190" s="2">
-        <v>84.8</v>
+        <v>18.8</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>260</v>
@@ -5824,14 +6115,11 @@
       <c r="A191" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G191" s="2">
-        <v>41.6</v>
-      </c>
       <c r="H191" s="2">
-        <v>30.4</v>
+        <v>56.4</v>
       </c>
       <c r="I191" s="2">
-        <v>9.6</v>
+        <v>39.6</v>
       </c>
       <c r="J191" s="4" t="s">
         <v>260</v>
@@ -5841,14 +6129,11 @@
       <c r="A192" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G192" s="2">
-        <v>41.2</v>
-      </c>
       <c r="H192" s="2">
-        <v>36.8</v>
+        <v>52</v>
       </c>
       <c r="I192" s="2">
-        <v>42.4</v>
+        <v>53.6</v>
       </c>
       <c r="J192" s="4" t="s">
         <v>260</v>
@@ -5858,14 +6143,11 @@
       <c r="A193" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G193" s="2">
-        <v>13.6</v>
-      </c>
       <c r="H193" s="2">
-        <v>19.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I193" s="2">
-        <v>17.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>260</v>
@@ -5876,13 +6158,13 @@
         <v>201</v>
       </c>
       <c r="G194" s="2">
-        <v>24.8</v>
+        <v>35.63</v>
       </c>
       <c r="H194" s="2">
-        <v>10.4</v>
+        <v>51.2</v>
       </c>
       <c r="I194" s="2">
-        <v>2</v>
+        <v>54.4</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>260</v>
@@ -5892,14 +6174,11 @@
       <c r="A195" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G195" s="2">
-        <v>56</v>
-      </c>
       <c r="H195" s="2">
         <v>41.2</v>
       </c>
       <c r="I195" s="2">
-        <v>41.2</v>
+        <v>36.8</v>
       </c>
       <c r="J195" s="4" t="s">
         <v>260</v>
@@ -5910,13 +6189,13 @@
         <v>203</v>
       </c>
       <c r="G196" s="2">
-        <v>49.6</v>
+        <v>13.79</v>
       </c>
       <c r="H196" s="2">
-        <v>45.2</v>
+        <v>10.4</v>
       </c>
       <c r="I196" s="2">
-        <v>38.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J196" s="4" t="s">
         <v>260</v>
@@ -5927,13 +6206,13 @@
         <v>204</v>
       </c>
       <c r="G197" s="2">
-        <v>68</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="H197" s="2">
-        <v>68.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I197" s="2">
-        <v>63.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J197" s="4" t="s">
         <v>260</v>
@@ -5943,14 +6222,11 @@
       <c r="A198" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G198" s="2">
-        <v>67.2</v>
-      </c>
       <c r="H198" s="2">
-        <v>66.8</v>
+        <v>24.8</v>
       </c>
       <c r="I198" s="2">
-        <v>73.59999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>260</v>
@@ -5961,13 +6237,13 @@
         <v>206</v>
       </c>
       <c r="G199" s="2">
-        <v>96.8</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="H199" s="2">
-        <v>98.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I199" s="2">
-        <v>88.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>260</v>
@@ -5977,14 +6253,11 @@
       <c r="A200" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G200" s="2">
-        <v>2.4</v>
-      </c>
       <c r="H200" s="2">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="I200" s="2">
-        <v>6</v>
+        <v>41.2</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>260</v>
@@ -5995,13 +6268,13 @@
         <v>208</v>
       </c>
       <c r="G201" s="2">
-        <v>19.6</v>
+        <v>66.67</v>
       </c>
       <c r="H201" s="2">
-        <v>10.8</v>
+        <v>64</v>
       </c>
       <c r="I201" s="2">
-        <v>8.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J201" s="4" t="s">
         <v>260</v>
@@ -6011,14 +6284,11 @@
       <c r="A202" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G202" s="2">
-        <v>50</v>
-      </c>
       <c r="H202" s="2">
-        <v>44.4</v>
+        <v>49.6</v>
       </c>
       <c r="I202" s="2">
-        <v>49.6</v>
+        <v>45.2</v>
       </c>
       <c r="J202" s="4" t="s">
         <v>260</v>
@@ -6028,14 +6298,11 @@
       <c r="A203" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="G203" s="2">
-        <v>49.2</v>
-      </c>
       <c r="H203" s="2">
-        <v>51.6</v>
+        <v>68</v>
       </c>
       <c r="I203" s="2">
-        <v>76.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>260</v>
@@ -6046,13 +6313,13 @@
         <v>211</v>
       </c>
       <c r="G204" s="2">
-        <v>93.2</v>
+        <v>19.54</v>
       </c>
       <c r="H204" s="2">
-        <v>97.59999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="I204" s="2">
-        <v>93.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>260</v>
@@ -6062,14 +6329,11 @@
       <c r="A205" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G205" s="2">
-        <v>3.6</v>
-      </c>
       <c r="H205" s="2">
-        <v>3.2</v>
+        <v>96.8</v>
       </c>
       <c r="I205" s="2">
-        <v>8.800000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="J205" s="4" t="s">
         <v>260</v>
@@ -6079,14 +6343,11 @@
       <c r="A206" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G206" s="2">
-        <v>23.2</v>
-      </c>
       <c r="H206" s="2">
-        <v>20.4</v>
+        <v>19.6</v>
       </c>
       <c r="I206" s="2">
-        <v>20.8</v>
+        <v>10.8</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>260</v>
@@ -6096,14 +6357,11 @@
       <c r="A207" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G207" s="2">
-        <v>90.8</v>
-      </c>
       <c r="H207" s="2">
-        <v>90.8</v>
+        <v>93.2</v>
       </c>
       <c r="I207" s="2">
-        <v>74</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>260</v>
@@ -6113,14 +6371,11 @@
       <c r="A208" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G208" s="2">
-        <v>10.8</v>
-      </c>
       <c r="H208" s="2">
-        <v>8</v>
+        <v>90.8</v>
       </c>
       <c r="I208" s="2">
-        <v>29.2</v>
+        <v>90.8</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>260</v>
@@ -6130,14 +6385,11 @@
       <c r="A209" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G209" s="2">
-        <v>43.2</v>
-      </c>
       <c r="H209" s="2">
-        <v>46.4</v>
+        <v>10.8</v>
       </c>
       <c r="I209" s="2">
-        <v>42.8</v>
+        <v>8</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>260</v>
@@ -6147,14 +6399,11 @@
       <c r="A210" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G210" s="2">
-        <v>47.2</v>
-      </c>
       <c r="H210" s="2">
-        <v>35.6</v>
+        <v>43.2</v>
       </c>
       <c r="I210" s="2">
-        <v>38</v>
+        <v>46.4</v>
       </c>
       <c r="J210" s="4" t="s">
         <v>260</v>
@@ -6164,14 +6413,11 @@
       <c r="A211" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G211" s="2">
-        <v>39.6</v>
-      </c>
       <c r="H211" s="2">
-        <v>50.4</v>
+        <v>47.2</v>
       </c>
       <c r="I211" s="2">
-        <v>28</v>
+        <v>35.6</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>260</v>
@@ -6181,14 +6427,11 @@
       <c r="A212" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G212" s="2">
-        <v>58</v>
-      </c>
       <c r="H212" s="2">
-        <v>65.2</v>
+        <v>39.6</v>
       </c>
       <c r="I212" s="2">
-        <v>76</v>
+        <v>50.4</v>
       </c>
       <c r="J212" s="4" t="s">
         <v>260</v>
@@ -6199,13 +6442,13 @@
         <v>220</v>
       </c>
       <c r="G213" s="2">
-        <v>32.8</v>
+        <v>11.49</v>
       </c>
       <c r="H213" s="2">
-        <v>40.4</v>
+        <v>24.4</v>
       </c>
       <c r="I213" s="2">
-        <v>34.8</v>
+        <v>17.2</v>
       </c>
       <c r="J213" s="4" t="s">
         <v>260</v>
@@ -6215,14 +6458,11 @@
       <c r="A214" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G214" s="2">
+      <c r="H214" s="2">
         <v>62.8</v>
       </c>
-      <c r="H214" s="2">
+      <c r="I214" s="2">
         <v>61.6</v>
-      </c>
-      <c r="I214" s="2">
-        <v>74.8</v>
       </c>
       <c r="J214" s="4" t="s">
         <v>260</v>
@@ -6233,13 +6473,13 @@
         <v>222</v>
       </c>
       <c r="G215" s="2">
-        <v>74.8</v>
+        <v>47.13</v>
       </c>
       <c r="H215" s="2">
-        <v>84</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I215" s="2">
-        <v>74.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="J215" s="4" t="s">
         <v>260</v>
@@ -6249,14 +6489,11 @@
       <c r="A216" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="G216" s="2">
-        <v>2</v>
-      </c>
       <c r="H216" s="2">
-        <v>7.6</v>
+        <v>74.8</v>
       </c>
       <c r="I216" s="2">
-        <v>6.8</v>
+        <v>84</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>260</v>
@@ -6267,13 +6504,13 @@
         <v>224</v>
       </c>
       <c r="G217" s="2">
-        <v>52.8</v>
+        <v>83.91</v>
       </c>
       <c r="H217" s="2">
-        <v>63.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I217" s="2">
-        <v>72</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J217" s="4" t="s">
         <v>260</v>
@@ -6283,14 +6520,11 @@
       <c r="A218" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G218" s="2">
-        <v>45.2</v>
-      </c>
       <c r="H218" s="2">
-        <v>68.8</v>
+        <v>22.4</v>
       </c>
       <c r="I218" s="2">
-        <v>75.2</v>
+        <v>28.8</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>260</v>
@@ -6301,13 +6535,13 @@
         <v>226</v>
       </c>
       <c r="G219" s="2">
-        <v>28</v>
+        <v>28.74</v>
       </c>
       <c r="H219" s="2">
-        <v>46</v>
+        <v>33.6</v>
       </c>
       <c r="I219" s="2">
-        <v>47.2</v>
+        <v>45.6</v>
       </c>
       <c r="J219" s="4" t="s">
         <v>260</v>
@@ -6317,14 +6551,11 @@
       <c r="A220" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="G220" s="2">
-        <v>22.4</v>
-      </c>
       <c r="H220" s="2">
-        <v>28.8</v>
+        <v>5.2</v>
       </c>
       <c r="I220" s="2">
-        <v>25.2</v>
+        <v>27.2</v>
       </c>
       <c r="J220" s="4" t="s">
         <v>260</v>
@@ -6334,14 +6565,11 @@
       <c r="A221" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G221" s="2">
-        <v>5.2</v>
-      </c>
       <c r="H221" s="2">
-        <v>27.2</v>
+        <v>8</v>
       </c>
       <c r="I221" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J221" s="4" t="s">
         <v>260</v>
@@ -6352,13 +6580,13 @@
         <v>229</v>
       </c>
       <c r="G222" s="2">
-        <v>8</v>
+        <v>70.11</v>
       </c>
       <c r="H222" s="2">
-        <v>2</v>
+        <v>72.8</v>
       </c>
       <c r="I222" s="2">
-        <v>19.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J222" s="4" t="s">
         <v>260</v>
@@ -6368,14 +6596,11 @@
       <c r="A223" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="G223" s="2">
-        <v>48.4</v>
-      </c>
       <c r="H223" s="2">
-        <v>2.8</v>
+        <v>29.2</v>
       </c>
       <c r="I223" s="2">
-        <v>7.2</v>
+        <v>31.2</v>
       </c>
       <c r="J223" s="4" t="s">
         <v>260</v>
@@ -6385,14 +6610,11 @@
       <c r="A224" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G224" s="2">
-        <v>14</v>
-      </c>
       <c r="H224" s="2">
-        <v>6.8</v>
+        <v>31.2</v>
       </c>
       <c r="I224" s="2">
-        <v>18.8</v>
+        <v>4.4</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>260</v>
@@ -6403,13 +6625,13 @@
         <v>232</v>
       </c>
       <c r="G225" s="2">
-        <v>29.2</v>
+        <v>56.32</v>
       </c>
       <c r="H225" s="2">
-        <v>31.2</v>
+        <v>22</v>
       </c>
       <c r="I225" s="2">
-        <v>22</v>
+        <v>13.2</v>
       </c>
       <c r="J225" s="4" t="s">
         <v>260</v>
@@ -6420,13 +6642,13 @@
         <v>233</v>
       </c>
       <c r="G226" s="2">
-        <v>31.2</v>
+        <v>5.75</v>
       </c>
       <c r="H226" s="2">
-        <v>4.4</v>
+        <v>19.2</v>
       </c>
       <c r="I226" s="2">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>260</v>
@@ -6436,14 +6658,11 @@
       <c r="A227" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G227" s="2">
-        <v>4</v>
-      </c>
       <c r="H227" s="2">
-        <v>15.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I227" s="2">
-        <v>23.2</v>
+        <v>5.2</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>260</v>
@@ -6453,14 +6672,11 @@
       <c r="A228" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G228" s="2">
-        <v>55.6</v>
-      </c>
       <c r="H228" s="2">
         <v>60</v>
       </c>
       <c r="I228" s="2">
-        <v>66.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="J228" s="4" t="s">
         <v>260</v>
@@ -6474,10 +6690,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H229" s="2">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="I229" s="2">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="J229" s="4" t="s">
         <v>260</v>
@@ -6487,14 +6703,11 @@
       <c r="A230" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="G230" s="2">
-        <v>15.2</v>
-      </c>
       <c r="H230" s="2">
-        <v>17.6</v>
+        <v>28.8</v>
       </c>
       <c r="I230" s="2">
-        <v>16.4</v>
+        <v>50.8</v>
       </c>
       <c r="J230" s="4" t="s">
         <v>260</v>
@@ -6505,13 +6718,13 @@
         <v>238</v>
       </c>
       <c r="G231" s="2">
-        <v>60</v>
+        <v>6.9</v>
       </c>
       <c r="H231" s="2">
-        <v>56.8</v>
+        <v>21.2</v>
       </c>
       <c r="I231" s="2">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="J231" s="4" t="s">
         <v>260</v>
@@ -6521,14 +6734,11 @@
       <c r="A232" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G232" s="2">
-        <v>28.8</v>
-      </c>
       <c r="H232" s="2">
-        <v>50.8</v>
+        <v>32.4</v>
       </c>
       <c r="I232" s="2">
-        <v>49.2</v>
+        <v>35.2</v>
       </c>
       <c r="J232" s="4" t="s">
         <v>260</v>
@@ -6538,14 +6748,11 @@
       <c r="A233" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G233" s="2">
-        <v>15.6</v>
-      </c>
       <c r="H233" s="2">
-        <v>21.6</v>
+        <v>44.4</v>
       </c>
       <c r="I233" s="2">
-        <v>17.6</v>
+        <v>54</v>
       </c>
       <c r="J233" s="4" t="s">
         <v>260</v>
@@ -6555,14 +6762,11 @@
       <c r="A234" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="G234" s="2">
-        <v>32.4</v>
-      </c>
       <c r="H234" s="2">
-        <v>35.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I234" s="2">
-        <v>30</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J234" s="4" t="s">
         <v>260</v>
@@ -6572,14 +6776,11 @@
       <c r="A235" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G235" s="2">
-        <v>1.6</v>
-      </c>
       <c r="H235" s="2">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="I235" s="2">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>260</v>
@@ -6589,14 +6790,11 @@
       <c r="A236" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G236" s="2">
-        <v>44.4</v>
-      </c>
       <c r="H236" s="2">
-        <v>54</v>
+        <v>30.4</v>
       </c>
       <c r="I236" s="2">
-        <v>51.2</v>
+        <v>13.6</v>
       </c>
       <c r="J236" s="4" t="s">
         <v>260</v>
@@ -6607,13 +6805,13 @@
         <v>244</v>
       </c>
       <c r="G237" s="2">
-        <v>72.40000000000001</v>
+        <v>22.99</v>
       </c>
       <c r="H237" s="2">
-        <v>71.59999999999999</v>
+        <v>38</v>
       </c>
       <c r="I237" s="2">
-        <v>78.8</v>
+        <v>22</v>
       </c>
       <c r="J237" s="4" t="s">
         <v>260</v>
@@ -6623,14 +6821,11 @@
       <c r="A238" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G238" s="2">
-        <v>9.6</v>
-      </c>
       <c r="H238" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I238" s="2">
-        <v>22.4</v>
+        <v>24.8</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>260</v>
@@ -6641,13 +6836,13 @@
         <v>246</v>
       </c>
       <c r="G239" s="2">
-        <v>53.6</v>
+        <v>58.62</v>
       </c>
       <c r="H239" s="2">
-        <v>48</v>
+        <v>69.2</v>
       </c>
       <c r="I239" s="2">
-        <v>68.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>260</v>
@@ -6658,13 +6853,13 @@
         <v>247</v>
       </c>
       <c r="G240" s="2">
-        <v>30.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H240" s="2">
-        <v>13.6</v>
+        <v>11.2</v>
       </c>
       <c r="I240" s="2">
-        <v>13.6</v>
+        <v>7.2</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>260</v>
@@ -6674,14 +6869,11 @@
       <c r="A241" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G241" s="2">
-        <v>24</v>
-      </c>
       <c r="H241" s="2">
-        <v>24.8</v>
+        <v>42.4</v>
       </c>
       <c r="I241" s="2">
-        <v>10.4</v>
+        <v>38.4</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>260</v>
@@ -6691,14 +6883,11 @@
       <c r="A242" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G242" s="2">
-        <v>42.4</v>
-      </c>
       <c r="H242" s="2">
-        <v>38.4</v>
+        <v>16</v>
       </c>
       <c r="I242" s="2">
-        <v>24</v>
+        <v>11.2</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>260</v>
@@ -6708,14 +6897,11 @@
       <c r="A243" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="G243" s="2">
-        <v>16</v>
-      </c>
       <c r="H243" s="2">
-        <v>11.2</v>
+        <v>17.2</v>
       </c>
       <c r="I243" s="2">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>260</v>
@@ -6726,13 +6912,13 @@
         <v>251</v>
       </c>
       <c r="G244" s="2">
-        <v>17.2</v>
+        <v>3.45</v>
       </c>
       <c r="H244" s="2">
-        <v>26</v>
+        <v>1.2</v>
       </c>
       <c r="I244" s="2">
-        <v>24.4</v>
+        <v>3.6</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>260</v>
@@ -6742,14 +6928,11 @@
       <c r="A245" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G245" s="2">
+      <c r="H245" s="2">
         <v>36.4</v>
       </c>
-      <c r="H245" s="2">
+      <c r="I245" s="2">
         <v>42</v>
-      </c>
-      <c r="I245" s="2">
-        <v>33.6</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>260</v>
@@ -6759,14 +6942,11 @@
       <c r="A246" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G246" s="2">
-        <v>18</v>
-      </c>
       <c r="H246" s="2">
-        <v>22.8</v>
+        <v>20</v>
       </c>
       <c r="I246" s="2">
-        <v>26.4</v>
+        <v>11.6</v>
       </c>
       <c r="J246" s="4" t="s">
         <v>260</v>
@@ -6777,13 +6957,13 @@
         <v>254</v>
       </c>
       <c r="G247" s="2">
-        <v>20</v>
+        <v>48.28</v>
       </c>
       <c r="H247" s="2">
-        <v>11.6</v>
+        <v>56.8</v>
       </c>
       <c r="I247" s="2">
-        <v>20.4</v>
+        <v>57.2</v>
       </c>
       <c r="J247" s="4" t="s">
         <v>260</v>
@@ -6793,14 +6973,11 @@
       <c r="A248" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G248" s="2">
+      <c r="H248" s="2">
         <v>55.2</v>
       </c>
-      <c r="H248" s="2">
+      <c r="I248" s="2">
         <v>83.2</v>
-      </c>
-      <c r="I248" s="2">
-        <v>79.2</v>
       </c>
       <c r="J248" s="4" t="s">
         <v>260</v>
@@ -6810,14 +6987,11 @@
       <c r="A249" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="G249" s="2">
+      <c r="H249" s="2">
         <v>40</v>
       </c>
-      <c r="H249" s="2">
+      <c r="I249" s="2">
         <v>49.2</v>
-      </c>
-      <c r="I249" s="2">
-        <v>42</v>
       </c>
       <c r="J249" s="4" t="s">
         <v>260</v>
@@ -6827,14 +7001,11 @@
       <c r="A250" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G250" s="2">
+      <c r="H250" s="2">
         <v>42.8</v>
       </c>
-      <c r="H250" s="2">
+      <c r="I250" s="2">
         <v>29.6</v>
-      </c>
-      <c r="I250" s="2">
-        <v>26.8</v>
       </c>
       <c r="J250" s="4" t="s">
         <v>260</v>
@@ -6845,13 +7016,13 @@
         <v>258</v>
       </c>
       <c r="G251" s="2">
-        <v>42</v>
+        <v>40.23</v>
       </c>
       <c r="H251" s="2">
-        <v>38.8</v>
+        <v>46.4</v>
       </c>
       <c r="I251" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J251" s="4" t="s">
         <v>260</v>
@@ -7160,7 +7331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -7202,86 +7373,86 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.97</v>
+        <v>364.05</v>
       </c>
       <c r="C2" s="2">
-        <v>167.74</v>
+        <v>190.29</v>
       </c>
       <c r="D2" s="2">
-        <v>64.79000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="E2" s="2">
-        <v>48.09</v>
+        <v>60.05</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>90</v>
-      </c>
-      <c r="I2" s="2">
-        <v>89.2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>557.05</v>
+        <v>638.9</v>
       </c>
       <c r="C3" s="2">
-        <v>209.44</v>
+        <v>259.28</v>
       </c>
       <c r="D3" s="2">
-        <v>20.26</v>
+        <v>13.49</v>
       </c>
       <c r="E3" s="2">
-        <v>-4.8</v>
+        <v>23.3</v>
       </c>
       <c r="F3" s="2">
-        <v>98.84</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>99.2</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="H3" s="2">
         <v>99.2</v>
       </c>
       <c r="I3" s="2">
-        <v>99.59999999999999</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>332.55</v>
+        <v>814.5</v>
       </c>
       <c r="C4" s="2">
-        <v>92.06999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D4" s="2">
-        <v>61.29</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E4" s="2">
-        <v>13.29</v>
+        <v>38.33</v>
       </c>
       <c r="F4" s="2">
-        <v>95.34999999999999</v>
+        <v>97.69</v>
       </c>
       <c r="G4" s="2">
-        <v>94</v>
+        <v>97.7</v>
       </c>
       <c r="H4" s="2">
-        <v>93.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
-        <v>90.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7289,264 +7460,119 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>222.95</v>
+        <v>96.88</v>
       </c>
       <c r="C5" s="2">
-        <v>112.52</v>
+        <v>130.17</v>
       </c>
       <c r="D5" s="2">
-        <v>24.57</v>
+        <v>35.9</v>
       </c>
       <c r="E5" s="2">
-        <v>13.24</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="2">
-        <v>94.19</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>97.2</v>
+        <v>90.8</v>
       </c>
       <c r="H5" s="2">
         <v>92.8</v>
       </c>
       <c r="I5" s="2">
-        <v>86.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>643.7</v>
+        <v>1277.1</v>
       </c>
       <c r="C6" s="2">
-        <v>98.45999999999999</v>
+        <v>100.94</v>
       </c>
       <c r="D6" s="2">
-        <v>32.9</v>
+        <v>56.8</v>
       </c>
       <c r="E6" s="2">
-        <v>15.86</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="2">
-        <v>93.02</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>97.59999999999999</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H6" s="2">
-        <v>96.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>94.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1">
-        <v>1861.6</v>
+        <v>1840</v>
       </c>
       <c r="C7" s="2">
-        <v>103.82</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D7" s="2">
-        <v>50.66</v>
+        <v>39.8</v>
       </c>
       <c r="E7" s="2">
-        <v>0.63</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>91.86</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="G7" s="2">
+        <v>91.95</v>
+      </c>
+      <c r="H7" s="2">
         <v>94.8</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>93.2</v>
-      </c>
-      <c r="I7" s="2">
-        <v>97.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1">
-        <v>88.66</v>
+        <v>222.88</v>
       </c>
       <c r="C8" s="2">
-        <v>127.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D8" s="2">
-        <v>18.8</v>
+        <v>16.87</v>
       </c>
       <c r="E8" s="2">
-        <v>-1.9</v>
+        <v>4.44</v>
       </c>
       <c r="F8" s="2">
-        <v>90.7</v>
+        <v>86.92</v>
       </c>
       <c r="G8" s="2">
+        <v>94.25</v>
+      </c>
+      <c r="H8" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="I8" s="2">
         <v>92.8</v>
       </c>
-      <c r="H8" s="2">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="I8" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1">
-        <v>238.05</v>
-      </c>
-      <c r="C9" s="2">
-        <v>82.37</v>
-      </c>
-      <c r="D9" s="2">
-        <v>39.83</v>
-      </c>
-      <c r="E9" s="2">
-        <v>7.07</v>
-      </c>
-      <c r="F9" s="2">
-        <v>89.53</v>
-      </c>
-      <c r="G9" s="2">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="H9" s="2">
-        <v>95.2</v>
-      </c>
-      <c r="I9" s="2">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1256.5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>102.86</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46.83</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-7.5</v>
-      </c>
-      <c r="F10" s="2">
-        <v>88.37</v>
-      </c>
-      <c r="G10" s="2">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="H10" s="2">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="I10" s="2">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2133.3</v>
-      </c>
-      <c r="C11" s="2">
-        <v>105</v>
-      </c>
-      <c r="D11" s="2">
-        <v>11.61</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-0.53</v>
-      </c>
-      <c r="F11" s="2">
-        <v>87.20999999999999</v>
-      </c>
-      <c r="G11" s="2">
-        <v>96</v>
-      </c>
-      <c r="H11" s="2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I11" s="2">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1">
-        <v>743.5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>67.02</v>
-      </c>
-      <c r="D12" s="2">
-        <v>29.62</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="F12" s="2">
-        <v>83.72</v>
-      </c>
-      <c r="G12" s="2">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="H12" s="2">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="I12" s="2">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1908</v>
-      </c>
-      <c r="C13" s="2">
-        <v>58.85</v>
-      </c>
-      <c r="D13" s="2">
-        <v>32.66</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1.88</v>
-      </c>
-      <c r="F13" s="2">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="G13" s="2">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="H13" s="2">
-        <v>88.8</v>
-      </c>
-      <c r="I13" s="2">
-        <v>91.2</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7554,7 +7580,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7562,7 +7588,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -7570,22 +7596,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -7596,7 +7622,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
@@ -7638,496 +7664,264 @@
         <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>323.97</v>
+        <v>364.05</v>
       </c>
       <c r="C2" s="2">
-        <v>167.74</v>
+        <v>190.29</v>
       </c>
       <c r="D2" s="2">
-        <v>64.79000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="E2" s="2">
-        <v>48.09</v>
+        <v>60.05</v>
       </c>
       <c r="F2" s="2">
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>99.59999999999999</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>90</v>
-      </c>
-      <c r="I2" s="2">
-        <v>89.2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>557.05</v>
+        <v>638.9</v>
       </c>
       <c r="C3" s="2">
-        <v>209.44</v>
+        <v>259.28</v>
       </c>
       <c r="D3" s="2">
-        <v>20.26</v>
+        <v>13.49</v>
       </c>
       <c r="E3" s="2">
-        <v>-4.8</v>
+        <v>23.3</v>
       </c>
       <c r="F3" s="2">
-        <v>98.84</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>99.2</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="H3" s="2">
         <v>99.2</v>
       </c>
       <c r="I3" s="2">
-        <v>99.59999999999999</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>816.2</v>
+        <v>814.5</v>
       </c>
       <c r="C4" s="2">
-        <v>57.57</v>
+        <v>90.5</v>
       </c>
       <c r="D4" s="2">
-        <v>68.48</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E4" s="2">
-        <v>40.11</v>
+        <v>38.33</v>
       </c>
       <c r="F4" s="2">
-        <v>97.67</v>
+        <v>97.69</v>
       </c>
       <c r="G4" s="2">
+        <v>97.7</v>
+      </c>
+      <c r="H4" s="2">
         <v>98</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>83.59999999999999</v>
-      </c>
-      <c r="I4" s="2">
-        <v>73.2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>332.55</v>
+        <v>96.88</v>
       </c>
       <c r="C5" s="2">
-        <v>92.06999999999999</v>
+        <v>130.17</v>
       </c>
       <c r="D5" s="2">
-        <v>61.29</v>
+        <v>35.9</v>
       </c>
       <c r="E5" s="2">
-        <v>13.29</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="2">
-        <v>95.34999999999999</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>94</v>
+        <v>90.8</v>
       </c>
       <c r="H5" s="2">
-        <v>93.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="I5" s="2">
-        <v>90.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>222.95</v>
+        <v>1277.1</v>
       </c>
       <c r="C6" s="2">
-        <v>112.52</v>
+        <v>100.94</v>
       </c>
       <c r="D6" s="2">
-        <v>24.57</v>
+        <v>56.8</v>
       </c>
       <c r="E6" s="2">
-        <v>13.24</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="2">
-        <v>94.19</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>97.2</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H6" s="2">
-        <v>92.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>86.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>643.7</v>
+        <v>5554</v>
       </c>
       <c r="C7" s="2">
-        <v>98.45999999999999</v>
+        <v>37.57</v>
       </c>
       <c r="D7" s="2">
-        <v>32.9</v>
+        <v>52.76</v>
       </c>
       <c r="E7" s="2">
-        <v>15.86</v>
+        <v>32.22</v>
       </c>
       <c r="F7" s="2">
-        <v>93.02</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>97.59999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="H7" s="2">
-        <v>96.40000000000001</v>
+        <v>33.2</v>
       </c>
       <c r="I7" s="2">
-        <v>94.40000000000001</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1">
-        <v>1861.6</v>
+        <v>1840</v>
       </c>
       <c r="C8" s="2">
-        <v>103.82</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D8" s="2">
-        <v>50.66</v>
+        <v>39.8</v>
       </c>
       <c r="E8" s="2">
-        <v>0.63</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>91.86</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="G8" s="2">
+        <v>91.95</v>
+      </c>
+      <c r="H8" s="2">
         <v>94.8</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>93.2</v>
-      </c>
-      <c r="I8" s="2">
-        <v>97.2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>88.66</v>
+        <v>222.88</v>
       </c>
       <c r="C9" s="2">
-        <v>127.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D9" s="2">
-        <v>18.8</v>
+        <v>16.87</v>
       </c>
       <c r="E9" s="2">
-        <v>-1.9</v>
+        <v>4.44</v>
       </c>
       <c r="F9" s="2">
-        <v>90.7</v>
+        <v>86.92</v>
       </c>
       <c r="G9" s="2">
+        <v>94.25</v>
+      </c>
+      <c r="H9" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="I9" s="2">
         <v>92.8</v>
-      </c>
-      <c r="H9" s="2">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="I9" s="2">
-        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1">
-        <v>238.05</v>
+        <v>83.5</v>
       </c>
       <c r="C10" s="2">
-        <v>82.37</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D10" s="2">
-        <v>39.83</v>
+        <v>23.33</v>
       </c>
       <c r="E10" s="2">
-        <v>7.07</v>
+        <v>5.87</v>
       </c>
       <c r="F10" s="2">
-        <v>89.53</v>
+        <v>85.38</v>
       </c>
       <c r="G10" s="2">
-        <v>95.59999999999999</v>
+        <v>85.06</v>
       </c>
       <c r="H10" s="2">
-        <v>95.2</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2">
-        <v>98.40000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1256.5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>102.86</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46.83</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-7.5</v>
-      </c>
-      <c r="F11" s="2">
-        <v>88.37</v>
-      </c>
-      <c r="G11" s="2">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="H11" s="2">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="I11" s="2">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2133.3</v>
-      </c>
-      <c r="C12" s="2">
-        <v>105</v>
-      </c>
-      <c r="D12" s="2">
-        <v>11.61</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-0.53</v>
-      </c>
-      <c r="F12" s="2">
-        <v>87.20999999999999</v>
-      </c>
-      <c r="G12" s="2">
-        <v>96</v>
-      </c>
-      <c r="H12" s="2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I12" s="2">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1">
-        <v>71.75</v>
-      </c>
-      <c r="C13" s="2">
-        <v>39.75</v>
-      </c>
-      <c r="D13" s="2">
-        <v>30.76</v>
-      </c>
-      <c r="E13" s="2">
-        <v>20.02</v>
-      </c>
-      <c r="F13" s="2">
-        <v>86.05</v>
-      </c>
-      <c r="G13" s="2">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="H13" s="2">
-        <v>75.2</v>
-      </c>
-      <c r="I13" s="2">
-        <v>63.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="C14" s="2">
-        <v>86.81999999999999</v>
-      </c>
-      <c r="D14" s="2">
-        <v>12.19</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2.88</v>
-      </c>
-      <c r="F14" s="2">
-        <v>84.88</v>
-      </c>
-      <c r="G14" s="2">
-        <v>84</v>
-      </c>
-      <c r="H14" s="2">
         <v>79.59999999999999</v>
       </c>
-      <c r="I14" s="2">
-        <v>83.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1">
-        <v>743.5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>67.02</v>
-      </c>
-      <c r="D15" s="2">
-        <v>29.62</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="F15" s="2">
-        <v>83.72</v>
-      </c>
-      <c r="G15" s="2">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="H15" s="2">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="I15" s="2">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1">
-        <v>403.2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>37.14</v>
-      </c>
-      <c r="D16" s="2">
-        <v>13.96</v>
-      </c>
-      <c r="E16" s="2">
-        <v>23.49</v>
-      </c>
-      <c r="F16" s="2">
-        <v>82.56</v>
-      </c>
-      <c r="G16" s="2">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H16" s="2">
-        <v>69.2</v>
-      </c>
-      <c r="I16" s="2">
-        <v>55.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1908</v>
-      </c>
-      <c r="C17" s="2">
-        <v>58.85</v>
-      </c>
-      <c r="D17" s="2">
-        <v>32.66</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1.88</v>
-      </c>
-      <c r="F17" s="2">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="G17" s="2">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="H17" s="2">
-        <v>88.8</v>
-      </c>
-      <c r="I17" s="2">
-        <v>91.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1">
-        <v>178.48</v>
-      </c>
-      <c r="C18" s="2">
-        <v>51.51</v>
-      </c>
-      <c r="D18" s="2">
-        <v>15.79</v>
-      </c>
-      <c r="E18" s="2">
-        <v>13.3</v>
-      </c>
-      <c r="F18" s="2">
-        <v>80.23</v>
-      </c>
-      <c r="G18" s="2">
-        <v>88</v>
-      </c>
-      <c r="H18" s="2">
-        <v>76</v>
-      </c>
-      <c r="I18" s="2">
-        <v>57.6</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C18">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8135,7 +7929,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8143,7 +7937,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -8151,22 +7945,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F18">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H18">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="cellIs" dxfId="2" priority="9" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
@@ -8202,13 +7996,13 @@
         <v>265</v>
       </c>
       <c r="B2" s="2">
-        <v>16.8</v>
+        <v>31.6</v>
       </c>
       <c r="C2" s="2">
-        <v>20</v>
+        <v>31.6</v>
       </c>
       <c r="D2" s="2">
-        <v>21.2</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8216,13 +8010,13 @@
         <v>266</v>
       </c>
       <c r="B3" s="2">
-        <v>34.4</v>
+        <v>17.2</v>
       </c>
       <c r="C3" s="2">
-        <v>51.6</v>
+        <v>20.4</v>
       </c>
       <c r="D3" s="2">
-        <v>57.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8230,13 +8024,13 @@
         <v>267</v>
       </c>
       <c r="B4" s="2">
-        <v>46</v>
+        <v>34.4</v>
       </c>
       <c r="C4" s="2">
-        <v>60.8</v>
+        <v>51.6</v>
       </c>
       <c r="D4" s="2">
-        <v>62</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8244,13 +8038,13 @@
         <v>268</v>
       </c>
       <c r="B5" s="2">
-        <v>64.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2">
-        <v>69.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D5" s="2">
-        <v>63.6</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Report/RSReport/NSE_250_Perception_Report.xlsx
+++ b/Report/RSReport/NSE_250_Perception_Report.xlsx
@@ -6890,7 +6890,7 @@
         <v>183</v>
       </c>
       <c r="B176" s="1">
-        <v>283.82</v>
+        <v>282.57</v>
       </c>
       <c r="C176" s="2">
         <v>-31.79</v>
@@ -11813,7 +11813,7 @@
         <v>51.6</v>
       </c>
       <c r="D3" s="2">
-        <v>57.6</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -11841,7 +11841,7 @@
         <v>59.2</v>
       </c>
       <c r="D5" s="2">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>
